--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\PCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A93C8F70-6D73-4392-8BBF-7A2C68C74ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B529843-B626-4633-AAB4-7865573CDD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23295" windowHeight="13380" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="54">
   <si>
     <t>Company Name</t>
   </si>
@@ -11428,10 +11428,10 @@
         <v>20</v>
       </c>
       <c r="G403" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H403" s="2">
-        <v>1.1574074074074075E-4</v>
+        <v>9.3055555555555548E-3</v>
       </c>
       <c r="I403" s="1">
         <v>46083.795370370368</v>
@@ -11444,10 +11444,32 @@
       </c>
     </row>
     <row r="404" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H404" s="2"/>
-      <c r="I404" s="1"/>
+      <c r="B404" t="s">
+        <v>29</v>
+      </c>
+      <c r="C404">
+        <v>3155</v>
+      </c>
+      <c r="D404" t="s">
+        <v>45</v>
+      </c>
+      <c r="F404" t="s">
+        <v>20</v>
+      </c>
+      <c r="G404" t="s">
+        <v>10</v>
+      </c>
+      <c r="H404" s="2">
+        <v>3.8425925925925928E-3</v>
+      </c>
+      <c r="I404" s="1">
+        <v>46083.795370370368</v>
+      </c>
+      <c r="J404">
+        <v>1</v>
+      </c>
       <c r="K404" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="405" spans="2:11" x14ac:dyDescent="0.25">
@@ -11455,10 +11477,10 @@
         <v>29</v>
       </c>
       <c r="C405">
-        <v>3155</v>
+        <v>3164</v>
       </c>
       <c r="D405" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F405" t="s">
         <v>20</v>
@@ -11467,13 +11489,13 @@
         <v>10</v>
       </c>
       <c r="H405" s="2">
-        <v>3.8425925925925928E-3</v>
+        <v>1.0185185185185186E-2</v>
       </c>
       <c r="I405" s="1">
-        <v>46083.795370370368</v>
+        <v>46083.796064814815</v>
       </c>
       <c r="J405">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K405" t="s">
         <v>11</v>
@@ -11484,10 +11506,10 @@
         <v>29</v>
       </c>
       <c r="C406">
-        <v>3164</v>
+        <v>3143</v>
       </c>
       <c r="D406" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F406" t="s">
         <v>20</v>
@@ -11496,10 +11518,10 @@
         <v>10</v>
       </c>
       <c r="H406" s="2">
-        <v>1.0185185185185186E-2</v>
+        <v>5.2430555555555555E-3</v>
       </c>
       <c r="I406" s="1">
-        <v>46083.796064814815</v>
+        <v>46083.796759259261</v>
       </c>
       <c r="J406">
         <v>0</v>
@@ -11509,33 +11531,8 @@
       </c>
     </row>
     <row r="407" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B407" t="s">
-        <v>29</v>
-      </c>
-      <c r="C407">
-        <v>3143</v>
-      </c>
-      <c r="D407" t="s">
-        <v>30</v>
-      </c>
-      <c r="F407" t="s">
-        <v>20</v>
-      </c>
-      <c r="G407" t="s">
-        <v>10</v>
-      </c>
-      <c r="H407" s="2">
-        <v>5.2430555555555555E-3</v>
-      </c>
-      <c r="I407" s="1">
-        <v>46083.796759259261</v>
-      </c>
-      <c r="J407">
-        <v>0</v>
-      </c>
-      <c r="K407" t="s">
-        <v>11</v>
-      </c>
+      <c r="H407" s="2"/>
+      <c r="I407" s="1"/>
     </row>
     <row r="408" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H408" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\PCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B529843-B626-4633-AAB4-7865573CDD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D41683-89AB-4E7B-9D19-268BD7977F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="55">
   <si>
     <t>Company Name</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Greg Magnuson</t>
   </si>
   <si>
-    <t>Robert Kitts</t>
-  </si>
-  <si>
     <t>Melissa Dowe</t>
   </si>
   <si>
@@ -201,6 +198,12 @@
   </si>
   <si>
     <t>Big Wins Through Behavior Change</t>
+  </si>
+  <si>
+    <t>William Burch</t>
+  </si>
+  <si>
+    <t>Adam James Loosle</t>
   </si>
 </sst>
 </file>
@@ -948,7 +951,7 @@
         <v>3153</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
         <v>27</v>
@@ -977,7 +980,7 @@
         <v>3162</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
         <v>27</v>
@@ -1006,7 +1009,7 @@
         <v>3164</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
         <v>27</v>
@@ -1035,7 +1038,7 @@
         <v>3194</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
@@ -1064,7 +1067,7 @@
         <v>3155</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
@@ -1093,7 +1096,7 @@
         <v>3147</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -1122,7 +1125,7 @@
         <v>3156</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
@@ -1151,7 +1154,7 @@
         <v>3157</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
@@ -1180,7 +1183,7 @@
         <v>3158</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
@@ -1209,7 +1212,7 @@
         <v>3159</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
@@ -1615,7 +1618,7 @@
         <v>3153</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
         <v>15</v>
@@ -1644,7 +1647,7 @@
         <v>3162</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" t="s">
         <v>15</v>
@@ -1673,7 +1676,7 @@
         <v>3164</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F38" t="s">
         <v>15</v>
@@ -1702,7 +1705,7 @@
         <v>3194</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
@@ -1731,7 +1734,7 @@
         <v>3155</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
@@ -1760,7 +1763,7 @@
         <v>3147</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -1789,7 +1792,7 @@
         <v>3156</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1818,7 +1821,7 @@
         <v>3157</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -1847,7 +1850,7 @@
         <v>3158</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
@@ -1876,7 +1879,7 @@
         <v>3159</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -1963,7 +1966,7 @@
         <v>3209</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F48" t="s">
         <v>27</v>
@@ -1992,7 +1995,7 @@
         <v>3194</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F49" t="s">
         <v>27</v>
@@ -2021,10 +2024,10 @@
         <v>3194</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
@@ -2376,7 +2379,7 @@
         <v>3153</v>
       </c>
       <c r="D63" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
@@ -2405,7 +2408,7 @@
         <v>3209</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F64" t="s">
         <v>27</v>
@@ -2434,7 +2437,7 @@
         <v>3162</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F65" t="s">
         <v>27</v>
@@ -2463,7 +2466,7 @@
         <v>3164</v>
       </c>
       <c r="D66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F66" t="s">
         <v>27</v>
@@ -2492,7 +2495,7 @@
         <v>3194</v>
       </c>
       <c r="D67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F67" t="s">
         <v>27</v>
@@ -2528,7 +2531,7 @@
         <v>3155</v>
       </c>
       <c r="D69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F69" t="s">
         <v>27</v>
@@ -2557,7 +2560,7 @@
         <v>3147</v>
       </c>
       <c r="D70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F70" t="s">
         <v>27</v>
@@ -2586,7 +2589,7 @@
         <v>3156</v>
       </c>
       <c r="D71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F71" t="s">
         <v>27</v>
@@ -2615,7 +2618,7 @@
         <v>3157</v>
       </c>
       <c r="D72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F72" t="s">
         <v>27</v>
@@ -2644,7 +2647,7 @@
         <v>3158</v>
       </c>
       <c r="D73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F73" t="s">
         <v>27</v>
@@ -2673,7 +2676,7 @@
         <v>3159</v>
       </c>
       <c r="D74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F74" t="s">
         <v>27</v>
@@ -3100,7 +3103,7 @@
         <v>3153</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
@@ -3129,7 +3132,7 @@
         <v>3209</v>
       </c>
       <c r="D92" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F92" t="s">
         <v>25</v>
@@ -3158,7 +3161,7 @@
         <v>3162</v>
       </c>
       <c r="D93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F93" t="s">
         <v>25</v>
@@ -3187,7 +3190,7 @@
         <v>3164</v>
       </c>
       <c r="D94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F94" t="s">
         <v>25</v>
@@ -3216,7 +3219,7 @@
         <v>3194</v>
       </c>
       <c r="D95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F95" t="s">
         <v>25</v>
@@ -3245,7 +3248,7 @@
         <v>3155</v>
       </c>
       <c r="D96" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F96" t="s">
         <v>25</v>
@@ -3281,7 +3284,7 @@
         <v>3147</v>
       </c>
       <c r="D98" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F98" t="s">
         <v>25</v>
@@ -3310,7 +3313,7 @@
         <v>3156</v>
       </c>
       <c r="D99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F99" t="s">
         <v>25</v>
@@ -3339,7 +3342,7 @@
         <v>3157</v>
       </c>
       <c r="D100" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
@@ -3368,7 +3371,7 @@
         <v>3158</v>
       </c>
       <c r="D101" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
@@ -3397,7 +3400,7 @@
         <v>3159</v>
       </c>
       <c r="D102" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
@@ -3636,7 +3639,7 @@
         <v>3155</v>
       </c>
       <c r="D111" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F111" t="s">
         <v>19</v>
@@ -3839,7 +3842,7 @@
         <v>3153</v>
       </c>
       <c r="D118" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F118" t="s">
         <v>19</v>
@@ -3868,7 +3871,7 @@
         <v>3209</v>
       </c>
       <c r="D119" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F119" t="s">
         <v>19</v>
@@ -3904,7 +3907,7 @@
         <v>3162</v>
       </c>
       <c r="D121" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F121" t="s">
         <v>19</v>
@@ -3933,7 +3936,7 @@
         <v>3164</v>
       </c>
       <c r="D122" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
@@ -3962,7 +3965,7 @@
         <v>3194</v>
       </c>
       <c r="D123" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
         <v>19</v>
@@ -3991,7 +3994,7 @@
         <v>3429</v>
       </c>
       <c r="D124" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F124" t="s">
         <v>19</v>
@@ -4020,7 +4023,7 @@
         <v>3147</v>
       </c>
       <c r="D125" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F125" t="s">
         <v>19</v>
@@ -4049,7 +4052,7 @@
         <v>3156</v>
       </c>
       <c r="D126" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F126" t="s">
         <v>19</v>
@@ -4078,7 +4081,7 @@
         <v>3157</v>
       </c>
       <c r="D127" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F127" t="s">
         <v>19</v>
@@ -4107,7 +4110,7 @@
         <v>3158</v>
       </c>
       <c r="D128" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F128" t="s">
         <v>19</v>
@@ -4165,7 +4168,7 @@
         <v>3159</v>
       </c>
       <c r="D130" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F130" t="s">
         <v>19</v>
@@ -4375,7 +4378,7 @@
         <v>3155</v>
       </c>
       <c r="D138" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F138" t="s">
         <v>15</v>
@@ -4585,7 +4588,7 @@
         <v>3153</v>
       </c>
       <c r="D146" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F146" t="s">
         <v>15</v>
@@ -4614,7 +4617,7 @@
         <v>3209</v>
       </c>
       <c r="D147" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F147" t="s">
         <v>15</v>
@@ -4643,7 +4646,7 @@
         <v>3162</v>
       </c>
       <c r="D148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F148" t="s">
         <v>15</v>
@@ -4672,7 +4675,7 @@
         <v>3194</v>
       </c>
       <c r="D149" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F149" t="s">
         <v>15</v>
@@ -4708,7 +4711,7 @@
         <v>3429</v>
       </c>
       <c r="D151" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F151" t="s">
         <v>15</v>
@@ -4737,7 +4740,7 @@
         <v>3147</v>
       </c>
       <c r="D152" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F152" t="s">
         <v>15</v>
@@ -4766,7 +4769,7 @@
         <v>3156</v>
       </c>
       <c r="D153" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F153" t="s">
         <v>15</v>
@@ -4795,7 +4798,7 @@
         <v>3157</v>
       </c>
       <c r="D154" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F154" t="s">
         <v>15</v>
@@ -4824,7 +4827,7 @@
         <v>3158</v>
       </c>
       <c r="D155" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F155" t="s">
         <v>15</v>
@@ -4882,7 +4885,7 @@
         <v>3159</v>
       </c>
       <c r="D157" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F157" t="s">
         <v>15</v>
@@ -4940,7 +4943,7 @@
         <v>3164</v>
       </c>
       <c r="D159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F159" t="s">
         <v>15</v>
@@ -5230,7 +5233,7 @@
         <v>3155</v>
       </c>
       <c r="D169" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F169" t="s">
         <v>24</v>
@@ -5259,7 +5262,7 @@
         <v>3209</v>
       </c>
       <c r="D170" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F170" t="s">
         <v>24</v>
@@ -5288,7 +5291,7 @@
         <v>3194</v>
       </c>
       <c r="D171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F171" t="s">
         <v>24</v>
@@ -5324,7 +5327,7 @@
         <v>3429</v>
       </c>
       <c r="D173" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F173" t="s">
         <v>24</v>
@@ -5353,7 +5356,7 @@
         <v>3147</v>
       </c>
       <c r="D174" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F174" t="s">
         <v>24</v>
@@ -5382,7 +5385,7 @@
         <v>3156</v>
       </c>
       <c r="D175" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F175" t="s">
         <v>24</v>
@@ -5411,7 +5414,7 @@
         <v>3157</v>
       </c>
       <c r="D176" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F176" t="s">
         <v>24</v>
@@ -5447,7 +5450,7 @@
         <v>3158</v>
       </c>
       <c r="D178" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F178" t="s">
         <v>24</v>
@@ -5534,7 +5537,7 @@
         <v>3162</v>
       </c>
       <c r="D181" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F181" t="s">
         <v>24</v>
@@ -5563,7 +5566,7 @@
         <v>3153</v>
       </c>
       <c r="D182" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F182" t="s">
         <v>24</v>
@@ -5592,7 +5595,7 @@
         <v>3159</v>
       </c>
       <c r="D183" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F183" t="s">
         <v>24</v>
@@ -5679,7 +5682,7 @@
         <v>3164</v>
       </c>
       <c r="D186" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F186" t="s">
         <v>24</v>
@@ -5998,7 +6001,7 @@
         <v>3155</v>
       </c>
       <c r="D197" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -6027,7 +6030,7 @@
         <v>3209</v>
       </c>
       <c r="D198" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -6063,7 +6066,7 @@
         <v>3194</v>
       </c>
       <c r="D200" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -6099,7 +6102,7 @@
         <v>3429</v>
       </c>
       <c r="D202" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -6135,7 +6138,7 @@
         <v>3147</v>
       </c>
       <c r="D204" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -6164,7 +6167,7 @@
         <v>3156</v>
       </c>
       <c r="D205" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -6193,7 +6196,7 @@
         <v>3157</v>
       </c>
       <c r="D206" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -6229,7 +6232,7 @@
         <v>3158</v>
       </c>
       <c r="D208" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -6258,7 +6261,7 @@
         <v>3162</v>
       </c>
       <c r="D209" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -6316,7 +6319,7 @@
         <v>3153</v>
       </c>
       <c r="D211" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -6345,7 +6348,7 @@
         <v>3159</v>
       </c>
       <c r="D212" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -6432,7 +6435,7 @@
         <v>3164</v>
       </c>
       <c r="D215" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -6751,7 +6754,7 @@
         <v>3155</v>
       </c>
       <c r="D226" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F226" t="s">
         <v>26</v>
@@ -6780,7 +6783,7 @@
         <v>3209</v>
       </c>
       <c r="D227" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F227" t="s">
         <v>26</v>
@@ -6809,7 +6812,7 @@
         <v>3194</v>
       </c>
       <c r="D228" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F228" t="s">
         <v>26</v>
@@ -6838,7 +6841,7 @@
         <v>3429</v>
       </c>
       <c r="D229" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F229" t="s">
         <v>26</v>
@@ -6867,7 +6870,7 @@
         <v>3147</v>
       </c>
       <c r="D230" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F230" t="s">
         <v>26</v>
@@ -6896,7 +6899,7 @@
         <v>3156</v>
       </c>
       <c r="D231" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F231" t="s">
         <v>26</v>
@@ -6925,7 +6928,7 @@
         <v>3157</v>
       </c>
       <c r="D232" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F232" t="s">
         <v>26</v>
@@ -6954,7 +6957,7 @@
         <v>3158</v>
       </c>
       <c r="D233" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F233" t="s">
         <v>26</v>
@@ -6983,7 +6986,7 @@
         <v>3162</v>
       </c>
       <c r="D234" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F234" t="s">
         <v>26</v>
@@ -7041,7 +7044,7 @@
         <v>3153</v>
       </c>
       <c r="D236" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F236" t="s">
         <v>26</v>
@@ -7070,7 +7073,7 @@
         <v>3159</v>
       </c>
       <c r="D237" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F237" t="s">
         <v>26</v>
@@ -7157,7 +7160,7 @@
         <v>3164</v>
       </c>
       <c r="D240" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F240" t="s">
         <v>26</v>
@@ -7418,7 +7421,7 @@
         <v>3155</v>
       </c>
       <c r="D249" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F249" t="s">
         <v>18</v>
@@ -7505,7 +7508,7 @@
         <v>3209</v>
       </c>
       <c r="D252" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F252" t="s">
         <v>18</v>
@@ -7534,7 +7537,7 @@
         <v>3194</v>
       </c>
       <c r="D253" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F253" t="s">
         <v>18</v>
@@ -7563,7 +7566,7 @@
         <v>3429</v>
       </c>
       <c r="D254" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F254" t="s">
         <v>18</v>
@@ -7592,7 +7595,7 @@
         <v>3147</v>
       </c>
       <c r="D255" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F255" t="s">
         <v>18</v>
@@ -7621,7 +7624,7 @@
         <v>3156</v>
       </c>
       <c r="D256" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F256" t="s">
         <v>18</v>
@@ -7650,7 +7653,7 @@
         <v>3157</v>
       </c>
       <c r="D257" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F257" t="s">
         <v>18</v>
@@ -7686,7 +7689,7 @@
         <v>3158</v>
       </c>
       <c r="D259" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F259" t="s">
         <v>18</v>
@@ -7715,7 +7718,7 @@
         <v>3162</v>
       </c>
       <c r="D260" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F260" t="s">
         <v>18</v>
@@ -7744,7 +7747,7 @@
         <v>3164</v>
       </c>
       <c r="D261" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F261" t="s">
         <v>18</v>
@@ -7838,7 +7841,7 @@
         <v>3153</v>
       </c>
       <c r="D265" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F265" t="s">
         <v>18</v>
@@ -7867,7 +7870,7 @@
         <v>3159</v>
       </c>
       <c r="D266" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F266" t="s">
         <v>18</v>
@@ -8164,7 +8167,7 @@
         <v>3209</v>
       </c>
       <c r="D277" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F277" t="s">
         <v>16</v>
@@ -8193,7 +8196,7 @@
         <v>3194</v>
       </c>
       <c r="D278" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -8222,7 +8225,7 @@
         <v>3429</v>
       </c>
       <c r="D279" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F279" t="s">
         <v>16</v>
@@ -8251,7 +8254,7 @@
         <v>3147</v>
       </c>
       <c r="D280" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -8280,7 +8283,7 @@
         <v>3156</v>
       </c>
       <c r="D281" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F281" t="s">
         <v>16</v>
@@ -8309,7 +8312,7 @@
         <v>3157</v>
       </c>
       <c r="D282" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F282" t="s">
         <v>16</v>
@@ -8345,7 +8348,7 @@
         <v>3158</v>
       </c>
       <c r="D284" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F284" t="s">
         <v>16</v>
@@ -8403,7 +8406,7 @@
         <v>3162</v>
       </c>
       <c r="D286" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F286" t="s">
         <v>16</v>
@@ -8432,7 +8435,7 @@
         <v>3164</v>
       </c>
       <c r="D287" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F287" t="s">
         <v>16</v>
@@ -8519,7 +8522,7 @@
         <v>3153</v>
       </c>
       <c r="D290" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F290" t="s">
         <v>16</v>
@@ -8548,7 +8551,7 @@
         <v>3159</v>
       </c>
       <c r="D291" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F291" t="s">
         <v>16</v>
@@ -8606,7 +8609,7 @@
         <v>3155</v>
       </c>
       <c r="D293" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -8946,7 +8949,7 @@
         <v>3209</v>
       </c>
       <c r="D307" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F307" t="s">
         <v>17</v>
@@ -8975,7 +8978,7 @@
         <v>3194</v>
       </c>
       <c r="D308" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F308" t="s">
         <v>17</v>
@@ -9011,7 +9014,7 @@
         <v>3429</v>
       </c>
       <c r="D310" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F310" t="s">
         <v>17</v>
@@ -9040,7 +9043,7 @@
         <v>3147</v>
       </c>
       <c r="D311" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F311" t="s">
         <v>17</v>
@@ -9069,7 +9072,7 @@
         <v>3156</v>
       </c>
       <c r="D312" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F312" t="s">
         <v>17</v>
@@ -9105,7 +9108,7 @@
         <v>3157</v>
       </c>
       <c r="D314" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F314" t="s">
         <v>17</v>
@@ -9141,7 +9144,7 @@
         <v>3158</v>
       </c>
       <c r="D316" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F316" t="s">
         <v>17</v>
@@ -9170,7 +9173,7 @@
         <v>3164</v>
       </c>
       <c r="D317" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F317" t="s">
         <v>17</v>
@@ -9264,7 +9267,7 @@
         <v>3153</v>
       </c>
       <c r="D321" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F321" t="s">
         <v>17</v>
@@ -9300,7 +9303,7 @@
         <v>3159</v>
       </c>
       <c r="D323" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F323" t="s">
         <v>17</v>
@@ -9365,7 +9368,7 @@
         <v>3155</v>
       </c>
       <c r="D326" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F326" t="s">
         <v>17</v>
@@ -9691,7 +9694,7 @@
         <v>3209</v>
       </c>
       <c r="D338" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F338" t="s">
         <v>22</v>
@@ -9720,7 +9723,7 @@
         <v>3194</v>
       </c>
       <c r="D339" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F339" t="s">
         <v>22</v>
@@ -9749,7 +9752,7 @@
         <v>3147</v>
       </c>
       <c r="D340" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F340" t="s">
         <v>22</v>
@@ -9778,7 +9781,7 @@
         <v>3156</v>
       </c>
       <c r="D341" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F341" t="s">
         <v>22</v>
@@ -9807,7 +9810,7 @@
         <v>3157</v>
       </c>
       <c r="D342" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F342" t="s">
         <v>22</v>
@@ -9836,7 +9839,7 @@
         <v>3158</v>
       </c>
       <c r="D343" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F343" t="s">
         <v>22</v>
@@ -9865,7 +9868,7 @@
         <v>3429</v>
       </c>
       <c r="D344" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F344" t="s">
         <v>22</v>
@@ -9952,7 +9955,7 @@
         <v>3153</v>
       </c>
       <c r="D347" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F347" t="s">
         <v>22</v>
@@ -9981,7 +9984,7 @@
         <v>3159</v>
       </c>
       <c r="D348" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F348" t="s">
         <v>22</v>
@@ -10046,7 +10049,7 @@
         <v>3155</v>
       </c>
       <c r="D351" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F351" t="s">
         <v>22</v>
@@ -10075,7 +10078,7 @@
         <v>3164</v>
       </c>
       <c r="D352" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F352" t="s">
         <v>22</v>
@@ -10133,10 +10136,10 @@
         <v>3209</v>
       </c>
       <c r="D354" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F354" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G354" t="s">
         <v>13</v>
@@ -10401,7 +10404,7 @@
         <v>3194</v>
       </c>
       <c r="D364" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F364" t="s">
         <v>23</v>
@@ -10437,7 +10440,7 @@
         <v>3147</v>
       </c>
       <c r="D366" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F366" t="s">
         <v>23</v>
@@ -10466,7 +10469,7 @@
         <v>3156</v>
       </c>
       <c r="D367" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F367" t="s">
         <v>23</v>
@@ -10495,7 +10498,7 @@
         <v>3157</v>
       </c>
       <c r="D368" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F368" t="s">
         <v>23</v>
@@ -10531,7 +10534,7 @@
         <v>3158</v>
       </c>
       <c r="D370" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F370" t="s">
         <v>23</v>
@@ -10560,7 +10563,7 @@
         <v>3429</v>
       </c>
       <c r="D371" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F371" t="s">
         <v>23</v>
@@ -10676,7 +10679,7 @@
         <v>3153</v>
       </c>
       <c r="D375" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F375" t="s">
         <v>23</v>
@@ -10705,7 +10708,7 @@
         <v>3159</v>
       </c>
       <c r="D376" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F376" t="s">
         <v>23</v>
@@ -10763,7 +10766,7 @@
         <v>3155</v>
       </c>
       <c r="D378" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F378" t="s">
         <v>23</v>
@@ -10792,7 +10795,7 @@
         <v>3164</v>
       </c>
       <c r="D379" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F379" t="s">
         <v>23</v>
@@ -10850,7 +10853,7 @@
         <v>3162</v>
       </c>
       <c r="D381" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F381" t="s">
         <v>23</v>
@@ -10894,7 +10897,7 @@
         <v>46083.809837962966</v>
       </c>
       <c r="J382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K382" t="s">
         <v>11</v>
@@ -11039,7 +11042,7 @@
         <v>46083.811921296299</v>
       </c>
       <c r="J387">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K387" t="s">
         <v>11</v>
@@ -11068,7 +11071,7 @@
         <v>46083.812615740739</v>
       </c>
       <c r="J388">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K388" t="s">
         <v>11</v>
@@ -11097,7 +11100,7 @@
         <v>46083.812615740739</v>
       </c>
       <c r="J389">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K389" t="s">
         <v>11</v>
@@ -11147,7 +11150,7 @@
         <v>3194</v>
       </c>
       <c r="D392" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F392" t="s">
         <v>20</v>
@@ -11183,7 +11186,7 @@
         <v>3162</v>
       </c>
       <c r="D394" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F394" t="s">
         <v>20</v>
@@ -11212,22 +11215,22 @@
         <v>3147</v>
       </c>
       <c r="D395" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F395" t="s">
         <v>20</v>
       </c>
       <c r="G395" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H395" s="2">
-        <v>0</v>
+        <v>5.9375000000000001E-3</v>
       </c>
       <c r="I395" s="1">
         <v>46083.816087962965</v>
       </c>
       <c r="J395">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K395" t="s">
         <v>11</v>
@@ -11241,7 +11244,7 @@
         <v>3156</v>
       </c>
       <c r="D396" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F396" t="s">
         <v>20</v>
@@ -11270,7 +11273,7 @@
         <v>3157</v>
       </c>
       <c r="D397" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F397" t="s">
         <v>20</v>
@@ -11306,7 +11309,7 @@
         <v>3158</v>
       </c>
       <c r="D399" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F399" t="s">
         <v>20</v>
@@ -11350,7 +11353,7 @@
         <v>46083.793981481482</v>
       </c>
       <c r="J400">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K400" t="s">
         <v>11</v>
@@ -11364,7 +11367,7 @@
         <v>3153</v>
       </c>
       <c r="D401" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F401" t="s">
         <v>20</v>
@@ -11393,7 +11396,7 @@
         <v>3159</v>
       </c>
       <c r="D402" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F402" t="s">
         <v>20</v>
@@ -11451,7 +11454,7 @@
         <v>3155</v>
       </c>
       <c r="D404" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F404" t="s">
         <v>20</v>
@@ -11480,7 +11483,7 @@
         <v>3164</v>
       </c>
       <c r="D405" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F405" t="s">
         <v>20</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D41683-89AB-4E7B-9D19-268BD7977F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B591B3-A058-46D6-8B7C-32B72BA7ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B591B3-A058-46D6-8B7C-32B72BA7ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC79C27E-6D08-4E45-9567-DF859B453C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="57">
   <si>
     <t>Company Name</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>Adam James Loosle</t>
+  </si>
+  <si>
+    <t>(Spanish) Rules for Safe Driving</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -11159,7 +11165,7 @@
         <v>12</v>
       </c>
       <c r="H392" s="2">
-        <v>1.3773148148148147E-3</v>
+        <v>0.24937500000000001</v>
       </c>
       <c r="I392" s="1">
         <v>46083.813310185185</v>
@@ -11434,7 +11440,7 @@
         <v>10</v>
       </c>
       <c r="H403" s="2">
-        <v>9.3055555555555548E-3</v>
+        <v>1.4467592592592593E-2</v>
       </c>
       <c r="I403" s="1">
         <v>46083.795370370368</v>
@@ -11534,234 +11540,1414 @@
       </c>
     </row>
     <row r="407" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H407" s="2"/>
-      <c r="I407" s="1"/>
+      <c r="B407" t="s">
+        <v>29</v>
+      </c>
+      <c r="C407">
+        <v>3160</v>
+      </c>
+      <c r="D407" t="s">
+        <v>34</v>
+      </c>
+      <c r="F407" t="s">
+        <v>55</v>
+      </c>
+      <c r="G407" t="s">
+        <v>13</v>
+      </c>
+      <c r="H407" s="2">
+        <v>0</v>
+      </c>
+      <c r="I407" s="1">
+        <v>46118.808564814812</v>
+      </c>
+      <c r="J407">
+        <v>1</v>
+      </c>
+      <c r="K407" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="408" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H408" s="2"/>
-      <c r="I408" s="1"/>
+      <c r="B408" t="s">
+        <v>29</v>
+      </c>
+      <c r="C408">
+        <v>3161</v>
+      </c>
+      <c r="D408" t="s">
+        <v>34</v>
+      </c>
+      <c r="F408" t="s">
+        <v>55</v>
+      </c>
+      <c r="G408" t="s">
+        <v>13</v>
+      </c>
+      <c r="H408" s="2">
+        <v>0</v>
+      </c>
+      <c r="I408" s="1">
+        <v>46118.809259259258</v>
+      </c>
+      <c r="J408">
+        <v>1</v>
+      </c>
+      <c r="K408" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="409" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H409" s="2"/>
-      <c r="I409" s="1"/>
+      <c r="B409" t="s">
+        <v>29</v>
+      </c>
+      <c r="C409">
+        <v>3146</v>
+      </c>
+      <c r="D409" t="s">
+        <v>35</v>
+      </c>
+      <c r="F409" t="s">
+        <v>55</v>
+      </c>
+      <c r="G409" t="s">
+        <v>12</v>
+      </c>
+      <c r="H409" s="2">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="I409" s="1">
+        <v>46118.809953703705</v>
+      </c>
+      <c r="J409">
+        <v>1</v>
+      </c>
+      <c r="K409" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="410" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H410" s="2"/>
       <c r="I410" s="1"/>
+      <c r="K410" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="411" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H411" s="2"/>
-      <c r="I411" s="1"/>
+      <c r="B411" t="s">
+        <v>29</v>
+      </c>
+      <c r="C411">
+        <v>3429</v>
+      </c>
+      <c r="D411" t="s">
+        <v>54</v>
+      </c>
+      <c r="F411" t="s">
+        <v>55</v>
+      </c>
+      <c r="G411" t="s">
+        <v>12</v>
+      </c>
+      <c r="H411" s="2">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I411" s="1">
+        <v>46118.809953703705</v>
+      </c>
+      <c r="J411">
+        <v>0</v>
+      </c>
+      <c r="K411" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="412" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H412" s="2"/>
       <c r="I412" s="1"/>
+      <c r="K412" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="413" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H413" s="2"/>
-      <c r="I413" s="1"/>
+      <c r="B413" t="s">
+        <v>29</v>
+      </c>
+      <c r="C413">
+        <v>3154</v>
+      </c>
+      <c r="D413" t="s">
+        <v>31</v>
+      </c>
+      <c r="F413" t="s">
+        <v>55</v>
+      </c>
+      <c r="G413" t="s">
+        <v>12</v>
+      </c>
+      <c r="H413" s="2">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="I413" s="1">
+        <v>46118.810648148145</v>
+      </c>
+      <c r="J413">
+        <v>0</v>
+      </c>
+      <c r="K413" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="414" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H414" s="2"/>
       <c r="I414" s="1"/>
+      <c r="K414" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="415" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H415" s="2"/>
-      <c r="I415" s="1"/>
+      <c r="B415" t="s">
+        <v>29</v>
+      </c>
+      <c r="C415">
+        <v>3144</v>
+      </c>
+      <c r="D415" t="s">
+        <v>32</v>
+      </c>
+      <c r="F415" t="s">
+        <v>55</v>
+      </c>
+      <c r="G415" t="s">
+        <v>13</v>
+      </c>
+      <c r="H415" s="2">
+        <v>0</v>
+      </c>
+      <c r="I415" s="1">
+        <v>46118.811342592591</v>
+      </c>
+      <c r="J415">
+        <v>1</v>
+      </c>
+      <c r="K415" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="416" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H416" s="2"/>
-      <c r="I416" s="1"/>
-    </row>
-    <row r="417" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H417" s="2"/>
-      <c r="I417" s="1"/>
-    </row>
-    <row r="418" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H418" s="2"/>
-      <c r="I418" s="1"/>
-    </row>
-    <row r="419" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H419" s="2"/>
-      <c r="I419" s="1"/>
-    </row>
-    <row r="420" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H420" s="2"/>
-      <c r="I420" s="1"/>
-    </row>
-    <row r="421" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B416" t="s">
+        <v>29</v>
+      </c>
+      <c r="C416">
+        <v>3145</v>
+      </c>
+      <c r="D416" t="s">
+        <v>33</v>
+      </c>
+      <c r="F416" t="s">
+        <v>55</v>
+      </c>
+      <c r="G416" t="s">
+        <v>13</v>
+      </c>
+      <c r="H416" s="2">
+        <v>0</v>
+      </c>
+      <c r="I416" s="1">
+        <v>46118.811342592591</v>
+      </c>
+      <c r="J416">
+        <v>1</v>
+      </c>
+      <c r="K416" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B417" t="s">
+        <v>29</v>
+      </c>
+      <c r="C417">
+        <v>3149</v>
+      </c>
+      <c r="D417" t="s">
+        <v>40</v>
+      </c>
+      <c r="F417" t="s">
+        <v>55</v>
+      </c>
+      <c r="G417" t="s">
+        <v>13</v>
+      </c>
+      <c r="H417" s="2">
+        <v>0</v>
+      </c>
+      <c r="I417" s="1">
+        <v>46118.812037037038</v>
+      </c>
+      <c r="J417">
+        <v>1</v>
+      </c>
+      <c r="K417" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B418" t="s">
+        <v>29</v>
+      </c>
+      <c r="C418">
+        <v>3151</v>
+      </c>
+      <c r="D418" t="s">
+        <v>39</v>
+      </c>
+      <c r="F418" t="s">
+        <v>55</v>
+      </c>
+      <c r="G418" t="s">
+        <v>13</v>
+      </c>
+      <c r="H418" s="2">
+        <v>0</v>
+      </c>
+      <c r="I418" s="1">
+        <v>46118.812037037038</v>
+      </c>
+      <c r="J418">
+        <v>1</v>
+      </c>
+      <c r="K418" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B419" t="s">
+        <v>29</v>
+      </c>
+      <c r="C419">
+        <v>3148</v>
+      </c>
+      <c r="D419" t="s">
+        <v>36</v>
+      </c>
+      <c r="F419" t="s">
+        <v>55</v>
+      </c>
+      <c r="G419" t="s">
+        <v>13</v>
+      </c>
+      <c r="H419" s="2">
+        <v>0</v>
+      </c>
+      <c r="I419" s="1">
+        <v>46118.812731481485</v>
+      </c>
+      <c r="J419">
+        <v>1</v>
+      </c>
+      <c r="K419" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B420" t="s">
+        <v>29</v>
+      </c>
+      <c r="C420">
+        <v>3164</v>
+      </c>
+      <c r="D420" t="s">
+        <v>42</v>
+      </c>
+      <c r="F420" t="s">
+        <v>55</v>
+      </c>
+      <c r="G420" t="s">
+        <v>12</v>
+      </c>
+      <c r="H420" s="2">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="I420" s="1">
+        <v>46118.813425925924</v>
+      </c>
+      <c r="J420">
+        <v>0</v>
+      </c>
+      <c r="K420" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H421" s="2"/>
       <c r="I421" s="1"/>
-    </row>
-    <row r="422" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H422" s="2"/>
-      <c r="I422" s="1"/>
-    </row>
-    <row r="423" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K421" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B422" t="s">
+        <v>29</v>
+      </c>
+      <c r="C422">
+        <v>3163</v>
+      </c>
+      <c r="D422" t="s">
+        <v>37</v>
+      </c>
+      <c r="F422" t="s">
+        <v>55</v>
+      </c>
+      <c r="G422" t="s">
+        <v>12</v>
+      </c>
+      <c r="H422" s="2">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="I422" s="1">
+        <v>46118.813425925924</v>
+      </c>
+      <c r="J422">
+        <v>1</v>
+      </c>
+      <c r="K422" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H423" s="2"/>
       <c r="I423" s="1"/>
-    </row>
-    <row r="424" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H424" s="2"/>
-      <c r="I424" s="1"/>
-    </row>
-    <row r="425" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K423" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B424" t="s">
+        <v>29</v>
+      </c>
+      <c r="C424">
+        <v>3194</v>
+      </c>
+      <c r="D424" t="s">
+        <v>43</v>
+      </c>
+      <c r="F424" t="s">
+        <v>55</v>
+      </c>
+      <c r="G424" t="s">
+        <v>12</v>
+      </c>
+      <c r="H424" s="2">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I424" s="1">
+        <v>46118.814120370371</v>
+      </c>
+      <c r="J424">
+        <v>0</v>
+      </c>
+      <c r="K424" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H425" s="2"/>
       <c r="I425" s="1"/>
-    </row>
-    <row r="426" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H426" s="2"/>
-      <c r="I426" s="1"/>
-    </row>
-    <row r="427" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H427" s="2"/>
-      <c r="I427" s="1"/>
-    </row>
-    <row r="428" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H428" s="2"/>
-      <c r="I428" s="1"/>
-    </row>
-    <row r="429" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K425" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B426" t="s">
+        <v>29</v>
+      </c>
+      <c r="C426">
+        <v>3162</v>
+      </c>
+      <c r="D426" t="s">
+        <v>41</v>
+      </c>
+      <c r="F426" t="s">
+        <v>55</v>
+      </c>
+      <c r="G426" t="s">
+        <v>13</v>
+      </c>
+      <c r="H426" s="2">
+        <v>0</v>
+      </c>
+      <c r="I426" s="1">
+        <v>46118.814120370371</v>
+      </c>
+      <c r="J426">
+        <v>1</v>
+      </c>
+      <c r="K426" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B427" t="s">
+        <v>29</v>
+      </c>
+      <c r="C427">
+        <v>3147</v>
+      </c>
+      <c r="D427" t="s">
+        <v>45</v>
+      </c>
+      <c r="F427" t="s">
+        <v>55</v>
+      </c>
+      <c r="G427" t="s">
+        <v>13</v>
+      </c>
+      <c r="H427" s="2">
+        <v>0</v>
+      </c>
+      <c r="I427" s="1">
+        <v>46118.814814814818</v>
+      </c>
+      <c r="J427">
+        <v>1</v>
+      </c>
+      <c r="K427" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B428" t="s">
+        <v>29</v>
+      </c>
+      <c r="C428">
+        <v>3156</v>
+      </c>
+      <c r="D428" t="s">
+        <v>46</v>
+      </c>
+      <c r="F428" t="s">
+        <v>55</v>
+      </c>
+      <c r="G428" t="s">
+        <v>12</v>
+      </c>
+      <c r="H428" s="2">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="I428" s="1">
+        <v>46118.815509259257</v>
+      </c>
+      <c r="J428">
+        <v>1</v>
+      </c>
+      <c r="K428" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H429" s="2"/>
       <c r="I429" s="1"/>
-    </row>
-    <row r="430" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H430" s="2"/>
-      <c r="I430" s="1"/>
-    </row>
-    <row r="431" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H431" s="2"/>
-      <c r="I431" s="1"/>
-    </row>
-    <row r="432" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H432" s="2"/>
-      <c r="I432" s="1"/>
-    </row>
-    <row r="433" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K429" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B430" t="s">
+        <v>29</v>
+      </c>
+      <c r="C430">
+        <v>3157</v>
+      </c>
+      <c r="D430" t="s">
+        <v>47</v>
+      </c>
+      <c r="F430" t="s">
+        <v>55</v>
+      </c>
+      <c r="G430" t="s">
+        <v>13</v>
+      </c>
+      <c r="H430" s="2">
+        <v>0</v>
+      </c>
+      <c r="I430" s="1">
+        <v>46118.79409722222</v>
+      </c>
+      <c r="J430">
+        <v>1</v>
+      </c>
+      <c r="K430" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B431" t="s">
+        <v>29</v>
+      </c>
+      <c r="C431">
+        <v>3158</v>
+      </c>
+      <c r="D431" t="s">
+        <v>48</v>
+      </c>
+      <c r="F431" t="s">
+        <v>55</v>
+      </c>
+      <c r="G431" t="s">
+        <v>13</v>
+      </c>
+      <c r="H431" s="2">
+        <v>0</v>
+      </c>
+      <c r="I431" s="1">
+        <v>46118.79409722222</v>
+      </c>
+      <c r="J431">
+        <v>1</v>
+      </c>
+      <c r="K431" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B432" t="s">
+        <v>29</v>
+      </c>
+      <c r="C432">
+        <v>3159</v>
+      </c>
+      <c r="D432" t="s">
+        <v>49</v>
+      </c>
+      <c r="F432" t="s">
+        <v>55</v>
+      </c>
+      <c r="G432" t="s">
+        <v>12</v>
+      </c>
+      <c r="H432" s="2">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="I432" s="1">
+        <v>46118.794791666667</v>
+      </c>
+      <c r="J432">
+        <v>1</v>
+      </c>
+      <c r="K432" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H433" s="2"/>
       <c r="I433" s="1"/>
-    </row>
-    <row r="434" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H434" s="2"/>
-      <c r="I434" s="1"/>
-    </row>
-    <row r="435" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K433" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B434" t="s">
+        <v>29</v>
+      </c>
+      <c r="C434">
+        <v>3150</v>
+      </c>
+      <c r="D434" t="s">
+        <v>38</v>
+      </c>
+      <c r="F434" t="s">
+        <v>55</v>
+      </c>
+      <c r="G434" t="s">
+        <v>12</v>
+      </c>
+      <c r="H434" s="2">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="I434" s="1">
+        <v>46118.795486111114</v>
+      </c>
+      <c r="J434">
+        <v>0</v>
+      </c>
+      <c r="K434" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H435" s="2"/>
       <c r="I435" s="1"/>
-    </row>
-    <row r="436" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H436" s="2"/>
-      <c r="I436" s="1"/>
-    </row>
-    <row r="437" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H437" s="2"/>
-      <c r="I437" s="1"/>
-    </row>
-    <row r="438" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H438" s="2"/>
-      <c r="I438" s="1"/>
-    </row>
-    <row r="439" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H439" s="2"/>
-      <c r="I439" s="1"/>
-    </row>
-    <row r="440" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H440" s="2"/>
-      <c r="I440" s="1"/>
-    </row>
-    <row r="441" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H441" s="2"/>
-      <c r="I441" s="1"/>
-    </row>
-    <row r="442" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H442" s="2"/>
-      <c r="I442" s="1"/>
-    </row>
-    <row r="443" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H443" s="2"/>
-      <c r="I443" s="1"/>
-    </row>
-    <row r="444" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H444" s="2"/>
-      <c r="I444" s="1"/>
-    </row>
-    <row r="445" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H445" s="2"/>
-      <c r="I445" s="1"/>
-    </row>
-    <row r="446" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H446" s="2"/>
-      <c r="I446" s="1"/>
-    </row>
-    <row r="447" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H447" s="2"/>
-      <c r="I447" s="1"/>
-    </row>
-    <row r="448" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H448" s="2"/>
-      <c r="I448" s="1"/>
-    </row>
-    <row r="449" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H449" s="2"/>
-      <c r="I449" s="1"/>
-    </row>
-    <row r="450" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H450" s="2"/>
-      <c r="I450" s="1"/>
-    </row>
-    <row r="451" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H451" s="2"/>
-      <c r="I451" s="1"/>
-    </row>
-    <row r="452" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H452" s="2"/>
-      <c r="I452" s="1"/>
-    </row>
-    <row r="453" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K435" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B436" t="s">
+        <v>29</v>
+      </c>
+      <c r="C436">
+        <v>3155</v>
+      </c>
+      <c r="D436" t="s">
+        <v>44</v>
+      </c>
+      <c r="F436" t="s">
+        <v>55</v>
+      </c>
+      <c r="G436" t="s">
+        <v>13</v>
+      </c>
+      <c r="H436" s="2">
+        <v>0</v>
+      </c>
+      <c r="I436" s="1">
+        <v>46118.796180555553</v>
+      </c>
+      <c r="J436">
+        <v>1</v>
+      </c>
+      <c r="K436" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B437" t="s">
+        <v>29</v>
+      </c>
+      <c r="C437">
+        <v>3143</v>
+      </c>
+      <c r="D437" t="s">
+        <v>30</v>
+      </c>
+      <c r="F437" t="s">
+        <v>55</v>
+      </c>
+      <c r="G437" t="s">
+        <v>13</v>
+      </c>
+      <c r="H437" s="2">
+        <v>0</v>
+      </c>
+      <c r="I437" s="1">
+        <v>46118.796180555553</v>
+      </c>
+      <c r="J437">
+        <v>1</v>
+      </c>
+      <c r="K437" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B438" t="s">
+        <v>29</v>
+      </c>
+      <c r="C438">
+        <v>3153</v>
+      </c>
+      <c r="D438" t="s">
+        <v>53</v>
+      </c>
+      <c r="F438" t="s">
+        <v>55</v>
+      </c>
+      <c r="G438" t="s">
+        <v>13</v>
+      </c>
+      <c r="H438" s="2">
+        <v>0</v>
+      </c>
+      <c r="I438" s="1">
+        <v>46118.796875</v>
+      </c>
+      <c r="J438">
+        <v>1</v>
+      </c>
+      <c r="K438" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B439" t="s">
+        <v>29</v>
+      </c>
+      <c r="C439">
+        <v>3160</v>
+      </c>
+      <c r="D439" t="s">
+        <v>34</v>
+      </c>
+      <c r="F439" t="s">
+        <v>56</v>
+      </c>
+      <c r="G439" t="s">
+        <v>13</v>
+      </c>
+      <c r="H439" s="2">
+        <v>0</v>
+      </c>
+      <c r="I439" s="1">
+        <v>46118.804513888892</v>
+      </c>
+      <c r="J439">
+        <v>1</v>
+      </c>
+      <c r="K439" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B440" t="s">
+        <v>29</v>
+      </c>
+      <c r="C440">
+        <v>3161</v>
+      </c>
+      <c r="D440" t="s">
+        <v>34</v>
+      </c>
+      <c r="F440" t="s">
+        <v>56</v>
+      </c>
+      <c r="G440" t="s">
+        <v>13</v>
+      </c>
+      <c r="H440" s="2">
+        <v>0</v>
+      </c>
+      <c r="I440" s="1">
+        <v>46118.804513888892</v>
+      </c>
+      <c r="J440">
+        <v>1</v>
+      </c>
+      <c r="K440" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B441" t="s">
+        <v>29</v>
+      </c>
+      <c r="C441">
+        <v>3146</v>
+      </c>
+      <c r="D441" t="s">
+        <v>35</v>
+      </c>
+      <c r="F441" t="s">
+        <v>56</v>
+      </c>
+      <c r="G441" t="s">
+        <v>10</v>
+      </c>
+      <c r="H441" s="2">
+        <v>5.6944444444444447E-3</v>
+      </c>
+      <c r="I441" s="1">
+        <v>46118.805208333331</v>
+      </c>
+      <c r="J441">
+        <v>0</v>
+      </c>
+      <c r="K441" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B442" t="s">
+        <v>29</v>
+      </c>
+      <c r="C442">
+        <v>3429</v>
+      </c>
+      <c r="D442" t="s">
+        <v>54</v>
+      </c>
+      <c r="F442" t="s">
+        <v>56</v>
+      </c>
+      <c r="G442" t="s">
+        <v>10</v>
+      </c>
+      <c r="H442" s="2">
+        <v>4.7337962962962967E-3</v>
+      </c>
+      <c r="I442" s="1">
+        <v>46118.805208333331</v>
+      </c>
+      <c r="J442">
+        <v>0</v>
+      </c>
+      <c r="K442" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B443" t="s">
+        <v>29</v>
+      </c>
+      <c r="C443">
+        <v>3154</v>
+      </c>
+      <c r="D443" t="s">
+        <v>31</v>
+      </c>
+      <c r="F443" t="s">
+        <v>56</v>
+      </c>
+      <c r="G443" t="s">
+        <v>10</v>
+      </c>
+      <c r="H443" s="2">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="I443" s="1">
+        <v>46118.805902777778</v>
+      </c>
+      <c r="J443">
+        <v>0</v>
+      </c>
+      <c r="K443" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B444" t="s">
+        <v>29</v>
+      </c>
+      <c r="C444">
+        <v>3144</v>
+      </c>
+      <c r="D444" t="s">
+        <v>32</v>
+      </c>
+      <c r="F444" t="s">
+        <v>56</v>
+      </c>
+      <c r="G444" t="s">
+        <v>13</v>
+      </c>
+      <c r="H444" s="2">
+        <v>0</v>
+      </c>
+      <c r="I444" s="1">
+        <v>46118.806597222225</v>
+      </c>
+      <c r="J444">
+        <v>1</v>
+      </c>
+      <c r="K444" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B445" t="s">
+        <v>29</v>
+      </c>
+      <c r="C445">
+        <v>3145</v>
+      </c>
+      <c r="D445" t="s">
+        <v>33</v>
+      </c>
+      <c r="F445" t="s">
+        <v>56</v>
+      </c>
+      <c r="G445" t="s">
+        <v>13</v>
+      </c>
+      <c r="H445" s="2">
+        <v>0</v>
+      </c>
+      <c r="I445" s="1">
+        <v>46118.806597222225</v>
+      </c>
+      <c r="J445">
+        <v>1</v>
+      </c>
+      <c r="K445" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="446" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B446" t="s">
+        <v>29</v>
+      </c>
+      <c r="C446">
+        <v>3149</v>
+      </c>
+      <c r="D446" t="s">
+        <v>40</v>
+      </c>
+      <c r="F446" t="s">
+        <v>56</v>
+      </c>
+      <c r="G446" t="s">
+        <v>13</v>
+      </c>
+      <c r="H446" s="2">
+        <v>0</v>
+      </c>
+      <c r="I446" s="1">
+        <v>46118.807291666664</v>
+      </c>
+      <c r="J446">
+        <v>1</v>
+      </c>
+      <c r="K446" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B447" t="s">
+        <v>29</v>
+      </c>
+      <c r="C447">
+        <v>3151</v>
+      </c>
+      <c r="D447" t="s">
+        <v>39</v>
+      </c>
+      <c r="F447" t="s">
+        <v>56</v>
+      </c>
+      <c r="G447" t="s">
+        <v>13</v>
+      </c>
+      <c r="H447" s="2">
+        <v>0</v>
+      </c>
+      <c r="I447" s="1">
+        <v>46118.807986111111</v>
+      </c>
+      <c r="J447">
+        <v>1</v>
+      </c>
+      <c r="K447" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B448" t="s">
+        <v>29</v>
+      </c>
+      <c r="C448">
+        <v>3148</v>
+      </c>
+      <c r="D448" t="s">
+        <v>36</v>
+      </c>
+      <c r="F448" t="s">
+        <v>56</v>
+      </c>
+      <c r="G448" t="s">
+        <v>13</v>
+      </c>
+      <c r="H448" s="2">
+        <v>0</v>
+      </c>
+      <c r="I448" s="1">
+        <v>46118.807986111111</v>
+      </c>
+      <c r="J448">
+        <v>1</v>
+      </c>
+      <c r="K448" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="449" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B449" t="s">
+        <v>29</v>
+      </c>
+      <c r="C449">
+        <v>3164</v>
+      </c>
+      <c r="D449" t="s">
+        <v>42</v>
+      </c>
+      <c r="F449" t="s">
+        <v>56</v>
+      </c>
+      <c r="G449" t="s">
+        <v>13</v>
+      </c>
+      <c r="H449" s="2">
+        <v>0</v>
+      </c>
+      <c r="I449" s="1">
+        <v>46118.808680555558</v>
+      </c>
+      <c r="J449">
+        <v>1</v>
+      </c>
+      <c r="K449" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="450" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B450" t="s">
+        <v>29</v>
+      </c>
+      <c r="C450">
+        <v>3163</v>
+      </c>
+      <c r="D450" t="s">
+        <v>37</v>
+      </c>
+      <c r="F450" t="s">
+        <v>56</v>
+      </c>
+      <c r="G450" t="s">
+        <v>10</v>
+      </c>
+      <c r="H450" s="2">
+        <v>7.858796296296296E-3</v>
+      </c>
+      <c r="I450" s="1">
+        <v>46118.808680555558</v>
+      </c>
+      <c r="J450">
+        <v>1</v>
+      </c>
+      <c r="K450" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="451" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B451" t="s">
+        <v>29</v>
+      </c>
+      <c r="C451">
+        <v>3194</v>
+      </c>
+      <c r="D451" t="s">
+        <v>43</v>
+      </c>
+      <c r="F451" t="s">
+        <v>56</v>
+      </c>
+      <c r="G451" t="s">
+        <v>13</v>
+      </c>
+      <c r="H451" s="2">
+        <v>0</v>
+      </c>
+      <c r="I451" s="1">
+        <v>46118.809374999997</v>
+      </c>
+      <c r="J451">
+        <v>1</v>
+      </c>
+      <c r="K451" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="452" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B452" t="s">
+        <v>29</v>
+      </c>
+      <c r="C452">
+        <v>3162</v>
+      </c>
+      <c r="D452" t="s">
+        <v>41</v>
+      </c>
+      <c r="F452" t="s">
+        <v>56</v>
+      </c>
+      <c r="G452" t="s">
+        <v>14</v>
+      </c>
+      <c r="H452" s="2">
+        <v>0</v>
+      </c>
+      <c r="I452" s="1">
+        <v>46118.810069444444</v>
+      </c>
+      <c r="J452">
+        <v>0</v>
+      </c>
+      <c r="K452" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H453" s="2"/>
       <c r="I453" s="1"/>
-    </row>
-    <row r="454" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H454" s="2"/>
-      <c r="I454" s="1"/>
-    </row>
-    <row r="455" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H455" s="2"/>
-      <c r="I455" s="1"/>
-    </row>
-    <row r="456" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H456" s="2"/>
-      <c r="I456" s="1"/>
-    </row>
-    <row r="457" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H457" s="2"/>
-      <c r="I457" s="1"/>
-    </row>
-    <row r="458" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H458" s="2"/>
-      <c r="I458" s="1"/>
-    </row>
-    <row r="459" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H459" s="2"/>
-      <c r="I459" s="1"/>
-    </row>
-    <row r="460" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H460" s="2"/>
-      <c r="I460" s="1"/>
-    </row>
-    <row r="461" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H461" s="2"/>
-      <c r="I461" s="1"/>
-    </row>
-    <row r="462" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H462" s="2"/>
-      <c r="I462" s="1"/>
-    </row>
-    <row r="463" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K453" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B454" t="s">
+        <v>29</v>
+      </c>
+      <c r="C454">
+        <v>3147</v>
+      </c>
+      <c r="D454" t="s">
+        <v>45</v>
+      </c>
+      <c r="F454" t="s">
+        <v>56</v>
+      </c>
+      <c r="G454" t="s">
+        <v>13</v>
+      </c>
+      <c r="H454" s="2">
+        <v>0</v>
+      </c>
+      <c r="I454" s="1">
+        <v>46118.810069444444</v>
+      </c>
+      <c r="J454">
+        <v>1</v>
+      </c>
+      <c r="K454" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="455" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B455" t="s">
+        <v>29</v>
+      </c>
+      <c r="C455">
+        <v>3156</v>
+      </c>
+      <c r="D455" t="s">
+        <v>46</v>
+      </c>
+      <c r="F455" t="s">
+        <v>56</v>
+      </c>
+      <c r="G455" t="s">
+        <v>10</v>
+      </c>
+      <c r="H455" s="2">
+        <v>7.6273148148148151E-3</v>
+      </c>
+      <c r="I455" s="1">
+        <v>46118.810763888891</v>
+      </c>
+      <c r="J455">
+        <v>1</v>
+      </c>
+      <c r="K455" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="456" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B456" t="s">
+        <v>29</v>
+      </c>
+      <c r="C456">
+        <v>3157</v>
+      </c>
+      <c r="D456" t="s">
+        <v>47</v>
+      </c>
+      <c r="F456" t="s">
+        <v>56</v>
+      </c>
+      <c r="G456" t="s">
+        <v>13</v>
+      </c>
+      <c r="H456" s="2">
+        <v>0</v>
+      </c>
+      <c r="I456" s="1">
+        <v>46118.810763888891</v>
+      </c>
+      <c r="J456">
+        <v>1</v>
+      </c>
+      <c r="K456" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="457" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B457" t="s">
+        <v>29</v>
+      </c>
+      <c r="C457">
+        <v>3158</v>
+      </c>
+      <c r="D457" t="s">
+        <v>48</v>
+      </c>
+      <c r="F457" t="s">
+        <v>56</v>
+      </c>
+      <c r="G457" t="s">
+        <v>10</v>
+      </c>
+      <c r="H457" s="2">
+        <v>7.6157407407407406E-3</v>
+      </c>
+      <c r="I457" s="1">
+        <v>46118.81145833333</v>
+      </c>
+      <c r="J457">
+        <v>1</v>
+      </c>
+      <c r="K457" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="458" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B458" t="s">
+        <v>29</v>
+      </c>
+      <c r="C458">
+        <v>3159</v>
+      </c>
+      <c r="D458" t="s">
+        <v>49</v>
+      </c>
+      <c r="F458" t="s">
+        <v>56</v>
+      </c>
+      <c r="G458" t="s">
+        <v>10</v>
+      </c>
+      <c r="H458" s="2">
+        <v>1.5590277777777778E-2</v>
+      </c>
+      <c r="I458" s="1">
+        <v>46118.812152777777</v>
+      </c>
+      <c r="J458">
+        <v>0</v>
+      </c>
+      <c r="K458" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="459" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B459" t="s">
+        <v>29</v>
+      </c>
+      <c r="C459">
+        <v>3150</v>
+      </c>
+      <c r="D459" t="s">
+        <v>38</v>
+      </c>
+      <c r="F459" t="s">
+        <v>56</v>
+      </c>
+      <c r="G459" t="s">
+        <v>10</v>
+      </c>
+      <c r="H459" s="2">
+        <v>9.3518518518518525E-3</v>
+      </c>
+      <c r="I459" s="1">
+        <v>46118.812152777777</v>
+      </c>
+      <c r="J459">
+        <v>0</v>
+      </c>
+      <c r="K459" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="460" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B460" t="s">
+        <v>29</v>
+      </c>
+      <c r="C460">
+        <v>3155</v>
+      </c>
+      <c r="D460" t="s">
+        <v>44</v>
+      </c>
+      <c r="F460" t="s">
+        <v>56</v>
+      </c>
+      <c r="G460" t="s">
+        <v>13</v>
+      </c>
+      <c r="H460" s="2">
+        <v>0</v>
+      </c>
+      <c r="I460" s="1">
+        <v>46118.812847222223</v>
+      </c>
+      <c r="J460">
+        <v>1</v>
+      </c>
+      <c r="K460" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B461" t="s">
+        <v>29</v>
+      </c>
+      <c r="C461">
+        <v>3143</v>
+      </c>
+      <c r="D461" t="s">
+        <v>30</v>
+      </c>
+      <c r="F461" t="s">
+        <v>56</v>
+      </c>
+      <c r="G461" t="s">
+        <v>13</v>
+      </c>
+      <c r="H461" s="2">
+        <v>0</v>
+      </c>
+      <c r="I461" s="1">
+        <v>46118.812847222223</v>
+      </c>
+      <c r="J461">
+        <v>1</v>
+      </c>
+      <c r="K461" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B462" t="s">
+        <v>29</v>
+      </c>
+      <c r="C462">
+        <v>3153</v>
+      </c>
+      <c r="D462" t="s">
+        <v>53</v>
+      </c>
+      <c r="F462" t="s">
+        <v>56</v>
+      </c>
+      <c r="G462" t="s">
+        <v>13</v>
+      </c>
+      <c r="H462" s="2">
+        <v>0</v>
+      </c>
+      <c r="I462" s="1">
+        <v>46118.81354166667</v>
+      </c>
+      <c r="J462">
+        <v>1</v>
+      </c>
+      <c r="K462" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H463" s="2"/>
       <c r="I463" s="1"/>
     </row>
-    <row r="464" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H464" s="2"/>
       <c r="I464" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC79C27E-6D08-4E45-9567-DF859B453C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CE0768-6387-47FD-BF53-F4457146EF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Ben Peppenger</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1250,7 @@
         <v>3160</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>27</v>
@@ -1914,7 +1917,7 @@
         <v>3160</v>
       </c>
       <c r="D46" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
@@ -2711,7 +2714,7 @@
         <v>3160</v>
       </c>
       <c r="D75" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F75" t="s">
         <v>27</v>
@@ -3435,7 +3438,7 @@
         <v>3160</v>
       </c>
       <c r="D103" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F103" t="s">
         <v>25</v>
@@ -4145,7 +4148,7 @@
         <v>3160</v>
       </c>
       <c r="D129" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F129" t="s">
         <v>19</v>
@@ -4862,7 +4865,7 @@
         <v>3160</v>
       </c>
       <c r="D156" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F156" t="s">
         <v>15</v>
@@ -5514,7 +5517,7 @@
         <v>3160</v>
       </c>
       <c r="D180" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F180" t="s">
         <v>24</v>
@@ -6296,7 +6299,7 @@
         <v>3160</v>
       </c>
       <c r="D210" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -7021,7 +7024,7 @@
         <v>3160</v>
       </c>
       <c r="D235" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F235" t="s">
         <v>26</v>
@@ -7782,7 +7785,7 @@
         <v>3160</v>
       </c>
       <c r="D262" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F262" t="s">
         <v>18</v>
@@ -8470,7 +8473,7 @@
         <v>3160</v>
       </c>
       <c r="D288" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -9208,7 +9211,7 @@
         <v>3160</v>
       </c>
       <c r="D318" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F318" t="s">
         <v>17</v>
@@ -9903,7 +9906,7 @@
         <v>3160</v>
       </c>
       <c r="D345" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F345" t="s">
         <v>22</v>
@@ -10598,7 +10601,7 @@
         <v>3160</v>
       </c>
       <c r="D372" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F372" t="s">
         <v>23</v>
@@ -11344,7 +11347,7 @@
         <v>3160</v>
       </c>
       <c r="D400" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F400" t="s">
         <v>20</v>
@@ -11547,7 +11550,7 @@
         <v>3160</v>
       </c>
       <c r="D407" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F407" t="s">
         <v>55</v>
@@ -11562,7 +11565,7 @@
         <v>46118.808564814812</v>
       </c>
       <c r="J407">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K407" t="s">
         <v>11</v>
@@ -11591,7 +11594,7 @@
         <v>46118.809259259258</v>
       </c>
       <c r="J408">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K408" t="s">
         <v>11</v>
@@ -11728,7 +11731,7 @@
         <v>46118.811342592591</v>
       </c>
       <c r="J415">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K415" t="s">
         <v>11</v>
@@ -11757,7 +11760,7 @@
         <v>46118.811342592591</v>
       </c>
       <c r="J416">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K416" t="s">
         <v>11</v>
@@ -11786,7 +11789,7 @@
         <v>46118.812037037038</v>
       </c>
       <c r="J417">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K417" t="s">
         <v>11</v>
@@ -11815,7 +11818,7 @@
         <v>46118.812037037038</v>
       </c>
       <c r="J418">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K418" t="s">
         <v>11</v>
@@ -11844,7 +11847,7 @@
         <v>46118.812731481485</v>
       </c>
       <c r="J419">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K419" t="s">
         <v>11</v>
@@ -11981,7 +11984,7 @@
         <v>46118.814120370371</v>
       </c>
       <c r="J426">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K426" t="s">
         <v>11</v>
@@ -12010,7 +12013,7 @@
         <v>46118.814814814818</v>
       </c>
       <c r="J427">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K427" t="s">
         <v>11</v>
@@ -12075,7 +12078,7 @@
         <v>46118.79409722222</v>
       </c>
       <c r="J430">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K430" t="s">
         <v>11</v>
@@ -12095,120 +12098,98 @@
         <v>55</v>
       </c>
       <c r="G431" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H431" s="2">
-        <v>0</v>
+        <v>1.1226851851851851E-3</v>
       </c>
       <c r="I431" s="1">
         <v>46118.79409722222</v>
       </c>
       <c r="J431">
+        <v>2</v>
+      </c>
+      <c r="K431" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H432" s="2"/>
+      <c r="I432" s="1"/>
+      <c r="K432" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B433" t="s">
+        <v>29</v>
+      </c>
+      <c r="C433">
+        <v>3159</v>
+      </c>
+      <c r="D433" t="s">
+        <v>49</v>
+      </c>
+      <c r="F433" t="s">
+        <v>55</v>
+      </c>
+      <c r="G433" t="s">
+        <v>12</v>
+      </c>
+      <c r="H433" s="2">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="I433" s="1">
+        <v>46118.794791666667</v>
+      </c>
+      <c r="J433">
         <v>1</v>
       </c>
-      <c r="K431" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B432" t="s">
-        <v>29</v>
-      </c>
-      <c r="C432">
-        <v>3159</v>
-      </c>
-      <c r="D432" t="s">
-        <v>49</v>
-      </c>
-      <c r="F432" t="s">
+      <c r="K433" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H434" s="2"/>
+      <c r="I434" s="1"/>
+      <c r="K434" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B435" t="s">
+        <v>29</v>
+      </c>
+      <c r="C435">
+        <v>3150</v>
+      </c>
+      <c r="D435" t="s">
+        <v>38</v>
+      </c>
+      <c r="F435" t="s">
         <v>55</v>
       </c>
-      <c r="G432" t="s">
+      <c r="G435" t="s">
         <v>12</v>
       </c>
-      <c r="H432" s="2">
+      <c r="H435" s="2">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="I432" s="1">
-        <v>46118.794791666667</v>
-      </c>
-      <c r="J432">
-        <v>1</v>
-      </c>
-      <c r="K432" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H433" s="2"/>
-      <c r="I433" s="1"/>
-      <c r="K433" t="s">
+      <c r="I435" s="1">
+        <v>46118.795486111114</v>
+      </c>
+      <c r="J435">
+        <v>0</v>
+      </c>
+      <c r="K435" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H436" s="2"/>
+      <c r="I436" s="1"/>
+      <c r="K436" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B434" t="s">
-        <v>29</v>
-      </c>
-      <c r="C434">
-        <v>3150</v>
-      </c>
-      <c r="D434" t="s">
-        <v>38</v>
-      </c>
-      <c r="F434" t="s">
-        <v>55</v>
-      </c>
-      <c r="G434" t="s">
-        <v>12</v>
-      </c>
-      <c r="H434" s="2">
-        <v>1.273148148148148E-4</v>
-      </c>
-      <c r="I434" s="1">
-        <v>46118.795486111114</v>
-      </c>
-      <c r="J434">
-        <v>0</v>
-      </c>
-      <c r="K434" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H435" s="2"/>
-      <c r="I435" s="1"/>
-      <c r="K435" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B436" t="s">
-        <v>29</v>
-      </c>
-      <c r="C436">
-        <v>3155</v>
-      </c>
-      <c r="D436" t="s">
-        <v>44</v>
-      </c>
-      <c r="F436" t="s">
-        <v>55</v>
-      </c>
-      <c r="G436" t="s">
-        <v>13</v>
-      </c>
-      <c r="H436" s="2">
-        <v>0</v>
-      </c>
-      <c r="I436" s="1">
-        <v>46118.796180555553</v>
-      </c>
-      <c r="J436">
-        <v>1</v>
-      </c>
-      <c r="K436" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="437" spans="2:11" x14ac:dyDescent="0.25">
@@ -12216,10 +12197,10 @@
         <v>29</v>
       </c>
       <c r="C437">
-        <v>3143</v>
+        <v>3155</v>
       </c>
       <c r="D437" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F437" t="s">
         <v>55</v>
@@ -12234,7 +12215,7 @@
         <v>46118.796180555553</v>
       </c>
       <c r="J437">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K437" t="s">
         <v>11</v>
@@ -12245,10 +12226,10 @@
         <v>29</v>
       </c>
       <c r="C438">
-        <v>3153</v>
+        <v>3143</v>
       </c>
       <c r="D438" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F438" t="s">
         <v>55</v>
@@ -12260,10 +12241,10 @@
         <v>0</v>
       </c>
       <c r="I438" s="1">
-        <v>46118.796875</v>
+        <v>46118.796180555553</v>
       </c>
       <c r="J438">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K438" t="s">
         <v>11</v>
@@ -12274,13 +12255,13 @@
         <v>29</v>
       </c>
       <c r="C439">
-        <v>3160</v>
+        <v>3153</v>
       </c>
       <c r="D439" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F439" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G439" t="s">
         <v>13</v>
@@ -12289,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="I439" s="1">
-        <v>46118.804513888892</v>
+        <v>46118.796875</v>
       </c>
       <c r="J439">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K439" t="s">
         <v>11</v>
@@ -12303,10 +12284,10 @@
         <v>29</v>
       </c>
       <c r="C440">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="D440" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F440" t="s">
         <v>56</v>
@@ -12321,7 +12302,7 @@
         <v>46118.804513888892</v>
       </c>
       <c r="J440">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K440" t="s">
         <v>11</v>
@@ -12332,25 +12313,25 @@
         <v>29</v>
       </c>
       <c r="C441">
-        <v>3146</v>
+        <v>3161</v>
       </c>
       <c r="D441" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F441" t="s">
         <v>56</v>
       </c>
       <c r="G441" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H441" s="2">
-        <v>5.6944444444444447E-3</v>
+        <v>0</v>
       </c>
       <c r="I441" s="1">
-        <v>46118.805208333331</v>
+        <v>46118.804513888892</v>
       </c>
       <c r="J441">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K441" t="s">
         <v>11</v>
@@ -12361,10 +12342,10 @@
         <v>29</v>
       </c>
       <c r="C442">
-        <v>3429</v>
+        <v>3146</v>
       </c>
       <c r="D442" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F442" t="s">
         <v>56</v>
@@ -12373,7 +12354,7 @@
         <v>10</v>
       </c>
       <c r="H442" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>5.6944444444444447E-3</v>
       </c>
       <c r="I442" s="1">
         <v>46118.805208333331</v>
@@ -12390,10 +12371,10 @@
         <v>29</v>
       </c>
       <c r="C443">
-        <v>3154</v>
+        <v>3429</v>
       </c>
       <c r="D443" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F443" t="s">
         <v>56</v>
@@ -12402,10 +12383,10 @@
         <v>10</v>
       </c>
       <c r="H443" s="2">
-        <v>7.2453703703703708E-3</v>
+        <v>4.7337962962962967E-3</v>
       </c>
       <c r="I443" s="1">
-        <v>46118.805902777778</v>
+        <v>46118.805208333331</v>
       </c>
       <c r="J443">
         <v>0</v>
@@ -12419,25 +12400,25 @@
         <v>29</v>
       </c>
       <c r="C444">
-        <v>3144</v>
+        <v>3154</v>
       </c>
       <c r="D444" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F444" t="s">
         <v>56</v>
       </c>
       <c r="G444" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H444" s="2">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="I444" s="1">
+        <v>46118.805902777778</v>
+      </c>
+      <c r="J444">
         <v>0</v>
-      </c>
-      <c r="I444" s="1">
-        <v>46118.806597222225</v>
-      </c>
-      <c r="J444">
-        <v>1</v>
       </c>
       <c r="K444" t="s">
         <v>11</v>
@@ -12448,10 +12429,10 @@
         <v>29</v>
       </c>
       <c r="C445">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D445" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F445" t="s">
         <v>56</v>
@@ -12466,7 +12447,7 @@
         <v>46118.806597222225</v>
       </c>
       <c r="J445">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K445" t="s">
         <v>11</v>
@@ -12477,10 +12458,10 @@
         <v>29</v>
       </c>
       <c r="C446">
-        <v>3149</v>
+        <v>3145</v>
       </c>
       <c r="D446" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F446" t="s">
         <v>56</v>
@@ -12492,10 +12473,10 @@
         <v>0</v>
       </c>
       <c r="I446" s="1">
-        <v>46118.807291666664</v>
+        <v>46118.806597222225</v>
       </c>
       <c r="J446">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K446" t="s">
         <v>11</v>
@@ -12506,10 +12487,10 @@
         <v>29</v>
       </c>
       <c r="C447">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="D447" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F447" t="s">
         <v>56</v>
@@ -12521,10 +12502,10 @@
         <v>0</v>
       </c>
       <c r="I447" s="1">
-        <v>46118.807986111111</v>
+        <v>46118.807291666664</v>
       </c>
       <c r="J447">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K447" t="s">
         <v>11</v>
@@ -12535,10 +12516,10 @@
         <v>29</v>
       </c>
       <c r="C448">
-        <v>3148</v>
+        <v>3151</v>
       </c>
       <c r="D448" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F448" t="s">
         <v>56</v>
@@ -12553,7 +12534,7 @@
         <v>46118.807986111111</v>
       </c>
       <c r="J448">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K448" t="s">
         <v>11</v>
@@ -12564,10 +12545,10 @@
         <v>29</v>
       </c>
       <c r="C449">
-        <v>3164</v>
+        <v>3148</v>
       </c>
       <c r="D449" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F449" t="s">
         <v>56</v>
@@ -12579,10 +12560,10 @@
         <v>0</v>
       </c>
       <c r="I449" s="1">
-        <v>46118.808680555558</v>
+        <v>46118.807986111111</v>
       </c>
       <c r="J449">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K449" t="s">
         <v>11</v>
@@ -12593,10 +12574,10 @@
         <v>29</v>
       </c>
       <c r="C450">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="D450" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F450" t="s">
         <v>56</v>
@@ -12605,13 +12586,13 @@
         <v>10</v>
       </c>
       <c r="H450" s="2">
-        <v>7.858796296296296E-3</v>
+        <v>8.6342592592592599E-3</v>
       </c>
       <c r="I450" s="1">
         <v>46118.808680555558</v>
       </c>
       <c r="J450">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K450" t="s">
         <v>11</v>
@@ -12622,22 +12603,22 @@
         <v>29</v>
       </c>
       <c r="C451">
-        <v>3194</v>
+        <v>3163</v>
       </c>
       <c r="D451" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F451" t="s">
         <v>56</v>
       </c>
       <c r="G451" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H451" s="2">
-        <v>0</v>
+        <v>7.858796296296296E-3</v>
       </c>
       <c r="I451" s="1">
-        <v>46118.809374999997</v>
+        <v>46118.808680555558</v>
       </c>
       <c r="J451">
         <v>1</v>
@@ -12651,64 +12632,64 @@
         <v>29</v>
       </c>
       <c r="C452">
-        <v>3162</v>
+        <v>3194</v>
       </c>
       <c r="D452" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F452" t="s">
         <v>56</v>
       </c>
       <c r="G452" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H452" s="2">
         <v>0</v>
       </c>
       <c r="I452" s="1">
+        <v>46118.809374999997</v>
+      </c>
+      <c r="J452">
+        <v>2</v>
+      </c>
+      <c r="K452" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B453" t="s">
+        <v>29</v>
+      </c>
+      <c r="C453">
+        <v>3162</v>
+      </c>
+      <c r="D453" t="s">
+        <v>41</v>
+      </c>
+      <c r="F453" t="s">
+        <v>56</v>
+      </c>
+      <c r="G453" t="s">
+        <v>14</v>
+      </c>
+      <c r="H453" s="2">
+        <v>0</v>
+      </c>
+      <c r="I453" s="1">
         <v>46118.810069444444</v>
       </c>
-      <c r="J452">
+      <c r="J453">
         <v>0</v>
       </c>
-      <c r="K452" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H453" s="2"/>
-      <c r="I453" s="1"/>
       <c r="K453" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H454" s="2"/>
+      <c r="I454" s="1"/>
+      <c r="K454" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B454" t="s">
-        <v>29</v>
-      </c>
-      <c r="C454">
-        <v>3147</v>
-      </c>
-      <c r="D454" t="s">
-        <v>45</v>
-      </c>
-      <c r="F454" t="s">
-        <v>56</v>
-      </c>
-      <c r="G454" t="s">
-        <v>13</v>
-      </c>
-      <c r="H454" s="2">
-        <v>0</v>
-      </c>
-      <c r="I454" s="1">
-        <v>46118.810069444444</v>
-      </c>
-      <c r="J454">
-        <v>1</v>
-      </c>
-      <c r="K454" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="455" spans="2:11" x14ac:dyDescent="0.25">
@@ -12716,25 +12697,25 @@
         <v>29</v>
       </c>
       <c r="C455">
-        <v>3156</v>
+        <v>3147</v>
       </c>
       <c r="D455" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F455" t="s">
         <v>56</v>
       </c>
       <c r="G455" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H455" s="2">
-        <v>7.6273148148148151E-3</v>
+        <v>0</v>
       </c>
       <c r="I455" s="1">
-        <v>46118.810763888891</v>
+        <v>46118.810069444444</v>
       </c>
       <c r="J455">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K455" t="s">
         <v>11</v>
@@ -12745,19 +12726,19 @@
         <v>29</v>
       </c>
       <c r="C456">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="D456" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F456" t="s">
         <v>56</v>
       </c>
       <c r="G456" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H456" s="2">
-        <v>0</v>
+        <v>7.6273148148148151E-3</v>
       </c>
       <c r="I456" s="1">
         <v>46118.810763888891</v>
@@ -12774,25 +12755,25 @@
         <v>29</v>
       </c>
       <c r="C457">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="D457" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F457" t="s">
         <v>56</v>
       </c>
       <c r="G457" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H457" s="2">
-        <v>7.6157407407407406E-3</v>
+        <v>0</v>
       </c>
       <c r="I457" s="1">
-        <v>46118.81145833333</v>
+        <v>46118.810763888891</v>
       </c>
       <c r="J457">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K457" t="s">
         <v>11</v>
@@ -12803,10 +12784,10 @@
         <v>29</v>
       </c>
       <c r="C458">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="D458" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F458" t="s">
         <v>56</v>
@@ -12815,13 +12796,13 @@
         <v>10</v>
       </c>
       <c r="H458" s="2">
-        <v>1.5590277777777778E-2</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I458" s="1">
-        <v>46118.812152777777</v>
+        <v>46118.81145833333</v>
       </c>
       <c r="J458">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K458" t="s">
         <v>11</v>
@@ -12832,10 +12813,10 @@
         <v>29</v>
       </c>
       <c r="C459">
-        <v>3150</v>
+        <v>3159</v>
       </c>
       <c r="D459" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F459" t="s">
         <v>56</v>
@@ -12844,7 +12825,7 @@
         <v>10</v>
       </c>
       <c r="H459" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>1.5590277777777778E-2</v>
       </c>
       <c r="I459" s="1">
         <v>46118.812152777777</v>
@@ -12861,25 +12842,25 @@
         <v>29</v>
       </c>
       <c r="C460">
-        <v>3155</v>
+        <v>3150</v>
       </c>
       <c r="D460" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F460" t="s">
         <v>56</v>
       </c>
       <c r="G460" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H460" s="2">
+        <v>9.3518518518518525E-3</v>
+      </c>
+      <c r="I460" s="1">
+        <v>46118.812152777777</v>
+      </c>
+      <c r="J460">
         <v>0</v>
-      </c>
-      <c r="I460" s="1">
-        <v>46118.812847222223</v>
-      </c>
-      <c r="J460">
-        <v>1</v>
       </c>
       <c r="K460" t="s">
         <v>11</v>
@@ -12890,19 +12871,19 @@
         <v>29</v>
       </c>
       <c r="C461">
-        <v>3143</v>
+        <v>3155</v>
       </c>
       <c r="D461" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F461" t="s">
         <v>56</v>
       </c>
       <c r="G461" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H461" s="2">
-        <v>0</v>
+        <v>7.4305555555555557E-3</v>
       </c>
       <c r="I461" s="1">
         <v>46118.812847222223</v>
@@ -12919,33 +12900,58 @@
         <v>29</v>
       </c>
       <c r="C462">
-        <v>3153</v>
+        <v>3143</v>
       </c>
       <c r="D462" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F462" t="s">
         <v>56</v>
       </c>
       <c r="G462" t="s">
+        <v>10</v>
+      </c>
+      <c r="H462" s="2">
+        <v>1.7777777777777778E-2</v>
+      </c>
+      <c r="I462" s="1">
+        <v>46118.812847222223</v>
+      </c>
+      <c r="J462">
+        <v>2</v>
+      </c>
+      <c r="K462" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B463" t="s">
+        <v>29</v>
+      </c>
+      <c r="C463">
+        <v>3153</v>
+      </c>
+      <c r="D463" t="s">
+        <v>53</v>
+      </c>
+      <c r="F463" t="s">
+        <v>56</v>
+      </c>
+      <c r="G463" t="s">
         <v>13</v>
       </c>
-      <c r="H462" s="2">
+      <c r="H463" s="2">
         <v>0</v>
       </c>
-      <c r="I462" s="1">
+      <c r="I463" s="1">
         <v>46118.81354166667</v>
       </c>
-      <c r="J462">
-        <v>1</v>
-      </c>
-      <c r="K462" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H463" s="2"/>
-      <c r="I463" s="1"/>
+      <c r="J463">
+        <v>2</v>
+      </c>
+      <c r="K463" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="464" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H464" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CE0768-6387-47FD-BF53-F4457146EF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DC6300-1426-47BC-9708-FC36770E2E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Jeff Schnippel</t>
   </si>
   <si>
-    <t>Greg Magnuson</t>
-  </si>
-  <si>
     <t>Melissa Dowe</t>
   </si>
   <si>
@@ -213,6 +210,9 @@
   </si>
   <si>
     <t>Ben Peppenger</t>
+  </si>
+  <si>
+    <t>NEW HIRE</t>
   </si>
 </sst>
 </file>
@@ -931,7 +931,7 @@
         <v>3149</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
         <v>27</v>
@@ -960,7 +960,7 @@
         <v>3153</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
         <v>27</v>
@@ -989,7 +989,7 @@
         <v>3162</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
         <v>27</v>
@@ -1018,7 +1018,7 @@
         <v>3164</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
         <v>27</v>
@@ -1047,7 +1047,7 @@
         <v>3194</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
@@ -1076,7 +1076,7 @@
         <v>3155</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
@@ -1105,7 +1105,7 @@
         <v>3147</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -1134,7 +1134,7 @@
         <v>3156</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
@@ -1163,7 +1163,7 @@
         <v>3157</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
@@ -1192,7 +1192,7 @@
         <v>3158</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
@@ -1221,7 +1221,7 @@
         <v>3159</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
@@ -1250,7 +1250,7 @@
         <v>3160</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
         <v>27</v>
@@ -1598,7 +1598,7 @@
         <v>3149</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F35" t="s">
         <v>15</v>
@@ -1627,7 +1627,7 @@
         <v>3153</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F36" t="s">
         <v>15</v>
@@ -1656,7 +1656,7 @@
         <v>3162</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F37" t="s">
         <v>15</v>
@@ -1685,7 +1685,7 @@
         <v>3164</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F38" t="s">
         <v>15</v>
@@ -1714,7 +1714,7 @@
         <v>3194</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
@@ -1743,7 +1743,7 @@
         <v>3155</v>
       </c>
       <c r="D40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
@@ -1772,7 +1772,7 @@
         <v>3147</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -1801,7 +1801,7 @@
         <v>3156</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1830,7 +1830,7 @@
         <v>3157</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -1859,7 +1859,7 @@
         <v>3158</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
@@ -1888,7 +1888,7 @@
         <v>3159</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -1917,7 +1917,7 @@
         <v>3160</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
@@ -1975,7 +1975,7 @@
         <v>3209</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F48" t="s">
         <v>27</v>
@@ -2004,7 +2004,7 @@
         <v>3194</v>
       </c>
       <c r="D49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F49" t="s">
         <v>27</v>
@@ -2033,10 +2033,10 @@
         <v>3194</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
@@ -2352,7 +2352,7 @@
         <v>3149</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F61" t="s">
         <v>27</v>
@@ -2388,7 +2388,7 @@
         <v>3153</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
@@ -2417,7 +2417,7 @@
         <v>3209</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F64" t="s">
         <v>27</v>
@@ -2446,7 +2446,7 @@
         <v>3162</v>
       </c>
       <c r="D65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F65" t="s">
         <v>27</v>
@@ -2475,7 +2475,7 @@
         <v>3164</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F66" t="s">
         <v>27</v>
@@ -2504,7 +2504,7 @@
         <v>3194</v>
       </c>
       <c r="D67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F67" t="s">
         <v>27</v>
@@ -2540,7 +2540,7 @@
         <v>3155</v>
       </c>
       <c r="D69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F69" t="s">
         <v>27</v>
@@ -2569,7 +2569,7 @@
         <v>3147</v>
       </c>
       <c r="D70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F70" t="s">
         <v>27</v>
@@ -2598,7 +2598,7 @@
         <v>3156</v>
       </c>
       <c r="D71" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F71" t="s">
         <v>27</v>
@@ -2627,7 +2627,7 @@
         <v>3157</v>
       </c>
       <c r="D72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F72" t="s">
         <v>27</v>
@@ -2656,7 +2656,7 @@
         <v>3158</v>
       </c>
       <c r="D73" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F73" t="s">
         <v>27</v>
@@ -2685,7 +2685,7 @@
         <v>3159</v>
       </c>
       <c r="D74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F74" t="s">
         <v>27</v>
@@ -2714,7 +2714,7 @@
         <v>3160</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F75" t="s">
         <v>27</v>
@@ -3076,7 +3076,7 @@
         <v>3149</v>
       </c>
       <c r="D89" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F89" t="s">
         <v>25</v>
@@ -3112,7 +3112,7 @@
         <v>3153</v>
       </c>
       <c r="D91" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
@@ -3141,7 +3141,7 @@
         <v>3209</v>
       </c>
       <c r="D92" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F92" t="s">
         <v>25</v>
@@ -3170,7 +3170,7 @@
         <v>3162</v>
       </c>
       <c r="D93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F93" t="s">
         <v>25</v>
@@ -3199,7 +3199,7 @@
         <v>3164</v>
       </c>
       <c r="D94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F94" t="s">
         <v>25</v>
@@ -3228,7 +3228,7 @@
         <v>3194</v>
       </c>
       <c r="D95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F95" t="s">
         <v>25</v>
@@ -3257,7 +3257,7 @@
         <v>3155</v>
       </c>
       <c r="D96" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F96" t="s">
         <v>25</v>
@@ -3293,7 +3293,7 @@
         <v>3147</v>
       </c>
       <c r="D98" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F98" t="s">
         <v>25</v>
@@ -3322,7 +3322,7 @@
         <v>3156</v>
       </c>
       <c r="D99" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F99" t="s">
         <v>25</v>
@@ -3351,7 +3351,7 @@
         <v>3157</v>
       </c>
       <c r="D100" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
@@ -3380,7 +3380,7 @@
         <v>3158</v>
       </c>
       <c r="D101" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
@@ -3409,7 +3409,7 @@
         <v>3159</v>
       </c>
       <c r="D102" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
@@ -3438,7 +3438,7 @@
         <v>3160</v>
       </c>
       <c r="D103" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F103" t="s">
         <v>25</v>
@@ -3648,7 +3648,7 @@
         <v>3155</v>
       </c>
       <c r="D111" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F111" t="s">
         <v>19</v>
@@ -3735,7 +3735,7 @@
         <v>3149</v>
       </c>
       <c r="D114" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F114" t="s">
         <v>19</v>
@@ -3851,7 +3851,7 @@
         <v>3153</v>
       </c>
       <c r="D118" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F118" t="s">
         <v>19</v>
@@ -3880,7 +3880,7 @@
         <v>3209</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F119" t="s">
         <v>19</v>
@@ -3916,7 +3916,7 @@
         <v>3162</v>
       </c>
       <c r="D121" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F121" t="s">
         <v>19</v>
@@ -3945,7 +3945,7 @@
         <v>3164</v>
       </c>
       <c r="D122" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
@@ -3974,7 +3974,7 @@
         <v>3194</v>
       </c>
       <c r="D123" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F123" t="s">
         <v>19</v>
@@ -4003,7 +4003,7 @@
         <v>3429</v>
       </c>
       <c r="D124" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F124" t="s">
         <v>19</v>
@@ -4032,7 +4032,7 @@
         <v>3147</v>
       </c>
       <c r="D125" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F125" t="s">
         <v>19</v>
@@ -4061,7 +4061,7 @@
         <v>3156</v>
       </c>
       <c r="D126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F126" t="s">
         <v>19</v>
@@ -4090,7 +4090,7 @@
         <v>3157</v>
       </c>
       <c r="D127" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F127" t="s">
         <v>19</v>
@@ -4119,7 +4119,7 @@
         <v>3158</v>
       </c>
       <c r="D128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F128" t="s">
         <v>19</v>
@@ -4148,7 +4148,7 @@
         <v>3160</v>
       </c>
       <c r="D129" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F129" t="s">
         <v>19</v>
@@ -4177,7 +4177,7 @@
         <v>3159</v>
       </c>
       <c r="D130" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F130" t="s">
         <v>19</v>
@@ -4387,7 +4387,7 @@
         <v>3155</v>
       </c>
       <c r="D138" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F138" t="s">
         <v>15</v>
@@ -4474,7 +4474,7 @@
         <v>3149</v>
       </c>
       <c r="D141" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F141" t="s">
         <v>15</v>
@@ -4597,7 +4597,7 @@
         <v>3153</v>
       </c>
       <c r="D146" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F146" t="s">
         <v>15</v>
@@ -4626,7 +4626,7 @@
         <v>3209</v>
       </c>
       <c r="D147" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F147" t="s">
         <v>15</v>
@@ -4655,7 +4655,7 @@
         <v>3162</v>
       </c>
       <c r="D148" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F148" t="s">
         <v>15</v>
@@ -4684,7 +4684,7 @@
         <v>3194</v>
       </c>
       <c r="D149" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F149" t="s">
         <v>15</v>
@@ -4720,7 +4720,7 @@
         <v>3429</v>
       </c>
       <c r="D151" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F151" t="s">
         <v>15</v>
@@ -4749,7 +4749,7 @@
         <v>3147</v>
       </c>
       <c r="D152" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F152" t="s">
         <v>15</v>
@@ -4778,7 +4778,7 @@
         <v>3156</v>
       </c>
       <c r="D153" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F153" t="s">
         <v>15</v>
@@ -4807,7 +4807,7 @@
         <v>3157</v>
       </c>
       <c r="D154" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F154" t="s">
         <v>15</v>
@@ -4836,7 +4836,7 @@
         <v>3158</v>
       </c>
       <c r="D155" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F155" t="s">
         <v>15</v>
@@ -4865,7 +4865,7 @@
         <v>3160</v>
       </c>
       <c r="D156" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F156" t="s">
         <v>15</v>
@@ -4894,7 +4894,7 @@
         <v>3159</v>
       </c>
       <c r="D157" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F157" t="s">
         <v>15</v>
@@ -4952,7 +4952,7 @@
         <v>3164</v>
       </c>
       <c r="D159" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F159" t="s">
         <v>15</v>
@@ -5155,7 +5155,7 @@
         <v>3149</v>
       </c>
       <c r="D166" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F166" t="s">
         <v>24</v>
@@ -5242,7 +5242,7 @@
         <v>3155</v>
       </c>
       <c r="D169" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F169" t="s">
         <v>24</v>
@@ -5271,7 +5271,7 @@
         <v>3209</v>
       </c>
       <c r="D170" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F170" t="s">
         <v>24</v>
@@ -5300,7 +5300,7 @@
         <v>3194</v>
       </c>
       <c r="D171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F171" t="s">
         <v>24</v>
@@ -5336,7 +5336,7 @@
         <v>3429</v>
       </c>
       <c r="D173" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F173" t="s">
         <v>24</v>
@@ -5365,7 +5365,7 @@
         <v>3147</v>
       </c>
       <c r="D174" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F174" t="s">
         <v>24</v>
@@ -5394,7 +5394,7 @@
         <v>3156</v>
       </c>
       <c r="D175" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F175" t="s">
         <v>24</v>
@@ -5423,7 +5423,7 @@
         <v>3157</v>
       </c>
       <c r="D176" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F176" t="s">
         <v>24</v>
@@ -5459,7 +5459,7 @@
         <v>3158</v>
       </c>
       <c r="D178" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F178" t="s">
         <v>24</v>
@@ -5517,7 +5517,7 @@
         <v>3160</v>
       </c>
       <c r="D180" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F180" t="s">
         <v>24</v>
@@ -5546,7 +5546,7 @@
         <v>3162</v>
       </c>
       <c r="D181" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F181" t="s">
         <v>24</v>
@@ -5575,7 +5575,7 @@
         <v>3153</v>
       </c>
       <c r="D182" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F182" t="s">
         <v>24</v>
@@ -5604,7 +5604,7 @@
         <v>3159</v>
       </c>
       <c r="D183" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F183" t="s">
         <v>24</v>
@@ -5691,7 +5691,7 @@
         <v>3164</v>
       </c>
       <c r="D186" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F186" t="s">
         <v>24</v>
@@ -5923,7 +5923,7 @@
         <v>3149</v>
       </c>
       <c r="D194" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>3155</v>
       </c>
       <c r="D197" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -6039,7 +6039,7 @@
         <v>3209</v>
       </c>
       <c r="D198" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>3194</v>
       </c>
       <c r="D200" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -6111,7 +6111,7 @@
         <v>3429</v>
       </c>
       <c r="D202" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -6147,7 +6147,7 @@
         <v>3147</v>
       </c>
       <c r="D204" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -6176,7 +6176,7 @@
         <v>3156</v>
       </c>
       <c r="D205" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -6205,7 +6205,7 @@
         <v>3157</v>
       </c>
       <c r="D206" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -6241,7 +6241,7 @@
         <v>3158</v>
       </c>
       <c r="D208" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -6270,7 +6270,7 @@
         <v>3162</v>
       </c>
       <c r="D209" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -6299,7 +6299,7 @@
         <v>3160</v>
       </c>
       <c r="D210" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -6328,7 +6328,7 @@
         <v>3153</v>
       </c>
       <c r="D211" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -6357,7 +6357,7 @@
         <v>3159</v>
       </c>
       <c r="D212" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -6444,7 +6444,7 @@
         <v>3164</v>
       </c>
       <c r="D215" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -6676,7 +6676,7 @@
         <v>3149</v>
       </c>
       <c r="D223" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F223" t="s">
         <v>26</v>
@@ -6763,7 +6763,7 @@
         <v>3155</v>
       </c>
       <c r="D226" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F226" t="s">
         <v>26</v>
@@ -6792,7 +6792,7 @@
         <v>3209</v>
       </c>
       <c r="D227" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F227" t="s">
         <v>26</v>
@@ -6821,7 +6821,7 @@
         <v>3194</v>
       </c>
       <c r="D228" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F228" t="s">
         <v>26</v>
@@ -6850,7 +6850,7 @@
         <v>3429</v>
       </c>
       <c r="D229" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F229" t="s">
         <v>26</v>
@@ -6879,7 +6879,7 @@
         <v>3147</v>
       </c>
       <c r="D230" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F230" t="s">
         <v>26</v>
@@ -6908,7 +6908,7 @@
         <v>3156</v>
       </c>
       <c r="D231" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F231" t="s">
         <v>26</v>
@@ -6937,7 +6937,7 @@
         <v>3157</v>
       </c>
       <c r="D232" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F232" t="s">
         <v>26</v>
@@ -6966,7 +6966,7 @@
         <v>3158</v>
       </c>
       <c r="D233" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F233" t="s">
         <v>26</v>
@@ -6995,7 +6995,7 @@
         <v>3162</v>
       </c>
       <c r="D234" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F234" t="s">
         <v>26</v>
@@ -7024,7 +7024,7 @@
         <v>3160</v>
       </c>
       <c r="D235" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F235" t="s">
         <v>26</v>
@@ -7053,7 +7053,7 @@
         <v>3153</v>
       </c>
       <c r="D236" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F236" t="s">
         <v>26</v>
@@ -7082,7 +7082,7 @@
         <v>3159</v>
       </c>
       <c r="D237" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F237" t="s">
         <v>26</v>
@@ -7169,7 +7169,7 @@
         <v>3164</v>
       </c>
       <c r="D240" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F240" t="s">
         <v>26</v>
@@ -7401,7 +7401,7 @@
         <v>3149</v>
       </c>
       <c r="D248" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F248" t="s">
         <v>18</v>
@@ -7430,7 +7430,7 @@
         <v>3155</v>
       </c>
       <c r="D249" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F249" t="s">
         <v>18</v>
@@ -7517,7 +7517,7 @@
         <v>3209</v>
       </c>
       <c r="D252" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F252" t="s">
         <v>18</v>
@@ -7546,7 +7546,7 @@
         <v>3194</v>
       </c>
       <c r="D253" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F253" t="s">
         <v>18</v>
@@ -7575,7 +7575,7 @@
         <v>3429</v>
       </c>
       <c r="D254" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F254" t="s">
         <v>18</v>
@@ -7604,7 +7604,7 @@
         <v>3147</v>
       </c>
       <c r="D255" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F255" t="s">
         <v>18</v>
@@ -7633,7 +7633,7 @@
         <v>3156</v>
       </c>
       <c r="D256" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F256" t="s">
         <v>18</v>
@@ -7662,7 +7662,7 @@
         <v>3157</v>
       </c>
       <c r="D257" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F257" t="s">
         <v>18</v>
@@ -7698,7 +7698,7 @@
         <v>3158</v>
       </c>
       <c r="D259" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F259" t="s">
         <v>18</v>
@@ -7727,7 +7727,7 @@
         <v>3162</v>
       </c>
       <c r="D260" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F260" t="s">
         <v>18</v>
@@ -7756,7 +7756,7 @@
         <v>3164</v>
       </c>
       <c r="D261" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F261" t="s">
         <v>18</v>
@@ -7785,7 +7785,7 @@
         <v>3160</v>
       </c>
       <c r="D262" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F262" t="s">
         <v>18</v>
@@ -7850,7 +7850,7 @@
         <v>3153</v>
       </c>
       <c r="D265" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F265" t="s">
         <v>18</v>
@@ -7879,7 +7879,7 @@
         <v>3159</v>
       </c>
       <c r="D266" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F266" t="s">
         <v>18</v>
@@ -8118,7 +8118,7 @@
         <v>3149</v>
       </c>
       <c r="D275" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F275" t="s">
         <v>16</v>
@@ -8176,7 +8176,7 @@
         <v>3209</v>
       </c>
       <c r="D277" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F277" t="s">
         <v>16</v>
@@ -8205,7 +8205,7 @@
         <v>3194</v>
       </c>
       <c r="D278" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -8234,7 +8234,7 @@
         <v>3429</v>
       </c>
       <c r="D279" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F279" t="s">
         <v>16</v>
@@ -8263,7 +8263,7 @@
         <v>3147</v>
       </c>
       <c r="D280" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -8292,7 +8292,7 @@
         <v>3156</v>
       </c>
       <c r="D281" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F281" t="s">
         <v>16</v>
@@ -8321,7 +8321,7 @@
         <v>3157</v>
       </c>
       <c r="D282" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F282" t="s">
         <v>16</v>
@@ -8357,7 +8357,7 @@
         <v>3158</v>
       </c>
       <c r="D284" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F284" t="s">
         <v>16</v>
@@ -8415,7 +8415,7 @@
         <v>3162</v>
       </c>
       <c r="D286" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F286" t="s">
         <v>16</v>
@@ -8444,7 +8444,7 @@
         <v>3164</v>
       </c>
       <c r="D287" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F287" t="s">
         <v>16</v>
@@ -8473,7 +8473,7 @@
         <v>3160</v>
       </c>
       <c r="D288" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -8531,7 +8531,7 @@
         <v>3153</v>
       </c>
       <c r="D290" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F290" t="s">
         <v>16</v>
@@ -8560,7 +8560,7 @@
         <v>3159</v>
       </c>
       <c r="D291" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F291" t="s">
         <v>16</v>
@@ -8618,7 +8618,7 @@
         <v>3155</v>
       </c>
       <c r="D293" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -8864,7 +8864,7 @@
         <v>3149</v>
       </c>
       <c r="D303" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F303" t="s">
         <v>17</v>
@@ -8958,7 +8958,7 @@
         <v>3209</v>
       </c>
       <c r="D307" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F307" t="s">
         <v>17</v>
@@ -8987,7 +8987,7 @@
         <v>3194</v>
       </c>
       <c r="D308" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F308" t="s">
         <v>17</v>
@@ -9023,7 +9023,7 @@
         <v>3429</v>
       </c>
       <c r="D310" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F310" t="s">
         <v>17</v>
@@ -9052,7 +9052,7 @@
         <v>3147</v>
       </c>
       <c r="D311" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F311" t="s">
         <v>17</v>
@@ -9081,7 +9081,7 @@
         <v>3156</v>
       </c>
       <c r="D312" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F312" t="s">
         <v>17</v>
@@ -9117,7 +9117,7 @@
         <v>3157</v>
       </c>
       <c r="D314" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F314" t="s">
         <v>17</v>
@@ -9153,7 +9153,7 @@
         <v>3158</v>
       </c>
       <c r="D316" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F316" t="s">
         <v>17</v>
@@ -9182,7 +9182,7 @@
         <v>3164</v>
       </c>
       <c r="D317" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F317" t="s">
         <v>17</v>
@@ -9211,7 +9211,7 @@
         <v>3160</v>
       </c>
       <c r="D318" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F318" t="s">
         <v>17</v>
@@ -9276,7 +9276,7 @@
         <v>3153</v>
       </c>
       <c r="D321" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F321" t="s">
         <v>17</v>
@@ -9312,7 +9312,7 @@
         <v>3159</v>
       </c>
       <c r="D323" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F323" t="s">
         <v>17</v>
@@ -9377,7 +9377,7 @@
         <v>3155</v>
       </c>
       <c r="D326" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F326" t="s">
         <v>17</v>
@@ -9616,7 +9616,7 @@
         <v>3149</v>
       </c>
       <c r="D335" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F335" t="s">
         <v>22</v>
@@ -9703,7 +9703,7 @@
         <v>3209</v>
       </c>
       <c r="D338" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F338" t="s">
         <v>22</v>
@@ -9732,7 +9732,7 @@
         <v>3194</v>
       </c>
       <c r="D339" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F339" t="s">
         <v>22</v>
@@ -9761,7 +9761,7 @@
         <v>3147</v>
       </c>
       <c r="D340" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F340" t="s">
         <v>22</v>
@@ -9790,7 +9790,7 @@
         <v>3156</v>
       </c>
       <c r="D341" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F341" t="s">
         <v>22</v>
@@ -9819,7 +9819,7 @@
         <v>3157</v>
       </c>
       <c r="D342" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F342" t="s">
         <v>22</v>
@@ -9848,7 +9848,7 @@
         <v>3158</v>
       </c>
       <c r="D343" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F343" t="s">
         <v>22</v>
@@ -9877,7 +9877,7 @@
         <v>3429</v>
       </c>
       <c r="D344" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F344" t="s">
         <v>22</v>
@@ -9906,7 +9906,7 @@
         <v>3160</v>
       </c>
       <c r="D345" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F345" t="s">
         <v>22</v>
@@ -9964,7 +9964,7 @@
         <v>3153</v>
       </c>
       <c r="D347" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F347" t="s">
         <v>22</v>
@@ -9993,7 +9993,7 @@
         <v>3159</v>
       </c>
       <c r="D348" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F348" t="s">
         <v>22</v>
@@ -10058,7 +10058,7 @@
         <v>3155</v>
       </c>
       <c r="D351" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F351" t="s">
         <v>22</v>
@@ -10087,7 +10087,7 @@
         <v>3164</v>
       </c>
       <c r="D352" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F352" t="s">
         <v>22</v>
@@ -10145,10 +10145,10 @@
         <v>3209</v>
       </c>
       <c r="D354" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F354" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G354" t="s">
         <v>13</v>
@@ -10290,7 +10290,7 @@
         <v>3149</v>
       </c>
       <c r="D359" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F359" t="s">
         <v>23</v>
@@ -10413,7 +10413,7 @@
         <v>3194</v>
       </c>
       <c r="D364" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F364" t="s">
         <v>23</v>
@@ -10449,7 +10449,7 @@
         <v>3147</v>
       </c>
       <c r="D366" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F366" t="s">
         <v>23</v>
@@ -10478,7 +10478,7 @@
         <v>3156</v>
       </c>
       <c r="D367" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F367" t="s">
         <v>23</v>
@@ -10507,7 +10507,7 @@
         <v>3157</v>
       </c>
       <c r="D368" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F368" t="s">
         <v>23</v>
@@ -10543,7 +10543,7 @@
         <v>3158</v>
       </c>
       <c r="D370" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F370" t="s">
         <v>23</v>
@@ -10572,7 +10572,7 @@
         <v>3429</v>
       </c>
       <c r="D371" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F371" t="s">
         <v>23</v>
@@ -10601,7 +10601,7 @@
         <v>3160</v>
       </c>
       <c r="D372" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F372" t="s">
         <v>23</v>
@@ -10688,7 +10688,7 @@
         <v>3153</v>
       </c>
       <c r="D375" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F375" t="s">
         <v>23</v>
@@ -10717,7 +10717,7 @@
         <v>3159</v>
       </c>
       <c r="D376" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F376" t="s">
         <v>23</v>
@@ -10775,7 +10775,7 @@
         <v>3155</v>
       </c>
       <c r="D378" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F378" t="s">
         <v>23</v>
@@ -10804,7 +10804,7 @@
         <v>3164</v>
       </c>
       <c r="D379" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F379" t="s">
         <v>23</v>
@@ -10862,7 +10862,7 @@
         <v>3162</v>
       </c>
       <c r="D381" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F381" t="s">
         <v>23</v>
@@ -11036,7 +11036,7 @@
         <v>3149</v>
       </c>
       <c r="D387" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F387" t="s">
         <v>20</v>
@@ -11159,7 +11159,7 @@
         <v>3194</v>
       </c>
       <c r="D392" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F392" t="s">
         <v>20</v>
@@ -11195,7 +11195,7 @@
         <v>3162</v>
       </c>
       <c r="D394" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F394" t="s">
         <v>20</v>
@@ -11224,7 +11224,7 @@
         <v>3147</v>
       </c>
       <c r="D395" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F395" t="s">
         <v>20</v>
@@ -11253,7 +11253,7 @@
         <v>3156</v>
       </c>
       <c r="D396" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F396" t="s">
         <v>20</v>
@@ -11282,7 +11282,7 @@
         <v>3157</v>
       </c>
       <c r="D397" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F397" t="s">
         <v>20</v>
@@ -11318,7 +11318,7 @@
         <v>3158</v>
       </c>
       <c r="D399" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F399" t="s">
         <v>20</v>
@@ -11347,7 +11347,7 @@
         <v>3160</v>
       </c>
       <c r="D400" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F400" t="s">
         <v>20</v>
@@ -11376,7 +11376,7 @@
         <v>3153</v>
       </c>
       <c r="D401" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F401" t="s">
         <v>20</v>
@@ -11405,7 +11405,7 @@
         <v>3159</v>
       </c>
       <c r="D402" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F402" t="s">
         <v>20</v>
@@ -11463,7 +11463,7 @@
         <v>3155</v>
       </c>
       <c r="D404" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F404" t="s">
         <v>20</v>
@@ -11492,7 +11492,7 @@
         <v>3164</v>
       </c>
       <c r="D405" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F405" t="s">
         <v>20</v>
@@ -11550,10 +11550,10 @@
         <v>3160</v>
       </c>
       <c r="D407" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F407" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G407" t="s">
         <v>13</v>
@@ -11565,7 +11565,7 @@
         <v>46118.808564814812</v>
       </c>
       <c r="J407">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K407" t="s">
         <v>11</v>
@@ -11582,7 +11582,7 @@
         <v>34</v>
       </c>
       <c r="F408" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G408" t="s">
         <v>13</v>
@@ -11594,7 +11594,7 @@
         <v>46118.809259259258</v>
       </c>
       <c r="J408">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K408" t="s">
         <v>11</v>
@@ -11611,7 +11611,7 @@
         <v>35</v>
       </c>
       <c r="F409" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G409" t="s">
         <v>12</v>
@@ -11644,10 +11644,10 @@
         <v>3429</v>
       </c>
       <c r="D411" t="s">
+        <v>53</v>
+      </c>
+      <c r="F411" t="s">
         <v>54</v>
-      </c>
-      <c r="F411" t="s">
-        <v>55</v>
       </c>
       <c r="G411" t="s">
         <v>12</v>
@@ -11683,7 +11683,7 @@
         <v>31</v>
       </c>
       <c r="F413" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G413" t="s">
         <v>12</v>
@@ -11719,51 +11719,29 @@
         <v>32</v>
       </c>
       <c r="F415" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G415" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H415" s="2">
-        <v>0</v>
+        <v>4.7453703703703704E-4</v>
       </c>
       <c r="I415" s="1">
         <v>46118.811342592591</v>
       </c>
       <c r="J415">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K415" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="416" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B416" t="s">
-        <v>29</v>
-      </c>
-      <c r="C416">
-        <v>3145</v>
-      </c>
-      <c r="D416" t="s">
-        <v>33</v>
-      </c>
-      <c r="F416" t="s">
-        <v>55</v>
-      </c>
-      <c r="G416" t="s">
-        <v>13</v>
-      </c>
-      <c r="H416" s="2">
-        <v>0</v>
-      </c>
-      <c r="I416" s="1">
-        <v>46118.811342592591</v>
-      </c>
-      <c r="J416">
-        <v>2</v>
-      </c>
+      <c r="H416" s="2"/>
+      <c r="I416" s="1"/>
       <c r="K416" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="417" spans="2:11" x14ac:dyDescent="0.25">
@@ -11771,13 +11749,13 @@
         <v>29</v>
       </c>
       <c r="C417">
-        <v>3149</v>
+        <v>3145</v>
       </c>
       <c r="D417" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F417" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G417" t="s">
         <v>13</v>
@@ -11786,10 +11764,10 @@
         <v>0</v>
       </c>
       <c r="I417" s="1">
-        <v>46118.812037037038</v>
+        <v>46118.811342592591</v>
       </c>
       <c r="J417">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K417" t="s">
         <v>11</v>
@@ -11800,13 +11778,13 @@
         <v>29</v>
       </c>
       <c r="C418">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="D418" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F418" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G418" t="s">
         <v>13</v>
@@ -11818,7 +11796,7 @@
         <v>46118.812037037038</v>
       </c>
       <c r="J418">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K418" t="s">
         <v>11</v>
@@ -11829,13 +11807,13 @@
         <v>29</v>
       </c>
       <c r="C419">
-        <v>3148</v>
+        <v>3151</v>
       </c>
       <c r="D419" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F419" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G419" t="s">
         <v>13</v>
@@ -11844,10 +11822,10 @@
         <v>0</v>
       </c>
       <c r="I419" s="1">
-        <v>46118.812731481485</v>
+        <v>46118.812037037038</v>
       </c>
       <c r="J419">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K419" t="s">
         <v>11</v>
@@ -11858,136 +11836,136 @@
         <v>29</v>
       </c>
       <c r="C420">
+        <v>3148</v>
+      </c>
+      <c r="D420" t="s">
+        <v>36</v>
+      </c>
+      <c r="F420" t="s">
+        <v>54</v>
+      </c>
+      <c r="G420" t="s">
+        <v>13</v>
+      </c>
+      <c r="H420" s="2">
+        <v>0</v>
+      </c>
+      <c r="I420" s="1">
+        <v>46118.812731481485</v>
+      </c>
+      <c r="J420">
+        <v>3</v>
+      </c>
+      <c r="K420" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B421" t="s">
+        <v>29</v>
+      </c>
+      <c r="C421">
         <v>3164</v>
       </c>
-      <c r="D420" t="s">
+      <c r="D421" t="s">
+        <v>41</v>
+      </c>
+      <c r="F421" t="s">
+        <v>54</v>
+      </c>
+      <c r="G421" t="s">
+        <v>12</v>
+      </c>
+      <c r="H421" s="2">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="I421" s="1">
+        <v>46118.813425925924</v>
+      </c>
+      <c r="J421">
+        <v>0</v>
+      </c>
+      <c r="K421" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H422" s="2"/>
+      <c r="I422" s="1"/>
+      <c r="K422" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B423" t="s">
+        <v>29</v>
+      </c>
+      <c r="C423">
+        <v>3163</v>
+      </c>
+      <c r="D423" t="s">
+        <v>37</v>
+      </c>
+      <c r="F423" t="s">
+        <v>54</v>
+      </c>
+      <c r="G423" t="s">
+        <v>12</v>
+      </c>
+      <c r="H423" s="2">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="I423" s="1">
+        <v>46118.813425925924</v>
+      </c>
+      <c r="J423">
+        <v>1</v>
+      </c>
+      <c r="K423" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H424" s="2"/>
+      <c r="I424" s="1"/>
+      <c r="K424" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B425" t="s">
+        <v>29</v>
+      </c>
+      <c r="C425">
+        <v>3194</v>
+      </c>
+      <c r="D425" t="s">
         <v>42</v>
       </c>
-      <c r="F420" t="s">
-        <v>55</v>
-      </c>
-      <c r="G420" t="s">
+      <c r="F425" t="s">
+        <v>54</v>
+      </c>
+      <c r="G425" t="s">
         <v>12</v>
       </c>
-      <c r="H420" s="2">
-        <v>8.1018518518518516E-4</v>
-      </c>
-      <c r="I420" s="1">
-        <v>46118.813425925924</v>
-      </c>
-      <c r="J420">
+      <c r="H425" s="2">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I425" s="1">
+        <v>46118.814120370371</v>
+      </c>
+      <c r="J425">
         <v>0</v>
       </c>
-      <c r="K420" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H421" s="2"/>
-      <c r="I421" s="1"/>
-      <c r="K421" t="s">
+      <c r="K425" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H426" s="2"/>
+      <c r="I426" s="1"/>
+      <c r="K426" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B422" t="s">
-        <v>29</v>
-      </c>
-      <c r="C422">
-        <v>3163</v>
-      </c>
-      <c r="D422" t="s">
-        <v>37</v>
-      </c>
-      <c r="F422" t="s">
-        <v>55</v>
-      </c>
-      <c r="G422" t="s">
-        <v>12</v>
-      </c>
-      <c r="H422" s="2">
-        <v>6.134259259259259E-4</v>
-      </c>
-      <c r="I422" s="1">
-        <v>46118.813425925924</v>
-      </c>
-      <c r="J422">
-        <v>1</v>
-      </c>
-      <c r="K422" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H423" s="2"/>
-      <c r="I423" s="1"/>
-      <c r="K423" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B424" t="s">
-        <v>29</v>
-      </c>
-      <c r="C424">
-        <v>3194</v>
-      </c>
-      <c r="D424" t="s">
-        <v>43</v>
-      </c>
-      <c r="F424" t="s">
-        <v>55</v>
-      </c>
-      <c r="G424" t="s">
-        <v>12</v>
-      </c>
-      <c r="H424" s="2">
-        <v>4.3981481481481481E-4</v>
-      </c>
-      <c r="I424" s="1">
-        <v>46118.814120370371</v>
-      </c>
-      <c r="J424">
-        <v>0</v>
-      </c>
-      <c r="K424" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H425" s="2"/>
-      <c r="I425" s="1"/>
-      <c r="K425" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B426" t="s">
-        <v>29</v>
-      </c>
-      <c r="C426">
-        <v>3162</v>
-      </c>
-      <c r="D426" t="s">
-        <v>41</v>
-      </c>
-      <c r="F426" t="s">
-        <v>55</v>
-      </c>
-      <c r="G426" t="s">
-        <v>13</v>
-      </c>
-      <c r="H426" s="2">
-        <v>0</v>
-      </c>
-      <c r="I426" s="1">
-        <v>46118.814120370371</v>
-      </c>
-      <c r="J426">
-        <v>2</v>
-      </c>
-      <c r="K426" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="427" spans="2:11" x14ac:dyDescent="0.25">
@@ -11995,13 +11973,13 @@
         <v>29</v>
       </c>
       <c r="C427">
-        <v>3147</v>
+        <v>3162</v>
       </c>
       <c r="D427" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F427" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G427" t="s">
         <v>13</v>
@@ -12010,10 +11988,10 @@
         <v>0</v>
       </c>
       <c r="I427" s="1">
-        <v>46118.814814814818</v>
+        <v>46118.814120370371</v>
       </c>
       <c r="J427">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K427" t="s">
         <v>11</v>
@@ -12024,64 +12002,64 @@
         <v>29</v>
       </c>
       <c r="C428">
+        <v>3147</v>
+      </c>
+      <c r="D428" t="s">
+        <v>44</v>
+      </c>
+      <c r="F428" t="s">
+        <v>54</v>
+      </c>
+      <c r="G428" t="s">
+        <v>13</v>
+      </c>
+      <c r="H428" s="2">
+        <v>0</v>
+      </c>
+      <c r="I428" s="1">
+        <v>46118.814814814818</v>
+      </c>
+      <c r="J428">
+        <v>3</v>
+      </c>
+      <c r="K428" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B429" t="s">
+        <v>29</v>
+      </c>
+      <c r="C429">
         <v>3156</v>
       </c>
-      <c r="D428" t="s">
-        <v>46</v>
-      </c>
-      <c r="F428" t="s">
-        <v>55</v>
-      </c>
-      <c r="G428" t="s">
+      <c r="D429" t="s">
+        <v>45</v>
+      </c>
+      <c r="F429" t="s">
+        <v>54</v>
+      </c>
+      <c r="G429" t="s">
         <v>12</v>
       </c>
-      <c r="H428" s="2">
+      <c r="H429" s="2">
         <v>5.4398148148148144E-4</v>
       </c>
-      <c r="I428" s="1">
+      <c r="I429" s="1">
         <v>46118.815509259257</v>
       </c>
-      <c r="J428">
+      <c r="J429">
         <v>1</v>
       </c>
-      <c r="K428" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H429" s="2"/>
-      <c r="I429" s="1"/>
       <c r="K429" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H430" s="2"/>
+      <c r="I430" s="1"/>
+      <c r="K430" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B430" t="s">
-        <v>29</v>
-      </c>
-      <c r="C430">
-        <v>3157</v>
-      </c>
-      <c r="D430" t="s">
-        <v>47</v>
-      </c>
-      <c r="F430" t="s">
-        <v>55</v>
-      </c>
-      <c r="G430" t="s">
-        <v>13</v>
-      </c>
-      <c r="H430" s="2">
-        <v>0</v>
-      </c>
-      <c r="I430" s="1">
-        <v>46118.79409722222</v>
-      </c>
-      <c r="J430">
-        <v>2</v>
-      </c>
-      <c r="K430" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="431" spans="2:11" x14ac:dyDescent="0.25">
@@ -12089,136 +12067,136 @@
         <v>29</v>
       </c>
       <c r="C431">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="D431" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F431" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G431" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H431" s="2">
-        <v>1.1226851851851851E-3</v>
+        <v>0</v>
       </c>
       <c r="I431" s="1">
         <v>46118.79409722222</v>
       </c>
       <c r="J431">
+        <v>3</v>
+      </c>
+      <c r="K431" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B432" t="s">
+        <v>29</v>
+      </c>
+      <c r="C432">
+        <v>3158</v>
+      </c>
+      <c r="D432" t="s">
+        <v>47</v>
+      </c>
+      <c r="F432" t="s">
+        <v>54</v>
+      </c>
+      <c r="G432" t="s">
+        <v>12</v>
+      </c>
+      <c r="H432" s="2">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="I432" s="1">
+        <v>46118.79409722222</v>
+      </c>
+      <c r="J432">
         <v>2</v>
       </c>
-      <c r="K431" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H432" s="2"/>
-      <c r="I432" s="1"/>
       <c r="K432" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H433" s="2"/>
+      <c r="I433" s="1"/>
+      <c r="K433" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B433" t="s">
-        <v>29</v>
-      </c>
-      <c r="C433">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B434" t="s">
+        <v>29</v>
+      </c>
+      <c r="C434">
         <v>3159</v>
       </c>
-      <c r="D433" t="s">
-        <v>49</v>
-      </c>
-      <c r="F433" t="s">
-        <v>55</v>
-      </c>
-      <c r="G433" t="s">
+      <c r="D434" t="s">
+        <v>48</v>
+      </c>
+      <c r="F434" t="s">
+        <v>54</v>
+      </c>
+      <c r="G434" t="s">
         <v>12</v>
       </c>
-      <c r="H433" s="2">
+      <c r="H434" s="2">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="I433" s="1">
+      <c r="I434" s="1">
         <v>46118.794791666667</v>
       </c>
-      <c r="J433">
+      <c r="J434">
         <v>1</v>
       </c>
-      <c r="K433" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H434" s="2"/>
-      <c r="I434" s="1"/>
       <c r="K434" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H435" s="2"/>
+      <c r="I435" s="1"/>
+      <c r="K435" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B435" t="s">
-        <v>29</v>
-      </c>
-      <c r="C435">
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B436" t="s">
+        <v>29</v>
+      </c>
+      <c r="C436">
         <v>3150</v>
       </c>
-      <c r="D435" t="s">
+      <c r="D436" t="s">
         <v>38</v>
       </c>
-      <c r="F435" t="s">
-        <v>55</v>
-      </c>
-      <c r="G435" t="s">
+      <c r="F436" t="s">
+        <v>54</v>
+      </c>
+      <c r="G436" t="s">
         <v>12</v>
       </c>
-      <c r="H435" s="2">
+      <c r="H436" s="2">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="I435" s="1">
+      <c r="I436" s="1">
         <v>46118.795486111114</v>
       </c>
-      <c r="J435">
+      <c r="J436">
         <v>0</v>
       </c>
-      <c r="K435" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H436" s="2"/>
-      <c r="I436" s="1"/>
       <c r="K436" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H437" s="2"/>
+      <c r="I437" s="1"/>
+      <c r="K437" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B437" t="s">
-        <v>29</v>
-      </c>
-      <c r="C437">
-        <v>3155</v>
-      </c>
-      <c r="D437" t="s">
-        <v>44</v>
-      </c>
-      <c r="F437" t="s">
-        <v>55</v>
-      </c>
-      <c r="G437" t="s">
-        <v>13</v>
-      </c>
-      <c r="H437" s="2">
-        <v>0</v>
-      </c>
-      <c r="I437" s="1">
-        <v>46118.796180555553</v>
-      </c>
-      <c r="J437">
-        <v>2</v>
-      </c>
-      <c r="K437" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="438" spans="2:11" x14ac:dyDescent="0.25">
@@ -12226,57 +12204,35 @@
         <v>29</v>
       </c>
       <c r="C438">
-        <v>3143</v>
+        <v>3155</v>
       </c>
       <c r="D438" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F438" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G438" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H438" s="2">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="I438" s="1">
         <v>46118.796180555553</v>
       </c>
       <c r="J438">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K438" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="439" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B439" t="s">
-        <v>29</v>
-      </c>
-      <c r="C439">
-        <v>3153</v>
-      </c>
-      <c r="D439" t="s">
-        <v>53</v>
-      </c>
-      <c r="F439" t="s">
-        <v>55</v>
-      </c>
-      <c r="G439" t="s">
-        <v>13</v>
-      </c>
-      <c r="H439" s="2">
-        <v>0</v>
-      </c>
-      <c r="I439" s="1">
-        <v>46118.796875</v>
-      </c>
-      <c r="J439">
-        <v>2</v>
-      </c>
+      <c r="H439" s="2"/>
+      <c r="I439" s="1"/>
       <c r="K439" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="440" spans="2:11" x14ac:dyDescent="0.25">
@@ -12284,57 +12240,35 @@
         <v>29</v>
       </c>
       <c r="C440">
-        <v>3160</v>
+        <v>3143</v>
       </c>
       <c r="D440" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="F440" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G440" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H440" s="2">
-        <v>0</v>
+        <v>2.4305555555555555E-4</v>
       </c>
       <c r="I440" s="1">
-        <v>46118.804513888892</v>
+        <v>46118.796180555553</v>
       </c>
       <c r="J440">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K440" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="441" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B441" t="s">
-        <v>29</v>
-      </c>
-      <c r="C441">
-        <v>3161</v>
-      </c>
-      <c r="D441" t="s">
-        <v>34</v>
-      </c>
-      <c r="F441" t="s">
-        <v>56</v>
-      </c>
-      <c r="G441" t="s">
-        <v>13</v>
-      </c>
-      <c r="H441" s="2">
-        <v>0</v>
-      </c>
-      <c r="I441" s="1">
-        <v>46118.804513888892</v>
-      </c>
-      <c r="J441">
-        <v>2</v>
-      </c>
+      <c r="H441" s="2"/>
+      <c r="I441" s="1"/>
       <c r="K441" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="442" spans="2:11" x14ac:dyDescent="0.25">
@@ -12342,25 +12276,25 @@
         <v>29</v>
       </c>
       <c r="C442">
-        <v>3146</v>
+        <v>3153</v>
       </c>
       <c r="D442" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F442" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G442" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H442" s="2">
-        <v>5.6944444444444447E-3</v>
+        <v>0</v>
       </c>
       <c r="I442" s="1">
-        <v>46118.805208333331</v>
+        <v>46118.796875</v>
       </c>
       <c r="J442">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K442" t="s">
         <v>11</v>
@@ -12371,25 +12305,25 @@
         <v>29</v>
       </c>
       <c r="C443">
-        <v>3429</v>
+        <v>3160</v>
       </c>
       <c r="D443" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F443" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G443" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H443" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>0</v>
       </c>
       <c r="I443" s="1">
-        <v>46118.805208333331</v>
+        <v>46118.804513888892</v>
       </c>
       <c r="J443">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K443" t="s">
         <v>11</v>
@@ -12400,25 +12334,25 @@
         <v>29</v>
       </c>
       <c r="C444">
-        <v>3154</v>
+        <v>3161</v>
       </c>
       <c r="D444" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F444" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G444" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H444" s="2">
-        <v>7.2453703703703708E-3</v>
+        <v>0</v>
       </c>
       <c r="I444" s="1">
-        <v>46118.805902777778</v>
+        <v>46118.804513888892</v>
       </c>
       <c r="J444">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K444" t="s">
         <v>11</v>
@@ -12429,25 +12363,25 @@
         <v>29</v>
       </c>
       <c r="C445">
-        <v>3144</v>
+        <v>3146</v>
       </c>
       <c r="D445" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F445" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G445" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H445" s="2">
+        <v>5.6944444444444447E-3</v>
+      </c>
+      <c r="I445" s="1">
+        <v>46118.805208333331</v>
+      </c>
+      <c r="J445">
         <v>0</v>
-      </c>
-      <c r="I445" s="1">
-        <v>46118.806597222225</v>
-      </c>
-      <c r="J445">
-        <v>2</v>
       </c>
       <c r="K445" t="s">
         <v>11</v>
@@ -12458,25 +12392,25 @@
         <v>29</v>
       </c>
       <c r="C446">
-        <v>3145</v>
+        <v>3429</v>
       </c>
       <c r="D446" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F446" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G446" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H446" s="2">
+        <v>4.7337962962962967E-3</v>
+      </c>
+      <c r="I446" s="1">
+        <v>46118.805208333331</v>
+      </c>
+      <c r="J446">
         <v>0</v>
-      </c>
-      <c r="I446" s="1">
-        <v>46118.806597222225</v>
-      </c>
-      <c r="J446">
-        <v>2</v>
       </c>
       <c r="K446" t="s">
         <v>11</v>
@@ -12487,25 +12421,25 @@
         <v>29</v>
       </c>
       <c r="C447">
-        <v>3149</v>
+        <v>3154</v>
       </c>
       <c r="D447" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F447" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G447" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H447" s="2">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="I447" s="1">
+        <v>46118.805902777778</v>
+      </c>
+      <c r="J447">
         <v>0</v>
-      </c>
-      <c r="I447" s="1">
-        <v>46118.807291666664</v>
-      </c>
-      <c r="J447">
-        <v>2</v>
       </c>
       <c r="K447" t="s">
         <v>11</v>
@@ -12516,22 +12450,22 @@
         <v>29</v>
       </c>
       <c r="C448">
-        <v>3151</v>
+        <v>3144</v>
       </c>
       <c r="D448" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F448" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G448" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H448" s="2">
-        <v>0</v>
+        <v>7.7083333333333335E-3</v>
       </c>
       <c r="I448" s="1">
-        <v>46118.807986111111</v>
+        <v>46118.806597222225</v>
       </c>
       <c r="J448">
         <v>2</v>
@@ -12545,25 +12479,25 @@
         <v>29</v>
       </c>
       <c r="C449">
-        <v>3148</v>
+        <v>3145</v>
       </c>
       <c r="D449" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F449" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G449" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H449" s="2">
-        <v>0</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I449" s="1">
-        <v>46118.807986111111</v>
+        <v>46118.806597222225</v>
       </c>
       <c r="J449">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K449" t="s">
         <v>11</v>
@@ -12574,25 +12508,25 @@
         <v>29</v>
       </c>
       <c r="C450">
-        <v>3164</v>
+        <v>3149</v>
       </c>
       <c r="D450" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F450" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G450" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H450" s="2">
-        <v>8.6342592592592599E-3</v>
+        <v>0</v>
       </c>
       <c r="I450" s="1">
-        <v>46118.808680555558</v>
+        <v>46118.807291666664</v>
       </c>
       <c r="J450">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K450" t="s">
         <v>11</v>
@@ -12603,25 +12537,25 @@
         <v>29</v>
       </c>
       <c r="C451">
-        <v>3163</v>
+        <v>3151</v>
       </c>
       <c r="D451" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F451" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G451" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H451" s="2">
-        <v>7.858796296296296E-3</v>
+        <v>0</v>
       </c>
       <c r="I451" s="1">
-        <v>46118.808680555558</v>
+        <v>46118.807986111111</v>
       </c>
       <c r="J451">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K451" t="s">
         <v>11</v>
@@ -12632,13 +12566,13 @@
         <v>29</v>
       </c>
       <c r="C452">
-        <v>3194</v>
+        <v>3148</v>
       </c>
       <c r="D452" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F452" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G452" t="s">
         <v>13</v>
@@ -12647,10 +12581,10 @@
         <v>0</v>
       </c>
       <c r="I452" s="1">
-        <v>46118.809374999997</v>
+        <v>46118.807986111111</v>
       </c>
       <c r="J452">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K452" t="s">
         <v>11</v>
@@ -12661,35 +12595,57 @@
         <v>29</v>
       </c>
       <c r="C453">
-        <v>3162</v>
+        <v>3164</v>
       </c>
       <c r="D453" t="s">
         <v>41</v>
       </c>
       <c r="F453" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G453" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H453" s="2">
-        <v>0</v>
+        <v>8.6342592592592599E-3</v>
       </c>
       <c r="I453" s="1">
-        <v>46118.810069444444</v>
+        <v>46118.808680555558</v>
       </c>
       <c r="J453">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K453" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="454" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H454" s="2"/>
-      <c r="I454" s="1"/>
+      <c r="B454" t="s">
+        <v>29</v>
+      </c>
+      <c r="C454">
+        <v>3163</v>
+      </c>
+      <c r="D454" t="s">
+        <v>37</v>
+      </c>
+      <c r="F454" t="s">
+        <v>55</v>
+      </c>
+      <c r="G454" t="s">
+        <v>10</v>
+      </c>
+      <c r="H454" s="2">
+        <v>7.858796296296296E-3</v>
+      </c>
+      <c r="I454" s="1">
+        <v>46118.808680555558</v>
+      </c>
+      <c r="J454">
+        <v>1</v>
+      </c>
       <c r="K454" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="455" spans="2:11" x14ac:dyDescent="0.25">
@@ -12697,13 +12653,13 @@
         <v>29</v>
       </c>
       <c r="C455">
-        <v>3147</v>
+        <v>3194</v>
       </c>
       <c r="D455" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F455" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G455" t="s">
         <v>13</v>
@@ -12712,10 +12668,10 @@
         <v>0</v>
       </c>
       <c r="I455" s="1">
-        <v>46118.810069444444</v>
+        <v>46118.809374999997</v>
       </c>
       <c r="J455">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K455" t="s">
         <v>11</v>
@@ -12726,57 +12682,35 @@
         <v>29</v>
       </c>
       <c r="C456">
-        <v>3156</v>
+        <v>3162</v>
       </c>
       <c r="D456" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F456" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G456" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H456" s="2">
-        <v>7.6273148148148151E-3</v>
+        <v>0</v>
       </c>
       <c r="I456" s="1">
-        <v>46118.810763888891</v>
+        <v>46118.810069444444</v>
       </c>
       <c r="J456">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K456" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="457" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B457" t="s">
-        <v>29</v>
-      </c>
-      <c r="C457">
-        <v>3157</v>
-      </c>
-      <c r="D457" t="s">
-        <v>47</v>
-      </c>
-      <c r="F457" t="s">
-        <v>56</v>
-      </c>
-      <c r="G457" t="s">
-        <v>13</v>
-      </c>
-      <c r="H457" s="2">
-        <v>0</v>
-      </c>
-      <c r="I457" s="1">
-        <v>46118.810763888891</v>
-      </c>
-      <c r="J457">
-        <v>2</v>
-      </c>
+      <c r="H457" s="2"/>
+      <c r="I457" s="1"/>
       <c r="K457" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="458" spans="2:11" x14ac:dyDescent="0.25">
@@ -12784,25 +12718,25 @@
         <v>29</v>
       </c>
       <c r="C458">
-        <v>3158</v>
+        <v>3147</v>
       </c>
       <c r="D458" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F458" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G458" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H458" s="2">
-        <v>7.6157407407407406E-3</v>
+        <v>0</v>
       </c>
       <c r="I458" s="1">
-        <v>46118.81145833333</v>
+        <v>46118.810069444444</v>
       </c>
       <c r="J458">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K458" t="s">
         <v>11</v>
@@ -12813,25 +12747,25 @@
         <v>29</v>
       </c>
       <c r="C459">
-        <v>3159</v>
+        <v>3156</v>
       </c>
       <c r="D459" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F459" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G459" t="s">
         <v>10</v>
       </c>
       <c r="H459" s="2">
-        <v>1.5590277777777778E-2</v>
+        <v>7.6273148148148151E-3</v>
       </c>
       <c r="I459" s="1">
-        <v>46118.812152777777</v>
+        <v>46118.810763888891</v>
       </c>
       <c r="J459">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K459" t="s">
         <v>11</v>
@@ -12842,25 +12776,25 @@
         <v>29</v>
       </c>
       <c r="C460">
-        <v>3150</v>
+        <v>3157</v>
       </c>
       <c r="D460" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F460" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G460" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H460" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>0</v>
       </c>
       <c r="I460" s="1">
-        <v>46118.812152777777</v>
+        <v>46118.810763888891</v>
       </c>
       <c r="J460">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K460" t="s">
         <v>11</v>
@@ -12871,22 +12805,22 @@
         <v>29</v>
       </c>
       <c r="C461">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="D461" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F461" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G461" t="s">
         <v>10</v>
       </c>
       <c r="H461" s="2">
-        <v>7.4305555555555557E-3</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I461" s="1">
-        <v>46118.812847222223</v>
+        <v>46118.81145833333</v>
       </c>
       <c r="J461">
         <v>1</v>
@@ -12900,25 +12834,25 @@
         <v>29</v>
       </c>
       <c r="C462">
-        <v>3143</v>
+        <v>3159</v>
       </c>
       <c r="D462" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F462" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G462" t="s">
         <v>10</v>
       </c>
       <c r="H462" s="2">
-        <v>1.7777777777777778E-2</v>
+        <v>1.5590277777777778E-2</v>
       </c>
       <c r="I462" s="1">
-        <v>46118.812847222223</v>
+        <v>46118.812152777777</v>
       </c>
       <c r="J462">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K462" t="s">
         <v>11</v>
@@ -12929,95 +12863,198 @@
         <v>29</v>
       </c>
       <c r="C463">
+        <v>3150</v>
+      </c>
+      <c r="D463" t="s">
+        <v>38</v>
+      </c>
+      <c r="F463" t="s">
+        <v>55</v>
+      </c>
+      <c r="G463" t="s">
+        <v>10</v>
+      </c>
+      <c r="H463" s="2">
+        <v>9.3518518518518525E-3</v>
+      </c>
+      <c r="I463" s="1">
+        <v>46118.812152777777</v>
+      </c>
+      <c r="J463">
+        <v>0</v>
+      </c>
+      <c r="K463" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B464" t="s">
+        <v>29</v>
+      </c>
+      <c r="C464">
+        <v>3155</v>
+      </c>
+      <c r="D464" t="s">
+        <v>43</v>
+      </c>
+      <c r="F464" t="s">
+        <v>55</v>
+      </c>
+      <c r="G464" t="s">
+        <v>10</v>
+      </c>
+      <c r="H464" s="2">
+        <v>7.4305555555555557E-3</v>
+      </c>
+      <c r="I464" s="1">
+        <v>46118.812847222223</v>
+      </c>
+      <c r="J464">
+        <v>1</v>
+      </c>
+      <c r="K464" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B465" t="s">
+        <v>29</v>
+      </c>
+      <c r="C465">
+        <v>3143</v>
+      </c>
+      <c r="D465" t="s">
+        <v>30</v>
+      </c>
+      <c r="F465" t="s">
+        <v>55</v>
+      </c>
+      <c r="G465" t="s">
+        <v>10</v>
+      </c>
+      <c r="H465" s="2">
+        <v>1.7777777777777778E-2</v>
+      </c>
+      <c r="I465" s="1">
+        <v>46118.812847222223</v>
+      </c>
+      <c r="J465">
+        <v>2</v>
+      </c>
+      <c r="K465" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B466" t="s">
+        <v>29</v>
+      </c>
+      <c r="C466">
         <v>3153</v>
       </c>
-      <c r="D463" t="s">
-        <v>53</v>
-      </c>
-      <c r="F463" t="s">
-        <v>56</v>
-      </c>
-      <c r="G463" t="s">
+      <c r="D466" t="s">
+        <v>52</v>
+      </c>
+      <c r="F466" t="s">
+        <v>55</v>
+      </c>
+      <c r="G466" t="s">
         <v>13</v>
       </c>
-      <c r="H463" s="2">
+      <c r="H466" s="2">
         <v>0</v>
       </c>
-      <c r="I463" s="1">
+      <c r="I466" s="1">
         <v>46118.81354166667</v>
       </c>
-      <c r="J463">
-        <v>2</v>
-      </c>
-      <c r="K463" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H464" s="2"/>
-      <c r="I464" s="1"/>
-    </row>
-    <row r="465" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H465" s="2"/>
-      <c r="I465" s="1"/>
-    </row>
-    <row r="466" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H466" s="2"/>
-      <c r="I466" s="1"/>
-    </row>
-    <row r="467" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H467" s="2"/>
-      <c r="I467" s="1"/>
-    </row>
-    <row r="468" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="J466">
+        <v>3</v>
+      </c>
+      <c r="K466" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B467" t="s">
+        <v>29</v>
+      </c>
+      <c r="C467">
+        <v>3158</v>
+      </c>
+      <c r="D467" t="s">
+        <v>47</v>
+      </c>
+      <c r="F467" t="s">
+        <v>15</v>
+      </c>
+      <c r="G467" t="s">
+        <v>12</v>
+      </c>
+      <c r="H467" s="2">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="I467" s="1">
+        <v>46131.543171296296</v>
+      </c>
+      <c r="J467">
+        <v>1</v>
+      </c>
+      <c r="K467" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H468" s="2"/>
       <c r="I468" s="1"/>
-    </row>
-    <row r="469" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K468" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H469" s="2"/>
       <c r="I469" s="1"/>
     </row>
-    <row r="470" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H470" s="2"/>
       <c r="I470" s="1"/>
     </row>
-    <row r="471" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H471" s="2"/>
       <c r="I471" s="1"/>
     </row>
-    <row r="472" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
     </row>
-    <row r="473" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H473" s="2"/>
       <c r="I473" s="1"/>
     </row>
-    <row r="474" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H474" s="2"/>
       <c r="I474" s="1"/>
     </row>
-    <row r="475" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H475" s="2"/>
       <c r="I475" s="1"/>
     </row>
-    <row r="476" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H476" s="2"/>
       <c r="I476" s="1"/>
     </row>
-    <row r="477" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H477" s="2"/>
       <c r="I477" s="1"/>
     </row>
-    <row r="478" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H478" s="2"/>
       <c r="I478" s="1"/>
     </row>
-    <row r="479" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H479" s="2"/>
       <c r="I479" s="1"/>
     </row>
-    <row r="480" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H480" s="2"/>
       <c r="I480" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DC6300-1426-47BC-9708-FC36770E2E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303EF3CE-8324-472D-ADF9-0F162F20DABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -11565,7 +11565,7 @@
         <v>46118.808564814812</v>
       </c>
       <c r="J407">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K407" t="s">
         <v>11</v>
@@ -11594,7 +11594,7 @@
         <v>46118.809259259258</v>
       </c>
       <c r="J408">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K408" t="s">
         <v>11</v>
@@ -11758,48 +11758,26 @@
         <v>54</v>
       </c>
       <c r="G417" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H417" s="2">
-        <v>0</v>
+        <v>2.4305555555555555E-4</v>
       </c>
       <c r="I417" s="1">
         <v>46118.811342592591</v>
       </c>
       <c r="J417">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K417" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="418" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B418" t="s">
-        <v>29</v>
-      </c>
-      <c r="C418">
-        <v>3149</v>
-      </c>
-      <c r="D418" t="s">
-        <v>57</v>
-      </c>
-      <c r="F418" t="s">
-        <v>54</v>
-      </c>
-      <c r="G418" t="s">
-        <v>13</v>
-      </c>
-      <c r="H418" s="2">
-        <v>0</v>
-      </c>
-      <c r="I418" s="1">
-        <v>46118.812037037038</v>
-      </c>
-      <c r="J418">
-        <v>3</v>
-      </c>
+      <c r="H418" s="2"/>
+      <c r="I418" s="1"/>
       <c r="K418" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="419" spans="2:11" x14ac:dyDescent="0.25">
@@ -11807,10 +11785,10 @@
         <v>29</v>
       </c>
       <c r="C419">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="D419" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F419" t="s">
         <v>54</v>
@@ -11825,7 +11803,7 @@
         <v>46118.812037037038</v>
       </c>
       <c r="J419">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K419" t="s">
         <v>11</v>
@@ -11836,10 +11814,10 @@
         <v>29</v>
       </c>
       <c r="C420">
-        <v>3148</v>
+        <v>3151</v>
       </c>
       <c r="D420" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F420" t="s">
         <v>54</v>
@@ -11851,10 +11829,10 @@
         <v>0</v>
       </c>
       <c r="I420" s="1">
-        <v>46118.812731481485</v>
+        <v>46118.812037037038</v>
       </c>
       <c r="J420">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K420" t="s">
         <v>11</v>
@@ -11865,136 +11843,136 @@
         <v>29</v>
       </c>
       <c r="C421">
-        <v>3164</v>
+        <v>3148</v>
       </c>
       <c r="D421" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F421" t="s">
         <v>54</v>
       </c>
       <c r="G421" t="s">
+        <v>13</v>
+      </c>
+      <c r="H421" s="2">
+        <v>0</v>
+      </c>
+      <c r="I421" s="1">
+        <v>46118.812731481485</v>
+      </c>
+      <c r="J421">
+        <v>4</v>
+      </c>
+      <c r="K421" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B422" t="s">
+        <v>29</v>
+      </c>
+      <c r="C422">
+        <v>3164</v>
+      </c>
+      <c r="D422" t="s">
+        <v>41</v>
+      </c>
+      <c r="F422" t="s">
+        <v>54</v>
+      </c>
+      <c r="G422" t="s">
         <v>12</v>
       </c>
-      <c r="H421" s="2">
+      <c r="H422" s="2">
         <v>8.1018518518518516E-4</v>
       </c>
-      <c r="I421" s="1">
+      <c r="I422" s="1">
         <v>46118.813425925924</v>
       </c>
-      <c r="J421">
+      <c r="J422">
         <v>0</v>
       </c>
-      <c r="K421" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H422" s="2"/>
-      <c r="I422" s="1"/>
       <c r="K422" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H423" s="2"/>
+      <c r="I423" s="1"/>
+      <c r="K423" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B423" t="s">
-        <v>29</v>
-      </c>
-      <c r="C423">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B424" t="s">
+        <v>29</v>
+      </c>
+      <c r="C424">
         <v>3163</v>
       </c>
-      <c r="D423" t="s">
+      <c r="D424" t="s">
         <v>37</v>
       </c>
-      <c r="F423" t="s">
+      <c r="F424" t="s">
         <v>54</v>
       </c>
-      <c r="G423" t="s">
+      <c r="G424" t="s">
         <v>12</v>
       </c>
-      <c r="H423" s="2">
+      <c r="H424" s="2">
         <v>6.134259259259259E-4</v>
       </c>
-      <c r="I423" s="1">
+      <c r="I424" s="1">
         <v>46118.813425925924</v>
       </c>
-      <c r="J423">
+      <c r="J424">
         <v>1</v>
       </c>
-      <c r="K423" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H424" s="2"/>
-      <c r="I424" s="1"/>
       <c r="K424" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H425" s="2"/>
+      <c r="I425" s="1"/>
+      <c r="K425" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B425" t="s">
-        <v>29</v>
-      </c>
-      <c r="C425">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B426" t="s">
+        <v>29</v>
+      </c>
+      <c r="C426">
         <v>3194</v>
       </c>
-      <c r="D425" t="s">
+      <c r="D426" t="s">
         <v>42</v>
       </c>
-      <c r="F425" t="s">
+      <c r="F426" t="s">
         <v>54</v>
       </c>
-      <c r="G425" t="s">
+      <c r="G426" t="s">
         <v>12</v>
       </c>
-      <c r="H425" s="2">
+      <c r="H426" s="2">
         <v>4.3981481481481481E-4</v>
       </c>
-      <c r="I425" s="1">
+      <c r="I426" s="1">
         <v>46118.814120370371</v>
       </c>
-      <c r="J425">
+      <c r="J426">
         <v>0</v>
       </c>
-      <c r="K425" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H426" s="2"/>
-      <c r="I426" s="1"/>
       <c r="K426" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H427" s="2"/>
+      <c r="I427" s="1"/>
+      <c r="K427" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B427" t="s">
-        <v>29</v>
-      </c>
-      <c r="C427">
-        <v>3162</v>
-      </c>
-      <c r="D427" t="s">
-        <v>40</v>
-      </c>
-      <c r="F427" t="s">
-        <v>54</v>
-      </c>
-      <c r="G427" t="s">
-        <v>13</v>
-      </c>
-      <c r="H427" s="2">
-        <v>0</v>
-      </c>
-      <c r="I427" s="1">
-        <v>46118.814120370371</v>
-      </c>
-      <c r="J427">
-        <v>3</v>
-      </c>
-      <c r="K427" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="428" spans="2:11" x14ac:dyDescent="0.25">
@@ -12002,93 +11980,71 @@
         <v>29</v>
       </c>
       <c r="C428">
-        <v>3147</v>
+        <v>3162</v>
       </c>
       <c r="D428" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F428" t="s">
         <v>54</v>
       </c>
       <c r="G428" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H428" s="2">
-        <v>0</v>
+        <v>2.3148148148148147E-5</v>
       </c>
       <c r="I428" s="1">
+        <v>46118.814120370371</v>
+      </c>
+      <c r="J428">
+        <v>4</v>
+      </c>
+      <c r="K428" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H429" s="2"/>
+      <c r="I429" s="1"/>
+      <c r="K429" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B430" t="s">
+        <v>29</v>
+      </c>
+      <c r="C430">
+        <v>3147</v>
+      </c>
+      <c r="D430" t="s">
+        <v>44</v>
+      </c>
+      <c r="F430" t="s">
+        <v>54</v>
+      </c>
+      <c r="G430" t="s">
+        <v>12</v>
+      </c>
+      <c r="H430" s="2">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="I430" s="1">
         <v>46118.814814814818</v>
       </c>
-      <c r="J428">
+      <c r="J430">
         <v>3</v>
       </c>
-      <c r="K428" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B429" t="s">
-        <v>29</v>
-      </c>
-      <c r="C429">
-        <v>3156</v>
-      </c>
-      <c r="D429" t="s">
-        <v>45</v>
-      </c>
-      <c r="F429" t="s">
-        <v>54</v>
-      </c>
-      <c r="G429" t="s">
-        <v>12</v>
-      </c>
-      <c r="H429" s="2">
-        <v>5.4398148148148144E-4</v>
-      </c>
-      <c r="I429" s="1">
-        <v>46118.815509259257</v>
-      </c>
-      <c r="J429">
-        <v>1</v>
-      </c>
-      <c r="K429" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H430" s="2"/>
-      <c r="I430" s="1"/>
       <c r="K430" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H431" s="2"/>
+      <c r="I431" s="1"/>
+      <c r="K431" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B431" t="s">
-        <v>29</v>
-      </c>
-      <c r="C431">
-        <v>3157</v>
-      </c>
-      <c r="D431" t="s">
-        <v>46</v>
-      </c>
-      <c r="F431" t="s">
-        <v>54</v>
-      </c>
-      <c r="G431" t="s">
-        <v>13</v>
-      </c>
-      <c r="H431" s="2">
-        <v>0</v>
-      </c>
-      <c r="I431" s="1">
-        <v>46118.79409722222</v>
-      </c>
-      <c r="J431">
-        <v>3</v>
-      </c>
-      <c r="K431" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="432" spans="2:11" x14ac:dyDescent="0.25">
@@ -12096,10 +12052,10 @@
         <v>29</v>
       </c>
       <c r="C432">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="D432" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F432" t="s">
         <v>54</v>
@@ -12108,13 +12064,13 @@
         <v>12</v>
       </c>
       <c r="H432" s="2">
-        <v>1.1226851851851851E-3</v>
+        <v>5.4398148148148144E-4</v>
       </c>
       <c r="I432" s="1">
-        <v>46118.79409722222</v>
+        <v>46118.815509259257</v>
       </c>
       <c r="J432">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K432" t="s">
         <v>11</v>
@@ -12132,172 +12088,172 @@
         <v>29</v>
       </c>
       <c r="C434">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="D434" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F434" t="s">
         <v>54</v>
       </c>
       <c r="G434" t="s">
+        <v>13</v>
+      </c>
+      <c r="H434" s="2">
+        <v>0</v>
+      </c>
+      <c r="I434" s="1">
+        <v>46118.79409722222</v>
+      </c>
+      <c r="J434">
+        <v>4</v>
+      </c>
+      <c r="K434" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B435" t="s">
+        <v>29</v>
+      </c>
+      <c r="C435">
+        <v>3158</v>
+      </c>
+      <c r="D435" t="s">
+        <v>47</v>
+      </c>
+      <c r="F435" t="s">
+        <v>54</v>
+      </c>
+      <c r="G435" t="s">
         <v>12</v>
       </c>
-      <c r="H434" s="2">
+      <c r="H435" s="2">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="I435" s="1">
+        <v>46118.79409722222</v>
+      </c>
+      <c r="J435">
+        <v>2</v>
+      </c>
+      <c r="K435" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H436" s="2"/>
+      <c r="I436" s="1"/>
+      <c r="K436" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B437" t="s">
+        <v>29</v>
+      </c>
+      <c r="C437">
+        <v>3159</v>
+      </c>
+      <c r="D437" t="s">
+        <v>48</v>
+      </c>
+      <c r="F437" t="s">
+        <v>54</v>
+      </c>
+      <c r="G437" t="s">
+        <v>12</v>
+      </c>
+      <c r="H437" s="2">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="I434" s="1">
+      <c r="I437" s="1">
         <v>46118.794791666667</v>
       </c>
-      <c r="J434">
+      <c r="J437">
         <v>1</v>
       </c>
-      <c r="K434" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H435" s="2"/>
-      <c r="I435" s="1"/>
-      <c r="K435" t="s">
+      <c r="K437" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H438" s="2"/>
+      <c r="I438" s="1"/>
+      <c r="K438" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B436" t="s">
-        <v>29</v>
-      </c>
-      <c r="C436">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B439" t="s">
+        <v>29</v>
+      </c>
+      <c r="C439">
         <v>3150</v>
       </c>
-      <c r="D436" t="s">
+      <c r="D439" t="s">
         <v>38</v>
       </c>
-      <c r="F436" t="s">
+      <c r="F439" t="s">
         <v>54</v>
       </c>
-      <c r="G436" t="s">
+      <c r="G439" t="s">
         <v>12</v>
       </c>
-      <c r="H436" s="2">
+      <c r="H439" s="2">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="I436" s="1">
+      <c r="I439" s="1">
         <v>46118.795486111114</v>
       </c>
-      <c r="J436">
+      <c r="J439">
         <v>0</v>
       </c>
-      <c r="K436" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H437" s="2"/>
-      <c r="I437" s="1"/>
-      <c r="K437" t="s">
+      <c r="K439" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H440" s="2"/>
+      <c r="I440" s="1"/>
+      <c r="K440" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B438" t="s">
-        <v>29</v>
-      </c>
-      <c r="C438">
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B441" t="s">
+        <v>29</v>
+      </c>
+      <c r="C441">
         <v>3155</v>
       </c>
-      <c r="D438" t="s">
+      <c r="D441" t="s">
         <v>43</v>
       </c>
-      <c r="F438" t="s">
+      <c r="F441" t="s">
         <v>54</v>
       </c>
-      <c r="G438" t="s">
+      <c r="G441" t="s">
         <v>12</v>
       </c>
-      <c r="H438" s="2">
+      <c r="H441" s="2">
         <v>2.5462962962962961E-4</v>
       </c>
-      <c r="I438" s="1">
+      <c r="I441" s="1">
         <v>46118.796180555553</v>
       </c>
-      <c r="J438">
+      <c r="J441">
         <v>3</v>
       </c>
-      <c r="K438" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H439" s="2"/>
-      <c r="I439" s="1"/>
-      <c r="K439" t="s">
+      <c r="K441" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H442" s="2"/>
+      <c r="I442" s="1"/>
+      <c r="K442" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B440" t="s">
-        <v>29</v>
-      </c>
-      <c r="C440">
-        <v>3143</v>
-      </c>
-      <c r="D440" t="s">
-        <v>30</v>
-      </c>
-      <c r="F440" t="s">
-        <v>54</v>
-      </c>
-      <c r="G440" t="s">
-        <v>12</v>
-      </c>
-      <c r="H440" s="2">
-        <v>2.4305555555555555E-4</v>
-      </c>
-      <c r="I440" s="1">
-        <v>46118.796180555553</v>
-      </c>
-      <c r="J440">
-        <v>3</v>
-      </c>
-      <c r="K440" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H441" s="2"/>
-      <c r="I441" s="1"/>
-      <c r="K441" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B442" t="s">
-        <v>29</v>
-      </c>
-      <c r="C442">
-        <v>3153</v>
-      </c>
-      <c r="D442" t="s">
-        <v>52</v>
-      </c>
-      <c r="F442" t="s">
-        <v>54</v>
-      </c>
-      <c r="G442" t="s">
-        <v>13</v>
-      </c>
-      <c r="H442" s="2">
-        <v>0</v>
-      </c>
-      <c r="I442" s="1">
-        <v>46118.796875</v>
-      </c>
-      <c r="J442">
-        <v>3</v>
-      </c>
-      <c r="K442" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="443" spans="2:11" x14ac:dyDescent="0.25">
@@ -12305,22 +12261,22 @@
         <v>29</v>
       </c>
       <c r="C443">
-        <v>3160</v>
+        <v>3143</v>
       </c>
       <c r="D443" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F443" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G443" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H443" s="2">
-        <v>0</v>
+        <v>2.4305555555555555E-4</v>
       </c>
       <c r="I443" s="1">
-        <v>46118.804513888892</v>
+        <v>46118.796180555553</v>
       </c>
       <c r="J443">
         <v>3</v>
@@ -12330,32 +12286,10 @@
       </c>
     </row>
     <row r="444" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B444" t="s">
-        <v>29</v>
-      </c>
-      <c r="C444">
-        <v>3161</v>
-      </c>
-      <c r="D444" t="s">
-        <v>34</v>
-      </c>
-      <c r="F444" t="s">
-        <v>55</v>
-      </c>
-      <c r="G444" t="s">
-        <v>13</v>
-      </c>
-      <c r="H444" s="2">
-        <v>0</v>
-      </c>
-      <c r="I444" s="1">
-        <v>46118.804513888892</v>
-      </c>
-      <c r="J444">
-        <v>3</v>
-      </c>
+      <c r="H444" s="2"/>
+      <c r="I444" s="1"/>
       <c r="K444" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="445" spans="2:11" x14ac:dyDescent="0.25">
@@ -12363,25 +12297,25 @@
         <v>29</v>
       </c>
       <c r="C445">
-        <v>3146</v>
+        <v>3153</v>
       </c>
       <c r="D445" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F445" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G445" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H445" s="2">
-        <v>5.6944444444444447E-3</v>
+        <v>0</v>
       </c>
       <c r="I445" s="1">
-        <v>46118.805208333331</v>
+        <v>46118.796875</v>
       </c>
       <c r="J445">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K445" t="s">
         <v>11</v>
@@ -12392,57 +12326,35 @@
         <v>29</v>
       </c>
       <c r="C446">
-        <v>3429</v>
+        <v>3160</v>
       </c>
       <c r="D446" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F446" t="s">
         <v>55</v>
       </c>
       <c r="G446" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H446" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="I446" s="1">
-        <v>46118.805208333331</v>
+        <v>46118.804513888892</v>
       </c>
       <c r="J446">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K446" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="447" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B447" t="s">
-        <v>29</v>
-      </c>
-      <c r="C447">
-        <v>3154</v>
-      </c>
-      <c r="D447" t="s">
-        <v>31</v>
-      </c>
-      <c r="F447" t="s">
-        <v>55</v>
-      </c>
-      <c r="G447" t="s">
-        <v>10</v>
-      </c>
-      <c r="H447" s="2">
-        <v>7.2453703703703708E-3</v>
-      </c>
-      <c r="I447" s="1">
-        <v>46118.805902777778</v>
-      </c>
-      <c r="J447">
-        <v>0</v>
-      </c>
+      <c r="H447" s="2"/>
+      <c r="I447" s="1"/>
       <c r="K447" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="448" spans="2:11" x14ac:dyDescent="0.25">
@@ -12450,25 +12362,25 @@
         <v>29</v>
       </c>
       <c r="C448">
-        <v>3144</v>
+        <v>3161</v>
       </c>
       <c r="D448" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F448" t="s">
         <v>55</v>
       </c>
       <c r="G448" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H448" s="2">
-        <v>7.7083333333333335E-3</v>
+        <v>0</v>
       </c>
       <c r="I448" s="1">
-        <v>46118.806597222225</v>
+        <v>46118.804513888892</v>
       </c>
       <c r="J448">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K448" t="s">
         <v>11</v>
@@ -12479,10 +12391,10 @@
         <v>29</v>
       </c>
       <c r="C449">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="D449" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F449" t="s">
         <v>55</v>
@@ -12491,13 +12403,13 @@
         <v>10</v>
       </c>
       <c r="H449" s="2">
-        <v>7.013888888888889E-3</v>
+        <v>5.6944444444444447E-3</v>
       </c>
       <c r="I449" s="1">
-        <v>46118.806597222225</v>
+        <v>46118.805208333331</v>
       </c>
       <c r="J449">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K449" t="s">
         <v>11</v>
@@ -12508,25 +12420,25 @@
         <v>29</v>
       </c>
       <c r="C450">
-        <v>3149</v>
+        <v>3429</v>
       </c>
       <c r="D450" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F450" t="s">
         <v>55</v>
       </c>
       <c r="G450" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H450" s="2">
+        <v>4.7337962962962967E-3</v>
+      </c>
+      <c r="I450" s="1">
+        <v>46118.805208333331</v>
+      </c>
+      <c r="J450">
         <v>0</v>
-      </c>
-      <c r="I450" s="1">
-        <v>46118.807291666664</v>
-      </c>
-      <c r="J450">
-        <v>3</v>
       </c>
       <c r="K450" t="s">
         <v>11</v>
@@ -12537,25 +12449,25 @@
         <v>29</v>
       </c>
       <c r="C451">
-        <v>3151</v>
+        <v>3154</v>
       </c>
       <c r="D451" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F451" t="s">
         <v>55</v>
       </c>
       <c r="G451" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H451" s="2">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="I451" s="1">
+        <v>46118.805902777778</v>
+      </c>
+      <c r="J451">
         <v>0</v>
-      </c>
-      <c r="I451" s="1">
-        <v>46118.807986111111</v>
-      </c>
-      <c r="J451">
-        <v>3</v>
       </c>
       <c r="K451" t="s">
         <v>11</v>
@@ -12566,25 +12478,25 @@
         <v>29</v>
       </c>
       <c r="C452">
-        <v>3148</v>
+        <v>3144</v>
       </c>
       <c r="D452" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F452" t="s">
         <v>55</v>
       </c>
       <c r="G452" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H452" s="2">
-        <v>0</v>
+        <v>7.7083333333333335E-3</v>
       </c>
       <c r="I452" s="1">
-        <v>46118.807986111111</v>
+        <v>46118.806597222225</v>
       </c>
       <c r="J452">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K452" t="s">
         <v>11</v>
@@ -12595,10 +12507,10 @@
         <v>29</v>
       </c>
       <c r="C453">
-        <v>3164</v>
+        <v>3145</v>
       </c>
       <c r="D453" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F453" t="s">
         <v>55</v>
@@ -12607,13 +12519,13 @@
         <v>10</v>
       </c>
       <c r="H453" s="2">
-        <v>8.6342592592592599E-3</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I453" s="1">
-        <v>46118.808680555558</v>
+        <v>46118.806597222225</v>
       </c>
       <c r="J453">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K453" t="s">
         <v>11</v>
@@ -12624,25 +12536,25 @@
         <v>29</v>
       </c>
       <c r="C454">
-        <v>3163</v>
+        <v>3149</v>
       </c>
       <c r="D454" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F454" t="s">
         <v>55</v>
       </c>
       <c r="G454" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H454" s="2">
-        <v>7.858796296296296E-3</v>
+        <v>0</v>
       </c>
       <c r="I454" s="1">
-        <v>46118.808680555558</v>
+        <v>46118.807291666664</v>
       </c>
       <c r="J454">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K454" t="s">
         <v>11</v>
@@ -12653,10 +12565,10 @@
         <v>29</v>
       </c>
       <c r="C455">
-        <v>3194</v>
+        <v>3151</v>
       </c>
       <c r="D455" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F455" t="s">
         <v>55</v>
@@ -12668,10 +12580,10 @@
         <v>0</v>
       </c>
       <c r="I455" s="1">
-        <v>46118.809374999997</v>
+        <v>46118.807986111111</v>
       </c>
       <c r="J455">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K455" t="s">
         <v>11</v>
@@ -12682,35 +12594,57 @@
         <v>29</v>
       </c>
       <c r="C456">
-        <v>3162</v>
+        <v>3148</v>
       </c>
       <c r="D456" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F456" t="s">
         <v>55</v>
       </c>
       <c r="G456" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H456" s="2">
         <v>0</v>
       </c>
       <c r="I456" s="1">
-        <v>46118.810069444444</v>
+        <v>46118.807986111111</v>
       </c>
       <c r="J456">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K456" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="457" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H457" s="2"/>
-      <c r="I457" s="1"/>
+      <c r="B457" t="s">
+        <v>29</v>
+      </c>
+      <c r="C457">
+        <v>3164</v>
+      </c>
+      <c r="D457" t="s">
+        <v>41</v>
+      </c>
+      <c r="F457" t="s">
+        <v>55</v>
+      </c>
+      <c r="G457" t="s">
+        <v>10</v>
+      </c>
+      <c r="H457" s="2">
+        <v>8.6342592592592599E-3</v>
+      </c>
+      <c r="I457" s="1">
+        <v>46118.808680555558</v>
+      </c>
+      <c r="J457">
+        <v>2</v>
+      </c>
       <c r="K457" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="458" spans="2:11" x14ac:dyDescent="0.25">
@@ -12718,25 +12652,25 @@
         <v>29</v>
       </c>
       <c r="C458">
-        <v>3147</v>
+        <v>3163</v>
       </c>
       <c r="D458" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F458" t="s">
         <v>55</v>
       </c>
       <c r="G458" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H458" s="2">
-        <v>0</v>
+        <v>7.858796296296296E-3</v>
       </c>
       <c r="I458" s="1">
-        <v>46118.810069444444</v>
+        <v>46118.808680555558</v>
       </c>
       <c r="J458">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K458" t="s">
         <v>11</v>
@@ -12747,25 +12681,25 @@
         <v>29</v>
       </c>
       <c r="C459">
-        <v>3156</v>
+        <v>3194</v>
       </c>
       <c r="D459" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
         <v>55</v>
       </c>
       <c r="G459" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H459" s="2">
-        <v>7.6273148148148151E-3</v>
+        <v>0</v>
       </c>
       <c r="I459" s="1">
-        <v>46118.810763888891</v>
+        <v>46118.809374999997</v>
       </c>
       <c r="J459">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K459" t="s">
         <v>11</v>
@@ -12776,57 +12710,35 @@
         <v>29</v>
       </c>
       <c r="C460">
-        <v>3157</v>
+        <v>3162</v>
       </c>
       <c r="D460" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F460" t="s">
         <v>55</v>
       </c>
       <c r="G460" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H460" s="2">
         <v>0</v>
       </c>
       <c r="I460" s="1">
-        <v>46118.810763888891</v>
+        <v>46118.810069444444</v>
       </c>
       <c r="J460">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K460" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="461" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B461" t="s">
-        <v>29</v>
-      </c>
-      <c r="C461">
-        <v>3158</v>
-      </c>
-      <c r="D461" t="s">
-        <v>47</v>
-      </c>
-      <c r="F461" t="s">
-        <v>55</v>
-      </c>
-      <c r="G461" t="s">
-        <v>10</v>
-      </c>
-      <c r="H461" s="2">
-        <v>7.6157407407407406E-3</v>
-      </c>
-      <c r="I461" s="1">
-        <v>46118.81145833333</v>
-      </c>
-      <c r="J461">
-        <v>1</v>
-      </c>
+      <c r="H461" s="2"/>
+      <c r="I461" s="1"/>
       <c r="K461" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="462" spans="2:11" x14ac:dyDescent="0.25">
@@ -12834,10 +12746,10 @@
         <v>29</v>
       </c>
       <c r="C462">
-        <v>3159</v>
+        <v>3147</v>
       </c>
       <c r="D462" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F462" t="s">
         <v>55</v>
@@ -12846,13 +12758,13 @@
         <v>10</v>
       </c>
       <c r="H462" s="2">
-        <v>1.5590277777777778E-2</v>
+        <v>3.7337962962962962E-2</v>
       </c>
       <c r="I462" s="1">
-        <v>46118.812152777777</v>
+        <v>46118.810069444444</v>
       </c>
       <c r="J462">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K462" t="s">
         <v>11</v>
@@ -12863,10 +12775,10 @@
         <v>29</v>
       </c>
       <c r="C463">
-        <v>3150</v>
+        <v>3156</v>
       </c>
       <c r="D463" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F463" t="s">
         <v>55</v>
@@ -12875,13 +12787,13 @@
         <v>10</v>
       </c>
       <c r="H463" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>7.6273148148148151E-3</v>
       </c>
       <c r="I463" s="1">
-        <v>46118.812152777777</v>
+        <v>46118.810763888891</v>
       </c>
       <c r="J463">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K463" t="s">
         <v>11</v>
@@ -12892,57 +12804,35 @@
         <v>29</v>
       </c>
       <c r="C464">
-        <v>3155</v>
+        <v>3157</v>
       </c>
       <c r="D464" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F464" t="s">
         <v>55</v>
       </c>
       <c r="G464" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H464" s="2">
-        <v>7.4305555555555557E-3</v>
+        <v>0</v>
       </c>
       <c r="I464" s="1">
-        <v>46118.812847222223</v>
+        <v>46118.810763888891</v>
       </c>
       <c r="J464">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K464" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="465" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B465" t="s">
-        <v>29</v>
-      </c>
-      <c r="C465">
-        <v>3143</v>
-      </c>
-      <c r="D465" t="s">
-        <v>30</v>
-      </c>
-      <c r="F465" t="s">
-        <v>55</v>
-      </c>
-      <c r="G465" t="s">
-        <v>10</v>
-      </c>
-      <c r="H465" s="2">
-        <v>1.7777777777777778E-2</v>
-      </c>
-      <c r="I465" s="1">
-        <v>46118.812847222223</v>
-      </c>
-      <c r="J465">
-        <v>2</v>
-      </c>
+      <c r="H465" s="2"/>
+      <c r="I465" s="1"/>
       <c r="K465" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="466" spans="2:11" x14ac:dyDescent="0.25">
@@ -12950,25 +12840,25 @@
         <v>29</v>
       </c>
       <c r="C466">
-        <v>3153</v>
+        <v>3158</v>
       </c>
       <c r="D466" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F466" t="s">
         <v>55</v>
       </c>
       <c r="G466" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H466" s="2">
-        <v>0</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I466" s="1">
-        <v>46118.81354166667</v>
+        <v>46118.81145833333</v>
       </c>
       <c r="J466">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K466" t="s">
         <v>11</v>
@@ -12979,210 +12869,916 @@
         <v>29</v>
       </c>
       <c r="C467">
+        <v>3159</v>
+      </c>
+      <c r="D467" t="s">
+        <v>48</v>
+      </c>
+      <c r="F467" t="s">
+        <v>55</v>
+      </c>
+      <c r="G467" t="s">
+        <v>10</v>
+      </c>
+      <c r="H467" s="2">
+        <v>1.5590277777777778E-2</v>
+      </c>
+      <c r="I467" s="1">
+        <v>46118.812152777777</v>
+      </c>
+      <c r="J467">
+        <v>0</v>
+      </c>
+      <c r="K467" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B468" t="s">
+        <v>29</v>
+      </c>
+      <c r="C468">
+        <v>3150</v>
+      </c>
+      <c r="D468" t="s">
+        <v>38</v>
+      </c>
+      <c r="F468" t="s">
+        <v>55</v>
+      </c>
+      <c r="G468" t="s">
+        <v>10</v>
+      </c>
+      <c r="H468" s="2">
+        <v>9.3518518518518525E-3</v>
+      </c>
+      <c r="I468" s="1">
+        <v>46118.812152777777</v>
+      </c>
+      <c r="J468">
+        <v>0</v>
+      </c>
+      <c r="K468" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B469" t="s">
+        <v>29</v>
+      </c>
+      <c r="C469">
+        <v>3155</v>
+      </c>
+      <c r="D469" t="s">
+        <v>43</v>
+      </c>
+      <c r="F469" t="s">
+        <v>55</v>
+      </c>
+      <c r="G469" t="s">
+        <v>10</v>
+      </c>
+      <c r="H469" s="2">
+        <v>7.4305555555555557E-3</v>
+      </c>
+      <c r="I469" s="1">
+        <v>46118.812847222223</v>
+      </c>
+      <c r="J469">
+        <v>1</v>
+      </c>
+      <c r="K469" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B470" t="s">
+        <v>29</v>
+      </c>
+      <c r="C470">
+        <v>3143</v>
+      </c>
+      <c r="D470" t="s">
+        <v>30</v>
+      </c>
+      <c r="F470" t="s">
+        <v>55</v>
+      </c>
+      <c r="G470" t="s">
+        <v>10</v>
+      </c>
+      <c r="H470" s="2">
+        <v>1.7777777777777778E-2</v>
+      </c>
+      <c r="I470" s="1">
+        <v>46118.812847222223</v>
+      </c>
+      <c r="J470">
+        <v>2</v>
+      </c>
+      <c r="K470" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B471" t="s">
+        <v>29</v>
+      </c>
+      <c r="C471">
+        <v>3153</v>
+      </c>
+      <c r="D471" t="s">
+        <v>52</v>
+      </c>
+      <c r="F471" t="s">
+        <v>55</v>
+      </c>
+      <c r="G471" t="s">
+        <v>13</v>
+      </c>
+      <c r="H471" s="2">
+        <v>0</v>
+      </c>
+      <c r="I471" s="1">
+        <v>46118.81354166667</v>
+      </c>
+      <c r="J471">
+        <v>4</v>
+      </c>
+      <c r="K471" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B472" t="s">
+        <v>29</v>
+      </c>
+      <c r="C472">
         <v>3158</v>
       </c>
-      <c r="D467" t="s">
+      <c r="D472" t="s">
         <v>47</v>
       </c>
-      <c r="F467" t="s">
+      <c r="F472" t="s">
         <v>15</v>
       </c>
-      <c r="G467" t="s">
+      <c r="G472" t="s">
         <v>12</v>
       </c>
-      <c r="H467" s="2">
+      <c r="H472" s="2">
         <v>4.2824074074074075E-4</v>
       </c>
-      <c r="I467" s="1">
+      <c r="I472" s="1">
         <v>46131.543171296296</v>
       </c>
-      <c r="J467">
+      <c r="J472">
         <v>1</v>
       </c>
-      <c r="K467" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H468" s="2"/>
-      <c r="I468" s="1"/>
-      <c r="K468" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H469" s="2"/>
-      <c r="I469" s="1"/>
-    </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H470" s="2"/>
-      <c r="I470" s="1"/>
-    </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H471" s="2"/>
-      <c r="I471" s="1"/>
-    </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H472" s="2"/>
-      <c r="I472" s="1"/>
+      <c r="K472" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="473" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H473" s="2"/>
       <c r="I473" s="1"/>
+      <c r="K473" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="474" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H474" s="2"/>
-      <c r="I474" s="1"/>
+      <c r="B474" t="s">
+        <v>29</v>
+      </c>
+      <c r="C474">
+        <v>3161</v>
+      </c>
+      <c r="D474" t="s">
+        <v>34</v>
+      </c>
+      <c r="F474" t="s">
+        <v>18</v>
+      </c>
+      <c r="G474" t="s">
+        <v>13</v>
+      </c>
+      <c r="H474" s="2">
+        <v>0</v>
+      </c>
+      <c r="I474" s="1">
+        <v>46146.722916666666</v>
+      </c>
+      <c r="J474">
+        <v>0</v>
+      </c>
+      <c r="K474" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="475" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H475" s="2"/>
-      <c r="I475" s="1"/>
+      <c r="B475" t="s">
+        <v>29</v>
+      </c>
+      <c r="C475">
+        <v>3146</v>
+      </c>
+      <c r="D475" t="s">
+        <v>35</v>
+      </c>
+      <c r="F475" t="s">
+        <v>18</v>
+      </c>
+      <c r="G475" t="s">
+        <v>10</v>
+      </c>
+      <c r="H475" s="2">
+        <v>6.1689814814814819E-3</v>
+      </c>
+      <c r="I475" s="1">
+        <v>46146.723611111112</v>
+      </c>
+      <c r="J475">
+        <v>0</v>
+      </c>
+      <c r="K475" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="476" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H476" s="2"/>
-      <c r="I476" s="1"/>
+      <c r="B476" t="s">
+        <v>29</v>
+      </c>
+      <c r="C476">
+        <v>3429</v>
+      </c>
+      <c r="D476" t="s">
+        <v>53</v>
+      </c>
+      <c r="F476" t="s">
+        <v>18</v>
+      </c>
+      <c r="G476" t="s">
+        <v>10</v>
+      </c>
+      <c r="H476" s="2">
+        <v>4.6527777777777774E-3</v>
+      </c>
+      <c r="I476" s="1">
+        <v>46146.724305555559</v>
+      </c>
+      <c r="J476">
+        <v>0</v>
+      </c>
+      <c r="K476" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="477" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H477" s="2"/>
-      <c r="I477" s="1"/>
+      <c r="B477" t="s">
+        <v>29</v>
+      </c>
+      <c r="C477">
+        <v>3160</v>
+      </c>
+      <c r="D477" t="s">
+        <v>56</v>
+      </c>
+      <c r="F477" t="s">
+        <v>18</v>
+      </c>
+      <c r="G477" t="s">
+        <v>13</v>
+      </c>
+      <c r="H477" s="2">
+        <v>0</v>
+      </c>
+      <c r="I477" s="1">
+        <v>46146.724305555559</v>
+      </c>
+      <c r="J477">
+        <v>0</v>
+      </c>
+      <c r="K477" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="478" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H478" s="2"/>
-      <c r="I478" s="1"/>
+      <c r="B478" t="s">
+        <v>29</v>
+      </c>
+      <c r="C478">
+        <v>3154</v>
+      </c>
+      <c r="D478" t="s">
+        <v>31</v>
+      </c>
+      <c r="F478" t="s">
+        <v>18</v>
+      </c>
+      <c r="G478" t="s">
+        <v>10</v>
+      </c>
+      <c r="H478" s="2">
+        <v>4.3055555555555555E-3</v>
+      </c>
+      <c r="I478" s="1">
+        <v>46146.724999999999</v>
+      </c>
+      <c r="J478">
+        <v>0</v>
+      </c>
+      <c r="K478" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="479" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H479" s="2"/>
-      <c r="I479" s="1"/>
+      <c r="B479" t="s">
+        <v>29</v>
+      </c>
+      <c r="C479">
+        <v>3144</v>
+      </c>
+      <c r="D479" t="s">
+        <v>32</v>
+      </c>
+      <c r="F479" t="s">
+        <v>18</v>
+      </c>
+      <c r="G479" t="s">
+        <v>10</v>
+      </c>
+      <c r="H479" s="2">
+        <v>5.0462962962962961E-3</v>
+      </c>
+      <c r="I479" s="1">
+        <v>46146.724999999999</v>
+      </c>
+      <c r="J479">
+        <v>0</v>
+      </c>
+      <c r="K479" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="480" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H480" s="2"/>
-      <c r="I480" s="1"/>
-    </row>
-    <row r="481" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H481" s="2"/>
-      <c r="I481" s="1"/>
-    </row>
-    <row r="482" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H482" s="2"/>
-      <c r="I482" s="1"/>
-    </row>
-    <row r="483" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H483" s="2"/>
-      <c r="I483" s="1"/>
-    </row>
-    <row r="484" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H484" s="2"/>
-      <c r="I484" s="1"/>
-    </row>
-    <row r="485" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H485" s="2"/>
-      <c r="I485" s="1"/>
-    </row>
-    <row r="486" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B480" t="s">
+        <v>29</v>
+      </c>
+      <c r="C480">
+        <v>3145</v>
+      </c>
+      <c r="D480" t="s">
+        <v>33</v>
+      </c>
+      <c r="F480" t="s">
+        <v>18</v>
+      </c>
+      <c r="G480" t="s">
+        <v>10</v>
+      </c>
+      <c r="H480" s="2">
+        <v>5.4976851851851853E-3</v>
+      </c>
+      <c r="I480" s="1">
+        <v>46146.725694444445</v>
+      </c>
+      <c r="J480">
+        <v>0</v>
+      </c>
+      <c r="K480" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="481" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B481" t="s">
+        <v>29</v>
+      </c>
+      <c r="C481">
+        <v>3151</v>
+      </c>
+      <c r="D481" t="s">
+        <v>39</v>
+      </c>
+      <c r="F481" t="s">
+        <v>18</v>
+      </c>
+      <c r="G481" t="s">
+        <v>13</v>
+      </c>
+      <c r="H481" s="2">
+        <v>0</v>
+      </c>
+      <c r="I481" s="1">
+        <v>46146.726388888892</v>
+      </c>
+      <c r="J481">
+        <v>0</v>
+      </c>
+      <c r="K481" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="482" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B482" t="s">
+        <v>29</v>
+      </c>
+      <c r="C482">
+        <v>3148</v>
+      </c>
+      <c r="D482" t="s">
+        <v>36</v>
+      </c>
+      <c r="F482" t="s">
+        <v>18</v>
+      </c>
+      <c r="G482" t="s">
+        <v>13</v>
+      </c>
+      <c r="H482" s="2">
+        <v>0</v>
+      </c>
+      <c r="I482" s="1">
+        <v>46146.726388888892</v>
+      </c>
+      <c r="J482">
+        <v>0</v>
+      </c>
+      <c r="K482" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="483" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B483" t="s">
+        <v>29</v>
+      </c>
+      <c r="C483">
+        <v>3164</v>
+      </c>
+      <c r="D483" t="s">
+        <v>41</v>
+      </c>
+      <c r="F483" t="s">
+        <v>18</v>
+      </c>
+      <c r="G483" t="s">
+        <v>13</v>
+      </c>
+      <c r="H483" s="2">
+        <v>0</v>
+      </c>
+      <c r="I483" s="1">
+        <v>46146.727083333331</v>
+      </c>
+      <c r="J483">
+        <v>0</v>
+      </c>
+      <c r="K483" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="484" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B484" t="s">
+        <v>29</v>
+      </c>
+      <c r="C484">
+        <v>3163</v>
+      </c>
+      <c r="D484" t="s">
+        <v>37</v>
+      </c>
+      <c r="F484" t="s">
+        <v>18</v>
+      </c>
+      <c r="G484" t="s">
+        <v>13</v>
+      </c>
+      <c r="H484" s="2">
+        <v>0</v>
+      </c>
+      <c r="I484" s="1">
+        <v>46146.727777777778</v>
+      </c>
+      <c r="J484">
+        <v>0</v>
+      </c>
+      <c r="K484" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="485" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B485" t="s">
+        <v>29</v>
+      </c>
+      <c r="C485">
+        <v>3194</v>
+      </c>
+      <c r="D485" t="s">
+        <v>42</v>
+      </c>
+      <c r="F485" t="s">
+        <v>18</v>
+      </c>
+      <c r="G485" t="s">
+        <v>12</v>
+      </c>
+      <c r="H485" s="2">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I485" s="1">
+        <v>46146.728472222225</v>
+      </c>
+      <c r="J485">
+        <v>0</v>
+      </c>
+      <c r="K485" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="486" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H486" s="2"/>
       <c r="I486" s="1"/>
-    </row>
-    <row r="487" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H487" s="2"/>
-      <c r="I487" s="1"/>
-    </row>
-    <row r="488" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H488" s="2"/>
-      <c r="I488" s="1"/>
-    </row>
-    <row r="489" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H489" s="2"/>
-      <c r="I489" s="1"/>
-    </row>
-    <row r="490" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H490" s="2"/>
-      <c r="I490" s="1"/>
-    </row>
-    <row r="491" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K486" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B487" t="s">
+        <v>29</v>
+      </c>
+      <c r="C487">
+        <v>3162</v>
+      </c>
+      <c r="D487" t="s">
+        <v>40</v>
+      </c>
+      <c r="F487" t="s">
+        <v>18</v>
+      </c>
+      <c r="G487" t="s">
+        <v>13</v>
+      </c>
+      <c r="H487" s="2">
+        <v>0</v>
+      </c>
+      <c r="I487" s="1">
+        <v>46146.728472222225</v>
+      </c>
+      <c r="J487">
+        <v>0</v>
+      </c>
+      <c r="K487" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="488" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B488" t="s">
+        <v>29</v>
+      </c>
+      <c r="C488">
+        <v>3147</v>
+      </c>
+      <c r="D488" t="s">
+        <v>44</v>
+      </c>
+      <c r="F488" t="s">
+        <v>18</v>
+      </c>
+      <c r="G488" t="s">
+        <v>13</v>
+      </c>
+      <c r="H488" s="2">
+        <v>0</v>
+      </c>
+      <c r="I488" s="1">
+        <v>46146.729166666664</v>
+      </c>
+      <c r="J488">
+        <v>0</v>
+      </c>
+      <c r="K488" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="489" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B489" t="s">
+        <v>29</v>
+      </c>
+      <c r="C489">
+        <v>3156</v>
+      </c>
+      <c r="D489" t="s">
+        <v>45</v>
+      </c>
+      <c r="F489" t="s">
+        <v>18</v>
+      </c>
+      <c r="G489" t="s">
+        <v>10</v>
+      </c>
+      <c r="H489" s="2">
+        <v>6.7824074074074071E-3</v>
+      </c>
+      <c r="I489" s="1">
+        <v>46146.729861111111</v>
+      </c>
+      <c r="J489">
+        <v>0</v>
+      </c>
+      <c r="K489" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="490" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B490" t="s">
+        <v>29</v>
+      </c>
+      <c r="C490">
+        <v>3157</v>
+      </c>
+      <c r="D490" t="s">
+        <v>46</v>
+      </c>
+      <c r="F490" t="s">
+        <v>18</v>
+      </c>
+      <c r="G490" t="s">
+        <v>14</v>
+      </c>
+      <c r="H490" s="2">
+        <v>0</v>
+      </c>
+      <c r="I490" s="1">
+        <v>46146.729861111111</v>
+      </c>
+      <c r="J490">
+        <v>0</v>
+      </c>
+      <c r="K490" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="491" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H491" s="2"/>
       <c r="I491" s="1"/>
-    </row>
-    <row r="492" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H492" s="2"/>
-      <c r="I492" s="1"/>
-    </row>
-    <row r="493" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H493" s="2"/>
-      <c r="I493" s="1"/>
-    </row>
-    <row r="494" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H494" s="2"/>
-      <c r="I494" s="1"/>
-    </row>
-    <row r="495" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H495" s="2"/>
-      <c r="I495" s="1"/>
-    </row>
-    <row r="496" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H496" s="2"/>
-      <c r="I496" s="1"/>
-    </row>
-    <row r="497" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H497" s="2"/>
-      <c r="I497" s="1"/>
-    </row>
-    <row r="498" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H498" s="2"/>
-      <c r="I498" s="1"/>
-    </row>
-    <row r="499" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K491" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B492" t="s">
+        <v>29</v>
+      </c>
+      <c r="C492">
+        <v>3158</v>
+      </c>
+      <c r="D492" t="s">
+        <v>47</v>
+      </c>
+      <c r="F492" t="s">
+        <v>18</v>
+      </c>
+      <c r="G492" t="s">
+        <v>10</v>
+      </c>
+      <c r="H492" s="2">
+        <v>7.5115740740740742E-3</v>
+      </c>
+      <c r="I492" s="1">
+        <v>46146.730555555558</v>
+      </c>
+      <c r="J492">
+        <v>0</v>
+      </c>
+      <c r="K492" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="493" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B493" t="s">
+        <v>29</v>
+      </c>
+      <c r="C493">
+        <v>3149</v>
+      </c>
+      <c r="D493" t="s">
+        <v>57</v>
+      </c>
+      <c r="F493" t="s">
+        <v>18</v>
+      </c>
+      <c r="G493" t="s">
+        <v>13</v>
+      </c>
+      <c r="H493" s="2">
+        <v>0</v>
+      </c>
+      <c r="I493" s="1">
+        <v>46146.731249999997</v>
+      </c>
+      <c r="J493">
+        <v>0</v>
+      </c>
+      <c r="K493" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="494" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B494" t="s">
+        <v>29</v>
+      </c>
+      <c r="C494">
+        <v>3159</v>
+      </c>
+      <c r="D494" t="s">
+        <v>48</v>
+      </c>
+      <c r="F494" t="s">
+        <v>18</v>
+      </c>
+      <c r="G494" t="s">
+        <v>10</v>
+      </c>
+      <c r="H494" s="2">
+        <v>6.053240740740741E-3</v>
+      </c>
+      <c r="I494" s="1">
+        <v>46146.731249999997</v>
+      </c>
+      <c r="J494">
+        <v>0</v>
+      </c>
+      <c r="K494" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="495" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B495" t="s">
+        <v>29</v>
+      </c>
+      <c r="C495">
+        <v>3150</v>
+      </c>
+      <c r="D495" t="s">
+        <v>38</v>
+      </c>
+      <c r="F495" t="s">
+        <v>18</v>
+      </c>
+      <c r="G495" t="s">
+        <v>13</v>
+      </c>
+      <c r="H495" s="2">
+        <v>0</v>
+      </c>
+      <c r="I495" s="1">
+        <v>46146.731944444444</v>
+      </c>
+      <c r="J495">
+        <v>0</v>
+      </c>
+      <c r="K495" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="496" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B496" t="s">
+        <v>29</v>
+      </c>
+      <c r="C496">
+        <v>3155</v>
+      </c>
+      <c r="D496" t="s">
+        <v>43</v>
+      </c>
+      <c r="F496" t="s">
+        <v>18</v>
+      </c>
+      <c r="G496" t="s">
+        <v>13</v>
+      </c>
+      <c r="H496" s="2">
+        <v>0</v>
+      </c>
+      <c r="I496" s="1">
+        <v>46146.732638888891</v>
+      </c>
+      <c r="J496">
+        <v>0</v>
+      </c>
+      <c r="K496" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="497" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B497" t="s">
+        <v>29</v>
+      </c>
+      <c r="C497">
+        <v>3143</v>
+      </c>
+      <c r="D497" t="s">
+        <v>30</v>
+      </c>
+      <c r="F497" t="s">
+        <v>18</v>
+      </c>
+      <c r="G497" t="s">
+        <v>13</v>
+      </c>
+      <c r="H497" s="2">
+        <v>0</v>
+      </c>
+      <c r="I497" s="1">
+        <v>46146.73333333333</v>
+      </c>
+      <c r="J497">
+        <v>0</v>
+      </c>
+      <c r="K497" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="498" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B498" t="s">
+        <v>29</v>
+      </c>
+      <c r="C498">
+        <v>3153</v>
+      </c>
+      <c r="D498" t="s">
+        <v>52</v>
+      </c>
+      <c r="F498" t="s">
+        <v>18</v>
+      </c>
+      <c r="G498" t="s">
+        <v>13</v>
+      </c>
+      <c r="H498" s="2">
+        <v>0</v>
+      </c>
+      <c r="I498" s="1">
+        <v>46146.710532407407</v>
+      </c>
+      <c r="J498">
+        <v>0</v>
+      </c>
+      <c r="K498" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="499" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H499" s="2"/>
       <c r="I499" s="1"/>
     </row>
-    <row r="500" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H500" s="2"/>
       <c r="I500" s="1"/>
     </row>
-    <row r="501" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H501" s="2"/>
       <c r="I501" s="1"/>
     </row>
-    <row r="502" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H502" s="2"/>
       <c r="I502" s="1"/>
     </row>
-    <row r="503" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H503" s="2"/>
       <c r="I503" s="1"/>
     </row>
-    <row r="504" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H504" s="2"/>
       <c r="I504" s="1"/>
     </row>
-    <row r="505" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H505" s="2"/>
       <c r="I505" s="1"/>
     </row>
-    <row r="506" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H506" s="2"/>
       <c r="I506" s="1"/>
     </row>
-    <row r="507" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H507" s="2"/>
       <c r="I507" s="1"/>
     </row>
-    <row r="508" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H508" s="2"/>
       <c r="I508" s="1"/>
     </row>
-    <row r="509" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H509" s="2"/>
       <c r="I509" s="1"/>
     </row>
-    <row r="510" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H510" s="2"/>
       <c r="I510" s="1"/>
     </row>
-    <row r="511" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H511" s="2"/>
       <c r="I511" s="1"/>
     </row>
-    <row r="512" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H512" s="2"/>
       <c r="I512" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303EF3CE-8324-472D-ADF9-0F162F20DABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2FB87A-8941-400E-80F5-3D042CE2DD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -11565,7 +11565,7 @@
         <v>46118.808564814812</v>
       </c>
       <c r="J407">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K407" t="s">
         <v>11</v>
@@ -11594,7 +11594,7 @@
         <v>46118.809259259258</v>
       </c>
       <c r="J408">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K408" t="s">
         <v>11</v>
@@ -11803,7 +11803,7 @@
         <v>46118.812037037038</v>
       </c>
       <c r="J419">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K419" t="s">
         <v>11</v>
@@ -11832,7 +11832,7 @@
         <v>46118.812037037038</v>
       </c>
       <c r="J420">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K420" t="s">
         <v>11</v>
@@ -11861,7 +11861,7 @@
         <v>46118.812731481485</v>
       </c>
       <c r="J421">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K421" t="s">
         <v>11</v>
@@ -12097,7 +12097,7 @@
         <v>54</v>
       </c>
       <c r="G434" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H434" s="2">
         <v>0</v>
@@ -12106,219 +12106,197 @@
         <v>46118.79409722222</v>
       </c>
       <c r="J434">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K434" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="435" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B435" t="s">
-        <v>29</v>
-      </c>
-      <c r="C435">
+      <c r="H435" s="2"/>
+      <c r="I435" s="1"/>
+      <c r="K435" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B436" t="s">
+        <v>29</v>
+      </c>
+      <c r="C436">
         <v>3158</v>
       </c>
-      <c r="D435" t="s">
+      <c r="D436" t="s">
         <v>47</v>
       </c>
-      <c r="F435" t="s">
+      <c r="F436" t="s">
         <v>54</v>
       </c>
-      <c r="G435" t="s">
+      <c r="G436" t="s">
         <v>12</v>
       </c>
-      <c r="H435" s="2">
+      <c r="H436" s="2">
         <v>1.1226851851851851E-3</v>
       </c>
-      <c r="I435" s="1">
+      <c r="I436" s="1">
         <v>46118.79409722222</v>
       </c>
-      <c r="J435">
+      <c r="J436">
         <v>2</v>
       </c>
-      <c r="K435" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H436" s="2"/>
-      <c r="I436" s="1"/>
       <c r="K436" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H437" s="2"/>
+      <c r="I437" s="1"/>
+      <c r="K437" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B437" t="s">
-        <v>29</v>
-      </c>
-      <c r="C437">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B438" t="s">
+        <v>29</v>
+      </c>
+      <c r="C438">
         <v>3159</v>
       </c>
-      <c r="D437" t="s">
+      <c r="D438" t="s">
         <v>48</v>
       </c>
-      <c r="F437" t="s">
+      <c r="F438" t="s">
         <v>54</v>
       </c>
-      <c r="G437" t="s">
+      <c r="G438" t="s">
         <v>12</v>
       </c>
-      <c r="H437" s="2">
+      <c r="H438" s="2">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="I437" s="1">
+      <c r="I438" s="1">
         <v>46118.794791666667</v>
       </c>
-      <c r="J437">
+      <c r="J438">
         <v>1</v>
       </c>
-      <c r="K437" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H438" s="2"/>
-      <c r="I438" s="1"/>
       <c r="K438" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H439" s="2"/>
+      <c r="I439" s="1"/>
+      <c r="K439" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B439" t="s">
-        <v>29</v>
-      </c>
-      <c r="C439">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B440" t="s">
+        <v>29</v>
+      </c>
+      <c r="C440">
         <v>3150</v>
       </c>
-      <c r="D439" t="s">
+      <c r="D440" t="s">
         <v>38</v>
       </c>
-      <c r="F439" t="s">
+      <c r="F440" t="s">
         <v>54</v>
       </c>
-      <c r="G439" t="s">
+      <c r="G440" t="s">
         <v>12</v>
       </c>
-      <c r="H439" s="2">
+      <c r="H440" s="2">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="I439" s="1">
+      <c r="I440" s="1">
         <v>46118.795486111114</v>
       </c>
-      <c r="J439">
+      <c r="J440">
         <v>0</v>
       </c>
-      <c r="K439" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H440" s="2"/>
-      <c r="I440" s="1"/>
       <c r="K440" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H441" s="2"/>
+      <c r="I441" s="1"/>
+      <c r="K441" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B441" t="s">
-        <v>29</v>
-      </c>
-      <c r="C441">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B442" t="s">
+        <v>29</v>
+      </c>
+      <c r="C442">
         <v>3155</v>
       </c>
-      <c r="D441" t="s">
+      <c r="D442" t="s">
         <v>43</v>
       </c>
-      <c r="F441" t="s">
+      <c r="F442" t="s">
         <v>54</v>
       </c>
-      <c r="G441" t="s">
+      <c r="G442" t="s">
         <v>12</v>
       </c>
-      <c r="H441" s="2">
+      <c r="H442" s="2">
         <v>2.5462962962962961E-4</v>
       </c>
-      <c r="I441" s="1">
+      <c r="I442" s="1">
         <v>46118.796180555553</v>
       </c>
-      <c r="J441">
+      <c r="J442">
         <v>3</v>
       </c>
-      <c r="K441" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H442" s="2"/>
-      <c r="I442" s="1"/>
       <c r="K442" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H443" s="2"/>
+      <c r="I443" s="1"/>
+      <c r="K443" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B443" t="s">
-        <v>29</v>
-      </c>
-      <c r="C443">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B444" t="s">
+        <v>29</v>
+      </c>
+      <c r="C444">
         <v>3143</v>
       </c>
-      <c r="D443" t="s">
+      <c r="D444" t="s">
         <v>30</v>
       </c>
-      <c r="F443" t="s">
+      <c r="F444" t="s">
         <v>54</v>
       </c>
-      <c r="G443" t="s">
+      <c r="G444" t="s">
         <v>12</v>
       </c>
-      <c r="H443" s="2">
+      <c r="H444" s="2">
         <v>2.4305555555555555E-4</v>
       </c>
-      <c r="I443" s="1">
+      <c r="I444" s="1">
         <v>46118.796180555553</v>
       </c>
-      <c r="J443">
+      <c r="J444">
         <v>3</v>
       </c>
-      <c r="K443" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H444" s="2"/>
-      <c r="I444" s="1"/>
       <c r="K444" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H445" s="2"/>
+      <c r="I445" s="1"/>
+      <c r="K445" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B445" t="s">
-        <v>29</v>
-      </c>
-      <c r="C445">
-        <v>3153</v>
-      </c>
-      <c r="D445" t="s">
-        <v>52</v>
-      </c>
-      <c r="F445" t="s">
-        <v>54</v>
-      </c>
-      <c r="G445" t="s">
-        <v>13</v>
-      </c>
-      <c r="H445" s="2">
-        <v>0</v>
-      </c>
-      <c r="I445" s="1">
-        <v>46118.796875</v>
-      </c>
-      <c r="J445">
-        <v>4</v>
-      </c>
-      <c r="K445" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="446" spans="2:11" x14ac:dyDescent="0.25">
@@ -12326,64 +12304,64 @@
         <v>29</v>
       </c>
       <c r="C446">
+        <v>3153</v>
+      </c>
+      <c r="D446" t="s">
+        <v>52</v>
+      </c>
+      <c r="F446" t="s">
+        <v>54</v>
+      </c>
+      <c r="G446" t="s">
+        <v>13</v>
+      </c>
+      <c r="H446" s="2">
+        <v>0</v>
+      </c>
+      <c r="I446" s="1">
+        <v>46118.796875</v>
+      </c>
+      <c r="J446">
+        <v>5</v>
+      </c>
+      <c r="K446" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B447" t="s">
+        <v>29</v>
+      </c>
+      <c r="C447">
         <v>3160</v>
       </c>
-      <c r="D446" t="s">
+      <c r="D447" t="s">
         <v>56</v>
       </c>
-      <c r="F446" t="s">
+      <c r="F447" t="s">
         <v>55</v>
       </c>
-      <c r="G446" t="s">
+      <c r="G447" t="s">
         <v>12</v>
       </c>
-      <c r="H446" s="2">
+      <c r="H447" s="2">
         <v>5.3240740740740744E-4</v>
       </c>
-      <c r="I446" s="1">
+      <c r="I447" s="1">
         <v>46118.804513888892</v>
       </c>
-      <c r="J446">
+      <c r="J447">
         <v>4</v>
       </c>
-      <c r="K446" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H447" s="2"/>
-      <c r="I447" s="1"/>
       <c r="K447" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H448" s="2"/>
+      <c r="I448" s="1"/>
+      <c r="K448" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B448" t="s">
-        <v>29</v>
-      </c>
-      <c r="C448">
-        <v>3161</v>
-      </c>
-      <c r="D448" t="s">
-        <v>34</v>
-      </c>
-      <c r="F448" t="s">
-        <v>55</v>
-      </c>
-      <c r="G448" t="s">
-        <v>13</v>
-      </c>
-      <c r="H448" s="2">
-        <v>0</v>
-      </c>
-      <c r="I448" s="1">
-        <v>46118.804513888892</v>
-      </c>
-      <c r="J448">
-        <v>4</v>
-      </c>
-      <c r="K448" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="449" spans="2:11" x14ac:dyDescent="0.25">
@@ -12391,25 +12369,25 @@
         <v>29</v>
       </c>
       <c r="C449">
-        <v>3146</v>
+        <v>3161</v>
       </c>
       <c r="D449" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F449" t="s">
         <v>55</v>
       </c>
       <c r="G449" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H449" s="2">
-        <v>5.6944444444444447E-3</v>
+        <v>0</v>
       </c>
       <c r="I449" s="1">
-        <v>46118.805208333331</v>
+        <v>46118.804513888892</v>
       </c>
       <c r="J449">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K449" t="s">
         <v>11</v>
@@ -12420,10 +12398,10 @@
         <v>29</v>
       </c>
       <c r="C450">
-        <v>3429</v>
+        <v>3146</v>
       </c>
       <c r="D450" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F450" t="s">
         <v>55</v>
@@ -12432,7 +12410,7 @@
         <v>10</v>
       </c>
       <c r="H450" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>5.6944444444444447E-3</v>
       </c>
       <c r="I450" s="1">
         <v>46118.805208333331</v>
@@ -12449,10 +12427,10 @@
         <v>29</v>
       </c>
       <c r="C451">
-        <v>3154</v>
+        <v>3429</v>
       </c>
       <c r="D451" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F451" t="s">
         <v>55</v>
@@ -12461,10 +12439,10 @@
         <v>10</v>
       </c>
       <c r="H451" s="2">
-        <v>7.2453703703703708E-3</v>
+        <v>4.7337962962962967E-3</v>
       </c>
       <c r="I451" s="1">
-        <v>46118.805902777778</v>
+        <v>46118.805208333331</v>
       </c>
       <c r="J451">
         <v>0</v>
@@ -12478,10 +12456,10 @@
         <v>29</v>
       </c>
       <c r="C452">
-        <v>3144</v>
+        <v>3154</v>
       </c>
       <c r="D452" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F452" t="s">
         <v>55</v>
@@ -12490,13 +12468,13 @@
         <v>10</v>
       </c>
       <c r="H452" s="2">
-        <v>7.7083333333333335E-3</v>
+        <v>7.2453703703703708E-3</v>
       </c>
       <c r="I452" s="1">
-        <v>46118.806597222225</v>
+        <v>46118.805902777778</v>
       </c>
       <c r="J452">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K452" t="s">
         <v>11</v>
@@ -12507,10 +12485,10 @@
         <v>29</v>
       </c>
       <c r="C453">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D453" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F453" t="s">
         <v>55</v>
@@ -12519,13 +12497,13 @@
         <v>10</v>
       </c>
       <c r="H453" s="2">
-        <v>7.013888888888889E-3</v>
+        <v>7.7083333333333335E-3</v>
       </c>
       <c r="I453" s="1">
         <v>46118.806597222225</v>
       </c>
       <c r="J453">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K453" t="s">
         <v>11</v>
@@ -12536,25 +12514,25 @@
         <v>29</v>
       </c>
       <c r="C454">
-        <v>3149</v>
+        <v>3145</v>
       </c>
       <c r="D454" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F454" t="s">
         <v>55</v>
       </c>
       <c r="G454" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H454" s="2">
-        <v>0</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I454" s="1">
-        <v>46118.807291666664</v>
+        <v>46118.806597222225</v>
       </c>
       <c r="J454">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K454" t="s">
         <v>11</v>
@@ -12565,10 +12543,10 @@
         <v>29</v>
       </c>
       <c r="C455">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="D455" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F455" t="s">
         <v>55</v>
@@ -12580,10 +12558,10 @@
         <v>0</v>
       </c>
       <c r="I455" s="1">
-        <v>46118.807986111111</v>
+        <v>46118.807291666664</v>
       </c>
       <c r="J455">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K455" t="s">
         <v>11</v>
@@ -12594,10 +12572,10 @@
         <v>29</v>
       </c>
       <c r="C456">
-        <v>3148</v>
+        <v>3151</v>
       </c>
       <c r="D456" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F456" t="s">
         <v>55</v>
@@ -12612,7 +12590,7 @@
         <v>46118.807986111111</v>
       </c>
       <c r="J456">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K456" t="s">
         <v>11</v>
@@ -12623,25 +12601,25 @@
         <v>29</v>
       </c>
       <c r="C457">
-        <v>3164</v>
+        <v>3148</v>
       </c>
       <c r="D457" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F457" t="s">
         <v>55</v>
       </c>
       <c r="G457" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H457" s="2">
-        <v>8.6342592592592599E-3</v>
+        <v>0</v>
       </c>
       <c r="I457" s="1">
-        <v>46118.808680555558</v>
+        <v>46118.807986111111</v>
       </c>
       <c r="J457">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K457" t="s">
         <v>11</v>
@@ -12652,10 +12630,10 @@
         <v>29</v>
       </c>
       <c r="C458">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="D458" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F458" t="s">
         <v>55</v>
@@ -12664,13 +12642,13 @@
         <v>10</v>
       </c>
       <c r="H458" s="2">
-        <v>7.858796296296296E-3</v>
+        <v>8.6342592592592599E-3</v>
       </c>
       <c r="I458" s="1">
         <v>46118.808680555558</v>
       </c>
       <c r="J458">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K458" t="s">
         <v>11</v>
@@ -12681,25 +12659,25 @@
         <v>29</v>
       </c>
       <c r="C459">
-        <v>3194</v>
+        <v>3163</v>
       </c>
       <c r="D459" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F459" t="s">
         <v>55</v>
       </c>
       <c r="G459" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H459" s="2">
-        <v>0</v>
+        <v>7.858796296296296E-3</v>
       </c>
       <c r="I459" s="1">
-        <v>46118.809374999997</v>
+        <v>46118.808680555558</v>
       </c>
       <c r="J459">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K459" t="s">
         <v>11</v>
@@ -12710,64 +12688,64 @@
         <v>29</v>
       </c>
       <c r="C460">
-        <v>3162</v>
+        <v>3194</v>
       </c>
       <c r="D460" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>55</v>
       </c>
       <c r="G460" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H460" s="2">
         <v>0</v>
       </c>
       <c r="I460" s="1">
+        <v>46118.809374999997</v>
+      </c>
+      <c r="J460">
+        <v>5</v>
+      </c>
+      <c r="K460" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B461" t="s">
+        <v>29</v>
+      </c>
+      <c r="C461">
+        <v>3162</v>
+      </c>
+      <c r="D461" t="s">
+        <v>40</v>
+      </c>
+      <c r="F461" t="s">
+        <v>55</v>
+      </c>
+      <c r="G461" t="s">
+        <v>14</v>
+      </c>
+      <c r="H461" s="2">
+        <v>0</v>
+      </c>
+      <c r="I461" s="1">
         <v>46118.810069444444</v>
       </c>
-      <c r="J460">
+      <c r="J461">
         <v>0</v>
       </c>
-      <c r="K460" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H461" s="2"/>
-      <c r="I461" s="1"/>
       <c r="K461" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H462" s="2"/>
+      <c r="I462" s="1"/>
+      <c r="K462" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B462" t="s">
-        <v>29</v>
-      </c>
-      <c r="C462">
-        <v>3147</v>
-      </c>
-      <c r="D462" t="s">
-        <v>44</v>
-      </c>
-      <c r="F462" t="s">
-        <v>55</v>
-      </c>
-      <c r="G462" t="s">
-        <v>10</v>
-      </c>
-      <c r="H462" s="2">
-        <v>3.7337962962962962E-2</v>
-      </c>
-      <c r="I462" s="1">
-        <v>46118.810069444444</v>
-      </c>
-      <c r="J462">
-        <v>3</v>
-      </c>
-      <c r="K462" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="463" spans="2:11" x14ac:dyDescent="0.25">
@@ -12775,10 +12753,10 @@
         <v>29</v>
       </c>
       <c r="C463">
-        <v>3156</v>
+        <v>3147</v>
       </c>
       <c r="D463" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F463" t="s">
         <v>55</v>
@@ -12787,13 +12765,13 @@
         <v>10</v>
       </c>
       <c r="H463" s="2">
-        <v>7.6273148148148151E-3</v>
+        <v>3.7337962962962962E-2</v>
       </c>
       <c r="I463" s="1">
-        <v>46118.810763888891</v>
+        <v>46118.810069444444</v>
       </c>
       <c r="J463">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K463" t="s">
         <v>11</v>
@@ -12804,64 +12782,64 @@
         <v>29</v>
       </c>
       <c r="C464">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="D464" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F464" t="s">
         <v>55</v>
       </c>
       <c r="G464" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H464" s="2">
-        <v>0</v>
+        <v>7.6273148148148151E-3</v>
       </c>
       <c r="I464" s="1">
         <v>46118.810763888891</v>
       </c>
       <c r="J464">
+        <v>1</v>
+      </c>
+      <c r="K464" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B465" t="s">
+        <v>29</v>
+      </c>
+      <c r="C465">
+        <v>3157</v>
+      </c>
+      <c r="D465" t="s">
+        <v>46</v>
+      </c>
+      <c r="F465" t="s">
+        <v>55</v>
+      </c>
+      <c r="G465" t="s">
+        <v>14</v>
+      </c>
+      <c r="H465" s="2">
+        <v>0</v>
+      </c>
+      <c r="I465" s="1">
+        <v>46118.810763888891</v>
+      </c>
+      <c r="J465">
         <v>4</v>
       </c>
-      <c r="K464" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H465" s="2"/>
-      <c r="I465" s="1"/>
       <c r="K465" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H466" s="2"/>
+      <c r="I466" s="1"/>
+      <c r="K466" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B466" t="s">
-        <v>29</v>
-      </c>
-      <c r="C466">
-        <v>3158</v>
-      </c>
-      <c r="D466" t="s">
-        <v>47</v>
-      </c>
-      <c r="F466" t="s">
-        <v>55</v>
-      </c>
-      <c r="G466" t="s">
-        <v>10</v>
-      </c>
-      <c r="H466" s="2">
-        <v>7.6157407407407406E-3</v>
-      </c>
-      <c r="I466" s="1">
-        <v>46118.81145833333</v>
-      </c>
-      <c r="J466">
-        <v>1</v>
-      </c>
-      <c r="K466" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="467" spans="2:11" x14ac:dyDescent="0.25">
@@ -12869,10 +12847,10 @@
         <v>29</v>
       </c>
       <c r="C467">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="D467" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F467" t="s">
         <v>55</v>
@@ -12881,13 +12859,13 @@
         <v>10</v>
       </c>
       <c r="H467" s="2">
-        <v>1.5590277777777778E-2</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I467" s="1">
-        <v>46118.812152777777</v>
+        <v>46118.81145833333</v>
       </c>
       <c r="J467">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K467" t="s">
         <v>11</v>
@@ -12898,10 +12876,10 @@
         <v>29</v>
       </c>
       <c r="C468">
-        <v>3150</v>
+        <v>3159</v>
       </c>
       <c r="D468" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F468" t="s">
         <v>55</v>
@@ -12910,7 +12888,7 @@
         <v>10</v>
       </c>
       <c r="H468" s="2">
-        <v>9.3518518518518525E-3</v>
+        <v>1.5590277777777778E-2</v>
       </c>
       <c r="I468" s="1">
         <v>46118.812152777777</v>
@@ -12927,10 +12905,10 @@
         <v>29</v>
       </c>
       <c r="C469">
-        <v>3155</v>
+        <v>3150</v>
       </c>
       <c r="D469" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F469" t="s">
         <v>55</v>
@@ -12939,13 +12917,13 @@
         <v>10</v>
       </c>
       <c r="H469" s="2">
-        <v>7.4305555555555557E-3</v>
+        <v>9.3518518518518525E-3</v>
       </c>
       <c r="I469" s="1">
-        <v>46118.812847222223</v>
+        <v>46118.812152777777</v>
       </c>
       <c r="J469">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K469" t="s">
         <v>11</v>
@@ -12956,10 +12934,10 @@
         <v>29</v>
       </c>
       <c r="C470">
-        <v>3143</v>
+        <v>3155</v>
       </c>
       <c r="D470" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F470" t="s">
         <v>55</v>
@@ -12968,13 +12946,13 @@
         <v>10</v>
       </c>
       <c r="H470" s="2">
-        <v>1.7777777777777778E-2</v>
+        <v>7.4305555555555557E-3</v>
       </c>
       <c r="I470" s="1">
         <v>46118.812847222223</v>
       </c>
       <c r="J470">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K470" t="s">
         <v>11</v>
@@ -12985,25 +12963,25 @@
         <v>29</v>
       </c>
       <c r="C471">
-        <v>3153</v>
+        <v>3143</v>
       </c>
       <c r="D471" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F471" t="s">
         <v>55</v>
       </c>
       <c r="G471" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H471" s="2">
-        <v>0</v>
+        <v>1.7777777777777778E-2</v>
       </c>
       <c r="I471" s="1">
-        <v>46118.81354166667</v>
+        <v>46118.812847222223</v>
       </c>
       <c r="J471">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K471" t="s">
         <v>11</v>
@@ -13014,64 +12992,64 @@
         <v>29</v>
       </c>
       <c r="C472">
+        <v>3153</v>
+      </c>
+      <c r="D472" t="s">
+        <v>52</v>
+      </c>
+      <c r="F472" t="s">
+        <v>55</v>
+      </c>
+      <c r="G472" t="s">
+        <v>13</v>
+      </c>
+      <c r="H472" s="2">
+        <v>0</v>
+      </c>
+      <c r="I472" s="1">
+        <v>46118.81354166667</v>
+      </c>
+      <c r="J472">
+        <v>5</v>
+      </c>
+      <c r="K472" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B473" t="s">
+        <v>29</v>
+      </c>
+      <c r="C473">
         <v>3158</v>
       </c>
-      <c r="D472" t="s">
+      <c r="D473" t="s">
         <v>47</v>
       </c>
-      <c r="F472" t="s">
+      <c r="F473" t="s">
         <v>15</v>
       </c>
-      <c r="G472" t="s">
+      <c r="G473" t="s">
         <v>12</v>
       </c>
-      <c r="H472" s="2">
+      <c r="H473" s="2">
         <v>4.2824074074074075E-4</v>
       </c>
-      <c r="I472" s="1">
+      <c r="I473" s="1">
         <v>46131.543171296296</v>
       </c>
-      <c r="J472">
+      <c r="J473">
         <v>1</v>
       </c>
-      <c r="K472" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H473" s="2"/>
-      <c r="I473" s="1"/>
       <c r="K473" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H474" s="2"/>
+      <c r="I474" s="1"/>
+      <c r="K474" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B474" t="s">
-        <v>29</v>
-      </c>
-      <c r="C474">
-        <v>3161</v>
-      </c>
-      <c r="D474" t="s">
-        <v>34</v>
-      </c>
-      <c r="F474" t="s">
-        <v>18</v>
-      </c>
-      <c r="G474" t="s">
-        <v>13</v>
-      </c>
-      <c r="H474" s="2">
-        <v>0</v>
-      </c>
-      <c r="I474" s="1">
-        <v>46146.722916666666</v>
-      </c>
-      <c r="J474">
-        <v>0</v>
-      </c>
-      <c r="K474" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="475" spans="2:11" x14ac:dyDescent="0.25">
@@ -13079,22 +13057,22 @@
         <v>29</v>
       </c>
       <c r="C475">
-        <v>3146</v>
+        <v>3161</v>
       </c>
       <c r="D475" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F475" t="s">
         <v>18</v>
       </c>
       <c r="G475" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H475" s="2">
-        <v>6.1689814814814819E-3</v>
+        <v>0</v>
       </c>
       <c r="I475" s="1">
-        <v>46146.723611111112</v>
+        <v>46146.722916666666</v>
       </c>
       <c r="J475">
         <v>0</v>
@@ -13108,10 +13086,10 @@
         <v>29</v>
       </c>
       <c r="C476">
-        <v>3429</v>
+        <v>3146</v>
       </c>
       <c r="D476" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F476" t="s">
         <v>18</v>
@@ -13120,10 +13098,10 @@
         <v>10</v>
       </c>
       <c r="H476" s="2">
-        <v>4.6527777777777774E-3</v>
+        <v>6.1689814814814819E-3</v>
       </c>
       <c r="I476" s="1">
-        <v>46146.724305555559</v>
+        <v>46146.723611111112</v>
       </c>
       <c r="J476">
         <v>0</v>
@@ -13137,19 +13115,19 @@
         <v>29</v>
       </c>
       <c r="C477">
-        <v>3160</v>
+        <v>3429</v>
       </c>
       <c r="D477" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F477" t="s">
         <v>18</v>
       </c>
       <c r="G477" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H477" s="2">
-        <v>0</v>
+        <v>4.6527777777777774E-3</v>
       </c>
       <c r="I477" s="1">
         <v>46146.724305555559</v>
@@ -13166,22 +13144,22 @@
         <v>29</v>
       </c>
       <c r="C478">
-        <v>3154</v>
+        <v>3160</v>
       </c>
       <c r="D478" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F478" t="s">
         <v>18</v>
       </c>
       <c r="G478" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H478" s="2">
-        <v>4.3055555555555555E-3</v>
+        <v>0</v>
       </c>
       <c r="I478" s="1">
-        <v>46146.724999999999</v>
+        <v>46146.724305555559</v>
       </c>
       <c r="J478">
         <v>0</v>
@@ -13195,10 +13173,10 @@
         <v>29</v>
       </c>
       <c r="C479">
-        <v>3144</v>
+        <v>3154</v>
       </c>
       <c r="D479" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F479" t="s">
         <v>18</v>
@@ -13207,7 +13185,7 @@
         <v>10</v>
       </c>
       <c r="H479" s="2">
-        <v>5.0462962962962961E-3</v>
+        <v>4.3055555555555555E-3</v>
       </c>
       <c r="I479" s="1">
         <v>46146.724999999999</v>
@@ -13224,10 +13202,10 @@
         <v>29</v>
       </c>
       <c r="C480">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D480" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F480" t="s">
         <v>18</v>
@@ -13236,10 +13214,10 @@
         <v>10</v>
       </c>
       <c r="H480" s="2">
-        <v>5.4976851851851853E-3</v>
+        <v>5.0462962962962961E-3</v>
       </c>
       <c r="I480" s="1">
-        <v>46146.725694444445</v>
+        <v>46146.724999999999</v>
       </c>
       <c r="J480">
         <v>0</v>
@@ -13253,22 +13231,22 @@
         <v>29</v>
       </c>
       <c r="C481">
-        <v>3151</v>
+        <v>3145</v>
       </c>
       <c r="D481" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F481" t="s">
         <v>18</v>
       </c>
       <c r="G481" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H481" s="2">
-        <v>0</v>
+        <v>5.4976851851851853E-3</v>
       </c>
       <c r="I481" s="1">
-        <v>46146.726388888892</v>
+        <v>46146.725694444445</v>
       </c>
       <c r="J481">
         <v>0</v>
@@ -13282,10 +13260,10 @@
         <v>29</v>
       </c>
       <c r="C482">
-        <v>3148</v>
+        <v>3151</v>
       </c>
       <c r="D482" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>18</v>
@@ -13311,10 +13289,10 @@
         <v>29</v>
       </c>
       <c r="C483">
-        <v>3164</v>
+        <v>3148</v>
       </c>
       <c r="D483" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>18</v>
@@ -13326,7 +13304,7 @@
         <v>0</v>
       </c>
       <c r="I483" s="1">
-        <v>46146.727083333331</v>
+        <v>46146.726388888892</v>
       </c>
       <c r="J483">
         <v>0</v>
@@ -13340,10 +13318,10 @@
         <v>29</v>
       </c>
       <c r="C484">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="D484" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F484" t="s">
         <v>18</v>
@@ -13355,7 +13333,7 @@
         <v>0</v>
       </c>
       <c r="I484" s="1">
-        <v>46146.727777777778</v>
+        <v>46146.727083333331</v>
       </c>
       <c r="J484">
         <v>0</v>
@@ -13369,22 +13347,22 @@
         <v>29</v>
       </c>
       <c r="C485">
-        <v>3194</v>
+        <v>3163</v>
       </c>
       <c r="D485" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F485" t="s">
         <v>18</v>
       </c>
       <c r="G485" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H485" s="2">
-        <v>2.0833333333333335E-4</v>
+        <v>0</v>
       </c>
       <c r="I485" s="1">
-        <v>46146.728472222225</v>
+        <v>46146.727777777778</v>
       </c>
       <c r="J485">
         <v>0</v>
@@ -13394,39 +13372,39 @@
       </c>
     </row>
     <row r="486" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H486" s="2"/>
-      <c r="I486" s="1"/>
+      <c r="B486" t="s">
+        <v>29</v>
+      </c>
+      <c r="C486">
+        <v>3194</v>
+      </c>
+      <c r="D486" t="s">
+        <v>42</v>
+      </c>
+      <c r="F486" t="s">
+        <v>18</v>
+      </c>
+      <c r="G486" t="s">
+        <v>12</v>
+      </c>
+      <c r="H486" s="2">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I486" s="1">
+        <v>46146.728472222225</v>
+      </c>
+      <c r="J486">
+        <v>0</v>
+      </c>
       <c r="K486" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H487" s="2"/>
+      <c r="I487" s="1"/>
+      <c r="K487" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B487" t="s">
-        <v>29</v>
-      </c>
-      <c r="C487">
-        <v>3162</v>
-      </c>
-      <c r="D487" t="s">
-        <v>40</v>
-      </c>
-      <c r="F487" t="s">
-        <v>18</v>
-      </c>
-      <c r="G487" t="s">
-        <v>13</v>
-      </c>
-      <c r="H487" s="2">
-        <v>0</v>
-      </c>
-      <c r="I487" s="1">
-        <v>46146.728472222225</v>
-      </c>
-      <c r="J487">
-        <v>0</v>
-      </c>
-      <c r="K487" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="488" spans="2:11" x14ac:dyDescent="0.25">
@@ -13434,10 +13412,10 @@
         <v>29</v>
       </c>
       <c r="C488">
-        <v>3147</v>
+        <v>3162</v>
       </c>
       <c r="D488" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F488" t="s">
         <v>18</v>
@@ -13449,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="I488" s="1">
-        <v>46146.729166666664</v>
+        <v>46146.728472222225</v>
       </c>
       <c r="J488">
         <v>0</v>
@@ -13463,22 +13441,22 @@
         <v>29</v>
       </c>
       <c r="C489">
-        <v>3156</v>
+        <v>3147</v>
       </c>
       <c r="D489" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F489" t="s">
         <v>18</v>
       </c>
       <c r="G489" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H489" s="2">
-        <v>6.7824074074074071E-3</v>
+        <v>0</v>
       </c>
       <c r="I489" s="1">
-        <v>46146.729861111111</v>
+        <v>46146.729166666664</v>
       </c>
       <c r="J489">
         <v>0</v>
@@ -13492,19 +13470,19 @@
         <v>29</v>
       </c>
       <c r="C490">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="D490" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F490" t="s">
         <v>18</v>
       </c>
       <c r="G490" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H490" s="2">
-        <v>0</v>
+        <v>6.7824074074074071E-3</v>
       </c>
       <c r="I490" s="1">
         <v>46146.729861111111</v>
@@ -13517,39 +13495,39 @@
       </c>
     </row>
     <row r="491" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H491" s="2"/>
-      <c r="I491" s="1"/>
+      <c r="B491" t="s">
+        <v>29</v>
+      </c>
+      <c r="C491">
+        <v>3157</v>
+      </c>
+      <c r="D491" t="s">
+        <v>46</v>
+      </c>
+      <c r="F491" t="s">
+        <v>18</v>
+      </c>
+      <c r="G491" t="s">
+        <v>14</v>
+      </c>
+      <c r="H491" s="2">
+        <v>0</v>
+      </c>
+      <c r="I491" s="1">
+        <v>46146.729861111111</v>
+      </c>
+      <c r="J491">
+        <v>0</v>
+      </c>
       <c r="K491" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H492" s="2"/>
+      <c r="I492" s="1"/>
+      <c r="K492" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B492" t="s">
-        <v>29</v>
-      </c>
-      <c r="C492">
-        <v>3158</v>
-      </c>
-      <c r="D492" t="s">
-        <v>47</v>
-      </c>
-      <c r="F492" t="s">
-        <v>18</v>
-      </c>
-      <c r="G492" t="s">
-        <v>10</v>
-      </c>
-      <c r="H492" s="2">
-        <v>7.5115740740740742E-3</v>
-      </c>
-      <c r="I492" s="1">
-        <v>46146.730555555558</v>
-      </c>
-      <c r="J492">
-        <v>0</v>
-      </c>
-      <c r="K492" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="493" spans="2:11" x14ac:dyDescent="0.25">
@@ -13557,22 +13535,22 @@
         <v>29</v>
       </c>
       <c r="C493">
-        <v>3149</v>
+        <v>3158</v>
       </c>
       <c r="D493" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F493" t="s">
         <v>18</v>
       </c>
       <c r="G493" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H493" s="2">
-        <v>0</v>
+        <v>7.5115740740740742E-3</v>
       </c>
       <c r="I493" s="1">
-        <v>46146.731249999997</v>
+        <v>46146.730555555558</v>
       </c>
       <c r="J493">
         <v>0</v>
@@ -13586,19 +13564,19 @@
         <v>29</v>
       </c>
       <c r="C494">
-        <v>3159</v>
+        <v>3149</v>
       </c>
       <c r="D494" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F494" t="s">
         <v>18</v>
       </c>
       <c r="G494" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H494" s="2">
-        <v>6.053240740740741E-3</v>
+        <v>0</v>
       </c>
       <c r="I494" s="1">
         <v>46146.731249999997</v>
@@ -13615,22 +13593,22 @@
         <v>29</v>
       </c>
       <c r="C495">
-        <v>3150</v>
+        <v>3159</v>
       </c>
       <c r="D495" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F495" t="s">
         <v>18</v>
       </c>
       <c r="G495" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H495" s="2">
-        <v>0</v>
+        <v>6.053240740740741E-3</v>
       </c>
       <c r="I495" s="1">
-        <v>46146.731944444444</v>
+        <v>46146.731249999997</v>
       </c>
       <c r="J495">
         <v>0</v>
@@ -13644,10 +13622,10 @@
         <v>29</v>
       </c>
       <c r="C496">
-        <v>3155</v>
+        <v>3150</v>
       </c>
       <c r="D496" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F496" t="s">
         <v>18</v>
@@ -13659,7 +13637,7 @@
         <v>0</v>
       </c>
       <c r="I496" s="1">
-        <v>46146.732638888891</v>
+        <v>46146.731944444444</v>
       </c>
       <c r="J496">
         <v>0</v>
@@ -13673,10 +13651,10 @@
         <v>29</v>
       </c>
       <c r="C497">
-        <v>3143</v>
+        <v>3155</v>
       </c>
       <c r="D497" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F497" t="s">
         <v>18</v>
@@ -13688,7 +13666,7 @@
         <v>0</v>
       </c>
       <c r="I497" s="1">
-        <v>46146.73333333333</v>
+        <v>46146.732638888891</v>
       </c>
       <c r="J497">
         <v>0</v>
@@ -13702,22 +13680,22 @@
         <v>29</v>
       </c>
       <c r="C498">
-        <v>3153</v>
+        <v>3143</v>
       </c>
       <c r="D498" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F498" t="s">
         <v>18</v>
       </c>
       <c r="G498" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H498" s="2">
-        <v>0</v>
+        <v>5.3819444444444444E-3</v>
       </c>
       <c r="I498" s="1">
-        <v>46146.710532407407</v>
+        <v>46146.73333333333</v>
       </c>
       <c r="J498">
         <v>0</v>
@@ -13727,8 +13705,33 @@
       </c>
     </row>
     <row r="499" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H499" s="2"/>
-      <c r="I499" s="1"/>
+      <c r="B499" t="s">
+        <v>29</v>
+      </c>
+      <c r="C499">
+        <v>3153</v>
+      </c>
+      <c r="D499" t="s">
+        <v>52</v>
+      </c>
+      <c r="F499" t="s">
+        <v>18</v>
+      </c>
+      <c r="G499" t="s">
+        <v>13</v>
+      </c>
+      <c r="H499" s="2">
+        <v>0</v>
+      </c>
+      <c r="I499" s="1">
+        <v>46146.710532407407</v>
+      </c>
+      <c r="J499">
+        <v>0</v>
+      </c>
+      <c r="K499" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="500" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H500" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\PCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE97D87E-93F9-4FAA-85DE-B11FFD06529C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE4192B-948C-43FC-B940-6E33C794FBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -149,9 +149,6 @@
     <t>Aaron Mutulo</t>
   </si>
   <si>
-    <t>John Gates</t>
-  </si>
-  <si>
     <t>Larry Simons</t>
   </si>
   <si>
@@ -213,6 +210,9 @@
   </si>
   <si>
     <t>NEW HIRE</t>
+  </si>
+  <si>
+    <t>Susan Cobliegh</t>
   </si>
 </sst>
 </file>
@@ -815,7 +815,7 @@
         <v>3148</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -844,7 +844,7 @@
         <v>3163</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
@@ -873,7 +873,7 @@
         <v>3150</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>
@@ -902,7 +902,7 @@
         <v>3151</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
         <v>27</v>
@@ -931,7 +931,7 @@
         <v>3149</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
         <v>27</v>
@@ -960,7 +960,7 @@
         <v>3153</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
         <v>27</v>
@@ -989,7 +989,7 @@
         <v>3162</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
         <v>27</v>
@@ -1018,7 +1018,7 @@
         <v>3164</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
         <v>27</v>
@@ -1047,7 +1047,7 @@
         <v>3194</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
@@ -1076,7 +1076,7 @@
         <v>3155</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
@@ -1105,7 +1105,7 @@
         <v>3147</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -1134,7 +1134,7 @@
         <v>3156</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
@@ -1163,7 +1163,7 @@
         <v>3157</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
@@ -1192,7 +1192,7 @@
         <v>3158</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
@@ -1221,7 +1221,7 @@
         <v>3159</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
@@ -1250,7 +1250,7 @@
         <v>3160</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s">
         <v>27</v>
@@ -1482,7 +1482,7 @@
         <v>3148</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s">
         <v>15</v>
@@ -1511,7 +1511,7 @@
         <v>3163</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" t="s">
         <v>15</v>
@@ -1540,7 +1540,7 @@
         <v>3150</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
         <v>15</v>
@@ -1569,7 +1569,7 @@
         <v>3151</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
         <v>15</v>
@@ -1598,7 +1598,7 @@
         <v>3149</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F35" t="s">
         <v>15</v>
@@ -1627,7 +1627,7 @@
         <v>3153</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
         <v>15</v>
@@ -1656,7 +1656,7 @@
         <v>3162</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
         <v>15</v>
@@ -1685,7 +1685,7 @@
         <v>3164</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
         <v>15</v>
@@ -1714,7 +1714,7 @@
         <v>3194</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
@@ -1743,7 +1743,7 @@
         <v>3155</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
@@ -1772,7 +1772,7 @@
         <v>3147</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -1801,7 +1801,7 @@
         <v>3156</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1830,7 +1830,7 @@
         <v>3157</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -1859,7 +1859,7 @@
         <v>3158</v>
       </c>
       <c r="D44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
@@ -1888,7 +1888,7 @@
         <v>3159</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -1917,7 +1917,7 @@
         <v>3160</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
@@ -1975,7 +1975,7 @@
         <v>3209</v>
       </c>
       <c r="D48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F48" t="s">
         <v>27</v>
@@ -2004,7 +2004,7 @@
         <v>3194</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F49" t="s">
         <v>27</v>
@@ -2033,10 +2033,10 @@
         <v>3194</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
@@ -2236,7 +2236,7 @@
         <v>3148</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F57" t="s">
         <v>27</v>
@@ -2265,7 +2265,7 @@
         <v>3163</v>
       </c>
       <c r="D58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
         <v>27</v>
@@ -2294,7 +2294,7 @@
         <v>3150</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F59" t="s">
         <v>27</v>
@@ -2323,7 +2323,7 @@
         <v>3151</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F60" t="s">
         <v>27</v>
@@ -2352,7 +2352,7 @@
         <v>3149</v>
       </c>
       <c r="D61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F61" t="s">
         <v>27</v>
@@ -2388,7 +2388,7 @@
         <v>3153</v>
       </c>
       <c r="D63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
@@ -2417,7 +2417,7 @@
         <v>3209</v>
       </c>
       <c r="D64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F64" t="s">
         <v>27</v>
@@ -2446,7 +2446,7 @@
         <v>3162</v>
       </c>
       <c r="D65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F65" t="s">
         <v>27</v>
@@ -2475,7 +2475,7 @@
         <v>3164</v>
       </c>
       <c r="D66" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F66" t="s">
         <v>27</v>
@@ -2504,7 +2504,7 @@
         <v>3194</v>
       </c>
       <c r="D67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F67" t="s">
         <v>27</v>
@@ -2540,7 +2540,7 @@
         <v>3155</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F69" t="s">
         <v>27</v>
@@ -2569,7 +2569,7 @@
         <v>3147</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F70" t="s">
         <v>27</v>
@@ -2598,7 +2598,7 @@
         <v>3156</v>
       </c>
       <c r="D71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F71" t="s">
         <v>27</v>
@@ -2627,7 +2627,7 @@
         <v>3157</v>
       </c>
       <c r="D72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F72" t="s">
         <v>27</v>
@@ -2656,7 +2656,7 @@
         <v>3158</v>
       </c>
       <c r="D73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F73" t="s">
         <v>27</v>
@@ -2685,7 +2685,7 @@
         <v>3159</v>
       </c>
       <c r="D74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F74" t="s">
         <v>27</v>
@@ -2714,7 +2714,7 @@
         <v>3160</v>
       </c>
       <c r="D75" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s">
         <v>27</v>
@@ -2946,7 +2946,7 @@
         <v>3148</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F83" t="s">
         <v>25</v>
@@ -2982,7 +2982,7 @@
         <v>3163</v>
       </c>
       <c r="D85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F85" t="s">
         <v>25</v>
@@ -3018,7 +3018,7 @@
         <v>3150</v>
       </c>
       <c r="D87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F87" t="s">
         <v>25</v>
@@ -3047,7 +3047,7 @@
         <v>3151</v>
       </c>
       <c r="D88" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F88" t="s">
         <v>25</v>
@@ -3076,7 +3076,7 @@
         <v>3149</v>
       </c>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F89" t="s">
         <v>25</v>
@@ -3112,7 +3112,7 @@
         <v>3153</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
@@ -3141,7 +3141,7 @@
         <v>3209</v>
       </c>
       <c r="D92" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F92" t="s">
         <v>25</v>
@@ -3170,7 +3170,7 @@
         <v>3162</v>
       </c>
       <c r="D93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F93" t="s">
         <v>25</v>
@@ -3199,7 +3199,7 @@
         <v>3164</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F94" t="s">
         <v>25</v>
@@ -3228,7 +3228,7 @@
         <v>3194</v>
       </c>
       <c r="D95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F95" t="s">
         <v>25</v>
@@ -3257,7 +3257,7 @@
         <v>3155</v>
       </c>
       <c r="D96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F96" t="s">
         <v>25</v>
@@ -3293,7 +3293,7 @@
         <v>3147</v>
       </c>
       <c r="D98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F98" t="s">
         <v>25</v>
@@ -3322,7 +3322,7 @@
         <v>3156</v>
       </c>
       <c r="D99" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F99" t="s">
         <v>25</v>
@@ -3351,7 +3351,7 @@
         <v>3157</v>
       </c>
       <c r="D100" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
@@ -3380,7 +3380,7 @@
         <v>3158</v>
       </c>
       <c r="D101" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
@@ -3409,7 +3409,7 @@
         <v>3159</v>
       </c>
       <c r="D102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
@@ -3438,7 +3438,7 @@
         <v>3160</v>
       </c>
       <c r="D103" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F103" t="s">
         <v>25</v>
@@ -3648,7 +3648,7 @@
         <v>3155</v>
       </c>
       <c r="D111" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F111" t="s">
         <v>19</v>
@@ -3677,7 +3677,7 @@
         <v>3148</v>
       </c>
       <c r="D112" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F112" t="s">
         <v>19</v>
@@ -3706,7 +3706,7 @@
         <v>3163</v>
       </c>
       <c r="D113" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F113" t="s">
         <v>19</v>
@@ -3735,7 +3735,7 @@
         <v>3149</v>
       </c>
       <c r="D114" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F114" t="s">
         <v>19</v>
@@ -3764,7 +3764,7 @@
         <v>3150</v>
       </c>
       <c r="D115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F115" t="s">
         <v>19</v>
@@ -3793,7 +3793,7 @@
         <v>3151</v>
       </c>
       <c r="D116" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F116" t="s">
         <v>19</v>
@@ -3851,7 +3851,7 @@
         <v>3153</v>
       </c>
       <c r="D118" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F118" t="s">
         <v>19</v>
@@ -3880,7 +3880,7 @@
         <v>3209</v>
       </c>
       <c r="D119" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F119" t="s">
         <v>19</v>
@@ -3916,7 +3916,7 @@
         <v>3162</v>
       </c>
       <c r="D121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F121" t="s">
         <v>19</v>
@@ -3945,7 +3945,7 @@
         <v>3164</v>
       </c>
       <c r="D122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
@@ -3974,7 +3974,7 @@
         <v>3194</v>
       </c>
       <c r="D123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F123" t="s">
         <v>19</v>
@@ -4003,7 +4003,7 @@
         <v>3429</v>
       </c>
       <c r="D124" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F124" t="s">
         <v>19</v>
@@ -4032,7 +4032,7 @@
         <v>3147</v>
       </c>
       <c r="D125" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F125" t="s">
         <v>19</v>
@@ -4061,7 +4061,7 @@
         <v>3156</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F126" t="s">
         <v>19</v>
@@ -4090,7 +4090,7 @@
         <v>3157</v>
       </c>
       <c r="D127" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F127" t="s">
         <v>19</v>
@@ -4119,7 +4119,7 @@
         <v>3158</v>
       </c>
       <c r="D128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F128" t="s">
         <v>19</v>
@@ -4148,7 +4148,7 @@
         <v>3160</v>
       </c>
       <c r="D129" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F129" t="s">
         <v>19</v>
@@ -4177,7 +4177,7 @@
         <v>3159</v>
       </c>
       <c r="D130" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F130" t="s">
         <v>19</v>
@@ -4387,7 +4387,7 @@
         <v>3155</v>
       </c>
       <c r="D138" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F138" t="s">
         <v>15</v>
@@ -4416,7 +4416,7 @@
         <v>3148</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F139" t="s">
         <v>15</v>
@@ -4445,7 +4445,7 @@
         <v>3163</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F140" t="s">
         <v>15</v>
@@ -4474,7 +4474,7 @@
         <v>3149</v>
       </c>
       <c r="D141" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F141" t="s">
         <v>15</v>
@@ -4510,7 +4510,7 @@
         <v>3150</v>
       </c>
       <c r="D143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F143" t="s">
         <v>15</v>
@@ -4539,7 +4539,7 @@
         <v>3151</v>
       </c>
       <c r="D144" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F144" t="s">
         <v>15</v>
@@ -4597,7 +4597,7 @@
         <v>3153</v>
       </c>
       <c r="D146" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F146" t="s">
         <v>15</v>
@@ -4626,7 +4626,7 @@
         <v>3209</v>
       </c>
       <c r="D147" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F147" t="s">
         <v>15</v>
@@ -4655,7 +4655,7 @@
         <v>3162</v>
       </c>
       <c r="D148" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F148" t="s">
         <v>15</v>
@@ -4684,7 +4684,7 @@
         <v>3194</v>
       </c>
       <c r="D149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F149" t="s">
         <v>15</v>
@@ -4720,7 +4720,7 @@
         <v>3429</v>
       </c>
       <c r="D151" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F151" t="s">
         <v>15</v>
@@ -4749,7 +4749,7 @@
         <v>3147</v>
       </c>
       <c r="D152" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F152" t="s">
         <v>15</v>
@@ -4778,7 +4778,7 @@
         <v>3156</v>
       </c>
       <c r="D153" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F153" t="s">
         <v>15</v>
@@ -4807,7 +4807,7 @@
         <v>3157</v>
       </c>
       <c r="D154" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F154" t="s">
         <v>15</v>
@@ -4836,7 +4836,7 @@
         <v>3158</v>
       </c>
       <c r="D155" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F155" t="s">
         <v>15</v>
@@ -4865,7 +4865,7 @@
         <v>3160</v>
       </c>
       <c r="D156" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F156" t="s">
         <v>15</v>
@@ -4894,7 +4894,7 @@
         <v>3159</v>
       </c>
       <c r="D157" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F157" t="s">
         <v>15</v>
@@ -4952,7 +4952,7 @@
         <v>3164</v>
       </c>
       <c r="D159" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F159" t="s">
         <v>15</v>
@@ -5097,7 +5097,7 @@
         <v>3148</v>
       </c>
       <c r="D164" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F164" t="s">
         <v>24</v>
@@ -5126,7 +5126,7 @@
         <v>3163</v>
       </c>
       <c r="D165" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F165" t="s">
         <v>24</v>
@@ -5155,7 +5155,7 @@
         <v>3149</v>
       </c>
       <c r="D166" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F166" t="s">
         <v>24</v>
@@ -5184,7 +5184,7 @@
         <v>3150</v>
       </c>
       <c r="D167" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F167" t="s">
         <v>24</v>
@@ -5213,7 +5213,7 @@
         <v>3151</v>
       </c>
       <c r="D168" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F168" t="s">
         <v>24</v>
@@ -5242,7 +5242,7 @@
         <v>3155</v>
       </c>
       <c r="D169" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F169" t="s">
         <v>24</v>
@@ -5271,7 +5271,7 @@
         <v>3209</v>
       </c>
       <c r="D170" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F170" t="s">
         <v>24</v>
@@ -5300,7 +5300,7 @@
         <v>3194</v>
       </c>
       <c r="D171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F171" t="s">
         <v>24</v>
@@ -5336,7 +5336,7 @@
         <v>3429</v>
       </c>
       <c r="D173" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F173" t="s">
         <v>24</v>
@@ -5365,7 +5365,7 @@
         <v>3147</v>
       </c>
       <c r="D174" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F174" t="s">
         <v>24</v>
@@ -5394,7 +5394,7 @@
         <v>3156</v>
       </c>
       <c r="D175" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F175" t="s">
         <v>24</v>
@@ -5423,7 +5423,7 @@
         <v>3157</v>
       </c>
       <c r="D176" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F176" t="s">
         <v>24</v>
@@ -5459,7 +5459,7 @@
         <v>3158</v>
       </c>
       <c r="D178" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F178" t="s">
         <v>24</v>
@@ -5517,7 +5517,7 @@
         <v>3160</v>
       </c>
       <c r="D180" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F180" t="s">
         <v>24</v>
@@ -5546,7 +5546,7 @@
         <v>3162</v>
       </c>
       <c r="D181" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F181" t="s">
         <v>24</v>
@@ -5575,7 +5575,7 @@
         <v>3153</v>
       </c>
       <c r="D182" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F182" t="s">
         <v>24</v>
@@ -5604,7 +5604,7 @@
         <v>3159</v>
       </c>
       <c r="D183" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F183" t="s">
         <v>24</v>
@@ -5691,7 +5691,7 @@
         <v>3164</v>
       </c>
       <c r="D186" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F186" t="s">
         <v>24</v>
@@ -5865,7 +5865,7 @@
         <v>3148</v>
       </c>
       <c r="D192" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -5894,7 +5894,7 @@
         <v>3163</v>
       </c>
       <c r="D193" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -5923,7 +5923,7 @@
         <v>3149</v>
       </c>
       <c r="D194" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -5952,7 +5952,7 @@
         <v>3150</v>
       </c>
       <c r="D195" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -5981,7 +5981,7 @@
         <v>3151</v>
       </c>
       <c r="D196" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>3155</v>
       </c>
       <c r="D197" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -6039,7 +6039,7 @@
         <v>3209</v>
       </c>
       <c r="D198" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>3194</v>
       </c>
       <c r="D200" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -6111,7 +6111,7 @@
         <v>3429</v>
       </c>
       <c r="D202" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -6147,7 +6147,7 @@
         <v>3147</v>
       </c>
       <c r="D204" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -6176,7 +6176,7 @@
         <v>3156</v>
       </c>
       <c r="D205" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -6205,7 +6205,7 @@
         <v>3157</v>
       </c>
       <c r="D206" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -6241,7 +6241,7 @@
         <v>3158</v>
       </c>
       <c r="D208" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -6270,7 +6270,7 @@
         <v>3162</v>
       </c>
       <c r="D209" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -6299,7 +6299,7 @@
         <v>3160</v>
       </c>
       <c r="D210" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -6328,7 +6328,7 @@
         <v>3153</v>
       </c>
       <c r="D211" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -6357,7 +6357,7 @@
         <v>3159</v>
       </c>
       <c r="D212" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -6444,7 +6444,7 @@
         <v>3164</v>
       </c>
       <c r="D215" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -6618,7 +6618,7 @@
         <v>3148</v>
       </c>
       <c r="D221" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F221" t="s">
         <v>26</v>
@@ -6647,7 +6647,7 @@
         <v>3163</v>
       </c>
       <c r="D222" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F222" t="s">
         <v>26</v>
@@ -6676,7 +6676,7 @@
         <v>3149</v>
       </c>
       <c r="D223" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F223" t="s">
         <v>26</v>
@@ -6705,7 +6705,7 @@
         <v>3150</v>
       </c>
       <c r="D224" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F224" t="s">
         <v>26</v>
@@ -6734,7 +6734,7 @@
         <v>3151</v>
       </c>
       <c r="D225" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F225" t="s">
         <v>26</v>
@@ -6763,7 +6763,7 @@
         <v>3155</v>
       </c>
       <c r="D226" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F226" t="s">
         <v>26</v>
@@ -6792,7 +6792,7 @@
         <v>3209</v>
       </c>
       <c r="D227" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F227" t="s">
         <v>26</v>
@@ -6821,7 +6821,7 @@
         <v>3194</v>
       </c>
       <c r="D228" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F228" t="s">
         <v>26</v>
@@ -6850,7 +6850,7 @@
         <v>3429</v>
       </c>
       <c r="D229" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F229" t="s">
         <v>26</v>
@@ -6879,7 +6879,7 @@
         <v>3147</v>
       </c>
       <c r="D230" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F230" t="s">
         <v>26</v>
@@ -6908,7 +6908,7 @@
         <v>3156</v>
       </c>
       <c r="D231" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F231" t="s">
         <v>26</v>
@@ -6937,7 +6937,7 @@
         <v>3157</v>
       </c>
       <c r="D232" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F232" t="s">
         <v>26</v>
@@ -6966,7 +6966,7 @@
         <v>3158</v>
       </c>
       <c r="D233" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F233" t="s">
         <v>26</v>
@@ -6995,7 +6995,7 @@
         <v>3162</v>
       </c>
       <c r="D234" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F234" t="s">
         <v>26</v>
@@ -7024,7 +7024,7 @@
         <v>3160</v>
       </c>
       <c r="D235" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F235" t="s">
         <v>26</v>
@@ -7053,7 +7053,7 @@
         <v>3153</v>
       </c>
       <c r="D236" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F236" t="s">
         <v>26</v>
@@ -7082,7 +7082,7 @@
         <v>3159</v>
       </c>
       <c r="D237" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F237" t="s">
         <v>26</v>
@@ -7169,7 +7169,7 @@
         <v>3164</v>
       </c>
       <c r="D240" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F240" t="s">
         <v>26</v>
@@ -7343,7 +7343,7 @@
         <v>3148</v>
       </c>
       <c r="D246" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F246" t="s">
         <v>18</v>
@@ -7372,7 +7372,7 @@
         <v>3163</v>
       </c>
       <c r="D247" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F247" t="s">
         <v>18</v>
@@ -7401,7 +7401,7 @@
         <v>3149</v>
       </c>
       <c r="D248" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F248" t="s">
         <v>18</v>
@@ -7430,7 +7430,7 @@
         <v>3155</v>
       </c>
       <c r="D249" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F249" t="s">
         <v>18</v>
@@ -7459,7 +7459,7 @@
         <v>3150</v>
       </c>
       <c r="D250" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F250" t="s">
         <v>18</v>
@@ -7488,7 +7488,7 @@
         <v>3151</v>
       </c>
       <c r="D251" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F251" t="s">
         <v>18</v>
@@ -7517,7 +7517,7 @@
         <v>3209</v>
       </c>
       <c r="D252" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F252" t="s">
         <v>18</v>
@@ -7546,7 +7546,7 @@
         <v>3194</v>
       </c>
       <c r="D253" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F253" t="s">
         <v>18</v>
@@ -7575,7 +7575,7 @@
         <v>3429</v>
       </c>
       <c r="D254" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F254" t="s">
         <v>18</v>
@@ -7604,7 +7604,7 @@
         <v>3147</v>
       </c>
       <c r="D255" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F255" t="s">
         <v>18</v>
@@ -7633,7 +7633,7 @@
         <v>3156</v>
       </c>
       <c r="D256" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F256" t="s">
         <v>18</v>
@@ -7662,7 +7662,7 @@
         <v>3157</v>
       </c>
       <c r="D257" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F257" t="s">
         <v>18</v>
@@ -7698,7 +7698,7 @@
         <v>3158</v>
       </c>
       <c r="D259" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F259" t="s">
         <v>18</v>
@@ -7727,7 +7727,7 @@
         <v>3162</v>
       </c>
       <c r="D260" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F260" t="s">
         <v>18</v>
@@ -7756,7 +7756,7 @@
         <v>3164</v>
       </c>
       <c r="D261" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F261" t="s">
         <v>18</v>
@@ -7785,7 +7785,7 @@
         <v>3160</v>
       </c>
       <c r="D262" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F262" t="s">
         <v>18</v>
@@ -7850,7 +7850,7 @@
         <v>3153</v>
       </c>
       <c r="D265" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F265" t="s">
         <v>18</v>
@@ -7879,7 +7879,7 @@
         <v>3159</v>
       </c>
       <c r="D266" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F266" t="s">
         <v>18</v>
@@ -8089,7 +8089,7 @@
         <v>3163</v>
       </c>
       <c r="D274" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F274" t="s">
         <v>16</v>
@@ -8118,7 +8118,7 @@
         <v>3149</v>
       </c>
       <c r="D275" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F275" t="s">
         <v>16</v>
@@ -8147,7 +8147,7 @@
         <v>3151</v>
       </c>
       <c r="D276" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F276" t="s">
         <v>16</v>
@@ -8176,7 +8176,7 @@
         <v>3209</v>
       </c>
       <c r="D277" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F277" t="s">
         <v>16</v>
@@ -8205,7 +8205,7 @@
         <v>3194</v>
       </c>
       <c r="D278" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -8234,7 +8234,7 @@
         <v>3429</v>
       </c>
       <c r="D279" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F279" t="s">
         <v>16</v>
@@ -8263,7 +8263,7 @@
         <v>3147</v>
       </c>
       <c r="D280" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -8292,7 +8292,7 @@
         <v>3156</v>
       </c>
       <c r="D281" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F281" t="s">
         <v>16</v>
@@ -8321,7 +8321,7 @@
         <v>3157</v>
       </c>
       <c r="D282" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F282" t="s">
         <v>16</v>
@@ -8357,7 +8357,7 @@
         <v>3158</v>
       </c>
       <c r="D284" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F284" t="s">
         <v>16</v>
@@ -8386,7 +8386,7 @@
         <v>3148</v>
       </c>
       <c r="D285" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F285" t="s">
         <v>16</v>
@@ -8415,7 +8415,7 @@
         <v>3162</v>
       </c>
       <c r="D286" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F286" t="s">
         <v>16</v>
@@ -8444,7 +8444,7 @@
         <v>3164</v>
       </c>
       <c r="D287" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F287" t="s">
         <v>16</v>
@@ -8473,7 +8473,7 @@
         <v>3160</v>
       </c>
       <c r="D288" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -8531,7 +8531,7 @@
         <v>3153</v>
       </c>
       <c r="D290" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F290" t="s">
         <v>16</v>
@@ -8560,7 +8560,7 @@
         <v>3159</v>
       </c>
       <c r="D291" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F291" t="s">
         <v>16</v>
@@ -8589,7 +8589,7 @@
         <v>3150</v>
       </c>
       <c r="D292" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F292" t="s">
         <v>16</v>
@@ -8618,7 +8618,7 @@
         <v>3155</v>
       </c>
       <c r="D293" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -8835,7 +8835,7 @@
         <v>3163</v>
       </c>
       <c r="D302" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F302" t="s">
         <v>17</v>
@@ -8864,7 +8864,7 @@
         <v>3149</v>
       </c>
       <c r="D303" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F303" t="s">
         <v>17</v>
@@ -8900,7 +8900,7 @@
         <v>3151</v>
       </c>
       <c r="D305" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F305" t="s">
         <v>17</v>
@@ -8929,7 +8929,7 @@
         <v>3148</v>
       </c>
       <c r="D306" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F306" t="s">
         <v>17</v>
@@ -8958,7 +8958,7 @@
         <v>3209</v>
       </c>
       <c r="D307" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F307" t="s">
         <v>17</v>
@@ -8987,7 +8987,7 @@
         <v>3194</v>
       </c>
       <c r="D308" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F308" t="s">
         <v>17</v>
@@ -9023,7 +9023,7 @@
         <v>3429</v>
       </c>
       <c r="D310" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F310" t="s">
         <v>17</v>
@@ -9052,7 +9052,7 @@
         <v>3147</v>
       </c>
       <c r="D311" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F311" t="s">
         <v>17</v>
@@ -9081,7 +9081,7 @@
         <v>3156</v>
       </c>
       <c r="D312" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F312" t="s">
         <v>17</v>
@@ -9117,7 +9117,7 @@
         <v>3157</v>
       </c>
       <c r="D314" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F314" t="s">
         <v>17</v>
@@ -9153,7 +9153,7 @@
         <v>3158</v>
       </c>
       <c r="D316" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F316" t="s">
         <v>17</v>
@@ -9182,7 +9182,7 @@
         <v>3164</v>
       </c>
       <c r="D317" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F317" t="s">
         <v>17</v>
@@ -9211,7 +9211,7 @@
         <v>3160</v>
       </c>
       <c r="D318" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F318" t="s">
         <v>17</v>
@@ -9276,7 +9276,7 @@
         <v>3153</v>
       </c>
       <c r="D321" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F321" t="s">
         <v>17</v>
@@ -9312,7 +9312,7 @@
         <v>3159</v>
       </c>
       <c r="D323" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F323" t="s">
         <v>17</v>
@@ -9341,7 +9341,7 @@
         <v>3150</v>
       </c>
       <c r="D324" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F324" t="s">
         <v>17</v>
@@ -9377,7 +9377,7 @@
         <v>3155</v>
       </c>
       <c r="D326" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F326" t="s">
         <v>17</v>
@@ -9587,7 +9587,7 @@
         <v>3163</v>
       </c>
       <c r="D334" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F334" t="s">
         <v>22</v>
@@ -9616,7 +9616,7 @@
         <v>3149</v>
       </c>
       <c r="D335" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F335" t="s">
         <v>22</v>
@@ -9645,7 +9645,7 @@
         <v>3151</v>
       </c>
       <c r="D336" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F336" t="s">
         <v>22</v>
@@ -9674,7 +9674,7 @@
         <v>3148</v>
       </c>
       <c r="D337" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F337" t="s">
         <v>22</v>
@@ -9703,7 +9703,7 @@
         <v>3209</v>
       </c>
       <c r="D338" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F338" t="s">
         <v>22</v>
@@ -9732,7 +9732,7 @@
         <v>3194</v>
       </c>
       <c r="D339" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F339" t="s">
         <v>22</v>
@@ -9761,7 +9761,7 @@
         <v>3147</v>
       </c>
       <c r="D340" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F340" t="s">
         <v>22</v>
@@ -9790,7 +9790,7 @@
         <v>3156</v>
       </c>
       <c r="D341" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F341" t="s">
         <v>22</v>
@@ -9819,7 +9819,7 @@
         <v>3157</v>
       </c>
       <c r="D342" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F342" t="s">
         <v>22</v>
@@ -9848,7 +9848,7 @@
         <v>3158</v>
       </c>
       <c r="D343" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F343" t="s">
         <v>22</v>
@@ -9877,7 +9877,7 @@
         <v>3429</v>
       </c>
       <c r="D344" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F344" t="s">
         <v>22</v>
@@ -9906,7 +9906,7 @@
         <v>3160</v>
       </c>
       <c r="D345" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F345" t="s">
         <v>22</v>
@@ -9964,7 +9964,7 @@
         <v>3153</v>
       </c>
       <c r="D347" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F347" t="s">
         <v>22</v>
@@ -9993,7 +9993,7 @@
         <v>3159</v>
       </c>
       <c r="D348" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F348" t="s">
         <v>22</v>
@@ -10022,7 +10022,7 @@
         <v>3150</v>
       </c>
       <c r="D349" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F349" t="s">
         <v>22</v>
@@ -10058,7 +10058,7 @@
         <v>3155</v>
       </c>
       <c r="D351" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F351" t="s">
         <v>22</v>
@@ -10087,7 +10087,7 @@
         <v>3164</v>
       </c>
       <c r="D352" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F352" t="s">
         <v>22</v>
@@ -10145,10 +10145,10 @@
         <v>3209</v>
       </c>
       <c r="D354" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F354" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G354" t="s">
         <v>13</v>
@@ -10290,7 +10290,7 @@
         <v>3149</v>
       </c>
       <c r="D359" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F359" t="s">
         <v>23</v>
@@ -10319,7 +10319,7 @@
         <v>3151</v>
       </c>
       <c r="D360" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F360" t="s">
         <v>23</v>
@@ -10348,7 +10348,7 @@
         <v>3148</v>
       </c>
       <c r="D361" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F361" t="s">
         <v>23</v>
@@ -10377,7 +10377,7 @@
         <v>3163</v>
       </c>
       <c r="D362" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F362" t="s">
         <v>23</v>
@@ -10413,7 +10413,7 @@
         <v>3194</v>
       </c>
       <c r="D364" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F364" t="s">
         <v>23</v>
@@ -10449,7 +10449,7 @@
         <v>3147</v>
       </c>
       <c r="D366" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F366" t="s">
         <v>23</v>
@@ -10478,7 +10478,7 @@
         <v>3156</v>
       </c>
       <c r="D367" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F367" t="s">
         <v>23</v>
@@ -10507,7 +10507,7 @@
         <v>3157</v>
       </c>
       <c r="D368" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F368" t="s">
         <v>23</v>
@@ -10543,7 +10543,7 @@
         <v>3158</v>
       </c>
       <c r="D370" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F370" t="s">
         <v>23</v>
@@ -10572,7 +10572,7 @@
         <v>3429</v>
       </c>
       <c r="D371" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F371" t="s">
         <v>23</v>
@@ -10601,7 +10601,7 @@
         <v>3160</v>
       </c>
       <c r="D372" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F372" t="s">
         <v>23</v>
@@ -10688,7 +10688,7 @@
         <v>3153</v>
       </c>
       <c r="D375" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F375" t="s">
         <v>23</v>
@@ -10717,7 +10717,7 @@
         <v>3159</v>
       </c>
       <c r="D376" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F376" t="s">
         <v>23</v>
@@ -10746,7 +10746,7 @@
         <v>3150</v>
       </c>
       <c r="D377" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F377" t="s">
         <v>23</v>
@@ -10775,7 +10775,7 @@
         <v>3155</v>
       </c>
       <c r="D378" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F378" t="s">
         <v>23</v>
@@ -10804,7 +10804,7 @@
         <v>3164</v>
       </c>
       <c r="D379" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F379" t="s">
         <v>23</v>
@@ -10862,7 +10862,7 @@
         <v>3162</v>
       </c>
       <c r="D381" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F381" t="s">
         <v>23</v>
@@ -11036,7 +11036,7 @@
         <v>3149</v>
       </c>
       <c r="D387" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F387" t="s">
         <v>20</v>
@@ -11065,7 +11065,7 @@
         <v>3151</v>
       </c>
       <c r="D388" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F388" t="s">
         <v>20</v>
@@ -11094,7 +11094,7 @@
         <v>3148</v>
       </c>
       <c r="D389" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F389" t="s">
         <v>20</v>
@@ -11123,7 +11123,7 @@
         <v>3163</v>
       </c>
       <c r="D390" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F390" t="s">
         <v>20</v>
@@ -11159,7 +11159,7 @@
         <v>3194</v>
       </c>
       <c r="D392" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F392" t="s">
         <v>20</v>
@@ -11195,7 +11195,7 @@
         <v>3162</v>
       </c>
       <c r="D394" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F394" t="s">
         <v>20</v>
@@ -11224,7 +11224,7 @@
         <v>3147</v>
       </c>
       <c r="D395" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F395" t="s">
         <v>20</v>
@@ -11253,7 +11253,7 @@
         <v>3156</v>
       </c>
       <c r="D396" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F396" t="s">
         <v>20</v>
@@ -11282,7 +11282,7 @@
         <v>3157</v>
       </c>
       <c r="D397" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F397" t="s">
         <v>20</v>
@@ -11318,7 +11318,7 @@
         <v>3158</v>
       </c>
       <c r="D399" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F399" t="s">
         <v>20</v>
@@ -11347,7 +11347,7 @@
         <v>3160</v>
       </c>
       <c r="D400" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F400" t="s">
         <v>20</v>
@@ -11376,7 +11376,7 @@
         <v>3153</v>
       </c>
       <c r="D401" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F401" t="s">
         <v>20</v>
@@ -11405,7 +11405,7 @@
         <v>3159</v>
       </c>
       <c r="D402" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F402" t="s">
         <v>20</v>
@@ -11434,7 +11434,7 @@
         <v>3150</v>
       </c>
       <c r="D403" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F403" t="s">
         <v>20</v>
@@ -11463,7 +11463,7 @@
         <v>3155</v>
       </c>
       <c r="D404" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F404" t="s">
         <v>20</v>
@@ -11492,7 +11492,7 @@
         <v>3164</v>
       </c>
       <c r="D405" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F405" t="s">
         <v>20</v>
@@ -11550,10 +11550,10 @@
         <v>3160</v>
       </c>
       <c r="D407" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F407" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G407" t="s">
         <v>12</v>
@@ -11589,7 +11589,7 @@
         <v>34</v>
       </c>
       <c r="F409" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G409" t="s">
         <v>13</v>
@@ -11618,7 +11618,7 @@
         <v>35</v>
       </c>
       <c r="F410" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G410" t="s">
         <v>12</v>
@@ -11651,10 +11651,10 @@
         <v>3429</v>
       </c>
       <c r="D412" t="s">
+        <v>52</v>
+      </c>
+      <c r="F412" t="s">
         <v>53</v>
-      </c>
-      <c r="F412" t="s">
-        <v>54</v>
       </c>
       <c r="G412" t="s">
         <v>12</v>
@@ -11690,7 +11690,7 @@
         <v>31</v>
       </c>
       <c r="F414" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G414" t="s">
         <v>12</v>
@@ -11726,7 +11726,7 @@
         <v>32</v>
       </c>
       <c r="F416" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G416" t="s">
         <v>12</v>
@@ -11762,7 +11762,7 @@
         <v>33</v>
       </c>
       <c r="F418" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G418" t="s">
         <v>12</v>
@@ -11795,10 +11795,10 @@
         <v>3149</v>
       </c>
       <c r="D420" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F420" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G420" t="s">
         <v>13</v>
@@ -11824,10 +11824,10 @@
         <v>3151</v>
       </c>
       <c r="D421" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F421" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G421" t="s">
         <v>13</v>
@@ -11853,10 +11853,10 @@
         <v>3148</v>
       </c>
       <c r="D422" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F422" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G422" t="s">
         <v>13</v>
@@ -11882,10 +11882,10 @@
         <v>3164</v>
       </c>
       <c r="D423" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F423" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G423" t="s">
         <v>12</v>
@@ -11918,10 +11918,10 @@
         <v>3163</v>
       </c>
       <c r="D425" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F425" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G425" t="s">
         <v>12</v>
@@ -11954,10 +11954,10 @@
         <v>3194</v>
       </c>
       <c r="D427" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F427" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G427" t="s">
         <v>12</v>
@@ -11990,10 +11990,10 @@
         <v>3162</v>
       </c>
       <c r="D429" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F429" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G429" t="s">
         <v>12</v>
@@ -12026,10 +12026,10 @@
         <v>3147</v>
       </c>
       <c r="D431" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F431" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G431" t="s">
         <v>12</v>
@@ -12062,10 +12062,10 @@
         <v>3156</v>
       </c>
       <c r="D433" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F433" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G433" t="s">
         <v>12</v>
@@ -12098,10 +12098,10 @@
         <v>3157</v>
       </c>
       <c r="D435" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F435" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G435" t="s">
         <v>12</v>
@@ -12134,10 +12134,10 @@
         <v>3158</v>
       </c>
       <c r="D437" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F437" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G437" t="s">
         <v>12</v>
@@ -12170,10 +12170,10 @@
         <v>3159</v>
       </c>
       <c r="D439" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G439" t="s">
         <v>12</v>
@@ -12206,10 +12206,10 @@
         <v>3150</v>
       </c>
       <c r="D441" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F441" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G441" t="s">
         <v>12</v>
@@ -12242,10 +12242,10 @@
         <v>3155</v>
       </c>
       <c r="D443" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F443" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G443" t="s">
         <v>12</v>
@@ -12281,7 +12281,7 @@
         <v>30</v>
       </c>
       <c r="F445" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G445" t="s">
         <v>12</v>
@@ -12314,10 +12314,10 @@
         <v>3153</v>
       </c>
       <c r="D447" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F447" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G447" t="s">
         <v>13</v>
@@ -12343,10 +12343,10 @@
         <v>3160</v>
       </c>
       <c r="D448" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F448" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G448" t="s">
         <v>10</v>
@@ -12375,7 +12375,7 @@
         <v>34</v>
       </c>
       <c r="F449" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G449" t="s">
         <v>13</v>
@@ -12404,7 +12404,7 @@
         <v>35</v>
       </c>
       <c r="F450" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G450" t="s">
         <v>10</v>
@@ -12430,10 +12430,10 @@
         <v>3429</v>
       </c>
       <c r="D451" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F451" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G451" t="s">
         <v>10</v>
@@ -12462,7 +12462,7 @@
         <v>31</v>
       </c>
       <c r="F452" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G452" t="s">
         <v>10</v>
@@ -12491,7 +12491,7 @@
         <v>32</v>
       </c>
       <c r="F453" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G453" t="s">
         <v>10</v>
@@ -12520,7 +12520,7 @@
         <v>33</v>
       </c>
       <c r="F454" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G454" t="s">
         <v>10</v>
@@ -12546,10 +12546,10 @@
         <v>3149</v>
       </c>
       <c r="D455" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F455" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G455" t="s">
         <v>13</v>
@@ -12575,10 +12575,10 @@
         <v>3151</v>
       </c>
       <c r="D456" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F456" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G456" t="s">
         <v>13</v>
@@ -12604,10 +12604,10 @@
         <v>3148</v>
       </c>
       <c r="D457" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F457" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G457" t="s">
         <v>13</v>
@@ -12633,10 +12633,10 @@
         <v>3164</v>
       </c>
       <c r="D458" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F458" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G458" t="s">
         <v>10</v>
@@ -12662,10 +12662,10 @@
         <v>3163</v>
       </c>
       <c r="D459" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F459" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G459" t="s">
         <v>10</v>
@@ -12691,10 +12691,10 @@
         <v>3194</v>
       </c>
       <c r="D460" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F460" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G460" t="s">
         <v>13</v>
@@ -12720,10 +12720,10 @@
         <v>3162</v>
       </c>
       <c r="D461" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F461" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G461" t="s">
         <v>14</v>
@@ -12756,10 +12756,10 @@
         <v>3147</v>
       </c>
       <c r="D463" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F463" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G463" t="s">
         <v>10</v>
@@ -12785,10 +12785,10 @@
         <v>3156</v>
       </c>
       <c r="D464" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F464" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G464" t="s">
         <v>10</v>
@@ -12814,10 +12814,10 @@
         <v>3157</v>
       </c>
       <c r="D465" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F465" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G465" t="s">
         <v>14</v>
@@ -12850,10 +12850,10 @@
         <v>3158</v>
       </c>
       <c r="D467" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F467" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G467" t="s">
         <v>10</v>
@@ -12879,10 +12879,10 @@
         <v>3159</v>
       </c>
       <c r="D468" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F468" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G468" t="s">
         <v>10</v>
@@ -12908,10 +12908,10 @@
         <v>3150</v>
       </c>
       <c r="D469" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F469" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G469" t="s">
         <v>10</v>
@@ -12937,10 +12937,10 @@
         <v>3155</v>
       </c>
       <c r="D470" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F470" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G470" t="s">
         <v>10</v>
@@ -12969,7 +12969,7 @@
         <v>30</v>
       </c>
       <c r="F471" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G471" t="s">
         <v>10</v>
@@ -12995,10 +12995,10 @@
         <v>3153</v>
       </c>
       <c r="D472" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F472" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G472" t="s">
         <v>13</v>
@@ -13024,7 +13024,7 @@
         <v>3158</v>
       </c>
       <c r="D473" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F473" t="s">
         <v>15</v>
@@ -13075,7 +13075,7 @@
         <v>46146.722916666666</v>
       </c>
       <c r="J475">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K475" t="s">
         <v>11</v>
@@ -13118,7 +13118,7 @@
         <v>3429</v>
       </c>
       <c r="D477" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F477" t="s">
         <v>18</v>
@@ -13147,7 +13147,7 @@
         <v>3160</v>
       </c>
       <c r="D478" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F478" t="s">
         <v>18</v>
@@ -13270,7 +13270,7 @@
         <v>3151</v>
       </c>
       <c r="D483" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F483" t="s">
         <v>18</v>
@@ -13285,7 +13285,7 @@
         <v>46146.726388888892</v>
       </c>
       <c r="J483">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K483" t="s">
         <v>11</v>
@@ -13299,7 +13299,7 @@
         <v>3148</v>
       </c>
       <c r="D484" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F484" t="s">
         <v>18</v>
@@ -13314,7 +13314,7 @@
         <v>46146.726388888892</v>
       </c>
       <c r="J484">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K484" t="s">
         <v>11</v>
@@ -13328,22 +13328,22 @@
         <v>3164</v>
       </c>
       <c r="D485" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F485" t="s">
         <v>18</v>
       </c>
       <c r="G485" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H485" s="2">
-        <v>0</v>
+        <v>2.8912037037037038E-2</v>
       </c>
       <c r="I485" s="1">
         <v>46146.727083333331</v>
       </c>
       <c r="J485">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K485" t="s">
         <v>11</v>
@@ -13357,7 +13357,7 @@
         <v>3163</v>
       </c>
       <c r="D486" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>18</v>
@@ -13393,7 +13393,7 @@
         <v>3194</v>
       </c>
       <c r="D488" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F488" t="s">
         <v>18</v>
@@ -13429,7 +13429,7 @@
         <v>3162</v>
       </c>
       <c r="D490" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F490" t="s">
         <v>18</v>
@@ -13444,7 +13444,7 @@
         <v>46146.728472222225</v>
       </c>
       <c r="J490">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K490" t="s">
         <v>11</v>
@@ -13458,7 +13458,7 @@
         <v>3147</v>
       </c>
       <c r="D491" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F491" t="s">
         <v>18</v>
@@ -13487,7 +13487,7 @@
         <v>3156</v>
       </c>
       <c r="D492" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F492" t="s">
         <v>18</v>
@@ -13516,7 +13516,7 @@
         <v>3157</v>
       </c>
       <c r="D493" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F493" t="s">
         <v>18</v>
@@ -13552,7 +13552,7 @@
         <v>3158</v>
       </c>
       <c r="D495" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F495" t="s">
         <v>18</v>
@@ -13581,7 +13581,7 @@
         <v>3149</v>
       </c>
       <c r="D496" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F496" t="s">
         <v>18</v>
@@ -13596,7 +13596,7 @@
         <v>46146.731249999997</v>
       </c>
       <c r="J496">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K496" t="s">
         <v>11</v>
@@ -13610,7 +13610,7 @@
         <v>3159</v>
       </c>
       <c r="D497" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F497" t="s">
         <v>18</v>
@@ -13639,7 +13639,7 @@
         <v>3150</v>
       </c>
       <c r="D498" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F498" t="s">
         <v>18</v>
@@ -13668,7 +13668,7 @@
         <v>3155</v>
       </c>
       <c r="D499" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F499" t="s">
         <v>18</v>
@@ -13726,7 +13726,7 @@
         <v>3153</v>
       </c>
       <c r="D501" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F501" t="s">
         <v>18</v>
@@ -13741,7 +13741,7 @@
         <v>46146.710532407407</v>
       </c>
       <c r="J501">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K501" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07D0AD9A-1F97-4B7B-A8AF-08406A58C1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0644FB20-0310-41D1-9F8A-FC4952459B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14101,7 +14101,7 @@
         <v>46176.425578703704</v>
       </c>
       <c r="J509">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K509" t="s">
         <v>11</v>
@@ -14246,7 +14246,7 @@
         <v>46176.42696759259</v>
       </c>
       <c r="J514">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K514" t="s">
         <v>11</v>
@@ -14275,7 +14275,7 @@
         <v>46176.42696759259</v>
       </c>
       <c r="J515">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K515" t="s">
         <v>11</v>
@@ -14295,16 +14295,16 @@
         <v>25</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H516" s="2">
-        <v>0</v>
+        <v>6.6203703703703702E-3</v>
       </c>
       <c r="I516" s="1">
         <v>46176.42696759259</v>
       </c>
       <c r="J516">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K516" t="s">
         <v>11</v>
@@ -14362,7 +14362,7 @@
         <v>46176.427662037036</v>
       </c>
       <c r="J518">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K518" t="s">
         <v>11</v>
@@ -14449,7 +14449,7 @@
         <v>46176.428356481483</v>
       </c>
       <c r="J521">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K521" t="s">
         <v>11</v>
@@ -14507,7 +14507,7 @@
         <v>46176.429050925923</v>
       </c>
       <c r="J523">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K523" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{591EA4AD-EB86-46F0-AE82-80D5FC6CEBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A02D01BC-9E41-41CF-AF62-EB297534CDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -104,6 +104,9 @@
     <t>Alert Driving</t>
   </si>
   <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
@@ -119,28 +122,28 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Driver Health</t>
+    <t>Camera Event Management (Onboarding)</t>
   </si>
   <si>
-    <t>Vehicle &amp; Roadside Inspections CMV</t>
+    <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>Jon Stanley</t>
+    <t>Webinar Behavior Change-Supervisors</t>
   </si>
   <si>
-    <t>Scene of an Accident</t>
-  </si>
-  <si>
-    <t>Camera Event Management (Onboarding)</t>
+    <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
     <t>(Spanish) Rules for Safe Driving</t>
   </si>
   <si>
     <t>Big Wins Through Behavior Change</t>
+  </si>
+  <si>
+    <t>Jon Stanley</t>
   </si>
   <si>
     <t>PCS Trucking</t>
@@ -210,9 +213,6 @@
   </si>
   <si>
     <t>Ben Peppenger</t>
-  </si>
-  <si>
-    <t>Webinar Behavior Change-Supervisors</t>
   </si>
 </sst>
 </file>
@@ -586,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -635,16 +635,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>3143</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -664,16 +664,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>3154</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>13</v>
@@ -693,16 +693,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>3144</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -722,16 +722,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>3145</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -751,16 +751,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>3152</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -780,16 +780,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>3146</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -809,16 +809,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>3148</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -838,16 +838,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>3163</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>3150</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -896,16 +896,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11">
         <v>3151</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -925,16 +925,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>3149</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -954,16 +954,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13">
         <v>3153</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -983,16 +983,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14">
         <v>3162</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -1012,16 +1012,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15">
         <v>3164</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>13</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16">
         <v>3194</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>13</v>
@@ -1070,16 +1070,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>3155</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>13</v>
@@ -1099,16 +1099,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>3147</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1128,16 +1128,16 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>3156</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1157,16 +1157,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>3157</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -1186,16 +1186,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>3158</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
@@ -1215,16 +1215,16 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22">
         <v>3159</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -1244,16 +1244,16 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23">
         <v>3160</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1273,16 +1273,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <v>3161</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>13</v>
@@ -1302,13 +1302,13 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25">
         <v>3143</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -1331,13 +1331,13 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26">
         <v>3154</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27">
         <v>3144</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -1389,13 +1389,13 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28">
         <v>3145</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -1418,13 +1418,13 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29">
         <v>3152</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30">
         <v>3146</v>
       </c>
       <c r="F30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -1476,13 +1476,13 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E31">
         <v>3148</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -1505,13 +1505,13 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32">
         <v>3163</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -1534,13 +1534,13 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E33">
         <v>3150</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -1563,13 +1563,13 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34">
         <v>3151</v>
       </c>
       <c r="F34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -1592,13 +1592,13 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E35">
         <v>3149</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36">
         <v>3153</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -1650,13 +1650,13 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>3162</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -1679,13 +1679,13 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E38">
         <v>3164</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -1708,13 +1708,13 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>3194</v>
       </c>
       <c r="F39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -1737,13 +1737,13 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40">
         <v>3155</v>
       </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -1766,13 +1766,13 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E41">
         <v>3147</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -1795,13 +1795,13 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E42">
         <v>3156</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -1824,13 +1824,13 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E43">
         <v>3157</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -1853,13 +1853,13 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E44">
         <v>3158</v>
       </c>
       <c r="F44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E45">
         <v>3159</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E46">
         <v>3160</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E47">
         <v>3161</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -1969,16 +1969,16 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E48">
         <v>3209</v>
       </c>
       <c r="F48" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>13</v>
@@ -1998,16 +1998,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E49">
         <v>3194</v>
       </c>
       <c r="F49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -2027,16 +2027,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E50">
         <v>3194</v>
       </c>
       <c r="F50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -2056,16 +2056,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E51">
         <v>3143</v>
       </c>
       <c r="F51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2085,16 +2085,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E52">
         <v>3154</v>
       </c>
       <c r="F52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E53">
         <v>3144</v>
       </c>
       <c r="F53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -2143,16 +2143,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E54">
         <v>3145</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2172,16 +2172,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E55">
         <v>3152</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2201,16 +2201,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E56">
         <v>3146</v>
       </c>
       <c r="F56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2230,16 +2230,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E57">
         <v>3148</v>
       </c>
       <c r="F57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2259,16 +2259,16 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E58">
         <v>3163</v>
       </c>
       <c r="F58" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2288,16 +2288,16 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E59">
         <v>3150</v>
       </c>
       <c r="F59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2317,16 +2317,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E60">
         <v>3151</v>
       </c>
       <c r="F60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2346,16 +2346,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E61">
         <v>3149</v>
       </c>
       <c r="F61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>12</v>
@@ -2379,21 +2379,21 @@
       <c r="J62" s="2"/>
       <c r="K62" s="1"/>
       <c r="M62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E63">
         <v>3153</v>
       </c>
       <c r="F63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2413,16 +2413,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E64">
         <v>3209</v>
       </c>
       <c r="F64" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2442,16 +2442,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E65">
         <v>3162</v>
       </c>
       <c r="F65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2471,16 +2471,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E66">
         <v>3164</v>
       </c>
       <c r="F66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2500,16 +2500,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E67">
         <v>3194</v>
       </c>
       <c r="F67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>12</v>
@@ -2533,21 +2533,21 @@
       <c r="J68" s="2"/>
       <c r="K68" s="1"/>
       <c r="M68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E69">
         <v>3155</v>
       </c>
       <c r="F69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2567,16 +2567,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E70">
         <v>3147</v>
       </c>
       <c r="F70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2596,16 +2596,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E71">
         <v>3156</v>
       </c>
       <c r="F71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2625,16 +2625,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E72">
         <v>3157</v>
       </c>
       <c r="F72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E73">
         <v>3158</v>
       </c>
       <c r="F73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2683,16 +2683,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E74">
         <v>3159</v>
       </c>
       <c r="F74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E75">
         <v>3160</v>
       </c>
       <c r="F75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>10</v>
@@ -2741,16 +2741,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E76">
         <v>3161</v>
       </c>
       <c r="F76" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2770,13 +2770,13 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E77">
         <v>3143</v>
       </c>
       <c r="F77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>19</v>
@@ -2799,13 +2799,13 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E78">
         <v>3154</v>
       </c>
       <c r="F78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>19</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E79">
         <v>3144</v>
       </c>
       <c r="F79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>19</v>
@@ -2857,13 +2857,13 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E80">
         <v>3145</v>
       </c>
       <c r="F80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>19</v>
@@ -2886,13 +2886,13 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E81">
         <v>3152</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>19</v>
@@ -2915,13 +2915,13 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E82">
         <v>3146</v>
       </c>
       <c r="F82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>19</v>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E83">
         <v>3148</v>
       </c>
       <c r="F83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>19</v>
@@ -2977,18 +2977,18 @@
       <c r="J84" s="2"/>
       <c r="K84" s="1"/>
       <c r="M84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E85">
         <v>3163</v>
       </c>
       <c r="F85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>19</v>
@@ -3015,18 +3015,18 @@
       <c r="J86" s="2"/>
       <c r="K86" s="1"/>
       <c r="M86" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E87">
         <v>3150</v>
       </c>
       <c r="F87" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>19</v>
@@ -3049,13 +3049,13 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E88">
         <v>3151</v>
       </c>
       <c r="F88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>19</v>
@@ -3078,13 +3078,13 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E89">
         <v>3149</v>
       </c>
       <c r="F89" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>19</v>
@@ -3111,18 +3111,18 @@
       <c r="J90" s="2"/>
       <c r="K90" s="1"/>
       <c r="M90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E91">
         <v>3153</v>
       </c>
       <c r="F91" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>19</v>
@@ -3145,13 +3145,13 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E92">
         <v>3209</v>
       </c>
       <c r="F92" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>19</v>
@@ -3174,13 +3174,13 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E93">
         <v>3162</v>
       </c>
       <c r="F93" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>19</v>
@@ -3203,13 +3203,13 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E94">
         <v>3164</v>
       </c>
       <c r="F94" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>19</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E95">
         <v>3194</v>
       </c>
       <c r="F95" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>19</v>
@@ -3261,13 +3261,13 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E96">
         <v>3155</v>
       </c>
       <c r="F96" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>19</v>
@@ -3294,18 +3294,18 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E98">
         <v>3147</v>
       </c>
       <c r="F98" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>19</v>
@@ -3328,13 +3328,13 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E99">
         <v>3156</v>
       </c>
       <c r="F99" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>19</v>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E100">
         <v>3157</v>
       </c>
       <c r="F100" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>19</v>
@@ -3386,13 +3386,13 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E101">
         <v>3158</v>
       </c>
       <c r="F101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>19</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E102">
         <v>3159</v>
       </c>
       <c r="F102" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>19</v>
@@ -3444,13 +3444,13 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E103">
         <v>3160</v>
       </c>
       <c r="F103" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>19</v>
@@ -3477,18 +3477,18 @@
       <c r="J104" s="2"/>
       <c r="K104" s="1"/>
       <c r="M104" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E105">
         <v>3161</v>
       </c>
       <c r="F105" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>19</v>
@@ -3511,16 +3511,16 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E106">
         <v>3143</v>
       </c>
       <c r="F106" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3540,16 +3540,16 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E107">
         <v>3154</v>
       </c>
       <c r="F107" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3569,16 +3569,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E108">
         <v>3144</v>
       </c>
       <c r="F108" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3598,16 +3598,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E109">
         <v>3145</v>
       </c>
       <c r="F109" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3627,16 +3627,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E110">
         <v>3152</v>
       </c>
       <c r="F110" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>13</v>
@@ -3656,16 +3656,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E111">
         <v>3155</v>
       </c>
       <c r="F111" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3685,16 +3685,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E112">
         <v>3148</v>
       </c>
       <c r="F112" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>13</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E113">
         <v>3163</v>
       </c>
       <c r="F113" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3743,16 +3743,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E114">
         <v>3149</v>
       </c>
       <c r="F114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -3772,16 +3772,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E115">
         <v>3150</v>
       </c>
       <c r="F115" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3801,16 +3801,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E116">
         <v>3151</v>
       </c>
       <c r="F116" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3830,16 +3830,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E117">
         <v>3146</v>
       </c>
       <c r="F117" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>13</v>
@@ -3859,16 +3859,16 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E118">
         <v>3153</v>
       </c>
       <c r="F118" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>13</v>
@@ -3888,16 +3888,16 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E119">
         <v>3209</v>
       </c>
       <c r="F119" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>12</v>
@@ -3921,21 +3921,21 @@
       <c r="J120" s="2"/>
       <c r="K120" s="1"/>
       <c r="M120" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E121">
         <v>3162</v>
       </c>
       <c r="F121" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3955,16 +3955,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E122">
         <v>3164</v>
       </c>
       <c r="F122" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3984,16 +3984,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E123">
         <v>3194</v>
       </c>
       <c r="F123" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -4013,16 +4013,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E124">
         <v>3429</v>
       </c>
       <c r="F124" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4042,16 +4042,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E125">
         <v>3147</v>
       </c>
       <c r="F125" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4071,16 +4071,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E126">
         <v>3156</v>
       </c>
       <c r="F126" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4100,16 +4100,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E127">
         <v>3157</v>
       </c>
       <c r="F127" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>10</v>
@@ -4129,16 +4129,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E128">
         <v>3158</v>
       </c>
       <c r="F128" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>10</v>
@@ -4158,16 +4158,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E129">
         <v>3160</v>
       </c>
       <c r="F129" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4187,16 +4187,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E130">
         <v>3159</v>
       </c>
       <c r="F130" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>10</v>
@@ -4216,16 +4216,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E131">
         <v>3161</v>
       </c>
       <c r="F131" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>12</v>
@@ -4249,18 +4249,18 @@
       <c r="J132" s="2"/>
       <c r="K132" s="1"/>
       <c r="M132" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E133">
         <v>3143</v>
       </c>
       <c r="F133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -4283,13 +4283,13 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E134">
         <v>3154</v>
       </c>
       <c r="F134" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E135">
         <v>3144</v>
       </c>
       <c r="F135" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -4341,13 +4341,13 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E136">
         <v>3145</v>
       </c>
       <c r="F136" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -4370,13 +4370,13 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E137">
         <v>3152</v>
       </c>
       <c r="F137" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -4399,13 +4399,13 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E138">
         <v>3155</v>
       </c>
       <c r="F138" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -4428,13 +4428,13 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E139">
         <v>3148</v>
       </c>
       <c r="F139" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -4457,13 +4457,13 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E140">
         <v>3163</v>
       </c>
       <c r="F140" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -4486,13 +4486,13 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E141">
         <v>3149</v>
       </c>
       <c r="F141" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -4519,18 +4519,18 @@
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
       <c r="M142" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E143">
         <v>3150</v>
       </c>
       <c r="F143" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -4553,13 +4553,13 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E144">
         <v>3151</v>
       </c>
       <c r="F144" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -4582,13 +4582,13 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E145">
         <v>3146</v>
       </c>
       <c r="F145" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -4611,13 +4611,13 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E146">
         <v>3153</v>
       </c>
       <c r="F146" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -4640,13 +4640,13 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E147">
         <v>3209</v>
       </c>
       <c r="F147" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -4669,13 +4669,13 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E148">
         <v>3162</v>
       </c>
       <c r="F148" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -4698,13 +4698,13 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E149">
         <v>3194</v>
       </c>
       <c r="F149" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -4731,18 +4731,18 @@
       <c r="J150" s="2"/>
       <c r="K150" s="1"/>
       <c r="M150" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E151">
         <v>3429</v>
       </c>
       <c r="F151" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -4765,13 +4765,13 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E152">
         <v>3147</v>
       </c>
       <c r="F152" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -4794,13 +4794,13 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E153">
         <v>3156</v>
       </c>
       <c r="F153" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -4823,13 +4823,13 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E154">
         <v>3157</v>
       </c>
       <c r="F154" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -4852,13 +4852,13 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E155">
         <v>3158</v>
       </c>
       <c r="F155" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -4881,13 +4881,13 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E156">
         <v>3160</v>
       </c>
       <c r="F156" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -4910,13 +4910,13 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E157">
         <v>3159</v>
       </c>
       <c r="F157" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -4939,13 +4939,13 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E158">
         <v>3161</v>
       </c>
       <c r="F158" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -4968,13 +4968,13 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E159">
         <v>3164</v>
       </c>
       <c r="F159" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -4997,13 +4997,13 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E160">
         <v>3154</v>
       </c>
       <c r="F160" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>20</v>
@@ -5026,13 +5026,13 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E161">
         <v>3144</v>
       </c>
       <c r="F161" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>20</v>
@@ -5055,13 +5055,13 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E162">
         <v>3145</v>
       </c>
       <c r="F162" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>20</v>
@@ -5084,13 +5084,13 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E163">
         <v>3152</v>
       </c>
       <c r="F163" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>20</v>
@@ -5113,13 +5113,13 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E164">
         <v>3148</v>
       </c>
       <c r="F164" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>20</v>
@@ -5142,13 +5142,13 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E165">
         <v>3163</v>
       </c>
       <c r="F165" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>20</v>
@@ -5171,13 +5171,13 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E166">
         <v>3149</v>
       </c>
       <c r="F166" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>20</v>
@@ -5200,13 +5200,13 @@
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E167">
         <v>3150</v>
       </c>
       <c r="F167" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>20</v>
@@ -5229,13 +5229,13 @@
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E168">
         <v>3151</v>
       </c>
       <c r="F168" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>20</v>
@@ -5258,13 +5258,13 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E169">
         <v>3155</v>
       </c>
       <c r="F169" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>20</v>
@@ -5287,13 +5287,13 @@
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E170">
         <v>3209</v>
       </c>
       <c r="F170" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>20</v>
@@ -5316,13 +5316,13 @@
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D171" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E171">
         <v>3194</v>
       </c>
       <c r="F171" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>20</v>
@@ -5349,18 +5349,18 @@
       <c r="J172" s="2"/>
       <c r="K172" s="1"/>
       <c r="M172" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E173">
         <v>3429</v>
       </c>
       <c r="F173" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>20</v>
@@ -5383,13 +5383,13 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E174">
         <v>3147</v>
       </c>
       <c r="F174" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>20</v>
@@ -5412,13 +5412,13 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E175">
         <v>3156</v>
       </c>
       <c r="F175" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>20</v>
@@ -5441,13 +5441,13 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E176">
         <v>3157</v>
       </c>
       <c r="F176" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>20</v>
@@ -5474,18 +5474,18 @@
       <c r="J177" s="2"/>
       <c r="K177" s="1"/>
       <c r="M177" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E178">
         <v>3158</v>
       </c>
       <c r="F178" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>20</v>
@@ -5508,13 +5508,13 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E179">
         <v>3146</v>
       </c>
       <c r="F179" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>20</v>
@@ -5537,13 +5537,13 @@
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D180" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E180">
         <v>3160</v>
       </c>
       <c r="F180" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>20</v>
@@ -5566,13 +5566,13 @@
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E181">
         <v>3162</v>
       </c>
       <c r="F181" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>20</v>
@@ -5595,13 +5595,13 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E182">
         <v>3153</v>
       </c>
       <c r="F182" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>20</v>
@@ -5624,13 +5624,13 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E183">
         <v>3159</v>
       </c>
       <c r="F183" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>20</v>
@@ -5653,13 +5653,13 @@
     </row>
     <row r="184" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E184">
         <v>3143</v>
       </c>
       <c r="F184" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>20</v>
@@ -5682,13 +5682,13 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E185">
         <v>3161</v>
       </c>
       <c r="F185" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>20</v>
@@ -5711,13 +5711,13 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E186">
         <v>3164</v>
       </c>
       <c r="F186" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>20</v>
@@ -5740,16 +5740,16 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E187">
         <v>3146</v>
       </c>
       <c r="F187" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5769,16 +5769,16 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E188">
         <v>3154</v>
       </c>
       <c r="F188" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>10</v>
@@ -5798,16 +5798,16 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E189">
         <v>3144</v>
       </c>
       <c r="F189" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5827,16 +5827,16 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E190">
         <v>3145</v>
       </c>
       <c r="F190" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5856,16 +5856,16 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E191">
         <v>3152</v>
       </c>
       <c r="F191" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5885,16 +5885,16 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E192">
         <v>3148</v>
       </c>
       <c r="F192" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5914,16 +5914,16 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E193">
         <v>3163</v>
       </c>
       <c r="F193" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5943,16 +5943,16 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E194">
         <v>3149</v>
       </c>
       <c r="F194" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>13</v>
@@ -5972,16 +5972,16 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E195">
         <v>3150</v>
       </c>
       <c r="F195" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -6001,16 +6001,16 @@
     </row>
     <row r="196" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E196">
         <v>3151</v>
       </c>
       <c r="F196" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -6030,16 +6030,16 @@
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E197">
         <v>3155</v>
       </c>
       <c r="F197" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -6059,16 +6059,16 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E198">
         <v>3209</v>
       </c>
       <c r="F198" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>12</v>
@@ -6092,21 +6092,21 @@
       <c r="J199" s="2"/>
       <c r="K199" s="1"/>
       <c r="M199" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E200">
         <v>3194</v>
       </c>
       <c r="F200" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>12</v>
@@ -6130,21 +6130,21 @@
       <c r="J201" s="2"/>
       <c r="K201" s="1"/>
       <c r="M201" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E202">
         <v>3429</v>
       </c>
       <c r="F202" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>12</v>
@@ -6168,21 +6168,21 @@
       <c r="J203" s="2"/>
       <c r="K203" s="1"/>
       <c r="M203" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E204">
         <v>3147</v>
       </c>
       <c r="F204" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6202,16 +6202,16 @@
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D205" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E205">
         <v>3156</v>
       </c>
       <c r="F205" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -6231,16 +6231,16 @@
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D206" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E206">
         <v>3157</v>
       </c>
       <c r="F206" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>14</v>
@@ -6264,21 +6264,21 @@
       <c r="J207" s="2"/>
       <c r="K207" s="1"/>
       <c r="M207" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D208" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E208">
         <v>3158</v>
       </c>
       <c r="F208" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6298,16 +6298,16 @@
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D209" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E209">
         <v>3162</v>
       </c>
       <c r="F209" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6327,16 +6327,16 @@
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D210" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E210">
         <v>3160</v>
       </c>
       <c r="F210" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6356,16 +6356,16 @@
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D211" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E211">
         <v>3153</v>
       </c>
       <c r="F211" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6385,16 +6385,16 @@
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D212" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E212">
         <v>3159</v>
       </c>
       <c r="F212" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6414,16 +6414,16 @@
     </row>
     <row r="213" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D213" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E213">
         <v>3143</v>
       </c>
       <c r="F213" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6443,16 +6443,16 @@
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D214" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E214">
         <v>3161</v>
       </c>
       <c r="F214" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6472,16 +6472,16 @@
     </row>
     <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E215">
         <v>3164</v>
       </c>
       <c r="F215" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>13</v>
@@ -6501,16 +6501,16 @@
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E216">
         <v>3146</v>
       </c>
       <c r="F216" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6530,16 +6530,16 @@
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E217">
         <v>3154</v>
       </c>
       <c r="F217" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6559,16 +6559,16 @@
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E218">
         <v>3144</v>
       </c>
       <c r="F218" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6588,16 +6588,16 @@
     </row>
     <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E219">
         <v>3145</v>
       </c>
       <c r="F219" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>10</v>
@@ -6617,16 +6617,16 @@
     </row>
     <row r="220" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D220" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E220">
         <v>3152</v>
       </c>
       <c r="F220" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6646,16 +6646,16 @@
     </row>
     <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D221" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E221">
         <v>3148</v>
       </c>
       <c r="F221" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>13</v>
@@ -6675,16 +6675,16 @@
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D222" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E222">
         <v>3163</v>
       </c>
       <c r="F222" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6704,16 +6704,16 @@
     </row>
     <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D223" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E223">
         <v>3149</v>
       </c>
       <c r="F223" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>10</v>
@@ -6733,16 +6733,16 @@
     </row>
     <row r="224" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D224" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E224">
         <v>3150</v>
       </c>
       <c r="F224" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6762,16 +6762,16 @@
     </row>
     <row r="225" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D225" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E225">
         <v>3151</v>
       </c>
       <c r="F225" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>10</v>
@@ -6791,16 +6791,16 @@
     </row>
     <row r="226" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D226" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E226">
         <v>3155</v>
       </c>
       <c r="F226" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>10</v>
@@ -6820,16 +6820,16 @@
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E227">
         <v>3209</v>
       </c>
       <c r="F227" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6849,16 +6849,16 @@
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D228" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E228">
         <v>3194</v>
       </c>
       <c r="F228" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -6878,16 +6878,16 @@
     </row>
     <row r="229" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D229" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E229">
         <v>3429</v>
       </c>
       <c r="F229" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6907,16 +6907,16 @@
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D230" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E230">
         <v>3147</v>
       </c>
       <c r="F230" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -6936,16 +6936,16 @@
     </row>
     <row r="231" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D231" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E231">
         <v>3156</v>
       </c>
       <c r="F231" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -6965,16 +6965,16 @@
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D232" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E232">
         <v>3157</v>
       </c>
       <c r="F232" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -6994,16 +6994,16 @@
     </row>
     <row r="233" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D233" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E233">
         <v>3158</v>
       </c>
       <c r="F233" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>10</v>
@@ -7023,16 +7023,16 @@
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E234">
         <v>3162</v>
       </c>
       <c r="F234" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7052,16 +7052,16 @@
     </row>
     <row r="235" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E235">
         <v>3160</v>
       </c>
       <c r="F235" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -7081,16 +7081,16 @@
     </row>
     <row r="236" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E236">
         <v>3153</v>
       </c>
       <c r="F236" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7110,16 +7110,16 @@
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E237">
         <v>3159</v>
       </c>
       <c r="F237" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7139,16 +7139,16 @@
     </row>
     <row r="238" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E238">
         <v>3143</v>
       </c>
       <c r="F238" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -7168,16 +7168,16 @@
     </row>
     <row r="239" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D239" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E239">
         <v>3161</v>
       </c>
       <c r="F239" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7197,16 +7197,16 @@
     </row>
     <row r="240" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D240" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E240">
         <v>3164</v>
       </c>
       <c r="F240" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7226,13 +7226,13 @@
     </row>
     <row r="241" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D241" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E241">
         <v>3146</v>
       </c>
       <c r="F241" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>18</v>
@@ -7255,13 +7255,13 @@
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D242" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E242">
         <v>3154</v>
       </c>
       <c r="F242" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>18</v>
@@ -7284,13 +7284,13 @@
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D243" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E243">
         <v>3144</v>
       </c>
       <c r="F243" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>18</v>
@@ -7313,13 +7313,13 @@
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D244" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E244">
         <v>3145</v>
       </c>
       <c r="F244" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>18</v>
@@ -7342,13 +7342,13 @@
     </row>
     <row r="245" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D245" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E245">
         <v>3152</v>
       </c>
       <c r="F245" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>18</v>
@@ -7371,13 +7371,13 @@
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D246" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E246">
         <v>3148</v>
       </c>
       <c r="F246" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>18</v>
@@ -7400,13 +7400,13 @@
     </row>
     <row r="247" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D247" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E247">
         <v>3163</v>
       </c>
       <c r="F247" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>18</v>
@@ -7429,13 +7429,13 @@
     </row>
     <row r="248" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D248" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E248">
         <v>3149</v>
       </c>
       <c r="F248" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>18</v>
@@ -7458,13 +7458,13 @@
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D249" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E249">
         <v>3155</v>
       </c>
       <c r="F249" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>18</v>
@@ -7487,13 +7487,13 @@
     </row>
     <row r="250" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D250" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E250">
         <v>3150</v>
       </c>
       <c r="F250" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>18</v>
@@ -7516,13 +7516,13 @@
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D251" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E251">
         <v>3151</v>
       </c>
       <c r="F251" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>18</v>
@@ -7545,13 +7545,13 @@
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D252" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E252">
         <v>3209</v>
       </c>
       <c r="F252" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>18</v>
@@ -7574,13 +7574,13 @@
     </row>
     <row r="253" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D253" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E253">
         <v>3194</v>
       </c>
       <c r="F253" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>18</v>
@@ -7603,13 +7603,13 @@
     </row>
     <row r="254" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D254" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E254">
         <v>3429</v>
       </c>
       <c r="F254" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>18</v>
@@ -7632,13 +7632,13 @@
     </row>
     <row r="255" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D255" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E255">
         <v>3147</v>
       </c>
       <c r="F255" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>18</v>
@@ -7661,13 +7661,13 @@
     </row>
     <row r="256" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D256" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E256">
         <v>3156</v>
       </c>
       <c r="F256" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>18</v>
@@ -7690,13 +7690,13 @@
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D257" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E257">
         <v>3157</v>
       </c>
       <c r="F257" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>18</v>
@@ -7723,18 +7723,18 @@
       <c r="J258" s="2"/>
       <c r="K258" s="1"/>
       <c r="M258" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D259" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E259">
         <v>3158</v>
       </c>
       <c r="F259" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>18</v>
@@ -7757,13 +7757,13 @@
     </row>
     <row r="260" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D260" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E260">
         <v>3162</v>
       </c>
       <c r="F260" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>18</v>
@@ -7786,13 +7786,13 @@
     </row>
     <row r="261" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D261" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E261">
         <v>3164</v>
       </c>
       <c r="F261" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>18</v>
@@ -7815,13 +7815,13 @@
     </row>
     <row r="262" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D262" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E262">
         <v>3160</v>
       </c>
       <c r="F262" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>18</v>
@@ -7848,18 +7848,18 @@
       <c r="J263" s="2"/>
       <c r="K263" s="1"/>
       <c r="M263" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D264" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E264">
         <v>3161</v>
       </c>
       <c r="F264" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>18</v>
@@ -7882,13 +7882,13 @@
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D265" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E265">
         <v>3153</v>
       </c>
       <c r="F265" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>18</v>
@@ -7911,13 +7911,13 @@
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D266" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E266">
         <v>3159</v>
       </c>
       <c r="F266" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>18</v>
@@ -7940,13 +7940,13 @@
     </row>
     <row r="267" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D267" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E267">
         <v>3143</v>
       </c>
       <c r="F267" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>18</v>
@@ -7973,18 +7973,18 @@
       <c r="J268" s="2"/>
       <c r="K268" s="1"/>
       <c r="M268" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D269" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E269">
         <v>3146</v>
       </c>
       <c r="F269" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>16</v>
@@ -8007,13 +8007,13 @@
     </row>
     <row r="270" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D270" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E270">
         <v>3154</v>
       </c>
       <c r="F270" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>16</v>
@@ -8036,13 +8036,13 @@
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D271" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E271">
         <v>3144</v>
       </c>
       <c r="F271" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>16</v>
@@ -8065,13 +8065,13 @@
     </row>
     <row r="272" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D272" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E272">
         <v>3145</v>
       </c>
       <c r="F272" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>16</v>
@@ -8094,13 +8094,13 @@
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D273" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E273">
         <v>3152</v>
       </c>
       <c r="F273" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>16</v>
@@ -8123,13 +8123,13 @@
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D274" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E274">
         <v>3163</v>
       </c>
       <c r="F274" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>16</v>
@@ -8152,13 +8152,13 @@
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D275" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E275">
         <v>3149</v>
       </c>
       <c r="F275" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>16</v>
@@ -8181,13 +8181,13 @@
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D276" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E276">
         <v>3151</v>
       </c>
       <c r="F276" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>16</v>
@@ -8210,13 +8210,13 @@
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D277" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E277">
         <v>3209</v>
       </c>
       <c r="F277" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>16</v>
@@ -8239,13 +8239,13 @@
     </row>
     <row r="278" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D278" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E278">
         <v>3194</v>
       </c>
       <c r="F278" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>16</v>
@@ -8268,13 +8268,13 @@
     </row>
     <row r="279" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D279" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E279">
         <v>3429</v>
       </c>
       <c r="F279" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>16</v>
@@ -8297,13 +8297,13 @@
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D280" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E280">
         <v>3147</v>
       </c>
       <c r="F280" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>16</v>
@@ -8326,13 +8326,13 @@
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D281" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E281">
         <v>3156</v>
       </c>
       <c r="F281" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>16</v>
@@ -8355,13 +8355,13 @@
     </row>
     <row r="282" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D282" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E282">
         <v>3157</v>
       </c>
       <c r="F282" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>16</v>
@@ -8388,18 +8388,18 @@
       <c r="J283" s="2"/>
       <c r="K283" s="1"/>
       <c r="M283" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D284" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E284">
         <v>3158</v>
       </c>
       <c r="F284" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>16</v>
@@ -8422,13 +8422,13 @@
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D285" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E285">
         <v>3148</v>
       </c>
       <c r="F285" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>16</v>
@@ -8451,13 +8451,13 @@
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D286" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E286">
         <v>3162</v>
       </c>
       <c r="F286" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>16</v>
@@ -8480,13 +8480,13 @@
     </row>
     <row r="287" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D287" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E287">
         <v>3164</v>
       </c>
       <c r="F287" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>16</v>
@@ -8509,13 +8509,13 @@
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D288" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E288">
         <v>3160</v>
       </c>
       <c r="F288" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>16</v>
@@ -8538,13 +8538,13 @@
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D289" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E289">
         <v>3161</v>
       </c>
       <c r="F289" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>16</v>
@@ -8567,13 +8567,13 @@
     </row>
     <row r="290" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D290" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E290">
         <v>3153</v>
       </c>
       <c r="F290" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>16</v>
@@ -8596,13 +8596,13 @@
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D291" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E291">
         <v>3159</v>
       </c>
       <c r="F291" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>16</v>
@@ -8625,13 +8625,13 @@
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D292" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E292">
         <v>3150</v>
       </c>
       <c r="F292" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>16</v>
@@ -8654,13 +8654,13 @@
     </row>
     <row r="293" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D293" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E293">
         <v>3155</v>
       </c>
       <c r="F293" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>16</v>
@@ -8687,18 +8687,18 @@
       <c r="J294" s="2"/>
       <c r="K294" s="1"/>
       <c r="M294" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D295" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E295">
         <v>3143</v>
       </c>
       <c r="F295" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>16</v>
@@ -8721,13 +8721,13 @@
     </row>
     <row r="296" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D296" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E296">
         <v>3146</v>
       </c>
       <c r="F296" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>17</v>
@@ -8750,13 +8750,13 @@
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D297" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E297">
         <v>3154</v>
       </c>
       <c r="F297" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>17</v>
@@ -8779,13 +8779,13 @@
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D298" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E298">
         <v>3144</v>
       </c>
       <c r="F298" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>17</v>
@@ -8812,18 +8812,18 @@
       <c r="J299" s="2"/>
       <c r="K299" s="1"/>
       <c r="M299" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D300" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E300">
         <v>3145</v>
       </c>
       <c r="F300" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>17</v>
@@ -8846,13 +8846,13 @@
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D301" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E301">
         <v>3152</v>
       </c>
       <c r="F301" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>17</v>
@@ -8875,13 +8875,13 @@
     </row>
     <row r="302" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D302" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E302">
         <v>3163</v>
       </c>
       <c r="F302" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>17</v>
@@ -8904,13 +8904,13 @@
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D303" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E303">
         <v>3149</v>
       </c>
       <c r="F303" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>17</v>
@@ -8937,18 +8937,18 @@
       <c r="J304" s="2"/>
       <c r="K304" s="1"/>
       <c r="M304" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D305" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E305">
         <v>3151</v>
       </c>
       <c r="F305" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>17</v>
@@ -8971,13 +8971,13 @@
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D306" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E306">
         <v>3148</v>
       </c>
       <c r="F306" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>17</v>
@@ -9000,13 +9000,13 @@
     </row>
     <row r="307" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D307" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E307">
         <v>3209</v>
       </c>
       <c r="F307" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>17</v>
@@ -9029,13 +9029,13 @@
     </row>
     <row r="308" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D308" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E308">
         <v>3194</v>
       </c>
       <c r="F308" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>17</v>
@@ -9062,18 +9062,18 @@
       <c r="J309" s="2"/>
       <c r="K309" s="1"/>
       <c r="M309" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D310" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E310">
         <v>3429</v>
       </c>
       <c r="F310" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>17</v>
@@ -9096,13 +9096,13 @@
     </row>
     <row r="311" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D311" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E311">
         <v>3147</v>
       </c>
       <c r="F311" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>17</v>
@@ -9125,13 +9125,13 @@
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D312" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E312">
         <v>3156</v>
       </c>
       <c r="F312" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>17</v>
@@ -9158,18 +9158,18 @@
       <c r="J313" s="2"/>
       <c r="K313" s="1"/>
       <c r="M313" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D314" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E314">
         <v>3157</v>
       </c>
       <c r="F314" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>17</v>
@@ -9196,18 +9196,18 @@
       <c r="J315" s="2"/>
       <c r="K315" s="1"/>
       <c r="M315" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D316" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E316">
         <v>3158</v>
       </c>
       <c r="F316" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>17</v>
@@ -9230,13 +9230,13 @@
     </row>
     <row r="317" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D317" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E317">
         <v>3164</v>
       </c>
       <c r="F317" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>17</v>
@@ -9259,13 +9259,13 @@
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D318" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E318">
         <v>3160</v>
       </c>
       <c r="F318" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>17</v>
@@ -9292,18 +9292,18 @@
       <c r="J319" s="2"/>
       <c r="K319" s="1"/>
       <c r="M319" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="320" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D320" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E320">
         <v>3161</v>
       </c>
       <c r="F320" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>17</v>
@@ -9326,13 +9326,13 @@
     </row>
     <row r="321" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D321" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E321">
         <v>3153</v>
       </c>
       <c r="F321" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>17</v>
@@ -9359,18 +9359,18 @@
       <c r="J322" s="2"/>
       <c r="K322" s="1"/>
       <c r="M322" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="323" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D323" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E323">
         <v>3159</v>
       </c>
       <c r="F323" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>17</v>
@@ -9393,13 +9393,13 @@
     </row>
     <row r="324" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D324" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E324">
         <v>3150</v>
       </c>
       <c r="F324" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>17</v>
@@ -9426,18 +9426,18 @@
       <c r="J325" s="2"/>
       <c r="K325" s="1"/>
       <c r="M325" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D326" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E326">
         <v>3155</v>
       </c>
       <c r="F326" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>17</v>
@@ -9464,18 +9464,18 @@
       <c r="J327" s="2"/>
       <c r="K327" s="1"/>
       <c r="M327" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D328" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E328">
         <v>3143</v>
       </c>
       <c r="F328" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>17</v>
@@ -9498,16 +9498,16 @@
     </row>
     <row r="329" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D329" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E329">
         <v>3146</v>
       </c>
       <c r="F329" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9527,16 +9527,16 @@
     </row>
     <row r="330" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D330" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E330">
         <v>3154</v>
       </c>
       <c r="F330" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9556,16 +9556,16 @@
     </row>
     <row r="331" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D331" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E331">
         <v>3144</v>
       </c>
       <c r="F331" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9585,16 +9585,16 @@
     </row>
     <row r="332" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D332" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E332">
         <v>3145</v>
       </c>
       <c r="F332" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>10</v>
@@ -9614,16 +9614,16 @@
     </row>
     <row r="333" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D333" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E333">
         <v>3152</v>
       </c>
       <c r="F333" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -9643,16 +9643,16 @@
     </row>
     <row r="334" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D334" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E334">
         <v>3163</v>
       </c>
       <c r="F334" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -9672,16 +9672,16 @@
     </row>
     <row r="335" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D335" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E335">
         <v>3149</v>
       </c>
       <c r="F335" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>10</v>
@@ -9701,16 +9701,16 @@
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D336" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E336">
         <v>3151</v>
       </c>
       <c r="F336" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>13</v>
@@ -9730,16 +9730,16 @@
     </row>
     <row r="337" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D337" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E337">
         <v>3148</v>
       </c>
       <c r="F337" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -9759,16 +9759,16 @@
     </row>
     <row r="338" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D338" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E338">
         <v>3209</v>
       </c>
       <c r="F338" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9788,16 +9788,16 @@
     </row>
     <row r="339" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D339" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E339">
         <v>3194</v>
       </c>
       <c r="F339" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9817,16 +9817,16 @@
     </row>
     <row r="340" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D340" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E340">
         <v>3147</v>
       </c>
       <c r="F340" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -9846,16 +9846,16 @@
     </row>
     <row r="341" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D341" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E341">
         <v>3156</v>
       </c>
       <c r="F341" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>10</v>
@@ -9875,16 +9875,16 @@
     </row>
     <row r="342" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D342" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E342">
         <v>3157</v>
       </c>
       <c r="F342" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -9904,16 +9904,16 @@
     </row>
     <row r="343" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D343" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E343">
         <v>3158</v>
       </c>
       <c r="F343" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9933,16 +9933,16 @@
     </row>
     <row r="344" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D344" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E344">
         <v>3429</v>
       </c>
       <c r="F344" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>13</v>
@@ -9962,16 +9962,16 @@
     </row>
     <row r="345" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D345" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E345">
         <v>3160</v>
       </c>
       <c r="F345" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -9991,16 +9991,16 @@
     </row>
     <row r="346" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D346" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E346">
         <v>3161</v>
       </c>
       <c r="F346" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10020,16 +10020,16 @@
     </row>
     <row r="347" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D347" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E347">
         <v>3153</v>
       </c>
       <c r="F347" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -10049,16 +10049,16 @@
     </row>
     <row r="348" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D348" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E348">
         <v>3159</v>
       </c>
       <c r="F348" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10078,16 +10078,16 @@
     </row>
     <row r="349" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D349" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E349">
         <v>3150</v>
       </c>
       <c r="F349" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>14</v>
@@ -10111,21 +10111,21 @@
       <c r="J350" s="2"/>
       <c r="K350" s="1"/>
       <c r="M350" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D351" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E351">
         <v>3155</v>
       </c>
       <c r="F351" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>10</v>
@@ -10145,16 +10145,16 @@
     </row>
     <row r="352" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D352" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E352">
         <v>3164</v>
       </c>
       <c r="F352" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>10</v>
@@ -10174,16 +10174,16 @@
     </row>
     <row r="353" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D353" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E353">
         <v>3143</v>
       </c>
       <c r="F353" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>10</v>
@@ -10203,13 +10203,13 @@
     </row>
     <row r="354" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D354" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E354">
         <v>3209</v>
       </c>
       <c r="F354" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>33</v>
@@ -10232,16 +10232,16 @@
     </row>
     <row r="355" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D355" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E355">
         <v>3146</v>
       </c>
       <c r="F355" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10261,16 +10261,16 @@
     </row>
     <row r="356" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D356" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E356">
         <v>3154</v>
       </c>
       <c r="F356" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10290,16 +10290,16 @@
     </row>
     <row r="357" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D357" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E357">
         <v>3144</v>
       </c>
       <c r="F357" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>10</v>
@@ -10319,16 +10319,16 @@
     </row>
     <row r="358" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D358" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E358">
         <v>3145</v>
       </c>
       <c r="F358" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>10</v>
@@ -10348,16 +10348,16 @@
     </row>
     <row r="359" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D359" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E359">
         <v>3149</v>
       </c>
       <c r="F359" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>10</v>
@@ -10377,16 +10377,16 @@
     </row>
     <row r="360" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D360" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E360">
         <v>3151</v>
       </c>
       <c r="F360" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>13</v>
@@ -10406,16 +10406,16 @@
     </row>
     <row r="361" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D361" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E361">
         <v>3148</v>
       </c>
       <c r="F361" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>13</v>
@@ -10435,16 +10435,16 @@
     </row>
     <row r="362" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D362" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E362">
         <v>3163</v>
       </c>
       <c r="F362" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>14</v>
@@ -10468,21 +10468,21 @@
       <c r="J363" s="2"/>
       <c r="K363" s="1"/>
       <c r="M363" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="364" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D364" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E364">
         <v>3194</v>
       </c>
       <c r="F364" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>12</v>
@@ -10506,21 +10506,21 @@
       <c r="J365" s="2"/>
       <c r="K365" s="1"/>
       <c r="M365" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="366" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D366" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E366">
         <v>3147</v>
       </c>
       <c r="F366" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>10</v>
@@ -10540,16 +10540,16 @@
     </row>
     <row r="367" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D367" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E367">
         <v>3156</v>
       </c>
       <c r="F367" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>10</v>
@@ -10569,16 +10569,16 @@
     </row>
     <row r="368" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D368" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E368">
         <v>3157</v>
       </c>
       <c r="F368" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>14</v>
@@ -10602,21 +10602,21 @@
       <c r="J369" s="2"/>
       <c r="K369" s="1"/>
       <c r="M369" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="370" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D370" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E370">
         <v>3158</v>
       </c>
       <c r="F370" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>10</v>
@@ -10636,16 +10636,16 @@
     </row>
     <row r="371" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D371" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E371">
         <v>3429</v>
       </c>
       <c r="F371" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>13</v>
@@ -10665,16 +10665,16 @@
     </row>
     <row r="372" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D372" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E372">
         <v>3160</v>
       </c>
       <c r="F372" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>13</v>
@@ -10694,16 +10694,16 @@
     </row>
     <row r="373" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D373" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E373">
         <v>3161</v>
       </c>
       <c r="F373" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>13</v>
@@ -10723,16 +10723,16 @@
     </row>
     <row r="374" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D374" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E374">
         <v>3152</v>
       </c>
       <c r="F374" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>13</v>
@@ -10752,16 +10752,16 @@
     </row>
     <row r="375" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D375" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E375">
         <v>3153</v>
       </c>
       <c r="F375" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -10781,16 +10781,16 @@
     </row>
     <row r="376" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D376" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E376">
         <v>3159</v>
       </c>
       <c r="F376" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -10810,16 +10810,16 @@
     </row>
     <row r="377" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D377" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E377">
         <v>3150</v>
       </c>
       <c r="F377" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>10</v>
@@ -10839,16 +10839,16 @@
     </row>
     <row r="378" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D378" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E378">
         <v>3155</v>
       </c>
       <c r="F378" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -10868,16 +10868,16 @@
     </row>
     <row r="379" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D379" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E379">
         <v>3164</v>
       </c>
       <c r="F379" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>10</v>
@@ -10897,16 +10897,16 @@
     </row>
     <row r="380" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D380" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E380">
         <v>3143</v>
       </c>
       <c r="F380" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -10926,16 +10926,16 @@
     </row>
     <row r="381" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D381" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E381">
         <v>3162</v>
       </c>
       <c r="F381" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>10</v>
@@ -10955,16 +10955,16 @@
     </row>
     <row r="382" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D382" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E382">
         <v>3161</v>
       </c>
       <c r="F382" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>13</v>
@@ -10984,16 +10984,16 @@
     </row>
     <row r="383" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D383" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E383">
         <v>3146</v>
       </c>
       <c r="F383" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>10</v>
@@ -11013,16 +11013,16 @@
     </row>
     <row r="384" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D384" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E384">
         <v>3154</v>
       </c>
       <c r="F384" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>10</v>
@@ -11042,16 +11042,16 @@
     </row>
     <row r="385" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D385" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E385">
         <v>3144</v>
       </c>
       <c r="F385" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>10</v>
@@ -11071,16 +11071,16 @@
     </row>
     <row r="386" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D386" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E386">
         <v>3145</v>
       </c>
       <c r="F386" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>10</v>
@@ -11100,16 +11100,16 @@
     </row>
     <row r="387" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D387" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E387">
         <v>3149</v>
       </c>
       <c r="F387" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>13</v>
@@ -11129,16 +11129,16 @@
     </row>
     <row r="388" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D388" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E388">
         <v>3151</v>
       </c>
       <c r="F388" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>13</v>
@@ -11158,16 +11158,16 @@
     </row>
     <row r="389" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D389" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E389">
         <v>3148</v>
       </c>
       <c r="F389" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>13</v>
@@ -11187,16 +11187,16 @@
     </row>
     <row r="390" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D390" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E390">
         <v>3163</v>
       </c>
       <c r="F390" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>12</v>
@@ -11220,21 +11220,21 @@
       <c r="J391" s="2"/>
       <c r="K391" s="1"/>
       <c r="M391" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="392" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D392" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E392">
         <v>3194</v>
       </c>
       <c r="F392" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>12</v>
@@ -11258,21 +11258,21 @@
       <c r="J393" s="2"/>
       <c r="K393" s="1"/>
       <c r="M393" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="394" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D394" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E394">
         <v>3162</v>
       </c>
       <c r="F394" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>10</v>
@@ -11292,16 +11292,16 @@
     </row>
     <row r="395" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D395" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E395">
         <v>3147</v>
       </c>
       <c r="F395" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>10</v>
@@ -11321,16 +11321,16 @@
     </row>
     <row r="396" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D396" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E396">
         <v>3156</v>
       </c>
       <c r="F396" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>10</v>
@@ -11350,16 +11350,16 @@
     </row>
     <row r="397" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D397" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E397">
         <v>3157</v>
       </c>
       <c r="F397" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>14</v>
@@ -11383,21 +11383,21 @@
       <c r="J398" s="2"/>
       <c r="K398" s="1"/>
       <c r="M398" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="399" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D399" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E399">
         <v>3158</v>
       </c>
       <c r="F399" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>10</v>
@@ -11417,16 +11417,16 @@
     </row>
     <row r="400" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D400" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E400">
         <v>3160</v>
       </c>
       <c r="F400" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>13</v>
@@ -11446,16 +11446,16 @@
     </row>
     <row r="401" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D401" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E401">
         <v>3153</v>
       </c>
       <c r="F401" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>10</v>
@@ -11475,16 +11475,16 @@
     </row>
     <row r="402" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D402" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E402">
         <v>3159</v>
       </c>
       <c r="F402" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>10</v>
@@ -11504,16 +11504,16 @@
     </row>
     <row r="403" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D403" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E403">
         <v>3150</v>
       </c>
       <c r="F403" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>10</v>
@@ -11533,16 +11533,16 @@
     </row>
     <row r="404" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D404" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E404">
         <v>3155</v>
       </c>
       <c r="F404" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>10</v>
@@ -11562,16 +11562,16 @@
     </row>
     <row r="405" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D405" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E405">
         <v>3164</v>
       </c>
       <c r="F405" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>10</v>
@@ -11591,16 +11591,16 @@
     </row>
     <row r="406" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D406" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E406">
         <v>3143</v>
       </c>
       <c r="F406" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>10</v>
@@ -11620,13 +11620,13 @@
     </row>
     <row r="407" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D407" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E407">
         <v>3160</v>
       </c>
       <c r="F407" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H407" s="2" t="s">
         <v>32</v>
@@ -11653,18 +11653,18 @@
       <c r="J408" s="2"/>
       <c r="K408" s="1"/>
       <c r="M408" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="409" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D409" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E409">
         <v>3161</v>
       </c>
       <c r="F409" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H409" s="2" t="s">
         <v>32</v>
@@ -11687,13 +11687,13 @@
     </row>
     <row r="410" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D410" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E410">
         <v>3146</v>
       </c>
       <c r="F410" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H410" s="2" t="s">
         <v>32</v>
@@ -11720,18 +11720,18 @@
       <c r="J411" s="2"/>
       <c r="K411" s="1"/>
       <c r="M411" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D412" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E412">
         <v>3429</v>
       </c>
       <c r="F412" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H412" s="2" t="s">
         <v>32</v>
@@ -11758,18 +11758,18 @@
       <c r="J413" s="2"/>
       <c r="K413" s="1"/>
       <c r="M413" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="414" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D414" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E414">
         <v>3154</v>
       </c>
       <c r="F414" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H414" s="2" t="s">
         <v>32</v>
@@ -11796,18 +11796,18 @@
       <c r="J415" s="2"/>
       <c r="K415" s="1"/>
       <c r="M415" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="416" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D416" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E416">
         <v>3144</v>
       </c>
       <c r="F416" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H416" s="2" t="s">
         <v>32</v>
@@ -11834,18 +11834,18 @@
       <c r="J417" s="2"/>
       <c r="K417" s="1"/>
       <c r="M417" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="418" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D418" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E418">
         <v>3145</v>
       </c>
       <c r="F418" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H418" s="2" t="s">
         <v>32</v>
@@ -11872,18 +11872,18 @@
       <c r="J419" s="2"/>
       <c r="K419" s="1"/>
       <c r="M419" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="420" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D420" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E420">
         <v>3149</v>
       </c>
       <c r="F420" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H420" s="2" t="s">
         <v>32</v>
@@ -11906,13 +11906,13 @@
     </row>
     <row r="421" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D421" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E421">
         <v>3151</v>
       </c>
       <c r="F421" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H421" s="2" t="s">
         <v>32</v>
@@ -11935,13 +11935,13 @@
     </row>
     <row r="422" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D422" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E422">
         <v>3148</v>
       </c>
       <c r="F422" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H422" s="2" t="s">
         <v>32</v>
@@ -11964,13 +11964,13 @@
     </row>
     <row r="423" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D423" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E423">
         <v>3164</v>
       </c>
       <c r="F423" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H423" s="2" t="s">
         <v>32</v>
@@ -11997,18 +11997,18 @@
       <c r="J424" s="2"/>
       <c r="K424" s="1"/>
       <c r="M424" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="425" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D425" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E425">
         <v>3163</v>
       </c>
       <c r="F425" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H425" s="2" t="s">
         <v>32</v>
@@ -12035,18 +12035,18 @@
       <c r="J426" s="2"/>
       <c r="K426" s="1"/>
       <c r="M426" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="427" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D427" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E427">
         <v>3194</v>
       </c>
       <c r="F427" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H427" s="2" t="s">
         <v>32</v>
@@ -12073,18 +12073,18 @@
       <c r="J428" s="2"/>
       <c r="K428" s="1"/>
       <c r="M428" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="429" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D429" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E429">
         <v>3162</v>
       </c>
       <c r="F429" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H429" s="2" t="s">
         <v>32</v>
@@ -12111,18 +12111,18 @@
       <c r="J430" s="2"/>
       <c r="K430" s="1"/>
       <c r="M430" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="431" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D431" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E431">
         <v>3147</v>
       </c>
       <c r="F431" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H431" s="2" t="s">
         <v>32</v>
@@ -12149,18 +12149,18 @@
       <c r="J432" s="2"/>
       <c r="K432" s="1"/>
       <c r="M432" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="433" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D433" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E433">
         <v>3156</v>
       </c>
       <c r="F433" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H433" s="2" t="s">
         <v>32</v>
@@ -12187,18 +12187,18 @@
       <c r="J434" s="2"/>
       <c r="K434" s="1"/>
       <c r="M434" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="435" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D435" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E435">
         <v>3157</v>
       </c>
       <c r="F435" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H435" s="2" t="s">
         <v>32</v>
@@ -12225,18 +12225,18 @@
       <c r="J436" s="2"/>
       <c r="K436" s="1"/>
       <c r="M436" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="437" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D437" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E437">
         <v>3158</v>
       </c>
       <c r="F437" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H437" s="2" t="s">
         <v>32</v>
@@ -12263,18 +12263,18 @@
       <c r="J438" s="2"/>
       <c r="K438" s="1"/>
       <c r="M438" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="439" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D439" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E439">
         <v>3159</v>
       </c>
       <c r="F439" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H439" s="2" t="s">
         <v>32</v>
@@ -12301,18 +12301,18 @@
       <c r="J440" s="2"/>
       <c r="K440" s="1"/>
       <c r="M440" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="441" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D441" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E441">
         <v>3150</v>
       </c>
       <c r="F441" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H441" s="2" t="s">
         <v>32</v>
@@ -12339,18 +12339,18 @@
       <c r="J442" s="2"/>
       <c r="K442" s="1"/>
       <c r="M442" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="443" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D443" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E443">
         <v>3155</v>
       </c>
       <c r="F443" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H443" s="2" t="s">
         <v>32</v>
@@ -12377,18 +12377,18 @@
       <c r="J444" s="2"/>
       <c r="K444" s="1"/>
       <c r="M444" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="445" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D445" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E445">
         <v>3143</v>
       </c>
       <c r="F445" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H445" s="2" t="s">
         <v>32</v>
@@ -12415,18 +12415,18 @@
       <c r="J446" s="2"/>
       <c r="K446" s="1"/>
       <c r="M446" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="447" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D447" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E447">
         <v>3153</v>
       </c>
       <c r="F447" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H447" s="2" t="s">
         <v>32</v>
@@ -12449,16 +12449,16 @@
     </row>
     <row r="448" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D448" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E448">
         <v>3160</v>
       </c>
       <c r="F448" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>10</v>
@@ -12478,16 +12478,16 @@
     </row>
     <row r="449" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D449" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E449">
         <v>3161</v>
       </c>
       <c r="F449" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H449" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I449" s="1" t="s">
         <v>13</v>
@@ -12507,16 +12507,16 @@
     </row>
     <row r="450" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D450" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E450">
         <v>3146</v>
       </c>
       <c r="F450" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>10</v>
@@ -12536,16 +12536,16 @@
     </row>
     <row r="451" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D451" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E451">
         <v>3429</v>
       </c>
       <c r="F451" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>10</v>
@@ -12565,16 +12565,16 @@
     </row>
     <row r="452" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D452" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E452">
         <v>3154</v>
       </c>
       <c r="F452" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>10</v>
@@ -12594,16 +12594,16 @@
     </row>
     <row r="453" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D453" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E453">
         <v>3144</v>
       </c>
       <c r="F453" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>10</v>
@@ -12623,16 +12623,16 @@
     </row>
     <row r="454" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D454" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E454">
         <v>3145</v>
       </c>
       <c r="F454" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>10</v>
@@ -12652,16 +12652,16 @@
     </row>
     <row r="455" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D455" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E455">
         <v>3149</v>
       </c>
       <c r="F455" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>13</v>
@@ -12681,16 +12681,16 @@
     </row>
     <row r="456" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D456" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E456">
         <v>3151</v>
       </c>
       <c r="F456" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -12710,16 +12710,16 @@
     </row>
     <row r="457" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D457" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E457">
         <v>3148</v>
       </c>
       <c r="F457" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>13</v>
@@ -12739,16 +12739,16 @@
     </row>
     <row r="458" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D458" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E458">
         <v>3164</v>
       </c>
       <c r="F458" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>10</v>
@@ -12768,16 +12768,16 @@
     </row>
     <row r="459" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D459" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E459">
         <v>3163</v>
       </c>
       <c r="F459" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>10</v>
@@ -12797,16 +12797,16 @@
     </row>
     <row r="460" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D460" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E460">
         <v>3194</v>
       </c>
       <c r="F460" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -12826,16 +12826,16 @@
     </row>
     <row r="461" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D461" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E461">
         <v>3162</v>
       </c>
       <c r="F461" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>14</v>
@@ -12859,21 +12859,21 @@
       <c r="J462" s="2"/>
       <c r="K462" s="1"/>
       <c r="M462" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="463" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D463" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E463">
         <v>3147</v>
       </c>
       <c r="F463" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>10</v>
@@ -12893,16 +12893,16 @@
     </row>
     <row r="464" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D464" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E464">
         <v>3156</v>
       </c>
       <c r="F464" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>10</v>
@@ -12922,16 +12922,16 @@
     </row>
     <row r="465" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D465" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E465">
         <v>3157</v>
       </c>
       <c r="F465" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>14</v>
@@ -12955,21 +12955,21 @@
       <c r="J466" s="2"/>
       <c r="K466" s="1"/>
       <c r="M466" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="467" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D467" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E467">
         <v>3158</v>
       </c>
       <c r="F467" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>10</v>
@@ -12989,16 +12989,16 @@
     </row>
     <row r="468" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D468" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E468">
         <v>3159</v>
       </c>
       <c r="F468" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>10</v>
@@ -13018,16 +13018,16 @@
     </row>
     <row r="469" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D469" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E469">
         <v>3150</v>
       </c>
       <c r="F469" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>10</v>
@@ -13047,16 +13047,16 @@
     </row>
     <row r="470" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D470" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E470">
         <v>3155</v>
       </c>
       <c r="F470" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -13076,16 +13076,16 @@
     </row>
     <row r="471" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D471" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E471">
         <v>3143</v>
       </c>
       <c r="F471" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>10</v>
@@ -13105,16 +13105,16 @@
     </row>
     <row r="472" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D472" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E472">
         <v>3153</v>
       </c>
       <c r="F472" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>13</v>
@@ -13134,13 +13134,13 @@
     </row>
     <row r="473" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D473" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E473">
         <v>3158</v>
       </c>
       <c r="F473" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H473" s="2" t="s">
         <v>15</v>
@@ -13167,18 +13167,18 @@
       <c r="J474" s="2"/>
       <c r="K474" s="1"/>
       <c r="M474" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="475" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D475" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E475">
         <v>3161</v>
       </c>
       <c r="F475" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H475" s="2" t="s">
         <v>18</v>
@@ -13201,13 +13201,13 @@
     </row>
     <row r="476" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D476" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E476">
         <v>3146</v>
       </c>
       <c r="F476" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H476" s="2" t="s">
         <v>18</v>
@@ -13230,13 +13230,13 @@
     </row>
     <row r="477" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D477" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E477">
         <v>3429</v>
       </c>
       <c r="F477" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H477" s="2" t="s">
         <v>18</v>
@@ -13259,13 +13259,13 @@
     </row>
     <row r="478" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D478" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E478">
         <v>3160</v>
       </c>
       <c r="F478" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H478" s="2" t="s">
         <v>18</v>
@@ -13292,18 +13292,18 @@
       <c r="J479" s="2"/>
       <c r="K479" s="1"/>
       <c r="M479" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="480" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D480" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E480">
         <v>3154</v>
       </c>
       <c r="F480" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H480" s="2" t="s">
         <v>18</v>
@@ -13326,13 +13326,13 @@
     </row>
     <row r="481" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D481" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E481">
         <v>3144</v>
       </c>
       <c r="F481" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H481" s="2" t="s">
         <v>18</v>
@@ -13355,13 +13355,13 @@
     </row>
     <row r="482" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D482" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E482">
         <v>3145</v>
       </c>
       <c r="F482" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H482" s="2" t="s">
         <v>18</v>
@@ -13384,13 +13384,13 @@
     </row>
     <row r="483" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D483" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E483">
         <v>3151</v>
       </c>
       <c r="F483" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H483" s="2" t="s">
         <v>18</v>
@@ -13413,13 +13413,13 @@
     </row>
     <row r="484" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D484" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E484">
         <v>3148</v>
       </c>
       <c r="F484" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H484" s="2" t="s">
         <v>18</v>
@@ -13442,13 +13442,13 @@
     </row>
     <row r="485" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D485" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E485">
         <v>3164</v>
       </c>
       <c r="F485" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H485" s="2" t="s">
         <v>18</v>
@@ -13471,13 +13471,13 @@
     </row>
     <row r="486" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D486" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E486">
         <v>3163</v>
       </c>
       <c r="F486" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H486" s="2" t="s">
         <v>18</v>
@@ -13504,18 +13504,18 @@
       <c r="J487" s="2"/>
       <c r="K487" s="1"/>
       <c r="M487" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="488" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D488" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E488">
         <v>3194</v>
       </c>
       <c r="F488" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H488" s="2" t="s">
         <v>18</v>
@@ -13542,18 +13542,18 @@
       <c r="J489" s="2"/>
       <c r="K489" s="1"/>
       <c r="M489" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="490" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D490" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E490">
         <v>3162</v>
       </c>
       <c r="F490" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H490" s="2" t="s">
         <v>18</v>
@@ -13576,13 +13576,13 @@
     </row>
     <row r="491" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D491" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E491">
         <v>3147</v>
       </c>
       <c r="F491" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H491" s="2" t="s">
         <v>18</v>
@@ -13605,13 +13605,13 @@
     </row>
     <row r="492" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D492" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E492">
         <v>3156</v>
       </c>
       <c r="F492" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H492" s="2" t="s">
         <v>18</v>
@@ -13634,13 +13634,13 @@
     </row>
     <row r="493" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D493" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E493">
         <v>3157</v>
       </c>
       <c r="F493" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H493" s="2" t="s">
         <v>18</v>
@@ -13667,18 +13667,18 @@
       <c r="J494" s="2"/>
       <c r="K494" s="1"/>
       <c r="M494" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="495" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D495" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E495">
         <v>3158</v>
       </c>
       <c r="F495" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H495" s="2" t="s">
         <v>18</v>
@@ -13701,13 +13701,13 @@
     </row>
     <row r="496" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D496" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E496">
         <v>3149</v>
       </c>
       <c r="F496" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H496" s="2" t="s">
         <v>18</v>
@@ -13730,13 +13730,13 @@
     </row>
     <row r="497" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D497" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E497">
         <v>3159</v>
       </c>
       <c r="F497" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H497" s="2" t="s">
         <v>18</v>
@@ -13759,13 +13759,13 @@
     </row>
     <row r="498" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D498" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E498">
         <v>3150</v>
       </c>
       <c r="F498" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H498" s="2" t="s">
         <v>18</v>
@@ -13788,13 +13788,13 @@
     </row>
     <row r="499" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D499" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E499">
         <v>3155</v>
       </c>
       <c r="F499" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H499" s="2" t="s">
         <v>18</v>
@@ -13817,13 +13817,13 @@
     </row>
     <row r="500" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D500" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E500">
         <v>3143</v>
       </c>
       <c r="F500" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H500" s="2" t="s">
         <v>18</v>
@@ -13846,13 +13846,13 @@
     </row>
     <row r="501" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D501" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E501">
         <v>3153</v>
       </c>
       <c r="F501" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H501" s="2" t="s">
         <v>18</v>
@@ -13875,13 +13875,13 @@
     </row>
     <row r="502" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D502" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E502">
         <v>3154</v>
       </c>
       <c r="F502" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H502" s="2" t="s">
         <v>15</v>
@@ -13904,13 +13904,13 @@
     </row>
     <row r="503" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D503" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E503">
         <v>3164</v>
       </c>
       <c r="F503" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H503" s="2" t="s">
         <v>15</v>
@@ -13933,13 +13933,13 @@
     </row>
     <row r="504" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D504" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E504">
         <v>3157</v>
       </c>
       <c r="F504" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H504" s="2" t="s">
         <v>15</v>
@@ -13962,13 +13962,13 @@
     </row>
     <row r="505" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D505" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E505">
         <v>3159</v>
       </c>
       <c r="F505" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H505" s="2" t="s">
         <v>15</v>
@@ -13991,13 +13991,13 @@
     </row>
     <row r="506" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D506" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E506">
         <v>3148</v>
       </c>
       <c r="F506" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H506" s="2" t="s">
         <v>15</v>
@@ -14020,13 +14020,13 @@
     </row>
     <row r="507" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D507" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E507">
         <v>3155</v>
       </c>
       <c r="F507" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H507" s="2" t="s">
         <v>15</v>
@@ -14049,13 +14049,13 @@
     </row>
     <row r="508" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D508" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E508">
         <v>3143</v>
       </c>
       <c r="F508" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H508" s="2" t="s">
         <v>15</v>
@@ -14078,16 +14078,16 @@
     </row>
     <row r="509" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D509" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E509">
         <v>3161</v>
       </c>
       <c r="F509" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>13</v>
@@ -14107,16 +14107,16 @@
     </row>
     <row r="510" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D510" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E510">
         <v>3146</v>
       </c>
       <c r="F510" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I510" s="1" t="s">
         <v>10</v>
@@ -14136,16 +14136,16 @@
     </row>
     <row r="511" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D511" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E511">
         <v>3160</v>
       </c>
       <c r="F511" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>10</v>
@@ -14165,16 +14165,16 @@
     </row>
     <row r="512" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D512" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E512">
         <v>3144</v>
       </c>
       <c r="F512" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>10</v>
@@ -14194,16 +14194,16 @@
     </row>
     <row r="513" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D513" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E513">
         <v>3145</v>
       </c>
       <c r="F513" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>10</v>
@@ -14223,16 +14223,16 @@
     </row>
     <row r="514" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D514" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E514">
         <v>3151</v>
       </c>
       <c r="F514" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>13</v>
@@ -14252,16 +14252,16 @@
     </row>
     <row r="515" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D515" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E515">
         <v>3163</v>
       </c>
       <c r="F515" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>13</v>
@@ -14281,16 +14281,16 @@
     </row>
     <row r="516" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D516" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E516">
         <v>3194</v>
       </c>
       <c r="F516" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>10</v>
@@ -14310,16 +14310,16 @@
     </row>
     <row r="517" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D517" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E517">
         <v>3162</v>
       </c>
       <c r="F517" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>10</v>
@@ -14339,16 +14339,16 @@
     </row>
     <row r="518" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D518" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E518">
         <v>3147</v>
       </c>
       <c r="F518" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>10</v>
@@ -14368,16 +14368,16 @@
     </row>
     <row r="519" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D519" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E519">
         <v>3156</v>
       </c>
       <c r="F519" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>10</v>
@@ -14397,16 +14397,16 @@
     </row>
     <row r="520" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D520" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E520">
         <v>3158</v>
       </c>
       <c r="F520" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I520" s="1" t="s">
         <v>10</v>
@@ -14426,16 +14426,16 @@
     </row>
     <row r="521" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D521" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E521">
         <v>3149</v>
       </c>
       <c r="F521" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>13</v>
@@ -14455,16 +14455,16 @@
     </row>
     <row r="522" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D522" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E522">
         <v>3150</v>
       </c>
       <c r="F522" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I522" s="1" t="s">
         <v>10</v>
@@ -14484,16 +14484,16 @@
     </row>
     <row r="523" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D523" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E523">
         <v>3153</v>
       </c>
       <c r="F523" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I523" s="1" t="s">
         <v>13</v>
@@ -49848,7 +49848,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A02D01BC-9E41-41CF-AF62-EB297534CDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8B1E2E8-BE91-48AE-9DF1-66F7364DB645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,7 +86,13 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>Big Wins Through Behavior Change</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -98,22 +104,22 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
+    <t>Speed Management</t>
+  </si>
+  <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
+    <t>Alert Driving: Big Three</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
-  </si>
-  <si>
-    <t>Alert Driving: Big Three</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -128,9 +134,6 @@
     <t>Scene of an Accident</t>
   </si>
   <si>
-    <t>Camera Event Management Orientation for Drivers</t>
-  </si>
-  <si>
     <t>Webinar Behavior Change-Supervisors</t>
   </si>
   <si>
@@ -138,9 +141,6 @@
   </si>
   <si>
     <t>(Spanish) Rules for Safe Driving</t>
-  </si>
-  <si>
-    <t>Big Wins Through Behavior Change</t>
   </si>
   <si>
     <t>Jon Stanley</t>
@@ -586,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -644,7 +644,7 @@
         <v>36</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -673,7 +673,7 @@
         <v>37</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>13</v>
@@ -702,7 +702,7 @@
         <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -731,7 +731,7 @@
         <v>39</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -760,7 +760,7 @@
         <v>40</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -789,7 +789,7 @@
         <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -818,7 +818,7 @@
         <v>42</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -847,7 +847,7 @@
         <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -876,7 +876,7 @@
         <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -905,7 +905,7 @@
         <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -934,7 +934,7 @@
         <v>46</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -963,7 +963,7 @@
         <v>47</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -992,7 +992,7 @@
         <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -1021,7 +1021,7 @@
         <v>49</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>13</v>
@@ -1050,7 +1050,7 @@
         <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>13</v>
@@ -1079,7 +1079,7 @@
         <v>51</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>13</v>
@@ -1108,7 +1108,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1137,7 +1137,7 @@
         <v>53</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1166,7 +1166,7 @@
         <v>54</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -1195,7 +1195,7 @@
         <v>55</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
@@ -1224,7 +1224,7 @@
         <v>56</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -1253,7 +1253,7 @@
         <v>57</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1282,7 +1282,7 @@
         <v>40</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>13</v>
@@ -1311,7 +1311,7 @@
         <v>36</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>13</v>
@@ -1340,7 +1340,7 @@
         <v>37</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -1369,7 +1369,7 @@
         <v>38</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -1398,7 +1398,7 @@
         <v>39</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1427,7 +1427,7 @@
         <v>40</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>13</v>
@@ -1456,7 +1456,7 @@
         <v>41</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1485,7 +1485,7 @@
         <v>42</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -1514,7 +1514,7 @@
         <v>43</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1543,7 +1543,7 @@
         <v>44</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1572,7 +1572,7 @@
         <v>45</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1601,7 +1601,7 @@
         <v>46</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1630,7 +1630,7 @@
         <v>47</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>13</v>
@@ -1659,7 +1659,7 @@
         <v>48</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1688,7 +1688,7 @@
         <v>49</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1717,7 +1717,7 @@
         <v>50</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>13</v>
@@ -1746,7 +1746,7 @@
         <v>51</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -1775,7 +1775,7 @@
         <v>52</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
@@ -1804,7 +1804,7 @@
         <v>53</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1833,7 +1833,7 @@
         <v>54</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1862,7 +1862,7 @@
         <v>55</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1891,7 +1891,7 @@
         <v>56</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -1920,7 +1920,7 @@
         <v>57</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1949,7 +1949,7 @@
         <v>40</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>13</v>
@@ -1978,7 +1978,7 @@
         <v>34</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>13</v>
@@ -2007,7 +2007,7 @@
         <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -2036,7 +2036,7 @@
         <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -2065,7 +2065,7 @@
         <v>36</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2094,7 +2094,7 @@
         <v>37</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>38</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>39</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2181,7 +2181,7 @@
         <v>40</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2210,7 +2210,7 @@
         <v>41</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>42</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2268,7 +2268,7 @@
         <v>43</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2297,7 +2297,7 @@
         <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2326,7 +2326,7 @@
         <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2355,7 +2355,7 @@
         <v>46</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>12</v>
@@ -2379,7 +2379,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="1"/>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
@@ -2393,7 +2393,7 @@
         <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2422,7 +2422,7 @@
         <v>34</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2451,7 +2451,7 @@
         <v>48</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2480,7 +2480,7 @@
         <v>49</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2509,7 +2509,7 @@
         <v>50</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>12</v>
@@ -2533,7 +2533,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="1"/>
       <c r="M68" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
@@ -2547,7 +2547,7 @@
         <v>51</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2576,7 +2576,7 @@
         <v>52</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2605,7 +2605,7 @@
         <v>53</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>54</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2663,7 +2663,7 @@
         <v>55</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>56</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>57</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>10</v>
@@ -2750,7 +2750,7 @@
         <v>40</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2779,7 +2779,7 @@
         <v>36</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2808,7 +2808,7 @@
         <v>37</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2837,7 +2837,7 @@
         <v>38</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2866,7 +2866,7 @@
         <v>39</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2895,7 +2895,7 @@
         <v>40</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2924,7 +2924,7 @@
         <v>41</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2953,7 +2953,7 @@
         <v>42</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>14</v>
@@ -2977,7 +2977,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="1"/>
       <c r="M84" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
@@ -2991,7 +2991,7 @@
         <v>43</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>12</v>
@@ -3015,7 +3015,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="1"/>
       <c r="M86" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
@@ -3029,7 +3029,7 @@
         <v>44</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -3058,7 +3058,7 @@
         <v>45</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -3087,7 +3087,7 @@
         <v>46</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>12</v>
@@ -3111,7 +3111,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="1"/>
       <c r="M90" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
@@ -3125,7 +3125,7 @@
         <v>47</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3154,7 +3154,7 @@
         <v>34</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3183,7 +3183,7 @@
         <v>48</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>49</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3241,7 +3241,7 @@
         <v>50</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3270,7 +3270,7 @@
         <v>51</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>12</v>
@@ -3294,7 +3294,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
@@ -3308,7 +3308,7 @@
         <v>52</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3337,7 +3337,7 @@
         <v>53</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3366,7 +3366,7 @@
         <v>54</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3395,7 +3395,7 @@
         <v>55</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3424,7 +3424,7 @@
         <v>56</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3453,7 +3453,7 @@
         <v>57</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>12</v>
@@ -3477,7 +3477,7 @@
       <c r="J104" s="2"/>
       <c r="K104" s="1"/>
       <c r="M104" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
@@ -3491,7 +3491,7 @@
         <v>40</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>13</v>
@@ -3921,7 +3921,7 @@
       <c r="J120" s="2"/>
       <c r="K120" s="1"/>
       <c r="M120" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
@@ -4249,7 +4249,7 @@
       <c r="J132" s="2"/>
       <c r="K132" s="1"/>
       <c r="M132" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
@@ -4263,7 +4263,7 @@
         <v>36</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4292,7 +4292,7 @@
         <v>37</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4321,7 +4321,7 @@
         <v>38</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4350,7 +4350,7 @@
         <v>39</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>40</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4408,7 +4408,7 @@
         <v>51</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4437,7 +4437,7 @@
         <v>42</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4466,7 +4466,7 @@
         <v>43</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4495,7 +4495,7 @@
         <v>46</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>12</v>
@@ -4519,7 +4519,7 @@
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
       <c r="M142" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
@@ -4533,7 +4533,7 @@
         <v>44</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4562,7 +4562,7 @@
         <v>45</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -4591,7 +4591,7 @@
         <v>41</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>13</v>
@@ -4620,7 +4620,7 @@
         <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4649,7 +4649,7 @@
         <v>34</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4678,7 +4678,7 @@
         <v>48</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4707,7 +4707,7 @@
         <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>12</v>
@@ -4731,7 +4731,7 @@
       <c r="J150" s="2"/>
       <c r="K150" s="1"/>
       <c r="M150" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
@@ -4745,7 +4745,7 @@
         <v>46</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>10</v>
@@ -4774,7 +4774,7 @@
         <v>52</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>53</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>10</v>
@@ -4832,7 +4832,7 @@
         <v>54</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4861,7 +4861,7 @@
         <v>55</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>10</v>
@@ -4890,7 +4890,7 @@
         <v>57</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -4919,7 +4919,7 @@
         <v>56</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -4948,7 +4948,7 @@
         <v>40</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4977,7 +4977,7 @@
         <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>10</v>
@@ -5006,7 +5006,7 @@
         <v>37</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -5035,7 +5035,7 @@
         <v>38</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>10</v>
@@ -5064,7 +5064,7 @@
         <v>39</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>10</v>
@@ -5093,7 +5093,7 @@
         <v>40</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>13</v>
@@ -5122,7 +5122,7 @@
         <v>42</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -5151,7 +5151,7 @@
         <v>43</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5180,7 +5180,7 @@
         <v>46</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>10</v>
@@ -5209,7 +5209,7 @@
         <v>44</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5238,7 +5238,7 @@
         <v>45</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5267,7 +5267,7 @@
         <v>51</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5296,7 +5296,7 @@
         <v>34</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>13</v>
@@ -5325,7 +5325,7 @@
         <v>50</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>12</v>
@@ -5349,7 +5349,7 @@
       <c r="J172" s="2"/>
       <c r="K172" s="1"/>
       <c r="M172" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
@@ -5363,7 +5363,7 @@
         <v>46</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>10</v>
@@ -5392,7 +5392,7 @@
         <v>52</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>10</v>
@@ -5421,7 +5421,7 @@
         <v>53</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5450,7 +5450,7 @@
         <v>54</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>14</v>
@@ -5474,7 +5474,7 @@
       <c r="J177" s="2"/>
       <c r="K177" s="1"/>
       <c r="M177" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
@@ -5488,7 +5488,7 @@
         <v>55</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5517,7 +5517,7 @@
         <v>41</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>13</v>
@@ -5546,7 +5546,7 @@
         <v>57</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>13</v>
@@ -5575,7 +5575,7 @@
         <v>48</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5604,7 +5604,7 @@
         <v>47</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5633,7 +5633,7 @@
         <v>56</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>13</v>
@@ -5662,7 +5662,7 @@
         <v>36</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5691,7 +5691,7 @@
         <v>40</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5720,7 +5720,7 @@
         <v>49</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>10</v>
@@ -5749,7 +5749,7 @@
         <v>41</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5778,7 +5778,7 @@
         <v>37</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>10</v>
@@ -5807,7 +5807,7 @@
         <v>38</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5836,7 +5836,7 @@
         <v>39</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5865,7 +5865,7 @@
         <v>40</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5894,7 +5894,7 @@
         <v>42</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5923,7 +5923,7 @@
         <v>43</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5952,7 +5952,7 @@
         <v>46</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>13</v>
@@ -5981,7 +5981,7 @@
         <v>44</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -6010,7 +6010,7 @@
         <v>45</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -6039,7 +6039,7 @@
         <v>51</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -6068,7 +6068,7 @@
         <v>34</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>12</v>
@@ -6092,7 +6092,7 @@
       <c r="J199" s="2"/>
       <c r="K199" s="1"/>
       <c r="M199" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
@@ -6106,7 +6106,7 @@
         <v>50</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>12</v>
@@ -6130,7 +6130,7 @@
       <c r="J201" s="2"/>
       <c r="K201" s="1"/>
       <c r="M201" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
@@ -6144,7 +6144,7 @@
         <v>46</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>12</v>
@@ -6168,7 +6168,7 @@
       <c r="J203" s="2"/>
       <c r="K203" s="1"/>
       <c r="M203" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
@@ -6182,7 +6182,7 @@
         <v>52</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6211,7 +6211,7 @@
         <v>53</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -6240,7 +6240,7 @@
         <v>54</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>14</v>
@@ -6264,7 +6264,7 @@
       <c r="J207" s="2"/>
       <c r="K207" s="1"/>
       <c r="M207" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
@@ -6278,7 +6278,7 @@
         <v>55</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6307,7 +6307,7 @@
         <v>48</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6336,7 +6336,7 @@
         <v>57</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6365,7 +6365,7 @@
         <v>47</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6394,7 +6394,7 @@
         <v>56</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6423,7 +6423,7 @@
         <v>36</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6452,7 +6452,7 @@
         <v>40</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6481,7 +6481,7 @@
         <v>49</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>13</v>
@@ -6510,7 +6510,7 @@
         <v>41</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6539,7 +6539,7 @@
         <v>37</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6568,7 +6568,7 @@
         <v>38</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6597,7 +6597,7 @@
         <v>39</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>10</v>
@@ -6626,7 +6626,7 @@
         <v>40</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6655,7 +6655,7 @@
         <v>42</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>13</v>
@@ -6684,7 +6684,7 @@
         <v>43</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6713,7 +6713,7 @@
         <v>46</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>10</v>
@@ -6742,7 +6742,7 @@
         <v>44</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6771,7 +6771,7 @@
         <v>45</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>10</v>
@@ -6800,7 +6800,7 @@
         <v>51</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>10</v>
@@ -6829,7 +6829,7 @@
         <v>34</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6858,7 +6858,7 @@
         <v>50</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -6887,7 +6887,7 @@
         <v>46</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6916,7 +6916,7 @@
         <v>52</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -6945,7 +6945,7 @@
         <v>53</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -6974,7 +6974,7 @@
         <v>54</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -7003,7 +7003,7 @@
         <v>55</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>10</v>
@@ -7032,7 +7032,7 @@
         <v>48</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7061,7 +7061,7 @@
         <v>57</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -7090,7 +7090,7 @@
         <v>47</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7119,7 +7119,7 @@
         <v>56</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7148,7 +7148,7 @@
         <v>36</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -7177,7 +7177,7 @@
         <v>40</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7206,7 +7206,7 @@
         <v>49</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7235,7 +7235,7 @@
         <v>41</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>10</v>
@@ -7264,7 +7264,7 @@
         <v>37</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7293,7 +7293,7 @@
         <v>38</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -7322,7 +7322,7 @@
         <v>39</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>10</v>
@@ -7351,7 +7351,7 @@
         <v>40</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -7380,7 +7380,7 @@
         <v>42</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7409,7 +7409,7 @@
         <v>43</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7438,7 +7438,7 @@
         <v>46</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>13</v>
@@ -7467,7 +7467,7 @@
         <v>51</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>10</v>
@@ -7496,7 +7496,7 @@
         <v>44</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7525,7 +7525,7 @@
         <v>45</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7554,7 +7554,7 @@
         <v>34</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7583,7 +7583,7 @@
         <v>50</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7612,7 +7612,7 @@
         <v>46</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7641,7 +7641,7 @@
         <v>52</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>13</v>
@@ -7670,7 +7670,7 @@
         <v>53</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7699,7 +7699,7 @@
         <v>54</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>14</v>
@@ -7723,7 +7723,7 @@
       <c r="J258" s="2"/>
       <c r="K258" s="1"/>
       <c r="M258" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
@@ -7737,7 +7737,7 @@
         <v>55</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>10</v>
@@ -7766,7 +7766,7 @@
         <v>48</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7795,7 +7795,7 @@
         <v>49</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>13</v>
@@ -7824,7 +7824,7 @@
         <v>57</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>14</v>
@@ -7848,7 +7848,7 @@
       <c r="J263" s="2"/>
       <c r="K263" s="1"/>
       <c r="M263" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
@@ -7862,7 +7862,7 @@
         <v>40</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7891,7 +7891,7 @@
         <v>47</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -7920,7 +7920,7 @@
         <v>56</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>12</v>
@@ -7973,7 +7973,7 @@
       <c r="J268" s="2"/>
       <c r="K268" s="1"/>
       <c r="M268" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="269" spans="4:13" x14ac:dyDescent="0.3">
@@ -7987,7 +7987,7 @@
         <v>41</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -8016,7 +8016,7 @@
         <v>37</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -8045,7 +8045,7 @@
         <v>38</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -8074,7 +8074,7 @@
         <v>39</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -8103,7 +8103,7 @@
         <v>40</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -8132,7 +8132,7 @@
         <v>43</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>46</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -8190,7 +8190,7 @@
         <v>45</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -8219,7 +8219,7 @@
         <v>34</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>13</v>
@@ -8248,7 +8248,7 @@
         <v>50</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -8277,7 +8277,7 @@
         <v>46</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>10</v>
@@ -8306,7 +8306,7 @@
         <v>52</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>10</v>
@@ -8335,7 +8335,7 @@
         <v>53</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8364,7 +8364,7 @@
         <v>54</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>14</v>
@@ -8388,7 +8388,7 @@
       <c r="J283" s="2"/>
       <c r="K283" s="1"/>
       <c r="M283" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
@@ -8402,7 +8402,7 @@
         <v>55</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>10</v>
@@ -8431,7 +8431,7 @@
         <v>42</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>13</v>
@@ -8460,7 +8460,7 @@
         <v>48</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8489,7 +8489,7 @@
         <v>49</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>10</v>
@@ -8518,7 +8518,7 @@
         <v>57</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>13</v>
@@ -8547,7 +8547,7 @@
         <v>40</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -8576,7 +8576,7 @@
         <v>47</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -8605,7 +8605,7 @@
         <v>56</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -8634,7 +8634,7 @@
         <v>44</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8663,7 +8663,7 @@
         <v>51</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>12</v>
@@ -8687,7 +8687,7 @@
       <c r="J294" s="2"/>
       <c r="K294" s="1"/>
       <c r="M294" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
@@ -8701,7 +8701,7 @@
         <v>36</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>10</v>
@@ -8730,7 +8730,7 @@
         <v>41</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8759,7 +8759,7 @@
         <v>37</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8788,7 +8788,7 @@
         <v>38</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>12</v>
@@ -8812,7 +8812,7 @@
       <c r="J299" s="2"/>
       <c r="K299" s="1"/>
       <c r="M299" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
@@ -8826,7 +8826,7 @@
         <v>39</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>10</v>
@@ -8855,7 +8855,7 @@
         <v>40</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>10</v>
@@ -8884,7 +8884,7 @@
         <v>43</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -8913,7 +8913,7 @@
         <v>46</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>12</v>
@@ -8937,7 +8937,7 @@
       <c r="J304" s="2"/>
       <c r="K304" s="1"/>
       <c r="M304" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="305" spans="4:13" x14ac:dyDescent="0.3">
@@ -8951,7 +8951,7 @@
         <v>45</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -8980,7 +8980,7 @@
         <v>42</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>13</v>
@@ -9009,7 +9009,7 @@
         <v>34</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>13</v>
@@ -9038,7 +9038,7 @@
         <v>50</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>12</v>
@@ -9062,7 +9062,7 @@
       <c r="J309" s="2"/>
       <c r="K309" s="1"/>
       <c r="M309" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
@@ -9076,7 +9076,7 @@
         <v>46</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -9105,7 +9105,7 @@
         <v>52</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>13</v>
@@ -9134,7 +9134,7 @@
         <v>53</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>12</v>
@@ -9158,7 +9158,7 @@
       <c r="J313" s="2"/>
       <c r="K313" s="1"/>
       <c r="M313" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
@@ -9172,7 +9172,7 @@
         <v>54</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>14</v>
@@ -9196,7 +9196,7 @@
       <c r="J315" s="2"/>
       <c r="K315" s="1"/>
       <c r="M315" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
@@ -9210,7 +9210,7 @@
         <v>55</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -9239,7 +9239,7 @@
         <v>49</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -9268,7 +9268,7 @@
         <v>57</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>14</v>
@@ -9292,7 +9292,7 @@
       <c r="J319" s="2"/>
       <c r="K319" s="1"/>
       <c r="M319" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320" spans="4:13" x14ac:dyDescent="0.3">
@@ -9306,7 +9306,7 @@
         <v>40</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>10</v>
@@ -9335,7 +9335,7 @@
         <v>47</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>12</v>
@@ -9359,7 +9359,7 @@
       <c r="J322" s="2"/>
       <c r="K322" s="1"/>
       <c r="M322" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="323" spans="4:13" x14ac:dyDescent="0.3">
@@ -9373,7 +9373,7 @@
         <v>56</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>10</v>
@@ -9402,7 +9402,7 @@
         <v>44</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>12</v>
@@ -9426,7 +9426,7 @@
       <c r="J325" s="2"/>
       <c r="K325" s="1"/>
       <c r="M325" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="326" spans="4:13" x14ac:dyDescent="0.3">
@@ -9440,7 +9440,7 @@
         <v>51</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>12</v>
@@ -9464,7 +9464,7 @@
       <c r="J327" s="2"/>
       <c r="K327" s="1"/>
       <c r="M327" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
@@ -9478,7 +9478,7 @@
         <v>36</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>10</v>
@@ -9507,7 +9507,7 @@
         <v>41</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9536,7 +9536,7 @@
         <v>37</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9565,7 +9565,7 @@
         <v>38</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9594,7 +9594,7 @@
         <v>39</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>10</v>
@@ -9623,7 +9623,7 @@
         <v>40</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -9652,7 +9652,7 @@
         <v>43</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -9681,7 +9681,7 @@
         <v>46</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>10</v>
@@ -9710,7 +9710,7 @@
         <v>45</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>13</v>
@@ -9739,7 +9739,7 @@
         <v>42</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -9768,7 +9768,7 @@
         <v>34</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9797,7 +9797,7 @@
         <v>50</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9826,7 +9826,7 @@
         <v>52</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -9855,7 +9855,7 @@
         <v>53</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>10</v>
@@ -9884,7 +9884,7 @@
         <v>54</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -9913,7 +9913,7 @@
         <v>55</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9942,7 +9942,7 @@
         <v>46</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>13</v>
@@ -9971,7 +9971,7 @@
         <v>57</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -10000,7 +10000,7 @@
         <v>40</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10029,7 +10029,7 @@
         <v>47</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -10058,7 +10058,7 @@
         <v>56</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10087,7 +10087,7 @@
         <v>44</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>14</v>
@@ -10111,7 +10111,7 @@
       <c r="J350" s="2"/>
       <c r="K350" s="1"/>
       <c r="M350" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="351" spans="4:13" x14ac:dyDescent="0.3">
@@ -10125,7 +10125,7 @@
         <v>51</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>10</v>
@@ -10154,7 +10154,7 @@
         <v>49</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>10</v>
@@ -10183,7 +10183,7 @@
         <v>36</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>10</v>
@@ -10212,7 +10212,7 @@
         <v>34</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>13</v>
@@ -10241,7 +10241,7 @@
         <v>41</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10270,7 +10270,7 @@
         <v>37</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10299,7 +10299,7 @@
         <v>38</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>10</v>
@@ -10328,7 +10328,7 @@
         <v>39</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>10</v>
@@ -10357,7 +10357,7 @@
         <v>46</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>10</v>
@@ -10386,7 +10386,7 @@
         <v>45</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>13</v>
@@ -10415,7 +10415,7 @@
         <v>42</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>13</v>
@@ -10444,7 +10444,7 @@
         <v>43</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>14</v>
@@ -10468,7 +10468,7 @@
       <c r="J363" s="2"/>
       <c r="K363" s="1"/>
       <c r="M363" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="364" spans="4:13" x14ac:dyDescent="0.3">
@@ -10482,7 +10482,7 @@
         <v>50</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>12</v>
@@ -10506,7 +10506,7 @@
       <c r="J365" s="2"/>
       <c r="K365" s="1"/>
       <c r="M365" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="366" spans="4:13" x14ac:dyDescent="0.3">
@@ -10520,7 +10520,7 @@
         <v>52</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>10</v>
@@ -10549,7 +10549,7 @@
         <v>53</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>10</v>
@@ -10578,7 +10578,7 @@
         <v>54</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>14</v>
@@ -10602,7 +10602,7 @@
       <c r="J369" s="2"/>
       <c r="K369" s="1"/>
       <c r="M369" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="370" spans="4:13" x14ac:dyDescent="0.3">
@@ -10616,7 +10616,7 @@
         <v>55</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>10</v>
@@ -10645,7 +10645,7 @@
         <v>46</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>13</v>
@@ -10674,7 +10674,7 @@
         <v>57</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>13</v>
@@ -10703,7 +10703,7 @@
         <v>40</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>13</v>
@@ -10732,7 +10732,7 @@
         <v>40</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>13</v>
@@ -10761,7 +10761,7 @@
         <v>47</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -10790,7 +10790,7 @@
         <v>56</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -10819,7 +10819,7 @@
         <v>44</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>10</v>
@@ -10848,7 +10848,7 @@
         <v>51</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -10877,7 +10877,7 @@
         <v>49</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>10</v>
@@ -10906,7 +10906,7 @@
         <v>36</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -10935,7 +10935,7 @@
         <v>48</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>10</v>
@@ -10964,7 +10964,7 @@
         <v>40</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>13</v>
@@ -10993,7 +10993,7 @@
         <v>41</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>10</v>
@@ -11022,7 +11022,7 @@
         <v>37</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>10</v>
@@ -11051,7 +11051,7 @@
         <v>38</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>10</v>
@@ -11080,7 +11080,7 @@
         <v>39</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>10</v>
@@ -11109,7 +11109,7 @@
         <v>46</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>13</v>
@@ -11138,7 +11138,7 @@
         <v>45</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>13</v>
@@ -11167,7 +11167,7 @@
         <v>42</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>13</v>
@@ -11196,7 +11196,7 @@
         <v>43</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>12</v>
@@ -11220,7 +11220,7 @@
       <c r="J391" s="2"/>
       <c r="K391" s="1"/>
       <c r="M391" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="392" spans="4:13" x14ac:dyDescent="0.3">
@@ -11234,7 +11234,7 @@
         <v>50</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>12</v>
@@ -11258,7 +11258,7 @@
       <c r="J393" s="2"/>
       <c r="K393" s="1"/>
       <c r="M393" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="394" spans="4:13" x14ac:dyDescent="0.3">
@@ -11272,7 +11272,7 @@
         <v>48</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>10</v>
@@ -11301,7 +11301,7 @@
         <v>52</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>10</v>
@@ -11330,7 +11330,7 @@
         <v>53</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>10</v>
@@ -11359,7 +11359,7 @@
         <v>54</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>14</v>
@@ -11383,7 +11383,7 @@
       <c r="J398" s="2"/>
       <c r="K398" s="1"/>
       <c r="M398" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="399" spans="4:13" x14ac:dyDescent="0.3">
@@ -11397,7 +11397,7 @@
         <v>55</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>10</v>
@@ -11426,7 +11426,7 @@
         <v>57</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>13</v>
@@ -11455,7 +11455,7 @@
         <v>47</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>10</v>
@@ -11484,7 +11484,7 @@
         <v>56</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>10</v>
@@ -11513,7 +11513,7 @@
         <v>44</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>10</v>
@@ -11542,7 +11542,7 @@
         <v>51</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>10</v>
@@ -11571,7 +11571,7 @@
         <v>49</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>10</v>
@@ -11600,7 +11600,7 @@
         <v>36</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>10</v>
@@ -11629,7 +11629,7 @@
         <v>57</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>12</v>
@@ -11653,7 +11653,7 @@
       <c r="J408" s="2"/>
       <c r="K408" s="1"/>
       <c r="M408" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="409" spans="4:13" x14ac:dyDescent="0.3">
@@ -11667,7 +11667,7 @@
         <v>40</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>13</v>
@@ -11696,7 +11696,7 @@
         <v>41</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>12</v>
@@ -11720,7 +11720,7 @@
       <c r="J411" s="2"/>
       <c r="K411" s="1"/>
       <c r="M411" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="412" spans="4:13" x14ac:dyDescent="0.3">
@@ -11734,7 +11734,7 @@
         <v>46</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>12</v>
@@ -11758,7 +11758,7 @@
       <c r="J413" s="2"/>
       <c r="K413" s="1"/>
       <c r="M413" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="414" spans="4:13" x14ac:dyDescent="0.3">
@@ -11772,7 +11772,7 @@
         <v>37</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>12</v>
@@ -11796,7 +11796,7 @@
       <c r="J415" s="2"/>
       <c r="K415" s="1"/>
       <c r="M415" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="416" spans="4:13" x14ac:dyDescent="0.3">
@@ -11810,7 +11810,7 @@
         <v>38</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>12</v>
@@ -11834,7 +11834,7 @@
       <c r="J417" s="2"/>
       <c r="K417" s="1"/>
       <c r="M417" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="418" spans="4:13" x14ac:dyDescent="0.3">
@@ -11848,7 +11848,7 @@
         <v>39</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>12</v>
@@ -11872,7 +11872,7 @@
       <c r="J419" s="2"/>
       <c r="K419" s="1"/>
       <c r="M419" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="420" spans="4:13" x14ac:dyDescent="0.3">
@@ -11886,7 +11886,7 @@
         <v>46</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>13</v>
@@ -11915,7 +11915,7 @@
         <v>45</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I421" s="1" t="s">
         <v>13</v>
@@ -11944,7 +11944,7 @@
         <v>42</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>13</v>
@@ -11973,7 +11973,7 @@
         <v>49</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>12</v>
@@ -11997,7 +11997,7 @@
       <c r="J424" s="2"/>
       <c r="K424" s="1"/>
       <c r="M424" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="425" spans="4:13" x14ac:dyDescent="0.3">
@@ -12011,7 +12011,7 @@
         <v>43</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>12</v>
@@ -12035,7 +12035,7 @@
       <c r="J426" s="2"/>
       <c r="K426" s="1"/>
       <c r="M426" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="427" spans="4:13" x14ac:dyDescent="0.3">
@@ -12049,7 +12049,7 @@
         <v>50</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>12</v>
@@ -12073,7 +12073,7 @@
       <c r="J428" s="2"/>
       <c r="K428" s="1"/>
       <c r="M428" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="429" spans="4:13" x14ac:dyDescent="0.3">
@@ -12087,7 +12087,7 @@
         <v>48</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>12</v>
@@ -12111,7 +12111,7 @@
       <c r="J430" s="2"/>
       <c r="K430" s="1"/>
       <c r="M430" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="431" spans="4:13" x14ac:dyDescent="0.3">
@@ -12125,7 +12125,7 @@
         <v>52</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>12</v>
@@ -12149,7 +12149,7 @@
       <c r="J432" s="2"/>
       <c r="K432" s="1"/>
       <c r="M432" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="433" spans="4:13" x14ac:dyDescent="0.3">
@@ -12163,7 +12163,7 @@
         <v>53</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>12</v>
@@ -12187,7 +12187,7 @@
       <c r="J434" s="2"/>
       <c r="K434" s="1"/>
       <c r="M434" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="435" spans="4:13" x14ac:dyDescent="0.3">
@@ -12201,7 +12201,7 @@
         <v>54</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>12</v>
@@ -12225,7 +12225,7 @@
       <c r="J436" s="2"/>
       <c r="K436" s="1"/>
       <c r="M436" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="437" spans="4:13" x14ac:dyDescent="0.3">
@@ -12239,7 +12239,7 @@
         <v>55</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>12</v>
@@ -12263,7 +12263,7 @@
       <c r="J438" s="2"/>
       <c r="K438" s="1"/>
       <c r="M438" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="439" spans="4:13" x14ac:dyDescent="0.3">
@@ -12277,7 +12277,7 @@
         <v>56</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>12</v>
@@ -12301,7 +12301,7 @@
       <c r="J440" s="2"/>
       <c r="K440" s="1"/>
       <c r="M440" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="441" spans="4:13" x14ac:dyDescent="0.3">
@@ -12315,7 +12315,7 @@
         <v>44</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>12</v>
@@ -12339,7 +12339,7 @@
       <c r="J442" s="2"/>
       <c r="K442" s="1"/>
       <c r="M442" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="443" spans="4:13" x14ac:dyDescent="0.3">
@@ -12353,7 +12353,7 @@
         <v>51</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>12</v>
@@ -12377,7 +12377,7 @@
       <c r="J444" s="2"/>
       <c r="K444" s="1"/>
       <c r="M444" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="445" spans="4:13" x14ac:dyDescent="0.3">
@@ -12391,7 +12391,7 @@
         <v>36</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>12</v>
@@ -12415,7 +12415,7 @@
       <c r="J446" s="2"/>
       <c r="K446" s="1"/>
       <c r="M446" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="447" spans="4:13" x14ac:dyDescent="0.3">
@@ -12429,7 +12429,7 @@
         <v>47</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>13</v>
@@ -12458,7 +12458,7 @@
         <v>57</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>10</v>
@@ -12487,7 +12487,7 @@
         <v>40</v>
       </c>
       <c r="H449" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I449" s="1" t="s">
         <v>13</v>
@@ -12516,7 +12516,7 @@
         <v>41</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>10</v>
@@ -12545,7 +12545,7 @@
         <v>46</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>10</v>
@@ -12574,7 +12574,7 @@
         <v>37</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>10</v>
@@ -12603,7 +12603,7 @@
         <v>38</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>10</v>
@@ -12632,7 +12632,7 @@
         <v>39</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>10</v>
@@ -12661,7 +12661,7 @@
         <v>46</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>13</v>
@@ -12690,7 +12690,7 @@
         <v>45</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -12719,7 +12719,7 @@
         <v>42</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>13</v>
@@ -12748,7 +12748,7 @@
         <v>49</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>10</v>
@@ -12777,7 +12777,7 @@
         <v>43</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>10</v>
@@ -12806,7 +12806,7 @@
         <v>50</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -12835,7 +12835,7 @@
         <v>48</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>14</v>
@@ -12859,7 +12859,7 @@
       <c r="J462" s="2"/>
       <c r="K462" s="1"/>
       <c r="M462" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="463" spans="4:13" x14ac:dyDescent="0.3">
@@ -12873,7 +12873,7 @@
         <v>52</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>10</v>
@@ -12902,7 +12902,7 @@
         <v>53</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>10</v>
@@ -12931,7 +12931,7 @@
         <v>54</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>14</v>
@@ -12955,7 +12955,7 @@
       <c r="J466" s="2"/>
       <c r="K466" s="1"/>
       <c r="M466" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="467" spans="4:13" x14ac:dyDescent="0.3">
@@ -12969,7 +12969,7 @@
         <v>55</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>10</v>
@@ -12998,7 +12998,7 @@
         <v>56</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>10</v>
@@ -13027,7 +13027,7 @@
         <v>44</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>10</v>
@@ -13056,7 +13056,7 @@
         <v>51</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -13085,7 +13085,7 @@
         <v>36</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>10</v>
@@ -13114,7 +13114,7 @@
         <v>47</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>13</v>
@@ -13143,7 +13143,7 @@
         <v>55</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>12</v>
@@ -13167,7 +13167,7 @@
       <c r="J474" s="2"/>
       <c r="K474" s="1"/>
       <c r="M474" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="475" spans="4:13" x14ac:dyDescent="0.3">
@@ -13181,7 +13181,7 @@
         <v>40</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>13</v>
@@ -13210,7 +13210,7 @@
         <v>41</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>10</v>
@@ -13239,7 +13239,7 @@
         <v>46</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>10</v>
@@ -13268,7 +13268,7 @@
         <v>57</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>12</v>
@@ -13292,7 +13292,7 @@
       <c r="J479" s="2"/>
       <c r="K479" s="1"/>
       <c r="M479" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="480" spans="4:13" x14ac:dyDescent="0.3">
@@ -13306,7 +13306,7 @@
         <v>37</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>10</v>
@@ -13335,7 +13335,7 @@
         <v>38</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>10</v>
@@ -13364,7 +13364,7 @@
         <v>39</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I482" s="1" t="s">
         <v>10</v>
@@ -13393,7 +13393,7 @@
         <v>45</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I483" s="1" t="s">
         <v>13</v>
@@ -13422,7 +13422,7 @@
         <v>42</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>10</v>
@@ -13451,7 +13451,7 @@
         <v>49</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>10</v>
@@ -13480,7 +13480,7 @@
         <v>43</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>14</v>
@@ -13504,7 +13504,7 @@
       <c r="J487" s="2"/>
       <c r="K487" s="1"/>
       <c r="M487" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="488" spans="4:13" x14ac:dyDescent="0.3">
@@ -13518,7 +13518,7 @@
         <v>50</v>
       </c>
       <c r="H488" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I488" s="1" t="s">
         <v>12</v>
@@ -13542,7 +13542,7 @@
       <c r="J489" s="2"/>
       <c r="K489" s="1"/>
       <c r="M489" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="490" spans="4:13" x14ac:dyDescent="0.3">
@@ -13556,7 +13556,7 @@
         <v>48</v>
       </c>
       <c r="H490" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I490" s="1" t="s">
         <v>13</v>
@@ -13585,7 +13585,7 @@
         <v>52</v>
       </c>
       <c r="H491" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>10</v>
@@ -13614,7 +13614,7 @@
         <v>53</v>
       </c>
       <c r="H492" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I492" s="1" t="s">
         <v>10</v>
@@ -13643,7 +13643,7 @@
         <v>54</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I493" s="1" t="s">
         <v>14</v>
@@ -13667,7 +13667,7 @@
       <c r="J494" s="2"/>
       <c r="K494" s="1"/>
       <c r="M494" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="495" spans="4:13" x14ac:dyDescent="0.3">
@@ -13681,7 +13681,7 @@
         <v>55</v>
       </c>
       <c r="H495" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I495" s="1" t="s">
         <v>10</v>
@@ -13710,7 +13710,7 @@
         <v>46</v>
       </c>
       <c r="H496" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I496" s="1" t="s">
         <v>13</v>
@@ -13739,7 +13739,7 @@
         <v>56</v>
       </c>
       <c r="H497" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I497" s="1" t="s">
         <v>10</v>
@@ -13768,7 +13768,7 @@
         <v>44</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>10</v>
@@ -13797,7 +13797,7 @@
         <v>51</v>
       </c>
       <c r="H499" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I499" s="1" t="s">
         <v>10</v>
@@ -13826,7 +13826,7 @@
         <v>36</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I500" s="1" t="s">
         <v>10</v>
@@ -13855,7 +13855,7 @@
         <v>47</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>13</v>
@@ -13884,7 +13884,7 @@
         <v>37</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I502" s="1" t="s">
         <v>10</v>
@@ -13913,7 +13913,7 @@
         <v>49</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I503" s="1" t="s">
         <v>10</v>
@@ -13942,7 +13942,7 @@
         <v>54</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I504" s="1" t="s">
         <v>10</v>
@@ -13971,7 +13971,7 @@
         <v>56</v>
       </c>
       <c r="H505" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I505" s="1" t="s">
         <v>10</v>
@@ -14000,7 +14000,7 @@
         <v>42</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I506" s="1" t="s">
         <v>10</v>
@@ -14029,7 +14029,7 @@
         <v>51</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I507" s="1" t="s">
         <v>10</v>
@@ -14058,7 +14058,7 @@
         <v>36</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I508" s="1" t="s">
         <v>10</v>
@@ -14087,7 +14087,7 @@
         <v>40</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>13</v>
@@ -14116,7 +14116,7 @@
         <v>41</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I510" s="1" t="s">
         <v>10</v>
@@ -14145,7 +14145,7 @@
         <v>57</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>10</v>
@@ -14174,7 +14174,7 @@
         <v>38</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>10</v>
@@ -14203,7 +14203,7 @@
         <v>39</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>10</v>
@@ -14232,7 +14232,7 @@
         <v>45</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>13</v>
@@ -14261,7 +14261,7 @@
         <v>43</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>13</v>
@@ -14290,7 +14290,7 @@
         <v>50</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>10</v>
@@ -14319,7 +14319,7 @@
         <v>48</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>10</v>
@@ -14348,7 +14348,7 @@
         <v>52</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>10</v>
@@ -14377,7 +14377,7 @@
         <v>53</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>10</v>
@@ -14406,7 +14406,7 @@
         <v>55</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I520" s="1" t="s">
         <v>10</v>
@@ -14435,7 +14435,7 @@
         <v>46</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>13</v>
@@ -14464,7 +14464,7 @@
         <v>44</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I522" s="1" t="s">
         <v>10</v>
@@ -14493,7 +14493,7 @@
         <v>47</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I523" s="1" t="s">
         <v>13</v>
@@ -14512,222 +14512,731 @@
       </c>
     </row>
     <row r="524" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H524" s="2"/>
-      <c r="I524" s="1"/>
-      <c r="J524" s="2"/>
-      <c r="K524" s="1"/>
+      <c r="D524" t="s">
+        <v>35</v>
+      </c>
+      <c r="E524">
+        <v>3161</v>
+      </c>
+      <c r="F524" t="s">
+        <v>40</v>
+      </c>
+      <c r="H524" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I524" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J524" s="2">
+        <v>0</v>
+      </c>
+      <c r="K524" s="1">
+        <v>46219.648379629631</v>
+      </c>
+      <c r="L524">
+        <v>0</v>
+      </c>
+      <c r="M524" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="525" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H525" s="2"/>
-      <c r="I525" s="1"/>
-      <c r="J525" s="2"/>
-      <c r="K525" s="1"/>
+      <c r="D525" t="s">
+        <v>35</v>
+      </c>
+      <c r="E525">
+        <v>3146</v>
+      </c>
+      <c r="F525" t="s">
+        <v>41</v>
+      </c>
+      <c r="H525" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I525" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J525" s="2">
+        <v>0</v>
+      </c>
+      <c r="K525" s="1">
+        <v>46219.649074074077</v>
+      </c>
+      <c r="L525">
+        <v>0</v>
+      </c>
+      <c r="M525" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="526" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H526" s="2"/>
-      <c r="I526" s="1"/>
-      <c r="J526" s="2"/>
-      <c r="K526" s="1"/>
+      <c r="D526" t="s">
+        <v>35</v>
+      </c>
+      <c r="E526">
+        <v>3160</v>
+      </c>
+      <c r="F526" t="s">
+        <v>57</v>
+      </c>
+      <c r="H526" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I526" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J526" s="2">
+        <v>0</v>
+      </c>
+      <c r="K526" s="1">
+        <v>46219.649768518517</v>
+      </c>
+      <c r="L526">
+        <v>0</v>
+      </c>
+      <c r="M526" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="527" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H527" s="2"/>
       <c r="I527" s="1"/>
       <c r="J527" s="2"/>
       <c r="K527" s="1"/>
+      <c r="M527" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="528" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H528" s="2"/>
-      <c r="I528" s="1"/>
-      <c r="J528" s="2"/>
-      <c r="K528" s="1"/>
-    </row>
-    <row r="529" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H529" s="2"/>
-      <c r="I529" s="1"/>
-      <c r="J529" s="2"/>
-      <c r="K529" s="1"/>
-    </row>
-    <row r="530" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H530" s="2"/>
-      <c r="I530" s="1"/>
-      <c r="J530" s="2"/>
-      <c r="K530" s="1"/>
-    </row>
-    <row r="531" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H531" s="2"/>
-      <c r="I531" s="1"/>
-      <c r="J531" s="2"/>
-      <c r="K531" s="1"/>
-    </row>
-    <row r="532" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H532" s="2"/>
-      <c r="I532" s="1"/>
-      <c r="J532" s="2"/>
-      <c r="K532" s="1"/>
-    </row>
-    <row r="533" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H533" s="2"/>
-      <c r="I533" s="1"/>
-      <c r="J533" s="2"/>
-      <c r="K533" s="1"/>
-    </row>
-    <row r="534" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H534" s="2"/>
-      <c r="I534" s="1"/>
-      <c r="J534" s="2"/>
-      <c r="K534" s="1"/>
-    </row>
-    <row r="535" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H535" s="2"/>
-      <c r="I535" s="1"/>
-      <c r="J535" s="2"/>
-      <c r="K535" s="1"/>
-    </row>
-    <row r="536" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H536" s="2"/>
-      <c r="I536" s="1"/>
-      <c r="J536" s="2"/>
-      <c r="K536" s="1"/>
-    </row>
-    <row r="537" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H537" s="2"/>
-      <c r="I537" s="1"/>
-      <c r="J537" s="2"/>
-      <c r="K537" s="1"/>
-    </row>
-    <row r="538" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H538" s="2"/>
-      <c r="I538" s="1"/>
-      <c r="J538" s="2"/>
-      <c r="K538" s="1"/>
-    </row>
-    <row r="539" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H539" s="2"/>
-      <c r="I539" s="1"/>
-      <c r="J539" s="2"/>
-      <c r="K539" s="1"/>
-    </row>
-    <row r="540" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H540" s="2"/>
-      <c r="I540" s="1"/>
-      <c r="J540" s="2"/>
-      <c r="K540" s="1"/>
-    </row>
-    <row r="541" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H541" s="2"/>
-      <c r="I541" s="1"/>
-      <c r="J541" s="2"/>
-      <c r="K541" s="1"/>
-    </row>
-    <row r="542" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H542" s="2"/>
-      <c r="I542" s="1"/>
-      <c r="J542" s="2"/>
-      <c r="K542" s="1"/>
-    </row>
-    <row r="543" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H543" s="2"/>
-      <c r="I543" s="1"/>
-      <c r="J543" s="2"/>
-      <c r="K543" s="1"/>
-    </row>
-    <row r="544" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H544" s="2"/>
-      <c r="I544" s="1"/>
-      <c r="J544" s="2"/>
-      <c r="K544" s="1"/>
-    </row>
-    <row r="545" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H545" s="2"/>
-      <c r="I545" s="1"/>
-      <c r="J545" s="2"/>
-      <c r="K545" s="1"/>
-    </row>
-    <row r="546" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H546" s="2"/>
-      <c r="I546" s="1"/>
-      <c r="J546" s="2"/>
-      <c r="K546" s="1"/>
-    </row>
-    <row r="547" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D528" t="s">
+        <v>35</v>
+      </c>
+      <c r="E528">
+        <v>3154</v>
+      </c>
+      <c r="F528" t="s">
+        <v>37</v>
+      </c>
+      <c r="H528" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I528" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J528" s="2">
+        <v>6.0416666666666665E-3</v>
+      </c>
+      <c r="K528" s="1">
+        <v>46219.649768518517</v>
+      </c>
+      <c r="L528">
+        <v>0</v>
+      </c>
+      <c r="M528" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="529" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D529" t="s">
+        <v>35</v>
+      </c>
+      <c r="E529">
+        <v>3144</v>
+      </c>
+      <c r="F529" t="s">
+        <v>38</v>
+      </c>
+      <c r="H529" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I529" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J529" s="2">
+        <v>0</v>
+      </c>
+      <c r="K529" s="1">
+        <v>46219.650462962964</v>
+      </c>
+      <c r="L529">
+        <v>0</v>
+      </c>
+      <c r="M529" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="530" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D530" t="s">
+        <v>35</v>
+      </c>
+      <c r="E530">
+        <v>3145</v>
+      </c>
+      <c r="F530" t="s">
+        <v>39</v>
+      </c>
+      <c r="H530" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I530" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J530" s="2">
+        <v>0</v>
+      </c>
+      <c r="K530" s="1">
+        <v>46219.65115740741</v>
+      </c>
+      <c r="L530">
+        <v>0</v>
+      </c>
+      <c r="M530" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="531" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D531" t="s">
+        <v>35</v>
+      </c>
+      <c r="E531">
+        <v>3151</v>
+      </c>
+      <c r="F531" t="s">
+        <v>45</v>
+      </c>
+      <c r="H531" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I531" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J531" s="2">
+        <v>0</v>
+      </c>
+      <c r="K531" s="1">
+        <v>46219.65185185185</v>
+      </c>
+      <c r="L531">
+        <v>0</v>
+      </c>
+      <c r="M531" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="532" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D532" t="s">
+        <v>35</v>
+      </c>
+      <c r="E532">
+        <v>3164</v>
+      </c>
+      <c r="F532" t="s">
+        <v>49</v>
+      </c>
+      <c r="H532" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I532" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J532" s="2">
+        <v>6.0069444444444441E-3</v>
+      </c>
+      <c r="K532" s="1">
+        <v>46219.65185185185</v>
+      </c>
+      <c r="L532">
+        <v>0</v>
+      </c>
+      <c r="M532" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="533" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D533" t="s">
+        <v>35</v>
+      </c>
+      <c r="E533">
+        <v>3163</v>
+      </c>
+      <c r="F533" t="s">
+        <v>43</v>
+      </c>
+      <c r="H533" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I533" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J533" s="2">
+        <v>0</v>
+      </c>
+      <c r="K533" s="1">
+        <v>46219.652546296296</v>
+      </c>
+      <c r="L533">
+        <v>0</v>
+      </c>
+      <c r="M533" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="534" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D534" t="s">
+        <v>35</v>
+      </c>
+      <c r="E534">
+        <v>3194</v>
+      </c>
+      <c r="F534" t="s">
+        <v>50</v>
+      </c>
+      <c r="H534" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I534" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J534" s="2">
+        <v>0</v>
+      </c>
+      <c r="K534" s="1">
+        <v>46219.627662037034</v>
+      </c>
+      <c r="L534">
+        <v>0</v>
+      </c>
+      <c r="M534" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="535" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D535" t="s">
+        <v>35</v>
+      </c>
+      <c r="E535">
+        <v>3162</v>
+      </c>
+      <c r="F535" t="s">
+        <v>48</v>
+      </c>
+      <c r="H535" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I535" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J535" s="2">
+        <v>0</v>
+      </c>
+      <c r="K535" s="1">
+        <v>46219.62835648148</v>
+      </c>
+      <c r="L535">
+        <v>0</v>
+      </c>
+      <c r="M535" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="536" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D536" t="s">
+        <v>35</v>
+      </c>
+      <c r="E536">
+        <v>3147</v>
+      </c>
+      <c r="F536" t="s">
+        <v>52</v>
+      </c>
+      <c r="H536" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I536" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J536" s="2">
+        <v>0</v>
+      </c>
+      <c r="K536" s="1">
+        <v>46219.62835648148</v>
+      </c>
+      <c r="L536">
+        <v>0</v>
+      </c>
+      <c r="M536" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="537" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D537" t="s">
+        <v>35</v>
+      </c>
+      <c r="E537">
+        <v>3156</v>
+      </c>
+      <c r="F537" t="s">
+        <v>53</v>
+      </c>
+      <c r="H537" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I537" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J537" s="2">
+        <v>9.4212962962962957E-3</v>
+      </c>
+      <c r="K537" s="1">
+        <v>46219.629050925927</v>
+      </c>
+      <c r="L537">
+        <v>0</v>
+      </c>
+      <c r="M537" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="538" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D538" t="s">
+        <v>35</v>
+      </c>
+      <c r="E538">
+        <v>3157</v>
+      </c>
+      <c r="F538" t="s">
+        <v>54</v>
+      </c>
+      <c r="H538" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I538" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J538" s="2">
+        <v>0</v>
+      </c>
+      <c r="K538" s="1">
+        <v>46219.629745370374</v>
+      </c>
+      <c r="L538">
+        <v>0</v>
+      </c>
+      <c r="M538" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="539" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D539" t="s">
+        <v>35</v>
+      </c>
+      <c r="E539">
+        <v>3158</v>
+      </c>
+      <c r="F539" t="s">
+        <v>55</v>
+      </c>
+      <c r="H539" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I539" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J539" s="2">
+        <v>1.0150462962962964E-2</v>
+      </c>
+      <c r="K539" s="1">
+        <v>46219.630439814813</v>
+      </c>
+      <c r="L539">
+        <v>0</v>
+      </c>
+      <c r="M539" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="540" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D540" t="s">
+        <v>35</v>
+      </c>
+      <c r="E540">
+        <v>3149</v>
+      </c>
+      <c r="F540" t="s">
+        <v>46</v>
+      </c>
+      <c r="H540" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I540" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J540" s="2">
+        <v>0</v>
+      </c>
+      <c r="K540" s="1">
+        <v>46219.630439814813</v>
+      </c>
+      <c r="L540">
+        <v>0</v>
+      </c>
+      <c r="M540" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="541" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D541" t="s">
+        <v>35</v>
+      </c>
+      <c r="E541">
+        <v>3159</v>
+      </c>
+      <c r="F541" t="s">
+        <v>56</v>
+      </c>
+      <c r="H541" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I541" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J541" s="2">
+        <v>1.170138888888889E-2</v>
+      </c>
+      <c r="K541" s="1">
+        <v>46219.63113425926</v>
+      </c>
+      <c r="L541">
+        <v>0</v>
+      </c>
+      <c r="M541" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="542" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D542" t="s">
+        <v>35</v>
+      </c>
+      <c r="E542">
+        <v>3150</v>
+      </c>
+      <c r="F542" t="s">
+        <v>44</v>
+      </c>
+      <c r="H542" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I542" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J542" s="2">
+        <v>6.7361111111111111E-3</v>
+      </c>
+      <c r="K542" s="1">
+        <v>46219.631828703707</v>
+      </c>
+      <c r="L542">
+        <v>0</v>
+      </c>
+      <c r="M542" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="543" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D543" t="s">
+        <v>35</v>
+      </c>
+      <c r="E543">
+        <v>3148</v>
+      </c>
+      <c r="F543" t="s">
+        <v>42</v>
+      </c>
+      <c r="H543" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I543" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J543" s="2">
+        <v>1.0173611111111111E-2</v>
+      </c>
+      <c r="K543" s="1">
+        <v>46219.632523148146</v>
+      </c>
+      <c r="L543">
+        <v>0</v>
+      </c>
+      <c r="M543" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="544" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D544" t="s">
+        <v>35</v>
+      </c>
+      <c r="E544">
+        <v>3155</v>
+      </c>
+      <c r="F544" t="s">
+        <v>51</v>
+      </c>
+      <c r="H544" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I544" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J544" s="2">
+        <v>6.4120370370370373E-3</v>
+      </c>
+      <c r="K544" s="1">
+        <v>46219.632523148146</v>
+      </c>
+      <c r="L544">
+        <v>0</v>
+      </c>
+      <c r="M544" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="545" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D545" t="s">
+        <v>35</v>
+      </c>
+      <c r="E545">
+        <v>3143</v>
+      </c>
+      <c r="F545" t="s">
+        <v>36</v>
+      </c>
+      <c r="H545" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I545" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J545" s="2">
+        <v>0</v>
+      </c>
+      <c r="K545" s="1">
+        <v>46219.633217592593</v>
+      </c>
+      <c r="L545">
+        <v>0</v>
+      </c>
+      <c r="M545" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="546" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D546" t="s">
+        <v>35</v>
+      </c>
+      <c r="E546">
+        <v>3153</v>
+      </c>
+      <c r="F546" t="s">
+        <v>47</v>
+      </c>
+      <c r="H546" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I546" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J546" s="2">
+        <v>0</v>
+      </c>
+      <c r="K546" s="1">
+        <v>46219.633912037039</v>
+      </c>
+      <c r="L546">
+        <v>0</v>
+      </c>
+      <c r="M546" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="547" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H547" s="2"/>
       <c r="I547" s="1"/>
       <c r="J547" s="2"/>
       <c r="K547" s="1"/>
     </row>
-    <row r="548" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="548" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H548" s="2"/>
       <c r="I548" s="1"/>
       <c r="J548" s="2"/>
       <c r="K548" s="1"/>
     </row>
-    <row r="549" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="549" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H549" s="2"/>
       <c r="I549" s="1"/>
       <c r="J549" s="2"/>
       <c r="K549" s="1"/>
     </row>
-    <row r="550" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="550" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H550" s="2"/>
       <c r="I550" s="1"/>
       <c r="J550" s="2"/>
       <c r="K550" s="1"/>
     </row>
-    <row r="551" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="551" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H551" s="2"/>
       <c r="I551" s="1"/>
       <c r="J551" s="2"/>
       <c r="K551" s="1"/>
     </row>
-    <row r="552" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="552" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H552" s="2"/>
       <c r="I552" s="1"/>
       <c r="J552" s="2"/>
       <c r="K552" s="1"/>
     </row>
-    <row r="553" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="553" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H553" s="2"/>
       <c r="I553" s="1"/>
       <c r="J553" s="2"/>
       <c r="K553" s="1"/>
     </row>
-    <row r="554" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="554" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H554" s="2"/>
       <c r="I554" s="1"/>
       <c r="J554" s="2"/>
       <c r="K554" s="1"/>
     </row>
-    <row r="555" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="555" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H555" s="2"/>
       <c r="I555" s="1"/>
       <c r="J555" s="2"/>
       <c r="K555" s="1"/>
     </row>
-    <row r="556" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="556" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H556" s="2"/>
       <c r="I556" s="1"/>
       <c r="J556" s="2"/>
       <c r="K556" s="1"/>
     </row>
-    <row r="557" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="557" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H557" s="2"/>
       <c r="I557" s="1"/>
       <c r="J557" s="2"/>
       <c r="K557" s="1"/>
     </row>
-    <row r="558" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="558" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H558" s="2"/>
       <c r="I558" s="1"/>
       <c r="J558" s="2"/>
       <c r="K558" s="1"/>
     </row>
-    <row r="559" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="559" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H559" s="2"/>
       <c r="I559" s="1"/>
       <c r="J559" s="2"/>
       <c r="K559" s="1"/>
     </row>
-    <row r="560" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="560" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H560" s="2"/>
       <c r="I560" s="1"/>
       <c r="J560" s="2"/>
@@ -16178,6 +16687,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -16453,6 +16963,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -19538,6 +20049,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -22861,6 +23373,7 @@
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1934" s="1"/>
+      <c r="J1934" s="2"/>
       <c r="K1934" s="1"/>
     </row>
     <row r="1935" spans="8:11" x14ac:dyDescent="0.3">
@@ -22871,14 +23384,17 @@
     <row r="1936" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
+      <c r="K1936" s="1"/>
     </row>
     <row r="1937" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
+      <c r="J1937" s="2"/>
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1938" s="1"/>
+      <c r="J1938" s="2"/>
       <c r="K1938" s="1"/>
     </row>
     <row r="1939" spans="8:11" x14ac:dyDescent="0.3">
@@ -22904,6 +23420,7 @@
     <row r="1943" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
+      <c r="J1943" s="2"/>
       <c r="K1943" s="1"/>
     </row>
     <row r="1944" spans="8:11" x14ac:dyDescent="0.3">
@@ -22913,9 +23430,11 @@
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
+      <c r="K1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1946" s="1"/>
+      <c r="J1946" s="2"/>
       <c r="K1946" s="1"/>
     </row>
     <row r="1947" spans="8:11" x14ac:dyDescent="0.3">
@@ -49853,6 +50372,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -49860,6 +50380,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -49867,6 +50388,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -49882,6 +50404,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -49891,6 +50414,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -49898,9 +50422,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -49908,12 +50438,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -49921,12 +50454,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -49938,9 +50474,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -49955,6 +50493,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -49981,6 +50520,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -49991,7 +50531,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -49999,6 +50544,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -50010,6 +50556,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -50017,6 +50564,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -50031,13 +50579,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -50048,15 +50602,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -50072,6 +50629,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -50090,6 +50648,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -50101,6 +50660,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -50118,18 +50678,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -50158,6 +50723,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -50165,9 +50731,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -50190,12 +50758,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -50210,9 +50781,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -50228,12 +50801,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -50254,6 +50829,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -50265,9 +50841,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -50279,6 +50857,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -50318,9 +50897,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -50328,9 +50909,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -50341,6 +50924,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -50348,18 +50932,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -50367,6 +50959,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -50377,6 +50970,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -50403,15 +50997,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -50433,6 +51031,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -50440,9 +51039,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -50450,6 +51051,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -50461,6 +51063,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -50475,6 +51078,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -50484,6 +51091,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -50495,6 +51103,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -50505,10 +51114,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -50516,6 +51130,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -50530,6 +51145,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -50552,6 +51168,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -50571,25 +51188,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -50597,6 +51226,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -50604,15 +51234,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -50626,6 +51263,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -50644,9 +51282,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -50654,9 +51294,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -50664,6 +51306,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -50680,10 +51323,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE1899FF-B52F-453E-96D2-57CC265C932D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A464F257-BF2C-4A3C-8978-E8FF0F420C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="57">
   <si>
     <t>Company Name</t>
   </si>
@@ -155,10 +155,7 @@
     <t>Tres Dimick</t>
   </si>
   <si>
-    <t>Blair Roberts</t>
-  </si>
-  <si>
-    <t>Brian Apgood</t>
+    <t>*New Hire*</t>
   </si>
   <si>
     <t>Chad Smith</t>
@@ -213,9 +210,6 @@
   </si>
   <si>
     <t>Steve Stoner</t>
-  </si>
-  <si>
-    <t>Julia Green</t>
   </si>
 </sst>
 </file>
@@ -589,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -665,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>36</v>
       </c>
@@ -702,7 +696,7 @@
         <v>3144</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -731,7 +725,7 @@
         <v>3145</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -760,7 +754,7 @@
         <v>3152</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -789,7 +783,7 @@
         <v>3146</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -818,7 +812,7 @@
         <v>3148</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -839,7 +833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -847,7 +841,7 @@
         <v>3163</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -876,7 +870,7 @@
         <v>3150</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -905,7 +899,7 @@
         <v>3151</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -934,7 +928,7 @@
         <v>3149</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -955,7 +949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>36</v>
       </c>
@@ -963,7 +957,7 @@
         <v>3153</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -992,7 +986,7 @@
         <v>3162</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -1021,7 +1015,7 @@
         <v>3164</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -1050,7 +1044,7 @@
         <v>3194</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -1079,7 +1073,7 @@
         <v>3155</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -1108,7 +1102,7 @@
         <v>3147</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -1137,7 +1131,7 @@
         <v>3156</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -1166,7 +1160,7 @@
         <v>3157</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -1195,7 +1189,7 @@
         <v>3158</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -1224,7 +1218,7 @@
         <v>3159</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -1253,7 +1247,7 @@
         <v>3160</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -1282,7 +1276,7 @@
         <v>3161</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -1332,7 +1326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>36</v>
       </c>
@@ -1369,7 +1363,7 @@
         <v>3144</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -1398,7 +1392,7 @@
         <v>3145</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -1427,7 +1421,7 @@
         <v>3152</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -1456,7 +1450,7 @@
         <v>3146</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -1485,7 +1479,7 @@
         <v>3148</v>
       </c>
       <c r="D31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s">
         <v>21</v>
@@ -1506,7 +1500,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>36</v>
       </c>
@@ -1514,7 +1508,7 @@
         <v>3163</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -1543,7 +1537,7 @@
         <v>3150</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -1572,7 +1566,7 @@
         <v>3151</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -1601,7 +1595,7 @@
         <v>3149</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -1630,7 +1624,7 @@
         <v>3153</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -1659,7 +1653,7 @@
         <v>3162</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -1688,7 +1682,7 @@
         <v>3164</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -1717,7 +1711,7 @@
         <v>3194</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -1746,7 +1740,7 @@
         <v>3155</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F40" t="s">
         <v>21</v>
@@ -1775,7 +1769,7 @@
         <v>3147</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -1796,7 +1790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>36</v>
       </c>
@@ -1804,7 +1798,7 @@
         <v>3156</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F42" t="s">
         <v>21</v>
@@ -1833,7 +1827,7 @@
         <v>3157</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -1862,7 +1856,7 @@
         <v>3158</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
@@ -1891,7 +1885,7 @@
         <v>3159</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
         <v>21</v>
@@ -1920,7 +1914,7 @@
         <v>3160</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
         <v>21</v>
@@ -1949,7 +1943,7 @@
         <v>3161</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F47" t="s">
         <v>21</v>
@@ -2007,7 +2001,7 @@
         <v>3194</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -2036,7 +2030,7 @@
         <v>3194</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F50" t="s">
         <v>35</v>
@@ -2123,7 +2117,7 @@
         <v>3144</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -2144,7 +2138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>36</v>
       </c>
@@ -2152,7 +2146,7 @@
         <v>3145</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -2181,7 +2175,7 @@
         <v>3152</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -2210,7 +2204,7 @@
         <v>3146</v>
       </c>
       <c r="D56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -2239,7 +2233,7 @@
         <v>3148</v>
       </c>
       <c r="D57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -2268,7 +2262,7 @@
         <v>3163</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -2297,7 +2291,7 @@
         <v>3150</v>
       </c>
       <c r="D59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -2326,7 +2320,7 @@
         <v>3151</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -2355,7 +2349,7 @@
         <v>3149</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -2392,7 +2386,7 @@
         <v>3153</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -2450,7 +2444,7 @@
         <v>3162</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -2479,7 +2473,7 @@
         <v>3164</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -2508,7 +2502,7 @@
         <v>3194</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -2545,7 +2539,7 @@
         <v>3155</v>
       </c>
       <c r="D69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -2574,7 +2568,7 @@
         <v>3147</v>
       </c>
       <c r="D70" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -2603,7 +2597,7 @@
         <v>3156</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -2632,7 +2626,7 @@
         <v>3157</v>
       </c>
       <c r="D72" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -2661,7 +2655,7 @@
         <v>3158</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -2682,7 +2676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>36</v>
       </c>
@@ -2690,7 +2684,7 @@
         <v>3159</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -2719,7 +2713,7 @@
         <v>3160</v>
       </c>
       <c r="D75" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -2748,7 +2742,7 @@
         <v>3161</v>
       </c>
       <c r="D76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -2835,7 +2829,7 @@
         <v>3144</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F79" t="s">
         <v>22</v>
@@ -2864,7 +2858,7 @@
         <v>3145</v>
       </c>
       <c r="D80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F80" t="s">
         <v>22</v>
@@ -2893,7 +2887,7 @@
         <v>3152</v>
       </c>
       <c r="D81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F81" t="s">
         <v>22</v>
@@ -2914,7 +2908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>36</v>
       </c>
@@ -2922,7 +2916,7 @@
         <v>3146</v>
       </c>
       <c r="D82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F82" t="s">
         <v>22</v>
@@ -2951,7 +2945,7 @@
         <v>3148</v>
       </c>
       <c r="D83" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F83" t="s">
         <v>22</v>
@@ -2988,7 +2982,7 @@
         <v>3163</v>
       </c>
       <c r="D85" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F85" t="s">
         <v>22</v>
@@ -3025,7 +3019,7 @@
         <v>3150</v>
       </c>
       <c r="D87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F87" t="s">
         <v>22</v>
@@ -3054,7 +3048,7 @@
         <v>3151</v>
       </c>
       <c r="D88" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F88" t="s">
         <v>22</v>
@@ -3083,7 +3077,7 @@
         <v>3149</v>
       </c>
       <c r="D89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F89" t="s">
         <v>22</v>
@@ -3120,7 +3114,7 @@
         <v>3153</v>
       </c>
       <c r="D91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F91" t="s">
         <v>22</v>
@@ -3141,7 +3135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>36</v>
       </c>
@@ -3178,7 +3172,7 @@
         <v>3162</v>
       </c>
       <c r="D93" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F93" t="s">
         <v>22</v>
@@ -3207,7 +3201,7 @@
         <v>3164</v>
       </c>
       <c r="D94" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F94" t="s">
         <v>22</v>
@@ -3236,7 +3230,7 @@
         <v>3194</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F95" t="s">
         <v>22</v>
@@ -3265,7 +3259,7 @@
         <v>3155</v>
       </c>
       <c r="D96" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F96" t="s">
         <v>22</v>
@@ -3302,7 +3296,7 @@
         <v>3147</v>
       </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F98" t="s">
         <v>22</v>
@@ -3331,7 +3325,7 @@
         <v>3156</v>
       </c>
       <c r="D99" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F99" t="s">
         <v>22</v>
@@ -3360,7 +3354,7 @@
         <v>3157</v>
       </c>
       <c r="D100" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F100" t="s">
         <v>22</v>
@@ -3389,7 +3383,7 @@
         <v>3158</v>
       </c>
       <c r="D101" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F101" t="s">
         <v>22</v>
@@ -3418,7 +3412,7 @@
         <v>3159</v>
       </c>
       <c r="D102" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F102" t="s">
         <v>22</v>
@@ -3447,7 +3441,7 @@
         <v>3160</v>
       </c>
       <c r="D103" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F103" t="s">
         <v>22</v>
@@ -3484,7 +3478,7 @@
         <v>3161</v>
       </c>
       <c r="D105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F105" t="s">
         <v>22</v>
@@ -3571,7 +3565,7 @@
         <v>3144</v>
       </c>
       <c r="D108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F108" t="s">
         <v>19</v>
@@ -3600,7 +3594,7 @@
         <v>3145</v>
       </c>
       <c r="D109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F109" t="s">
         <v>19</v>
@@ -3629,7 +3623,7 @@
         <v>3152</v>
       </c>
       <c r="D110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F110" t="s">
         <v>19</v>
@@ -3658,7 +3652,7 @@
         <v>3155</v>
       </c>
       <c r="D111" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F111" t="s">
         <v>19</v>
@@ -3679,7 +3673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>36</v>
       </c>
@@ -3687,7 +3681,7 @@
         <v>3148</v>
       </c>
       <c r="D112" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F112" t="s">
         <v>19</v>
@@ -3716,7 +3710,7 @@
         <v>3163</v>
       </c>
       <c r="D113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F113" t="s">
         <v>19</v>
@@ -3745,7 +3739,7 @@
         <v>3149</v>
       </c>
       <c r="D114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F114" t="s">
         <v>19</v>
@@ -3766,7 +3760,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>36</v>
       </c>
@@ -3774,7 +3768,7 @@
         <v>3150</v>
       </c>
       <c r="D115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F115" t="s">
         <v>19</v>
@@ -3803,7 +3797,7 @@
         <v>3151</v>
       </c>
       <c r="D116" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F116" t="s">
         <v>19</v>
@@ -3832,7 +3826,7 @@
         <v>3146</v>
       </c>
       <c r="D117" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F117" t="s">
         <v>19</v>
@@ -3861,7 +3855,7 @@
         <v>3153</v>
       </c>
       <c r="D118" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F118" t="s">
         <v>19</v>
@@ -3927,7 +3921,7 @@
         <v>3162</v>
       </c>
       <c r="D121" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F121" t="s">
         <v>19</v>
@@ -3956,7 +3950,7 @@
         <v>3164</v>
       </c>
       <c r="D122" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
@@ -3985,7 +3979,7 @@
         <v>3194</v>
       </c>
       <c r="D123" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F123" t="s">
         <v>19</v>
@@ -4014,7 +4008,7 @@
         <v>3429</v>
       </c>
       <c r="D124" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F124" t="s">
         <v>19</v>
@@ -4043,7 +4037,7 @@
         <v>3147</v>
       </c>
       <c r="D125" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F125" t="s">
         <v>19</v>
@@ -4072,7 +4066,7 @@
         <v>3156</v>
       </c>
       <c r="D126" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F126" t="s">
         <v>19</v>
@@ -4093,7 +4087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>36</v>
       </c>
@@ -4101,7 +4095,7 @@
         <v>3157</v>
       </c>
       <c r="D127" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F127" t="s">
         <v>19</v>
@@ -4130,7 +4124,7 @@
         <v>3158</v>
       </c>
       <c r="D128" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F128" t="s">
         <v>19</v>
@@ -4159,7 +4153,7 @@
         <v>3160</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F129" t="s">
         <v>19</v>
@@ -4188,7 +4182,7 @@
         <v>3159</v>
       </c>
       <c r="D130" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F130" t="s">
         <v>19</v>
@@ -4217,7 +4211,7 @@
         <v>3161</v>
       </c>
       <c r="D131" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F131" t="s">
         <v>19</v>
@@ -4312,7 +4306,7 @@
         <v>3144</v>
       </c>
       <c r="D135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F135" t="s">
         <v>21</v>
@@ -4341,7 +4335,7 @@
         <v>3145</v>
       </c>
       <c r="D136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F136" t="s">
         <v>21</v>
@@ -4370,7 +4364,7 @@
         <v>3152</v>
       </c>
       <c r="D137" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F137" t="s">
         <v>21</v>
@@ -4399,7 +4393,7 @@
         <v>3155</v>
       </c>
       <c r="D138" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F138" t="s">
         <v>21</v>
@@ -4428,7 +4422,7 @@
         <v>3148</v>
       </c>
       <c r="D139" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F139" t="s">
         <v>21</v>
@@ -4457,7 +4451,7 @@
         <v>3163</v>
       </c>
       <c r="D140" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F140" t="s">
         <v>21</v>
@@ -4486,7 +4480,7 @@
         <v>3149</v>
       </c>
       <c r="D141" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F141" t="s">
         <v>21</v>
@@ -4523,7 +4517,7 @@
         <v>3150</v>
       </c>
       <c r="D143" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F143" t="s">
         <v>21</v>
@@ -4552,7 +4546,7 @@
         <v>3151</v>
       </c>
       <c r="D144" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F144" t="s">
         <v>21</v>
@@ -4581,7 +4575,7 @@
         <v>3146</v>
       </c>
       <c r="D145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F145" t="s">
         <v>21</v>
@@ -4610,7 +4604,7 @@
         <v>3153</v>
       </c>
       <c r="D146" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F146" t="s">
         <v>21</v>
@@ -4668,7 +4662,7 @@
         <v>3162</v>
       </c>
       <c r="D148" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F148" t="s">
         <v>21</v>
@@ -4697,7 +4691,7 @@
         <v>3194</v>
       </c>
       <c r="D149" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F149" t="s">
         <v>21</v>
@@ -4734,7 +4728,7 @@
         <v>3429</v>
       </c>
       <c r="D151" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F151" t="s">
         <v>21</v>
@@ -4763,7 +4757,7 @@
         <v>3147</v>
       </c>
       <c r="D152" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F152" t="s">
         <v>21</v>
@@ -4792,7 +4786,7 @@
         <v>3156</v>
       </c>
       <c r="D153" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F153" t="s">
         <v>21</v>
@@ -4821,7 +4815,7 @@
         <v>3157</v>
       </c>
       <c r="D154" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F154" t="s">
         <v>21</v>
@@ -4850,7 +4844,7 @@
         <v>3158</v>
       </c>
       <c r="D155" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F155" t="s">
         <v>21</v>
@@ -4879,7 +4873,7 @@
         <v>3160</v>
       </c>
       <c r="D156" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F156" t="s">
         <v>21</v>
@@ -4908,7 +4902,7 @@
         <v>3159</v>
       </c>
       <c r="D157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F157" t="s">
         <v>21</v>
@@ -4937,7 +4931,7 @@
         <v>3161</v>
       </c>
       <c r="D158" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F158" t="s">
         <v>21</v>
@@ -4966,7 +4960,7 @@
         <v>3164</v>
       </c>
       <c r="D159" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F159" t="s">
         <v>21</v>
@@ -5024,7 +5018,7 @@
         <v>3144</v>
       </c>
       <c r="D161" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F161" t="s">
         <v>20</v>
@@ -5053,7 +5047,7 @@
         <v>3145</v>
       </c>
       <c r="D162" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F162" t="s">
         <v>20</v>
@@ -5082,7 +5076,7 @@
         <v>3152</v>
       </c>
       <c r="D163" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F163" t="s">
         <v>20</v>
@@ -5111,7 +5105,7 @@
         <v>3148</v>
       </c>
       <c r="D164" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F164" t="s">
         <v>20</v>
@@ -5140,7 +5134,7 @@
         <v>3163</v>
       </c>
       <c r="D165" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F165" t="s">
         <v>20</v>
@@ -5169,7 +5163,7 @@
         <v>3149</v>
       </c>
       <c r="D166" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F166" t="s">
         <v>20</v>
@@ -5198,7 +5192,7 @@
         <v>3150</v>
       </c>
       <c r="D167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F167" t="s">
         <v>20</v>
@@ -5227,7 +5221,7 @@
         <v>3151</v>
       </c>
       <c r="D168" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F168" t="s">
         <v>20</v>
@@ -5256,7 +5250,7 @@
         <v>3155</v>
       </c>
       <c r="D169" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F169" t="s">
         <v>20</v>
@@ -5314,7 +5308,7 @@
         <v>3194</v>
       </c>
       <c r="D171" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F171" t="s">
         <v>20</v>
@@ -5351,7 +5345,7 @@
         <v>3429</v>
       </c>
       <c r="D173" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F173" t="s">
         <v>20</v>
@@ -5372,7 +5366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>36</v>
       </c>
@@ -5380,7 +5374,7 @@
         <v>3147</v>
       </c>
       <c r="D174" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F174" t="s">
         <v>20</v>
@@ -5409,7 +5403,7 @@
         <v>3156</v>
       </c>
       <c r="D175" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F175" t="s">
         <v>20</v>
@@ -5438,7 +5432,7 @@
         <v>3157</v>
       </c>
       <c r="D176" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F176" t="s">
         <v>20</v>
@@ -5475,7 +5469,7 @@
         <v>3158</v>
       </c>
       <c r="D178" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F178" t="s">
         <v>20</v>
@@ -5496,7 +5490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>36</v>
       </c>
@@ -5504,7 +5498,7 @@
         <v>3146</v>
       </c>
       <c r="D179" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F179" t="s">
         <v>20</v>
@@ -5533,7 +5527,7 @@
         <v>3160</v>
       </c>
       <c r="D180" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F180" t="s">
         <v>20</v>
@@ -5562,7 +5556,7 @@
         <v>3162</v>
       </c>
       <c r="D181" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F181" t="s">
         <v>20</v>
@@ -5591,7 +5585,7 @@
         <v>3153</v>
       </c>
       <c r="D182" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F182" t="s">
         <v>20</v>
@@ -5620,7 +5614,7 @@
         <v>3159</v>
       </c>
       <c r="D183" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F183" t="s">
         <v>20</v>
@@ -5678,7 +5672,7 @@
         <v>3161</v>
       </c>
       <c r="D185" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F185" t="s">
         <v>20</v>
@@ -5707,7 +5701,7 @@
         <v>3164</v>
       </c>
       <c r="D186" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F186" t="s">
         <v>20</v>
@@ -5736,7 +5730,7 @@
         <v>3146</v>
       </c>
       <c r="D187" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F187" t="s">
         <v>31</v>
@@ -5786,7 +5780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>36</v>
       </c>
@@ -5794,7 +5788,7 @@
         <v>3144</v>
       </c>
       <c r="D189" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F189" t="s">
         <v>31</v>
@@ -5823,7 +5817,7 @@
         <v>3145</v>
       </c>
       <c r="D190" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -5852,7 +5846,7 @@
         <v>3152</v>
       </c>
       <c r="D191" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F191" t="s">
         <v>31</v>
@@ -5881,7 +5875,7 @@
         <v>3148</v>
       </c>
       <c r="D192" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F192" t="s">
         <v>31</v>
@@ -5910,7 +5904,7 @@
         <v>3163</v>
       </c>
       <c r="D193" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F193" t="s">
         <v>31</v>
@@ -5939,7 +5933,7 @@
         <v>3149</v>
       </c>
       <c r="D194" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F194" t="s">
         <v>31</v>
@@ -5968,7 +5962,7 @@
         <v>3150</v>
       </c>
       <c r="D195" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F195" t="s">
         <v>31</v>
@@ -5997,7 +5991,7 @@
         <v>3151</v>
       </c>
       <c r="D196" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F196" t="s">
         <v>31</v>
@@ -6026,7 +6020,7 @@
         <v>3155</v>
       </c>
       <c r="D197" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F197" t="s">
         <v>31</v>
@@ -6092,7 +6086,7 @@
         <v>3194</v>
       </c>
       <c r="D200" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F200" t="s">
         <v>31</v>
@@ -6129,7 +6123,7 @@
         <v>3429</v>
       </c>
       <c r="D202" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F202" t="s">
         <v>31</v>
@@ -6166,7 +6160,7 @@
         <v>3147</v>
       </c>
       <c r="D204" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F204" t="s">
         <v>31</v>
@@ -6195,7 +6189,7 @@
         <v>3156</v>
       </c>
       <c r="D205" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F205" t="s">
         <v>31</v>
@@ -6224,7 +6218,7 @@
         <v>3157</v>
       </c>
       <c r="D206" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F206" t="s">
         <v>31</v>
@@ -6245,7 +6239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -6261,7 +6255,7 @@
         <v>3158</v>
       </c>
       <c r="D208" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F208" t="s">
         <v>31</v>
@@ -6290,7 +6284,7 @@
         <v>3162</v>
       </c>
       <c r="D209" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F209" t="s">
         <v>31</v>
@@ -6319,7 +6313,7 @@
         <v>3160</v>
       </c>
       <c r="D210" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F210" t="s">
         <v>31</v>
@@ -6348,7 +6342,7 @@
         <v>3153</v>
       </c>
       <c r="D211" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F211" t="s">
         <v>31</v>
@@ -6377,7 +6371,7 @@
         <v>3159</v>
       </c>
       <c r="D212" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F212" t="s">
         <v>31</v>
@@ -6435,7 +6429,7 @@
         <v>3161</v>
       </c>
       <c r="D214" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F214" t="s">
         <v>31</v>
@@ -6464,7 +6458,7 @@
         <v>3164</v>
       </c>
       <c r="D215" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F215" t="s">
         <v>31</v>
@@ -6493,7 +6487,7 @@
         <v>3146</v>
       </c>
       <c r="D216" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F216" t="s">
         <v>29</v>
@@ -6551,7 +6545,7 @@
         <v>3144</v>
       </c>
       <c r="D218" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F218" t="s">
         <v>29</v>
@@ -6580,7 +6574,7 @@
         <v>3145</v>
       </c>
       <c r="D219" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F219" t="s">
         <v>29</v>
@@ -6609,7 +6603,7 @@
         <v>3152</v>
       </c>
       <c r="D220" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F220" t="s">
         <v>29</v>
@@ -6638,7 +6632,7 @@
         <v>3148</v>
       </c>
       <c r="D221" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F221" t="s">
         <v>29</v>
@@ -6667,7 +6661,7 @@
         <v>3163</v>
       </c>
       <c r="D222" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F222" t="s">
         <v>29</v>
@@ -6696,7 +6690,7 @@
         <v>3149</v>
       </c>
       <c r="D223" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F223" t="s">
         <v>29</v>
@@ -6725,7 +6719,7 @@
         <v>3150</v>
       </c>
       <c r="D224" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F224" t="s">
         <v>29</v>
@@ -6754,7 +6748,7 @@
         <v>3151</v>
       </c>
       <c r="D225" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F225" t="s">
         <v>29</v>
@@ -6783,7 +6777,7 @@
         <v>3155</v>
       </c>
       <c r="D226" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F226" t="s">
         <v>29</v>
@@ -6841,7 +6835,7 @@
         <v>3194</v>
       </c>
       <c r="D228" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F228" t="s">
         <v>29</v>
@@ -6870,7 +6864,7 @@
         <v>3429</v>
       </c>
       <c r="D229" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F229" t="s">
         <v>29</v>
@@ -6899,7 +6893,7 @@
         <v>3147</v>
       </c>
       <c r="D230" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F230" t="s">
         <v>29</v>
@@ -6928,7 +6922,7 @@
         <v>3156</v>
       </c>
       <c r="D231" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F231" t="s">
         <v>29</v>
@@ -6957,7 +6951,7 @@
         <v>3157</v>
       </c>
       <c r="D232" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F232" t="s">
         <v>29</v>
@@ -6986,7 +6980,7 @@
         <v>3158</v>
       </c>
       <c r="D233" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F233" t="s">
         <v>29</v>
@@ -7015,7 +7009,7 @@
         <v>3162</v>
       </c>
       <c r="D234" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F234" t="s">
         <v>29</v>
@@ -7044,7 +7038,7 @@
         <v>3160</v>
       </c>
       <c r="D235" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F235" t="s">
         <v>29</v>
@@ -7073,7 +7067,7 @@
         <v>3153</v>
       </c>
       <c r="D236" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F236" t="s">
         <v>29</v>
@@ -7102,7 +7096,7 @@
         <v>3159</v>
       </c>
       <c r="D237" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F237" t="s">
         <v>29</v>
@@ -7152,7 +7146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>36</v>
       </c>
@@ -7160,7 +7154,7 @@
         <v>3161</v>
       </c>
       <c r="D239" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F239" t="s">
         <v>29</v>
@@ -7189,7 +7183,7 @@
         <v>3164</v>
       </c>
       <c r="D240" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F240" t="s">
         <v>29</v>
@@ -7218,7 +7212,7 @@
         <v>3146</v>
       </c>
       <c r="D241" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F241" t="s">
         <v>18</v>
@@ -7276,7 +7270,7 @@
         <v>3144</v>
       </c>
       <c r="D243" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F243" t="s">
         <v>18</v>
@@ -7305,7 +7299,7 @@
         <v>3145</v>
       </c>
       <c r="D244" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F244" t="s">
         <v>18</v>
@@ -7334,7 +7328,7 @@
         <v>3152</v>
       </c>
       <c r="D245" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F245" t="s">
         <v>18</v>
@@ -7363,7 +7357,7 @@
         <v>3148</v>
       </c>
       <c r="D246" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F246" t="s">
         <v>18</v>
@@ -7392,7 +7386,7 @@
         <v>3163</v>
       </c>
       <c r="D247" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F247" t="s">
         <v>18</v>
@@ -7421,7 +7415,7 @@
         <v>3149</v>
       </c>
       <c r="D248" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F248" t="s">
         <v>18</v>
@@ -7450,7 +7444,7 @@
         <v>3155</v>
       </c>
       <c r="D249" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F249" t="s">
         <v>18</v>
@@ -7479,7 +7473,7 @@
         <v>3150</v>
       </c>
       <c r="D250" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F250" t="s">
         <v>18</v>
@@ -7508,7 +7502,7 @@
         <v>3151</v>
       </c>
       <c r="D251" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F251" t="s">
         <v>18</v>
@@ -7566,7 +7560,7 @@
         <v>3194</v>
       </c>
       <c r="D253" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F253" t="s">
         <v>18</v>
@@ -7595,7 +7589,7 @@
         <v>3429</v>
       </c>
       <c r="D254" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F254" t="s">
         <v>18</v>
@@ -7624,7 +7618,7 @@
         <v>3147</v>
       </c>
       <c r="D255" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F255" t="s">
         <v>18</v>
@@ -7653,7 +7647,7 @@
         <v>3156</v>
       </c>
       <c r="D256" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F256" t="s">
         <v>18</v>
@@ -7682,7 +7676,7 @@
         <v>3157</v>
       </c>
       <c r="D257" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F257" t="s">
         <v>18</v>
@@ -7719,7 +7713,7 @@
         <v>3158</v>
       </c>
       <c r="D259" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F259" t="s">
         <v>18</v>
@@ -7748,7 +7742,7 @@
         <v>3162</v>
       </c>
       <c r="D260" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F260" t="s">
         <v>18</v>
@@ -7777,7 +7771,7 @@
         <v>3164</v>
       </c>
       <c r="D261" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F261" t="s">
         <v>18</v>
@@ -7806,7 +7800,7 @@
         <v>3160</v>
       </c>
       <c r="D262" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F262" t="s">
         <v>18</v>
@@ -7843,7 +7837,7 @@
         <v>3161</v>
       </c>
       <c r="D264" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F264" t="s">
         <v>18</v>
@@ -7872,7 +7866,7 @@
         <v>3153</v>
       </c>
       <c r="D265" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F265" t="s">
         <v>18</v>
@@ -7901,7 +7895,7 @@
         <v>3159</v>
       </c>
       <c r="D266" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F266" t="s">
         <v>18</v>
@@ -7967,7 +7961,7 @@
         <v>3146</v>
       </c>
       <c r="D269" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F269" t="s">
         <v>16</v>
@@ -8025,7 +8019,7 @@
         <v>3144</v>
       </c>
       <c r="D271" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F271" t="s">
         <v>16</v>
@@ -8054,7 +8048,7 @@
         <v>3145</v>
       </c>
       <c r="D272" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F272" t="s">
         <v>16</v>
@@ -8083,7 +8077,7 @@
         <v>3152</v>
       </c>
       <c r="D273" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F273" t="s">
         <v>16</v>
@@ -8112,7 +8106,7 @@
         <v>3163</v>
       </c>
       <c r="D274" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F274" t="s">
         <v>16</v>
@@ -8141,7 +8135,7 @@
         <v>3149</v>
       </c>
       <c r="D275" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F275" t="s">
         <v>16</v>
@@ -8170,7 +8164,7 @@
         <v>3151</v>
       </c>
       <c r="D276" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F276" t="s">
         <v>16</v>
@@ -8228,7 +8222,7 @@
         <v>3194</v>
       </c>
       <c r="D278" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -8257,7 +8251,7 @@
         <v>3429</v>
       </c>
       <c r="D279" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F279" t="s">
         <v>16</v>
@@ -8286,7 +8280,7 @@
         <v>3147</v>
       </c>
       <c r="D280" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -8315,7 +8309,7 @@
         <v>3156</v>
       </c>
       <c r="D281" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F281" t="s">
         <v>16</v>
@@ -8344,7 +8338,7 @@
         <v>3157</v>
       </c>
       <c r="D282" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F282" t="s">
         <v>16</v>
@@ -8381,7 +8375,7 @@
         <v>3158</v>
       </c>
       <c r="D284" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F284" t="s">
         <v>16</v>
@@ -8410,7 +8404,7 @@
         <v>3148</v>
       </c>
       <c r="D285" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F285" t="s">
         <v>16</v>
@@ -8439,7 +8433,7 @@
         <v>3162</v>
       </c>
       <c r="D286" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F286" t="s">
         <v>16</v>
@@ -8468,7 +8462,7 @@
         <v>3164</v>
       </c>
       <c r="D287" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F287" t="s">
         <v>16</v>
@@ -8497,7 +8491,7 @@
         <v>3160</v>
       </c>
       <c r="D288" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -8526,7 +8520,7 @@
         <v>3161</v>
       </c>
       <c r="D289" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F289" t="s">
         <v>16</v>
@@ -8555,7 +8549,7 @@
         <v>3153</v>
       </c>
       <c r="D290" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F290" t="s">
         <v>16</v>
@@ -8584,7 +8578,7 @@
         <v>3159</v>
       </c>
       <c r="D291" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F291" t="s">
         <v>16</v>
@@ -8613,7 +8607,7 @@
         <v>3150</v>
       </c>
       <c r="D292" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F292" t="s">
         <v>16</v>
@@ -8642,7 +8636,7 @@
         <v>3155</v>
       </c>
       <c r="D293" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -8708,7 +8702,7 @@
         <v>3146</v>
       </c>
       <c r="D296" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F296" t="s">
         <v>17</v>
@@ -8766,7 +8760,7 @@
         <v>3144</v>
       </c>
       <c r="D298" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F298" t="s">
         <v>17</v>
@@ -8803,7 +8797,7 @@
         <v>3145</v>
       </c>
       <c r="D300" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F300" t="s">
         <v>17</v>
@@ -8832,7 +8826,7 @@
         <v>3152</v>
       </c>
       <c r="D301" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F301" t="s">
         <v>17</v>
@@ -8861,7 +8855,7 @@
         <v>3163</v>
       </c>
       <c r="D302" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F302" t="s">
         <v>17</v>
@@ -8890,7 +8884,7 @@
         <v>3149</v>
       </c>
       <c r="D303" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F303" t="s">
         <v>17</v>
@@ -8927,7 +8921,7 @@
         <v>3151</v>
       </c>
       <c r="D305" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F305" t="s">
         <v>17</v>
@@ -8956,7 +8950,7 @@
         <v>3148</v>
       </c>
       <c r="D306" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F306" t="s">
         <v>17</v>
@@ -9014,7 +9008,7 @@
         <v>3194</v>
       </c>
       <c r="D308" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F308" t="s">
         <v>17</v>
@@ -9051,7 +9045,7 @@
         <v>3429</v>
       </c>
       <c r="D310" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F310" t="s">
         <v>17</v>
@@ -9080,7 +9074,7 @@
         <v>3147</v>
       </c>
       <c r="D311" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F311" t="s">
         <v>17</v>
@@ -9109,7 +9103,7 @@
         <v>3156</v>
       </c>
       <c r="D312" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F312" t="s">
         <v>17</v>
@@ -9146,7 +9140,7 @@
         <v>3157</v>
       </c>
       <c r="D314" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F314" t="s">
         <v>17</v>
@@ -9183,7 +9177,7 @@
         <v>3158</v>
       </c>
       <c r="D316" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F316" t="s">
         <v>17</v>
@@ -9212,7 +9206,7 @@
         <v>3164</v>
       </c>
       <c r="D317" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F317" t="s">
         <v>17</v>
@@ -9241,7 +9235,7 @@
         <v>3160</v>
       </c>
       <c r="D318" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F318" t="s">
         <v>17</v>
@@ -9278,7 +9272,7 @@
         <v>3161</v>
       </c>
       <c r="D320" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F320" t="s">
         <v>17</v>
@@ -9307,7 +9301,7 @@
         <v>3153</v>
       </c>
       <c r="D321" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F321" t="s">
         <v>17</v>
@@ -9344,7 +9338,7 @@
         <v>3159</v>
       </c>
       <c r="D323" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F323" t="s">
         <v>17</v>
@@ -9373,7 +9367,7 @@
         <v>3150</v>
       </c>
       <c r="D324" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F324" t="s">
         <v>17</v>
@@ -9394,7 +9388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -9410,7 +9404,7 @@
         <v>3155</v>
       </c>
       <c r="D326" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F326" t="s">
         <v>17</v>
@@ -9476,7 +9470,7 @@
         <v>3146</v>
       </c>
       <c r="D329" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F329" t="s">
         <v>23</v>
@@ -9534,7 +9528,7 @@
         <v>3144</v>
       </c>
       <c r="D331" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F331" t="s">
         <v>23</v>
@@ -9563,7 +9557,7 @@
         <v>3145</v>
       </c>
       <c r="D332" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F332" t="s">
         <v>23</v>
@@ -9592,7 +9586,7 @@
         <v>3152</v>
       </c>
       <c r="D333" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F333" t="s">
         <v>23</v>
@@ -9621,7 +9615,7 @@
         <v>3163</v>
       </c>
       <c r="D334" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F334" t="s">
         <v>23</v>
@@ -9650,7 +9644,7 @@
         <v>3149</v>
       </c>
       <c r="D335" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F335" t="s">
         <v>23</v>
@@ -9671,7 +9665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>36</v>
       </c>
@@ -9679,7 +9673,7 @@
         <v>3151</v>
       </c>
       <c r="D336" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F336" t="s">
         <v>23</v>
@@ -9708,7 +9702,7 @@
         <v>3148</v>
       </c>
       <c r="D337" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F337" t="s">
         <v>23</v>
@@ -9729,7 +9723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>36</v>
       </c>
@@ -9766,7 +9760,7 @@
         <v>3194</v>
       </c>
       <c r="D339" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F339" t="s">
         <v>23</v>
@@ -9795,7 +9789,7 @@
         <v>3147</v>
       </c>
       <c r="D340" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F340" t="s">
         <v>23</v>
@@ -9824,7 +9818,7 @@
         <v>3156</v>
       </c>
       <c r="D341" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F341" t="s">
         <v>23</v>
@@ -9853,7 +9847,7 @@
         <v>3157</v>
       </c>
       <c r="D342" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F342" t="s">
         <v>23</v>
@@ -9882,7 +9876,7 @@
         <v>3158</v>
       </c>
       <c r="D343" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F343" t="s">
         <v>23</v>
@@ -9911,7 +9905,7 @@
         <v>3429</v>
       </c>
       <c r="D344" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F344" t="s">
         <v>23</v>
@@ -9940,7 +9934,7 @@
         <v>3160</v>
       </c>
       <c r="D345" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F345" t="s">
         <v>23</v>
@@ -9969,7 +9963,7 @@
         <v>3161</v>
       </c>
       <c r="D346" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F346" t="s">
         <v>23</v>
@@ -9998,7 +9992,7 @@
         <v>3153</v>
       </c>
       <c r="D347" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F347" t="s">
         <v>23</v>
@@ -10027,7 +10021,7 @@
         <v>3159</v>
       </c>
       <c r="D348" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F348" t="s">
         <v>23</v>
@@ -10056,7 +10050,7 @@
         <v>3150</v>
       </c>
       <c r="D349" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F349" t="s">
         <v>23</v>
@@ -10093,7 +10087,7 @@
         <v>3155</v>
       </c>
       <c r="D351" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F351" t="s">
         <v>23</v>
@@ -10122,7 +10116,7 @@
         <v>3164</v>
       </c>
       <c r="D352" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F352" t="s">
         <v>23</v>
@@ -10172,7 +10166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>36</v>
       </c>
@@ -10209,7 +10203,7 @@
         <v>3146</v>
       </c>
       <c r="D355" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F355" t="s">
         <v>30</v>
@@ -10230,7 +10224,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>36</v>
       </c>
@@ -10267,7 +10261,7 @@
         <v>3144</v>
       </c>
       <c r="D357" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F357" t="s">
         <v>30</v>
@@ -10296,7 +10290,7 @@
         <v>3145</v>
       </c>
       <c r="D358" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F358" t="s">
         <v>30</v>
@@ -10325,7 +10319,7 @@
         <v>3149</v>
       </c>
       <c r="D359" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F359" t="s">
         <v>30</v>
@@ -10354,7 +10348,7 @@
         <v>3151</v>
       </c>
       <c r="D360" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F360" t="s">
         <v>30</v>
@@ -10383,7 +10377,7 @@
         <v>3148</v>
       </c>
       <c r="D361" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F361" t="s">
         <v>30</v>
@@ -10412,7 +10406,7 @@
         <v>3163</v>
       </c>
       <c r="D362" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F362" t="s">
         <v>30</v>
@@ -10449,7 +10443,7 @@
         <v>3194</v>
       </c>
       <c r="D364" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F364" t="s">
         <v>30</v>
@@ -10486,7 +10480,7 @@
         <v>3147</v>
       </c>
       <c r="D366" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F366" t="s">
         <v>30</v>
@@ -10515,7 +10509,7 @@
         <v>3156</v>
       </c>
       <c r="D367" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F367" t="s">
         <v>30</v>
@@ -10544,7 +10538,7 @@
         <v>3157</v>
       </c>
       <c r="D368" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F368" t="s">
         <v>30</v>
@@ -10581,7 +10575,7 @@
         <v>3158</v>
       </c>
       <c r="D370" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F370" t="s">
         <v>30</v>
@@ -10610,7 +10604,7 @@
         <v>3429</v>
       </c>
       <c r="D371" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F371" t="s">
         <v>30</v>
@@ -10631,7 +10625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>36</v>
       </c>
@@ -10639,7 +10633,7 @@
         <v>3160</v>
       </c>
       <c r="D372" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F372" t="s">
         <v>30</v>
@@ -10668,7 +10662,7 @@
         <v>3161</v>
       </c>
       <c r="D373" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F373" t="s">
         <v>30</v>
@@ -10697,7 +10691,7 @@
         <v>3152</v>
       </c>
       <c r="D374" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F374" t="s">
         <v>30</v>
@@ -10726,7 +10720,7 @@
         <v>3153</v>
       </c>
       <c r="D375" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F375" t="s">
         <v>30</v>
@@ -10755,7 +10749,7 @@
         <v>3159</v>
       </c>
       <c r="D376" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F376" t="s">
         <v>30</v>
@@ -10784,7 +10778,7 @@
         <v>3150</v>
       </c>
       <c r="D377" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F377" t="s">
         <v>30</v>
@@ -10813,7 +10807,7 @@
         <v>3155</v>
       </c>
       <c r="D378" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F378" t="s">
         <v>30</v>
@@ -10842,7 +10836,7 @@
         <v>3164</v>
       </c>
       <c r="D379" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F379" t="s">
         <v>30</v>
@@ -10900,7 +10894,7 @@
         <v>3162</v>
       </c>
       <c r="D381" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F381" t="s">
         <v>30</v>
@@ -10921,7 +10915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>36</v>
       </c>
@@ -10929,7 +10923,7 @@
         <v>3161</v>
       </c>
       <c r="D382" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F382" t="s">
         <v>24</v>
@@ -10958,7 +10952,7 @@
         <v>3146</v>
       </c>
       <c r="D383" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F383" t="s">
         <v>24</v>
@@ -11016,7 +11010,7 @@
         <v>3144</v>
       </c>
       <c r="D385" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F385" t="s">
         <v>24</v>
@@ -11045,7 +11039,7 @@
         <v>3145</v>
       </c>
       <c r="D386" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F386" t="s">
         <v>24</v>
@@ -11074,7 +11068,7 @@
         <v>3149</v>
       </c>
       <c r="D387" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F387" t="s">
         <v>24</v>
@@ -11103,7 +11097,7 @@
         <v>3151</v>
       </c>
       <c r="D388" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F388" t="s">
         <v>24</v>
@@ -11132,7 +11126,7 @@
         <v>3148</v>
       </c>
       <c r="D389" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F389" t="s">
         <v>24</v>
@@ -11161,7 +11155,7 @@
         <v>3163</v>
       </c>
       <c r="D390" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F390" t="s">
         <v>24</v>
@@ -11198,7 +11192,7 @@
         <v>3194</v>
       </c>
       <c r="D392" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F392" t="s">
         <v>24</v>
@@ -11235,7 +11229,7 @@
         <v>3162</v>
       </c>
       <c r="D394" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F394" t="s">
         <v>24</v>
@@ -11264,7 +11258,7 @@
         <v>3147</v>
       </c>
       <c r="D395" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F395" t="s">
         <v>24</v>
@@ -11293,7 +11287,7 @@
         <v>3156</v>
       </c>
       <c r="D396" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F396" t="s">
         <v>24</v>
@@ -11322,7 +11316,7 @@
         <v>3157</v>
       </c>
       <c r="D397" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F397" t="s">
         <v>24</v>
@@ -11359,7 +11353,7 @@
         <v>3158</v>
       </c>
       <c r="D399" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F399" t="s">
         <v>24</v>
@@ -11388,7 +11382,7 @@
         <v>3160</v>
       </c>
       <c r="D400" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F400" t="s">
         <v>24</v>
@@ -11417,7 +11411,7 @@
         <v>3153</v>
       </c>
       <c r="D401" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F401" t="s">
         <v>24</v>
@@ -11446,7 +11440,7 @@
         <v>3159</v>
       </c>
       <c r="D402" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F402" t="s">
         <v>24</v>
@@ -11475,7 +11469,7 @@
         <v>3150</v>
       </c>
       <c r="D403" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F403" t="s">
         <v>24</v>
@@ -11504,7 +11498,7 @@
         <v>3155</v>
       </c>
       <c r="D404" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F404" t="s">
         <v>24</v>
@@ -11533,7 +11527,7 @@
         <v>3164</v>
       </c>
       <c r="D405" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F405" t="s">
         <v>24</v>
@@ -11591,7 +11585,7 @@
         <v>3160</v>
       </c>
       <c r="D407" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F407" t="s">
         <v>32</v>
@@ -11628,7 +11622,7 @@
         <v>3161</v>
       </c>
       <c r="D409" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F409" t="s">
         <v>32</v>
@@ -11657,7 +11651,7 @@
         <v>3146</v>
       </c>
       <c r="D410" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F410" t="s">
         <v>32</v>
@@ -11694,7 +11688,7 @@
         <v>3429</v>
       </c>
       <c r="D412" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F412" t="s">
         <v>32</v>
@@ -11768,7 +11762,7 @@
         <v>3144</v>
       </c>
       <c r="D416" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F416" t="s">
         <v>32</v>
@@ -11805,7 +11799,7 @@
         <v>3145</v>
       </c>
       <c r="D418" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F418" t="s">
         <v>32</v>
@@ -11842,7 +11836,7 @@
         <v>3149</v>
       </c>
       <c r="D420" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F420" t="s">
         <v>32</v>
@@ -11871,7 +11865,7 @@
         <v>3151</v>
       </c>
       <c r="D421" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F421" t="s">
         <v>32</v>
@@ -11900,7 +11894,7 @@
         <v>3148</v>
       </c>
       <c r="D422" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F422" t="s">
         <v>32</v>
@@ -11929,7 +11923,7 @@
         <v>3164</v>
       </c>
       <c r="D423" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F423" t="s">
         <v>32</v>
@@ -11966,7 +11960,7 @@
         <v>3163</v>
       </c>
       <c r="D425" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F425" t="s">
         <v>32</v>
@@ -12003,7 +11997,7 @@
         <v>3194</v>
       </c>
       <c r="D427" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F427" t="s">
         <v>32</v>
@@ -12040,7 +12034,7 @@
         <v>3162</v>
       </c>
       <c r="D429" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F429" t="s">
         <v>32</v>
@@ -12077,7 +12071,7 @@
         <v>3147</v>
       </c>
       <c r="D431" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F431" t="s">
         <v>32</v>
@@ -12114,7 +12108,7 @@
         <v>3156</v>
       </c>
       <c r="D433" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F433" t="s">
         <v>32</v>
@@ -12151,7 +12145,7 @@
         <v>3157</v>
       </c>
       <c r="D435" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F435" t="s">
         <v>32</v>
@@ -12188,7 +12182,7 @@
         <v>3158</v>
       </c>
       <c r="D437" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F437" t="s">
         <v>32</v>
@@ -12225,7 +12219,7 @@
         <v>3159</v>
       </c>
       <c r="D439" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F439" t="s">
         <v>32</v>
@@ -12262,7 +12256,7 @@
         <v>3150</v>
       </c>
       <c r="D441" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F441" t="s">
         <v>32</v>
@@ -12299,7 +12293,7 @@
         <v>3155</v>
       </c>
       <c r="D443" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F443" t="s">
         <v>32</v>
@@ -12373,7 +12367,7 @@
         <v>3153</v>
       </c>
       <c r="D447" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F447" t="s">
         <v>32</v>
@@ -12402,7 +12396,7 @@
         <v>3160</v>
       </c>
       <c r="D448" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F448" t="s">
         <v>25</v>
@@ -12431,7 +12425,7 @@
         <v>3161</v>
       </c>
       <c r="D449" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F449" t="s">
         <v>25</v>
@@ -12460,7 +12454,7 @@
         <v>3146</v>
       </c>
       <c r="D450" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F450" t="s">
         <v>25</v>
@@ -12489,7 +12483,7 @@
         <v>3429</v>
       </c>
       <c r="D451" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>25</v>
@@ -12547,7 +12541,7 @@
         <v>3144</v>
       </c>
       <c r="D453" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F453" t="s">
         <v>25</v>
@@ -12576,7 +12570,7 @@
         <v>3145</v>
       </c>
       <c r="D454" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F454" t="s">
         <v>25</v>
@@ -12605,7 +12599,7 @@
         <v>3149</v>
       </c>
       <c r="D455" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F455" t="s">
         <v>25</v>
@@ -12634,7 +12628,7 @@
         <v>3151</v>
       </c>
       <c r="D456" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F456" t="s">
         <v>25</v>
@@ -12663,7 +12657,7 @@
         <v>3148</v>
       </c>
       <c r="D457" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F457" t="s">
         <v>25</v>
@@ -12692,7 +12686,7 @@
         <v>3164</v>
       </c>
       <c r="D458" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F458" t="s">
         <v>25</v>
@@ -12721,7 +12715,7 @@
         <v>3163</v>
       </c>
       <c r="D459" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F459" t="s">
         <v>25</v>
@@ -12750,7 +12744,7 @@
         <v>3194</v>
       </c>
       <c r="D460" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F460" t="s">
         <v>25</v>
@@ -12779,7 +12773,7 @@
         <v>3162</v>
       </c>
       <c r="D461" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F461" t="s">
         <v>25</v>
@@ -12816,7 +12810,7 @@
         <v>3147</v>
       </c>
       <c r="D463" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F463" t="s">
         <v>25</v>
@@ -12845,7 +12839,7 @@
         <v>3156</v>
       </c>
       <c r="D464" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F464" t="s">
         <v>25</v>
@@ -12874,7 +12868,7 @@
         <v>3157</v>
       </c>
       <c r="D465" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F465" t="s">
         <v>25</v>
@@ -12911,7 +12905,7 @@
         <v>3158</v>
       </c>
       <c r="D467" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F467" t="s">
         <v>25</v>
@@ -12940,7 +12934,7 @@
         <v>3159</v>
       </c>
       <c r="D468" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F468" t="s">
         <v>25</v>
@@ -12969,7 +12963,7 @@
         <v>3150</v>
       </c>
       <c r="D469" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F469" t="s">
         <v>25</v>
@@ -12998,7 +12992,7 @@
         <v>3155</v>
       </c>
       <c r="D470" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F470" t="s">
         <v>25</v>
@@ -13056,7 +13050,7 @@
         <v>3153</v>
       </c>
       <c r="D472" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F472" t="s">
         <v>25</v>
@@ -13085,7 +13079,7 @@
         <v>3158</v>
       </c>
       <c r="D473" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F473" t="s">
         <v>21</v>
@@ -13122,7 +13116,7 @@
         <v>3161</v>
       </c>
       <c r="D475" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F475" t="s">
         <v>18</v>
@@ -13151,7 +13145,7 @@
         <v>3146</v>
       </c>
       <c r="D476" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F476" t="s">
         <v>18</v>
@@ -13180,7 +13174,7 @@
         <v>3429</v>
       </c>
       <c r="D477" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F477" t="s">
         <v>18</v>
@@ -13209,7 +13203,7 @@
         <v>3160</v>
       </c>
       <c r="D478" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F478" t="s">
         <v>18</v>
@@ -13275,7 +13269,7 @@
         <v>3144</v>
       </c>
       <c r="D481" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F481" t="s">
         <v>18</v>
@@ -13304,7 +13298,7 @@
         <v>3145</v>
       </c>
       <c r="D482" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>18</v>
@@ -13333,7 +13327,7 @@
         <v>3151</v>
       </c>
       <c r="D483" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F483" t="s">
         <v>18</v>
@@ -13362,7 +13356,7 @@
         <v>3148</v>
       </c>
       <c r="D484" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F484" t="s">
         <v>18</v>
@@ -13391,7 +13385,7 @@
         <v>3164</v>
       </c>
       <c r="D485" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F485" t="s">
         <v>18</v>
@@ -13420,7 +13414,7 @@
         <v>3163</v>
       </c>
       <c r="D486" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F486" t="s">
         <v>18</v>
@@ -13457,7 +13451,7 @@
         <v>3194</v>
       </c>
       <c r="D488" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F488" t="s">
         <v>18</v>
@@ -13494,7 +13488,7 @@
         <v>3162</v>
       </c>
       <c r="D490" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F490" t="s">
         <v>18</v>
@@ -13523,7 +13517,7 @@
         <v>3147</v>
       </c>
       <c r="D491" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F491" t="s">
         <v>18</v>
@@ -13552,7 +13546,7 @@
         <v>3156</v>
       </c>
       <c r="D492" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F492" t="s">
         <v>18</v>
@@ -13581,7 +13575,7 @@
         <v>3157</v>
       </c>
       <c r="D493" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F493" t="s">
         <v>18</v>
@@ -13618,7 +13612,7 @@
         <v>3158</v>
       </c>
       <c r="D495" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F495" t="s">
         <v>18</v>
@@ -13647,7 +13641,7 @@
         <v>3149</v>
       </c>
       <c r="D496" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F496" t="s">
         <v>18</v>
@@ -13676,7 +13670,7 @@
         <v>3159</v>
       </c>
       <c r="D497" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F497" t="s">
         <v>18</v>
@@ -13705,7 +13699,7 @@
         <v>3150</v>
       </c>
       <c r="D498" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F498" t="s">
         <v>18</v>
@@ -13734,7 +13728,7 @@
         <v>3155</v>
       </c>
       <c r="D499" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F499" t="s">
         <v>18</v>
@@ -13792,7 +13786,7 @@
         <v>3153</v>
       </c>
       <c r="D501" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F501" t="s">
         <v>18</v>
@@ -13850,7 +13844,7 @@
         <v>3164</v>
       </c>
       <c r="D503" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F503" t="s">
         <v>21</v>
@@ -13879,7 +13873,7 @@
         <v>3157</v>
       </c>
       <c r="D504" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F504" t="s">
         <v>21</v>
@@ -13908,7 +13902,7 @@
         <v>3159</v>
       </c>
       <c r="D505" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F505" t="s">
         <v>21</v>
@@ -13937,7 +13931,7 @@
         <v>3148</v>
       </c>
       <c r="D506" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F506" t="s">
         <v>21</v>
@@ -13966,7 +13960,7 @@
         <v>3155</v>
       </c>
       <c r="D507" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F507" t="s">
         <v>21</v>
@@ -14024,7 +14018,7 @@
         <v>3161</v>
       </c>
       <c r="D509" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F509" t="s">
         <v>26</v>
@@ -14053,7 +14047,7 @@
         <v>3146</v>
       </c>
       <c r="D510" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F510" t="s">
         <v>26</v>
@@ -14082,7 +14076,7 @@
         <v>3160</v>
       </c>
       <c r="D511" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F511" t="s">
         <v>26</v>
@@ -14111,7 +14105,7 @@
         <v>3144</v>
       </c>
       <c r="D512" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F512" t="s">
         <v>26</v>
@@ -14140,7 +14134,7 @@
         <v>3145</v>
       </c>
       <c r="D513" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F513" t="s">
         <v>26</v>
@@ -14169,7 +14163,7 @@
         <v>3151</v>
       </c>
       <c r="D514" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F514" t="s">
         <v>26</v>
@@ -14198,7 +14192,7 @@
         <v>3163</v>
       </c>
       <c r="D515" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F515" t="s">
         <v>26</v>
@@ -14227,7 +14221,7 @@
         <v>3194</v>
       </c>
       <c r="D516" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F516" t="s">
         <v>26</v>
@@ -14256,7 +14250,7 @@
         <v>3162</v>
       </c>
       <c r="D517" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F517" t="s">
         <v>26</v>
@@ -14285,7 +14279,7 @@
         <v>3147</v>
       </c>
       <c r="D518" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F518" t="s">
         <v>26</v>
@@ -14314,7 +14308,7 @@
         <v>3156</v>
       </c>
       <c r="D519" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F519" t="s">
         <v>26</v>
@@ -14343,7 +14337,7 @@
         <v>3158</v>
       </c>
       <c r="D520" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F520" t="s">
         <v>26</v>
@@ -14372,7 +14366,7 @@
         <v>3149</v>
       </c>
       <c r="D521" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F521" t="s">
         <v>26</v>
@@ -14401,7 +14395,7 @@
         <v>3150</v>
       </c>
       <c r="D522" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F522" t="s">
         <v>26</v>
@@ -14430,7 +14424,7 @@
         <v>3153</v>
       </c>
       <c r="D523" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F523" t="s">
         <v>26</v>
@@ -14459,7 +14453,7 @@
         <v>3161</v>
       </c>
       <c r="D524" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F524" t="s">
         <v>19</v>
@@ -14488,7 +14482,7 @@
         <v>3146</v>
       </c>
       <c r="D525" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F525" t="s">
         <v>19</v>
@@ -14517,7 +14511,7 @@
         <v>3160</v>
       </c>
       <c r="D526" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F526" t="s">
         <v>19</v>
@@ -14583,7 +14577,7 @@
         <v>3144</v>
       </c>
       <c r="D529" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F529" t="s">
         <v>19</v>
@@ -14612,7 +14606,7 @@
         <v>3145</v>
       </c>
       <c r="D530" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F530" t="s">
         <v>19</v>
@@ -14641,7 +14635,7 @@
         <v>3151</v>
       </c>
       <c r="D531" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F531" t="s">
         <v>19</v>
@@ -14670,7 +14664,7 @@
         <v>3164</v>
       </c>
       <c r="D532" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F532" t="s">
         <v>19</v>
@@ -14699,7 +14693,7 @@
         <v>3163</v>
       </c>
       <c r="D533" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F533" t="s">
         <v>19</v>
@@ -14728,7 +14722,7 @@
         <v>3194</v>
       </c>
       <c r="D534" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F534" t="s">
         <v>19</v>
@@ -14757,7 +14751,7 @@
         <v>3162</v>
       </c>
       <c r="D535" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F535" t="s">
         <v>19</v>
@@ -14786,7 +14780,7 @@
         <v>3147</v>
       </c>
       <c r="D536" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F536" t="s">
         <v>19</v>
@@ -14815,7 +14809,7 @@
         <v>3156</v>
       </c>
       <c r="D537" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F537" t="s">
         <v>19</v>
@@ -14844,7 +14838,7 @@
         <v>3157</v>
       </c>
       <c r="D538" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F538" t="s">
         <v>19</v>
@@ -14873,7 +14867,7 @@
         <v>3158</v>
       </c>
       <c r="D539" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F539" t="s">
         <v>19</v>
@@ -14902,7 +14896,7 @@
         <v>3149</v>
       </c>
       <c r="D540" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F540" t="s">
         <v>19</v>
@@ -14931,7 +14925,7 @@
         <v>3159</v>
       </c>
       <c r="D541" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F541" t="s">
         <v>19</v>
@@ -14960,7 +14954,7 @@
         <v>3150</v>
       </c>
       <c r="D542" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F542" t="s">
         <v>19</v>
@@ -14989,7 +14983,7 @@
         <v>3148</v>
       </c>
       <c r="D543" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F543" t="s">
         <v>19</v>
@@ -15018,7 +15012,7 @@
         <v>3155</v>
       </c>
       <c r="D544" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F544" t="s">
         <v>19</v>
@@ -15076,7 +15070,7 @@
         <v>3153</v>
       </c>
       <c r="D546" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F546" t="s">
         <v>19</v>
@@ -15105,7 +15099,7 @@
         <v>3161</v>
       </c>
       <c r="D547" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F547" t="s">
         <v>27</v>
@@ -15120,7 +15114,7 @@
         <v>46237.812384259261</v>
       </c>
       <c r="J547" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K547" s="1" t="s">
         <v>11</v>
@@ -15134,7 +15128,7 @@
         <v>3146</v>
       </c>
       <c r="D548" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F548" t="s">
         <v>27</v>
@@ -15178,7 +15172,7 @@
         <v>46237.813078703701</v>
       </c>
       <c r="J549" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K549" s="1" t="s">
         <v>11</v>
@@ -15192,7 +15186,7 @@
         <v>3144</v>
       </c>
       <c r="D550" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F550" t="s">
         <v>27</v>
@@ -15207,7 +15201,7 @@
         <v>46237.813773148147</v>
       </c>
       <c r="J550" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K550" s="1" t="s">
         <v>11</v>
@@ -15221,7 +15215,7 @@
         <v>3145</v>
       </c>
       <c r="D551" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F551" t="s">
         <v>27</v>
@@ -15250,7 +15244,7 @@
         <v>3151</v>
       </c>
       <c r="D552" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F552" t="s">
         <v>27</v>
@@ -15265,7 +15259,7 @@
         <v>46237.814467592594</v>
       </c>
       <c r="J552" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K552" s="1" t="s">
         <v>11</v>
@@ -15279,7 +15273,7 @@
         <v>3160</v>
       </c>
       <c r="D553" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F553" t="s">
         <v>27</v>
@@ -15294,7 +15288,7 @@
         <v>46237.815162037034</v>
       </c>
       <c r="J553" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K553" s="1" t="s">
         <v>11</v>
@@ -15308,7 +15302,7 @@
         <v>3164</v>
       </c>
       <c r="D554" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F554" t="s">
         <v>27</v>
@@ -15337,7 +15331,7 @@
         <v>3163</v>
       </c>
       <c r="D555" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F555" t="s">
         <v>27</v>
@@ -15352,7 +15346,7 @@
         <v>46237.81585648148</v>
       </c>
       <c r="J555" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K555" s="1" t="s">
         <v>11</v>
@@ -15366,7 +15360,7 @@
         <v>3194</v>
       </c>
       <c r="D556" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F556" t="s">
         <v>27</v>
@@ -15381,7 +15375,7 @@
         <v>46237.816550925927</v>
       </c>
       <c r="J556" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K556" s="1" t="s">
         <v>11</v>
@@ -15395,7 +15389,7 @@
         <v>3162</v>
       </c>
       <c r="D557" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F557" t="s">
         <v>27</v>
@@ -15424,7 +15418,7 @@
         <v>3147</v>
       </c>
       <c r="D558" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F558" t="s">
         <v>27</v>
@@ -15439,7 +15433,7 @@
         <v>46237.817245370374</v>
       </c>
       <c r="J558" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K558" s="1" t="s">
         <v>11</v>
@@ -15453,22 +15447,22 @@
         <v>3156</v>
       </c>
       <c r="D559" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F559" t="s">
         <v>27</v>
       </c>
       <c r="G559" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H559" s="2">
-        <v>0</v>
+        <v>6.2615740740740739E-3</v>
       </c>
       <c r="I559" s="1">
         <v>46237.835416666669</v>
       </c>
       <c r="J559" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K559" s="1" t="s">
         <v>11</v>
@@ -15482,7 +15476,7 @@
         <v>3157</v>
       </c>
       <c r="D560" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F560" t="s">
         <v>27</v>
@@ -15497,7 +15491,7 @@
         <v>46237.836111111108</v>
       </c>
       <c r="J560" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K560" s="1" t="s">
         <v>11</v>
@@ -15511,7 +15505,7 @@
         <v>3158</v>
       </c>
       <c r="D561" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F561" t="s">
         <v>27</v>
@@ -15540,7 +15534,7 @@
         <v>3149</v>
       </c>
       <c r="D562" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F562" t="s">
         <v>27</v>
@@ -15555,7 +15549,7 @@
         <v>46237.836805555555</v>
       </c>
       <c r="J562" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K562" s="1" t="s">
         <v>11</v>
@@ -15569,7 +15563,7 @@
         <v>3159</v>
       </c>
       <c r="D563" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F563" t="s">
         <v>27</v>
@@ -15598,7 +15592,7 @@
         <v>3150</v>
       </c>
       <c r="D564" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F564" t="s">
         <v>27</v>
@@ -15613,7 +15607,7 @@
         <v>46237.838194444441</v>
       </c>
       <c r="J564" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K564" s="1" t="s">
         <v>11</v>
@@ -15627,7 +15621,7 @@
         <v>3148</v>
       </c>
       <c r="D565" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F565" t="s">
         <v>27</v>
@@ -15656,7 +15650,7 @@
         <v>3155</v>
       </c>
       <c r="D566" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F566" t="s">
         <v>27</v>
@@ -15700,7 +15694,7 @@
         <v>46237.839583333334</v>
       </c>
       <c r="J567" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K567" s="1" t="s">
         <v>11</v>
@@ -15714,7 +15708,7 @@
         <v>3153</v>
       </c>
       <c r="D568" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F568" t="s">
         <v>27</v>
@@ -15729,7 +15723,7 @@
         <v>46237.839583333334</v>
       </c>
       <c r="J568" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K568" s="1" t="s">
         <v>11</v>
@@ -24027,6 +24021,7 @@
       <c r="K1957" s="1"/>
     </row>
     <row r="1958" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
       <c r="K1958" s="1"/>
     </row>
@@ -24064,6 +24059,7 @@
       <c r="K1964" s="1"/>
     </row>
     <row r="1965" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
       <c r="K1965" s="1"/>
     </row>
@@ -24128,6 +24124,7 @@
       <c r="K1976" s="1"/>
     </row>
     <row r="1977" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:11" x14ac:dyDescent="0.25">
@@ -24159,11 +24156,11 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
     <row r="1984" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
       <c r="K1984" s="1"/>
     </row>
@@ -24174,6 +24171,7 @@
       <c r="K1985" s="1"/>
     </row>
     <row r="1986" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
       <c r="K1986" s="1"/>
     </row>
@@ -24249,6 +24247,7 @@
       <c r="K1999" s="1"/>
     </row>
     <row r="2000" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
       <c r="K2000" s="1"/>
     </row>
@@ -24259,6 +24258,7 @@
       <c r="K2001" s="1"/>
     </row>
     <row r="2002" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:11" x14ac:dyDescent="0.25">
@@ -24290,7 +24290,6 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -53583,6 +53582,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -53875,6 +53875,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -54185,6 +54187,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -54309,6 +54312,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -54320,6 +54324,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -54468,6 +54473,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -54478,10 +54484,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -54515,15 +54523,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -54564,18 +54575,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -54591,6 +54606,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -54600,10 +54616,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -54639,10 +54657,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -54668,6 +54688,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -54682,6 +54703,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -54716,6 +54738,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -54725,6 +54748,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -54734,6 +54758,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -54748,15 +54773,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -54786,6 +54812,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -54806,11 +54833,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -54819,6 +54848,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -54848,6 +54878,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -54857,10 +54888,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -54875,14 +54908,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -54902,10 +54938,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -54925,9 +54963,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -54962,18 +55003,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -54988,12 +55033,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -55008,10 +55053,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -55031,6 +55078,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -55050,6 +55098,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -55059,6 +55108,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -55104,6 +55154,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -55113,6 +55164,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -55127,6 +55179,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -55136,10 +55189,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -55154,6 +55209,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -55163,6 +55219,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -55182,6 +55239,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -55201,10 +55259,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -55214,6 +55274,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -55224,10 +55285,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -55242,18 +55305,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -55273,10 +55340,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -55296,6 +55365,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -55326,7 +55396,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -55341,10 +55410,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -55359,6 +55430,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -55373,11 +55445,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -55387,6 +55459,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -55402,6 +55475,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -55416,6 +55490,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -55436,6 +55511,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -55461,11 +55537,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -55484,15 +55562,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -55502,6 +55581,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -55521,6 +55601,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -55535,6 +55616,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -55554,10 +55636,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -55567,6 +55651,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -55577,6 +55662,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -55613,7 +55699,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -55622,6 +55707,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -55635,10 +55721,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\PCS-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A464F257-BF2C-4A3C-8978-E8FF0F420C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6991A5BF-B54D-424B-BCE3-F9F4846A57A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -134,13 +134,13 @@
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>Vehicle &amp; Roadside Inspections CMV</t>
-  </si>
-  <si>
     <t>(Spanish) Rules for Safe Driving</t>
   </si>
   <si>
     <t>Big Wins Through Behavior Change</t>
+  </si>
+  <si>
+    <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
     <t>Jon Stanley</t>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -659,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>36</v>
       </c>
@@ -833,7 +833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -949,7 +949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>36</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>36</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>36</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>36</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>36</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>36</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>36</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>36</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>36</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>36</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>36</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>36</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>36</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>41</v>
       </c>
       <c r="F187" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G187" t="s">
         <v>10</v>
@@ -5762,7 +5762,7 @@
         <v>38</v>
       </c>
       <c r="F188" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G188" t="s">
         <v>10</v>
@@ -5780,7 +5780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>36</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>38</v>
       </c>
       <c r="F189" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G189" t="s">
         <v>10</v>
@@ -5820,7 +5820,7 @@
         <v>39</v>
       </c>
       <c r="F190" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G190" t="s">
         <v>10</v>
@@ -5849,7 +5849,7 @@
         <v>40</v>
       </c>
       <c r="F191" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G191" t="s">
         <v>10</v>
@@ -5878,7 +5878,7 @@
         <v>42</v>
       </c>
       <c r="F192" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G192" t="s">
         <v>13</v>
@@ -5907,7 +5907,7 @@
         <v>43</v>
       </c>
       <c r="F193" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G193" t="s">
         <v>10</v>
@@ -5936,7 +5936,7 @@
         <v>46</v>
       </c>
       <c r="F194" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G194" t="s">
         <v>13</v>
@@ -5965,7 +5965,7 @@
         <v>44</v>
       </c>
       <c r="F195" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G195" t="s">
         <v>10</v>
@@ -5994,7 +5994,7 @@
         <v>45</v>
       </c>
       <c r="F196" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G196" t="s">
         <v>10</v>
@@ -6023,7 +6023,7 @@
         <v>51</v>
       </c>
       <c r="F197" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G197" t="s">
         <v>10</v>
@@ -6052,7 +6052,7 @@
         <v>34</v>
       </c>
       <c r="F198" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G198" t="s">
         <v>12</v>
@@ -6089,7 +6089,7 @@
         <v>50</v>
       </c>
       <c r="F200" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G200" t="s">
         <v>12</v>
@@ -6126,7 +6126,7 @@
         <v>46</v>
       </c>
       <c r="F202" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G202" t="s">
         <v>12</v>
@@ -6163,7 +6163,7 @@
         <v>52</v>
       </c>
       <c r="F204" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G204" t="s">
         <v>10</v>
@@ -6192,7 +6192,7 @@
         <v>53</v>
       </c>
       <c r="F205" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G205" t="s">
         <v>10</v>
@@ -6221,7 +6221,7 @@
         <v>54</v>
       </c>
       <c r="F206" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G206" t="s">
         <v>14</v>
@@ -6239,7 +6239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -6258,7 +6258,7 @@
         <v>55</v>
       </c>
       <c r="F208" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G208" t="s">
         <v>10</v>
@@ -6287,7 +6287,7 @@
         <v>48</v>
       </c>
       <c r="F209" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G209" t="s">
         <v>13</v>
@@ -6316,7 +6316,7 @@
         <v>38</v>
       </c>
       <c r="F210" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G210" t="s">
         <v>13</v>
@@ -6345,7 +6345,7 @@
         <v>47</v>
       </c>
       <c r="F211" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G211" t="s">
         <v>10</v>
@@ -6374,7 +6374,7 @@
         <v>56</v>
       </c>
       <c r="F212" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G212" t="s">
         <v>10</v>
@@ -6403,7 +6403,7 @@
         <v>37</v>
       </c>
       <c r="F213" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G213" t="s">
         <v>10</v>
@@ -6432,7 +6432,7 @@
         <v>40</v>
       </c>
       <c r="F214" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G214" t="s">
         <v>13</v>
@@ -6461,7 +6461,7 @@
         <v>49</v>
       </c>
       <c r="F215" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G215" t="s">
         <v>13</v>
@@ -7146,7 +7146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>36</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -9665,7 +9665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>36</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>36</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>36</v>
       </c>
@@ -10177,7 +10177,7 @@
         <v>34</v>
       </c>
       <c r="F354" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G354" t="s">
         <v>13</v>
@@ -10224,7 +10224,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>36</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>36</v>
       </c>
@@ -10915,7 +10915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>36</v>
       </c>
@@ -11588,7 +11588,7 @@
         <v>38</v>
       </c>
       <c r="F407" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G407" t="s">
         <v>12</v>
@@ -11625,7 +11625,7 @@
         <v>40</v>
       </c>
       <c r="F409" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G409" t="s">
         <v>13</v>
@@ -11654,7 +11654,7 @@
         <v>41</v>
       </c>
       <c r="F410" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G410" t="s">
         <v>12</v>
@@ -11691,7 +11691,7 @@
         <v>46</v>
       </c>
       <c r="F412" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G412" t="s">
         <v>12</v>
@@ -11728,7 +11728,7 @@
         <v>38</v>
       </c>
       <c r="F414" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G414" t="s">
         <v>12</v>
@@ -11765,7 +11765,7 @@
         <v>38</v>
       </c>
       <c r="F416" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G416" t="s">
         <v>12</v>
@@ -11802,7 +11802,7 @@
         <v>39</v>
       </c>
       <c r="F418" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G418" t="s">
         <v>12</v>
@@ -11839,7 +11839,7 @@
         <v>46</v>
       </c>
       <c r="F420" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G420" t="s">
         <v>13</v>
@@ -11868,7 +11868,7 @@
         <v>45</v>
       </c>
       <c r="F421" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G421" t="s">
         <v>13</v>
@@ -11897,7 +11897,7 @@
         <v>42</v>
       </c>
       <c r="F422" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G422" t="s">
         <v>13</v>
@@ -11926,7 +11926,7 @@
         <v>49</v>
       </c>
       <c r="F423" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G423" t="s">
         <v>12</v>
@@ -11963,7 +11963,7 @@
         <v>43</v>
       </c>
       <c r="F425" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G425" t="s">
         <v>12</v>
@@ -12000,7 +12000,7 @@
         <v>50</v>
       </c>
       <c r="F427" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G427" t="s">
         <v>12</v>
@@ -12037,7 +12037,7 @@
         <v>48</v>
       </c>
       <c r="F429" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G429" t="s">
         <v>12</v>
@@ -12074,7 +12074,7 @@
         <v>52</v>
       </c>
       <c r="F431" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G431" t="s">
         <v>12</v>
@@ -12111,7 +12111,7 @@
         <v>53</v>
       </c>
       <c r="F433" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G433" t="s">
         <v>12</v>
@@ -12148,7 +12148,7 @@
         <v>54</v>
       </c>
       <c r="F435" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G435" t="s">
         <v>12</v>
@@ -12185,7 +12185,7 @@
         <v>55</v>
       </c>
       <c r="F437" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G437" t="s">
         <v>12</v>
@@ -12222,7 +12222,7 @@
         <v>56</v>
       </c>
       <c r="F439" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G439" t="s">
         <v>12</v>
@@ -12259,7 +12259,7 @@
         <v>44</v>
       </c>
       <c r="F441" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G441" t="s">
         <v>12</v>
@@ -12296,7 +12296,7 @@
         <v>51</v>
       </c>
       <c r="F443" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G443" t="s">
         <v>12</v>
@@ -12333,7 +12333,7 @@
         <v>37</v>
       </c>
       <c r="F445" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G445" t="s">
         <v>12</v>
@@ -12370,7 +12370,7 @@
         <v>47</v>
       </c>
       <c r="F447" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G447" t="s">
         <v>13</v>
@@ -24008,6 +24008,7 @@
       <c r="K1954" s="1"/>
     </row>
     <row r="1955" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
       <c r="K1955" s="1"/>
     </row>
@@ -24017,6 +24018,7 @@
       <c r="K1956" s="1"/>
     </row>
     <row r="1957" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
       <c r="K1957" s="1"/>
     </row>
@@ -24156,6 +24158,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -24209,7 +24212,6 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -53582,7 +53584,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -53875,8 +53876,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -54187,7 +54186,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -54312,7 +54310,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -54324,7 +54321,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -54473,35 +54469,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -54512,44 +54502,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -54560,37 +54541,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -54601,52 +54575,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -54657,17 +54621,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -54678,32 +54639,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -54713,106 +54668,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -54822,7 +54757,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -54833,127 +54767,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -54963,62 +54871,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -55038,67 +54933,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -55108,38 +54990,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -55154,117 +55029,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -55273,99 +55125,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -55375,23 +55208,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -55400,52 +55229,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -55459,38 +55278,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -55500,7 +55312,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -55511,23 +55322,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -55537,37 +55344,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -55576,72 +55376,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -55651,76 +55437,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
